--- a/uploads/inbox/SPV_ROSTER_TEMPLATE_AVISUITE_COLORS.xlsx
+++ b/uploads/inbox/SPV_ROSTER_TEMPLATE_AVISUITE_COLORS.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ROSTER" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'ROSTER'!$A$1:$AI$70</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'ROSTER'!$A$1:$AI$69</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="32">
+  <fonts count="34">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -48,7 +48,7 @@
     <font>
       <name val="Times New Roman"/>
       <b val="1"/>
-      <color rgb="0015803D"/>
+      <color rgb="00196B24"/>
       <sz val="12"/>
     </font>
     <font>
@@ -60,14 +60,14 @@
     <font>
       <name val="Times New Roman"/>
       <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="10"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="14"/>
     </font>
     <font>
       <name val="Times New Roman"/>
       <b val="1"/>
       <color rgb="00000000"/>
-      <sz val="9"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Times New Roman"/>
@@ -94,12 +94,18 @@
       <name val="Times New Roman"/>
       <b val="1"/>
       <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Times New Roman"/>
       <b val="1"/>
-      <color rgb="0015803D"/>
+      <color rgb="00196B24"/>
       <sz val="10"/>
     </font>
     <font>
@@ -209,8 +215,14 @@
       <color rgb="00713F12"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Times New Roman"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="24">
+  <fills count="18">
     <fill>
       <patternFill/>
     </fill>
@@ -219,42 +231,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0015803D"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00196B24"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EEF2F0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A5A5A5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00D0CECE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFF99"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00DAE3F3"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
     <fill>
@@ -338,23 +320,23 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00C9CFD6"/>
+        <color rgb="00B7BCC2"/>
       </left>
       <right style="thin">
-        <color rgb="00C9CFD6"/>
+        <color rgb="00B7BCC2"/>
       </right>
       <top style="thin">
-        <color rgb="00C9CFD6"/>
+        <color rgb="00B7BCC2"/>
       </top>
       <bottom style="thin">
-        <color rgb="00C9CFD6"/>
+        <color rgb="00B7BCC2"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -371,16 +353,16 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -395,102 +377,99 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="27" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="28" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="20" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="29" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="30" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="22" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="31" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="23" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="32" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="33" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -670,14 +649,14 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="00E2EFDA"/>
+          <bgColor rgb="00DBEDD5"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="00B4C6E7"/>
+          <bgColor rgb="00A1BFCC"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1043,7 +1022,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AK116"/>
+  <dimension ref="A1:AK115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6.8" customWidth="1" min="1" max="1"/>
@@ -1119,288 +1098,326 @@
         <v/>
       </c>
     </row>
-    <row r="3" ht="17" customHeight="1">
+    <row r="3" ht="16" customHeight="1">
       <c r="A3" s="6" t="inlineStr">
         <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>PRN</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>NAME</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>Posn</t>
+        </is>
+      </c>
+      <c r="E3" s="7">
+        <f>IF(1&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,1),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="F3" s="7">
+        <f>IF(2&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,2),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="G3" s="7">
+        <f>IF(3&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,3),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="H3" s="7">
+        <f>IF(4&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,4),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="I3" s="7">
+        <f>IF(5&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,5),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="J3" s="7">
+        <f>IF(6&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,6),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="K3" s="7">
+        <f>IF(7&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,7),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="L3" s="7">
+        <f>IF(8&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,8),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="M3" s="7">
+        <f>IF(9&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,9),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="N3" s="7">
+        <f>IF(10&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,10),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="O3" s="7">
+        <f>IF(11&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,11),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="P3" s="7">
+        <f>IF(12&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,12),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="Q3" s="7">
+        <f>IF(13&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,13),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="R3" s="7">
+        <f>IF(14&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,14),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="S3" s="7">
+        <f>IF(15&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,15),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="T3" s="7">
+        <f>IF(16&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,16),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="U3" s="7">
+        <f>IF(17&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,17),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="V3" s="7">
+        <f>IF(18&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,18),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="W3" s="7">
+        <f>IF(19&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,19),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="X3" s="7">
+        <f>IF(20&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,20),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="Y3" s="7">
+        <f>IF(21&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,21),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="Z3" s="7">
+        <f>IF(22&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,22),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="AA3" s="7">
+        <f>IF(23&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,23),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="AB3" s="7">
+        <f>IF(24&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,24),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="AC3" s="7">
+        <f>IF(25&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,25),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="AD3" s="7">
+        <f>IF(26&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,26),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="AE3" s="7">
+        <f>IF(27&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,27),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="AF3" s="7">
+        <f>IF(28&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,28),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="AG3" s="7">
+        <f>IF(29&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,29),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="AH3" s="7">
+        <f>IF(30&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,30),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="AI3" s="7">
+        <f>IF(31&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,31),"ddd"),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
           <t>CREW 1</t>
         </is>
       </c>
-    </row>
-    <row r="4" ht="13" customHeight="1">
-      <c r="E4" s="7">
-        <f>IF(1&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,1),"ddd"),"")</f>
-        <v/>
-      </c>
-      <c r="F4" s="7">
-        <f>IF(2&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,2),"ddd"),"")</f>
-        <v/>
-      </c>
-      <c r="G4" s="7">
-        <f>IF(3&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,3),"ddd"),"")</f>
-        <v/>
-      </c>
-      <c r="H4" s="7">
-        <f>IF(4&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,4),"ddd"),"")</f>
-        <v/>
-      </c>
-      <c r="I4" s="7">
-        <f>IF(5&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,5),"ddd"),"")</f>
-        <v/>
-      </c>
-      <c r="J4" s="7">
-        <f>IF(6&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,6),"ddd"),"")</f>
-        <v/>
-      </c>
-      <c r="K4" s="7">
-        <f>IF(7&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,7),"ddd"),"")</f>
-        <v/>
-      </c>
-      <c r="L4" s="7">
-        <f>IF(8&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,8),"ddd"),"")</f>
-        <v/>
-      </c>
-      <c r="M4" s="7">
-        <f>IF(9&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,9),"ddd"),"")</f>
-        <v/>
-      </c>
-      <c r="N4" s="7">
-        <f>IF(10&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,10),"ddd"),"")</f>
-        <v/>
-      </c>
-      <c r="O4" s="7">
-        <f>IF(11&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,11),"ddd"),"")</f>
-        <v/>
-      </c>
-      <c r="P4" s="7">
-        <f>IF(12&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,12),"ddd"),"")</f>
-        <v/>
-      </c>
-      <c r="Q4" s="7">
-        <f>IF(13&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,13),"ddd"),"")</f>
-        <v/>
-      </c>
-      <c r="R4" s="7">
-        <f>IF(14&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,14),"ddd"),"")</f>
-        <v/>
-      </c>
-      <c r="S4" s="7">
-        <f>IF(15&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,15),"ddd"),"")</f>
-        <v/>
-      </c>
-      <c r="T4" s="7">
-        <f>IF(16&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,16),"ddd"),"")</f>
-        <v/>
-      </c>
-      <c r="U4" s="7">
-        <f>IF(17&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,17),"ddd"),"")</f>
-        <v/>
-      </c>
-      <c r="V4" s="7">
-        <f>IF(18&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,18),"ddd"),"")</f>
-        <v/>
-      </c>
-      <c r="W4" s="7">
-        <f>IF(19&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,19),"ddd"),"")</f>
-        <v/>
-      </c>
-      <c r="X4" s="7">
-        <f>IF(20&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,20),"ddd"),"")</f>
-        <v/>
-      </c>
-      <c r="Y4" s="7">
-        <f>IF(21&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,21),"ddd"),"")</f>
-        <v/>
-      </c>
-      <c r="Z4" s="7">
-        <f>IF(22&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,22),"ddd"),"")</f>
-        <v/>
-      </c>
-      <c r="AA4" s="7">
-        <f>IF(23&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,23),"ddd"),"")</f>
-        <v/>
-      </c>
-      <c r="AB4" s="7">
-        <f>IF(24&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,24),"ddd"),"")</f>
-        <v/>
-      </c>
-      <c r="AC4" s="7">
-        <f>IF(25&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,25),"ddd"),"")</f>
-        <v/>
-      </c>
-      <c r="AD4" s="7">
-        <f>IF(26&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,26),"ddd"),"")</f>
-        <v/>
-      </c>
-      <c r="AE4" s="7">
-        <f>IF(27&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,27),"ddd"),"")</f>
-        <v/>
-      </c>
-      <c r="AF4" s="7">
-        <f>IF(28&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,28),"ddd"),"")</f>
-        <v/>
-      </c>
-      <c r="AG4" s="7">
-        <f>IF(29&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,29),"ddd"),"")</f>
-        <v/>
-      </c>
-      <c r="AH4" s="7">
-        <f>IF(30&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,30),"ddd"),"")</f>
-        <v/>
-      </c>
-      <c r="AI4" s="7">
-        <f>IF(31&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,31),"ddd"),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5" ht="16" customHeight="1">
-      <c r="A5" s="8" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B5" s="8" t="inlineStr">
-        <is>
-          <t>PRN</t>
-        </is>
-      </c>
-      <c r="C5" s="8" t="inlineStr">
-        <is>
-          <t>NAME</t>
-        </is>
-      </c>
-      <c r="D5" s="8" t="inlineStr">
-        <is>
-          <t>Posn</t>
-        </is>
-      </c>
-      <c r="E5" s="9">
+      <c r="E4" s="9">
         <f>IF(1&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),1,"")</f>
         <v/>
       </c>
-      <c r="F5" s="9">
+      <c r="F4" s="9">
         <f>IF(2&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),2,"")</f>
         <v/>
       </c>
-      <c r="G5" s="9">
+      <c r="G4" s="9">
         <f>IF(3&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),3,"")</f>
         <v/>
       </c>
-      <c r="H5" s="9">
+      <c r="H4" s="9">
         <f>IF(4&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),4,"")</f>
         <v/>
       </c>
-      <c r="I5" s="9">
+      <c r="I4" s="9">
         <f>IF(5&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),5,"")</f>
         <v/>
       </c>
-      <c r="J5" s="9">
+      <c r="J4" s="9">
         <f>IF(6&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),6,"")</f>
         <v/>
       </c>
-      <c r="K5" s="9">
+      <c r="K4" s="9">
         <f>IF(7&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),7,"")</f>
         <v/>
       </c>
-      <c r="L5" s="9">
+      <c r="L4" s="9">
         <f>IF(8&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),8,"")</f>
         <v/>
       </c>
-      <c r="M5" s="9">
+      <c r="M4" s="9">
         <f>IF(9&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),9,"")</f>
         <v/>
       </c>
-      <c r="N5" s="9">
+      <c r="N4" s="9">
         <f>IF(10&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),10,"")</f>
         <v/>
       </c>
-      <c r="O5" s="9">
+      <c r="O4" s="9">
         <f>IF(11&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),11,"")</f>
         <v/>
       </c>
-      <c r="P5" s="9">
+      <c r="P4" s="9">
         <f>IF(12&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),12,"")</f>
         <v/>
       </c>
-      <c r="Q5" s="9">
+      <c r="Q4" s="9">
         <f>IF(13&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),13,"")</f>
         <v/>
       </c>
-      <c r="R5" s="9">
+      <c r="R4" s="9">
         <f>IF(14&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),14,"")</f>
         <v/>
       </c>
-      <c r="S5" s="9">
+      <c r="S4" s="9">
         <f>IF(15&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),15,"")</f>
         <v/>
       </c>
-      <c r="T5" s="9">
+      <c r="T4" s="9">
         <f>IF(16&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),16,"")</f>
         <v/>
       </c>
-      <c r="U5" s="9">
+      <c r="U4" s="9">
         <f>IF(17&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),17,"")</f>
         <v/>
       </c>
-      <c r="V5" s="9">
+      <c r="V4" s="9">
         <f>IF(18&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),18,"")</f>
         <v/>
       </c>
-      <c r="W5" s="9">
+      <c r="W4" s="9">
         <f>IF(19&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),19,"")</f>
         <v/>
       </c>
-      <c r="X5" s="9">
+      <c r="X4" s="9">
         <f>IF(20&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),20,"")</f>
         <v/>
       </c>
-      <c r="Y5" s="9">
+      <c r="Y4" s="9">
         <f>IF(21&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),21,"")</f>
         <v/>
       </c>
-      <c r="Z5" s="9">
+      <c r="Z4" s="9">
         <f>IF(22&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),22,"")</f>
         <v/>
       </c>
-      <c r="AA5" s="9">
+      <c r="AA4" s="9">
         <f>IF(23&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),23,"")</f>
         <v/>
       </c>
-      <c r="AB5" s="9">
+      <c r="AB4" s="9">
         <f>IF(24&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),24,"")</f>
         <v/>
       </c>
-      <c r="AC5" s="9">
+      <c r="AC4" s="9">
         <f>IF(25&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),25,"")</f>
         <v/>
       </c>
-      <c r="AD5" s="9">
+      <c r="AD4" s="9">
         <f>IF(26&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),26,"")</f>
         <v/>
       </c>
-      <c r="AE5" s="9">
+      <c r="AE4" s="9">
         <f>IF(27&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),27,"")</f>
         <v/>
       </c>
-      <c r="AF5" s="9">
+      <c r="AF4" s="9">
         <f>IF(28&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),28,"")</f>
         <v/>
       </c>
-      <c r="AG5" s="9">
+      <c r="AG4" s="9">
         <f>IF(29&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),29,"")</f>
         <v/>
       </c>
-      <c r="AH5" s="9">
+      <c r="AH4" s="9">
         <f>IF(30&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),30,"")</f>
         <v/>
       </c>
-      <c r="AI5" s="9">
+      <c r="AI4" s="9">
         <f>IF(31&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),31,"")</f>
         <v/>
       </c>
+    </row>
+    <row r="5" ht="17" customHeight="1">
+      <c r="A5" s="10">
+        <f>IF($C5="","",ROW()-4)</f>
+        <v/>
+      </c>
+      <c r="B5" s="11" t="n"/>
+      <c r="C5" s="12" t="n"/>
+      <c r="D5" s="11" t="n"/>
+      <c r="E5" s="13" t="n"/>
+      <c r="F5" s="13" t="n"/>
+      <c r="G5" s="13" t="n"/>
+      <c r="H5" s="13" t="n"/>
+      <c r="I5" s="13" t="n"/>
+      <c r="J5" s="13" t="n"/>
+      <c r="K5" s="13" t="n"/>
+      <c r="L5" s="13" t="n"/>
+      <c r="M5" s="13" t="n"/>
+      <c r="N5" s="13" t="n"/>
+      <c r="O5" s="13" t="n"/>
+      <c r="P5" s="13" t="n"/>
+      <c r="Q5" s="13" t="n"/>
+      <c r="R5" s="13" t="n"/>
+      <c r="S5" s="13" t="n"/>
+      <c r="T5" s="13" t="n"/>
+      <c r="U5" s="13" t="n"/>
+      <c r="V5" s="13" t="n"/>
+      <c r="W5" s="13" t="n"/>
+      <c r="X5" s="13" t="n"/>
+      <c r="Y5" s="13" t="n"/>
+      <c r="Z5" s="13" t="n"/>
+      <c r="AA5" s="13" t="n"/>
+      <c r="AB5" s="13" t="n"/>
+      <c r="AC5" s="13" t="n"/>
+      <c r="AD5" s="13" t="n"/>
+      <c r="AE5" s="13" t="n"/>
+      <c r="AF5" s="13" t="n"/>
+      <c r="AG5" s="13" t="n"/>
+      <c r="AH5" s="13" t="n"/>
+      <c r="AI5" s="13" t="n"/>
     </row>
     <row r="6" ht="17" customHeight="1">
       <c r="A6" s="10">
-        <f>IF($C6="","",ROW()-5)</f>
+        <f>IF($C6="","",ROW()-4)</f>
         <v/>
       </c>
       <c r="B6" s="11" t="n"/>
@@ -1440,7 +1457,7 @@
     </row>
     <row r="7" ht="17" customHeight="1">
       <c r="A7" s="10">
-        <f>IF($C7="","",ROW()-5)</f>
+        <f>IF($C7="","",ROW()-4)</f>
         <v/>
       </c>
       <c r="B7" s="11" t="n"/>
@@ -1480,7 +1497,7 @@
     </row>
     <row r="8" ht="17" customHeight="1">
       <c r="A8" s="10">
-        <f>IF($C8="","",ROW()-5)</f>
+        <f>IF($C8="","",ROW()-4)</f>
         <v/>
       </c>
       <c r="B8" s="11" t="n"/>
@@ -1520,7 +1537,7 @@
     </row>
     <row r="9" ht="17" customHeight="1">
       <c r="A9" s="10">
-        <f>IF($C9="","",ROW()-5)</f>
+        <f>IF($C9="","",ROW()-4)</f>
         <v/>
       </c>
       <c r="B9" s="11" t="n"/>
@@ -1560,7 +1577,7 @@
     </row>
     <row r="10" ht="17" customHeight="1">
       <c r="A10" s="10">
-        <f>IF($C10="","",ROW()-5)</f>
+        <f>IF($C10="","",ROW()-4)</f>
         <v/>
       </c>
       <c r="B10" s="11" t="n"/>
@@ -1600,7 +1617,7 @@
     </row>
     <row r="11" ht="17" customHeight="1">
       <c r="A11" s="10">
-        <f>IF($C11="","",ROW()-5)</f>
+        <f>IF($C11="","",ROW()-4)</f>
         <v/>
       </c>
       <c r="B11" s="11" t="n"/>
@@ -1640,7 +1657,7 @@
     </row>
     <row r="12" ht="17" customHeight="1">
       <c r="A12" s="10">
-        <f>IF($C12="","",ROW()-5)</f>
+        <f>IF($C12="","",ROW()-4)</f>
         <v/>
       </c>
       <c r="B12" s="11" t="n"/>
@@ -1680,7 +1697,7 @@
     </row>
     <row r="13" ht="17" customHeight="1">
       <c r="A13" s="10">
-        <f>IF($C13="","",ROW()-5)</f>
+        <f>IF($C13="","",ROW()-4)</f>
         <v/>
       </c>
       <c r="B13" s="11" t="n"/>
@@ -1720,7 +1737,7 @@
     </row>
     <row r="14" ht="17" customHeight="1">
       <c r="A14" s="10">
-        <f>IF($C14="","",ROW()-5)</f>
+        <f>IF($C14="","",ROW()-4)</f>
         <v/>
       </c>
       <c r="B14" s="11" t="n"/>
@@ -1760,7 +1777,7 @@
     </row>
     <row r="15" ht="17" customHeight="1">
       <c r="A15" s="10">
-        <f>IF($C15="","",ROW()-5)</f>
+        <f>IF($C15="","",ROW()-4)</f>
         <v/>
       </c>
       <c r="B15" s="11" t="n"/>
@@ -1800,7 +1817,7 @@
     </row>
     <row r="16" ht="17" customHeight="1">
       <c r="A16" s="10">
-        <f>IF($C16="","",ROW()-5)</f>
+        <f>IF($C16="","",ROW()-4)</f>
         <v/>
       </c>
       <c r="B16" s="11" t="n"/>
@@ -1840,7 +1857,7 @@
     </row>
     <row r="17" ht="17" customHeight="1">
       <c r="A17" s="10">
-        <f>IF($C17="","",ROW()-5)</f>
+        <f>IF($C17="","",ROW()-4)</f>
         <v/>
       </c>
       <c r="B17" s="11" t="n"/>
@@ -1880,7 +1897,7 @@
     </row>
     <row r="18" ht="17" customHeight="1">
       <c r="A18" s="10">
-        <f>IF($C18="","",ROW()-5)</f>
+        <f>IF($C18="","",ROW()-4)</f>
         <v/>
       </c>
       <c r="B18" s="11" t="n"/>
@@ -1920,7 +1937,7 @@
     </row>
     <row r="19" ht="17" customHeight="1">
       <c r="A19" s="10">
-        <f>IF($C19="","",ROW()-5)</f>
+        <f>IF($C19="","",ROW()-4)</f>
         <v/>
       </c>
       <c r="B19" s="11" t="n"/>
@@ -1960,7 +1977,7 @@
     </row>
     <row r="20" ht="17" customHeight="1">
       <c r="A20" s="10">
-        <f>IF($C20="","",ROW()-5)</f>
+        <f>IF($C20="","",ROW()-4)</f>
         <v/>
       </c>
       <c r="B20" s="11" t="n"/>
@@ -2000,7 +2017,7 @@
     </row>
     <row r="21" ht="17" customHeight="1">
       <c r="A21" s="10">
-        <f>IF($C21="","",ROW()-5)</f>
+        <f>IF($C21="","",ROW()-4)</f>
         <v/>
       </c>
       <c r="B21" s="11" t="n"/>
@@ -2040,7 +2057,7 @@
     </row>
     <row r="22" ht="17" customHeight="1">
       <c r="A22" s="10">
-        <f>IF($C22="","",ROW()-5)</f>
+        <f>IF($C22="","",ROW()-4)</f>
         <v/>
       </c>
       <c r="B22" s="11" t="n"/>
@@ -2078,328 +2095,326 @@
       <c r="AH22" s="13" t="n"/>
       <c r="AI22" s="13" t="n"/>
     </row>
-    <row r="23" ht="17" customHeight="1">
-      <c r="A23" s="10">
-        <f>IF($C23="","",ROW()-5)</f>
-        <v/>
-      </c>
-      <c r="B23" s="11" t="n"/>
-      <c r="C23" s="12" t="n"/>
-      <c r="D23" s="11" t="n"/>
-      <c r="E23" s="13" t="n"/>
-      <c r="F23" s="13" t="n"/>
-      <c r="G23" s="13" t="n"/>
-      <c r="H23" s="13" t="n"/>
-      <c r="I23" s="13" t="n"/>
-      <c r="J23" s="13" t="n"/>
-      <c r="K23" s="13" t="n"/>
-      <c r="L23" s="13" t="n"/>
-      <c r="M23" s="13" t="n"/>
-      <c r="N23" s="13" t="n"/>
-      <c r="O23" s="13" t="n"/>
-      <c r="P23" s="13" t="n"/>
-      <c r="Q23" s="13" t="n"/>
-      <c r="R23" s="13" t="n"/>
-      <c r="S23" s="13" t="n"/>
-      <c r="T23" s="13" t="n"/>
-      <c r="U23" s="13" t="n"/>
-      <c r="V23" s="13" t="n"/>
-      <c r="W23" s="13" t="n"/>
-      <c r="X23" s="13" t="n"/>
-      <c r="Y23" s="13" t="n"/>
-      <c r="Z23" s="13" t="n"/>
-      <c r="AA23" s="13" t="n"/>
-      <c r="AB23" s="13" t="n"/>
-      <c r="AC23" s="13" t="n"/>
-      <c r="AD23" s="13" t="n"/>
-      <c r="AE23" s="13" t="n"/>
-      <c r="AF23" s="13" t="n"/>
-      <c r="AG23" s="13" t="n"/>
-      <c r="AH23" s="13" t="n"/>
-      <c r="AI23" s="13" t="n"/>
-    </row>
-    <row r="24" ht="17" customHeight="1">
+    <row r="24" ht="16" customHeight="1">
       <c r="A24" s="6" t="inlineStr">
         <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>PRN</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>NAME</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>Posn</t>
+        </is>
+      </c>
+      <c r="E24" s="7">
+        <f>IF(1&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,1),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="F24" s="7">
+        <f>IF(2&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,2),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="G24" s="7">
+        <f>IF(3&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,3),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="H24" s="7">
+        <f>IF(4&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,4),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="I24" s="7">
+        <f>IF(5&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,5),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="J24" s="7">
+        <f>IF(6&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,6),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="K24" s="7">
+        <f>IF(7&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,7),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="L24" s="7">
+        <f>IF(8&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,8),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="M24" s="7">
+        <f>IF(9&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,9),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="N24" s="7">
+        <f>IF(10&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,10),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="O24" s="7">
+        <f>IF(11&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,11),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="P24" s="7">
+        <f>IF(12&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,12),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="Q24" s="7">
+        <f>IF(13&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,13),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="R24" s="7">
+        <f>IF(14&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,14),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="S24" s="7">
+        <f>IF(15&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,15),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="T24" s="7">
+        <f>IF(16&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,16),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="U24" s="7">
+        <f>IF(17&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,17),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="V24" s="7">
+        <f>IF(18&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,18),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="W24" s="7">
+        <f>IF(19&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,19),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="X24" s="7">
+        <f>IF(20&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,20),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="Y24" s="7">
+        <f>IF(21&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,21),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="Z24" s="7">
+        <f>IF(22&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,22),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="AA24" s="7">
+        <f>IF(23&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,23),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="AB24" s="7">
+        <f>IF(24&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,24),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="AC24" s="7">
+        <f>IF(25&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,25),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="AD24" s="7">
+        <f>IF(26&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,26),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="AE24" s="7">
+        <f>IF(27&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,27),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="AF24" s="7">
+        <f>IF(28&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,28),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="AG24" s="7">
+        <f>IF(29&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,29),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="AH24" s="7">
+        <f>IF(30&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,30),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="AI24" s="7">
+        <f>IF(31&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,31),"ddd"),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
           <t>CREW 2</t>
         </is>
       </c>
-    </row>
-    <row r="25" ht="13" customHeight="1">
-      <c r="E25" s="7">
-        <f>IF(1&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,1),"ddd"),"")</f>
-        <v/>
-      </c>
-      <c r="F25" s="7">
-        <f>IF(2&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,2),"ddd"),"")</f>
-        <v/>
-      </c>
-      <c r="G25" s="7">
-        <f>IF(3&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,3),"ddd"),"")</f>
-        <v/>
-      </c>
-      <c r="H25" s="7">
-        <f>IF(4&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,4),"ddd"),"")</f>
-        <v/>
-      </c>
-      <c r="I25" s="7">
-        <f>IF(5&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,5),"ddd"),"")</f>
-        <v/>
-      </c>
-      <c r="J25" s="7">
-        <f>IF(6&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,6),"ddd"),"")</f>
-        <v/>
-      </c>
-      <c r="K25" s="7">
-        <f>IF(7&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,7),"ddd"),"")</f>
-        <v/>
-      </c>
-      <c r="L25" s="7">
-        <f>IF(8&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,8),"ddd"),"")</f>
-        <v/>
-      </c>
-      <c r="M25" s="7">
-        <f>IF(9&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,9),"ddd"),"")</f>
-        <v/>
-      </c>
-      <c r="N25" s="7">
-        <f>IF(10&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,10),"ddd"),"")</f>
-        <v/>
-      </c>
-      <c r="O25" s="7">
-        <f>IF(11&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,11),"ddd"),"")</f>
-        <v/>
-      </c>
-      <c r="P25" s="7">
-        <f>IF(12&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,12),"ddd"),"")</f>
-        <v/>
-      </c>
-      <c r="Q25" s="7">
-        <f>IF(13&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,13),"ddd"),"")</f>
-        <v/>
-      </c>
-      <c r="R25" s="7">
-        <f>IF(14&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,14),"ddd"),"")</f>
-        <v/>
-      </c>
-      <c r="S25" s="7">
-        <f>IF(15&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,15),"ddd"),"")</f>
-        <v/>
-      </c>
-      <c r="T25" s="7">
-        <f>IF(16&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,16),"ddd"),"")</f>
-        <v/>
-      </c>
-      <c r="U25" s="7">
-        <f>IF(17&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,17),"ddd"),"")</f>
-        <v/>
-      </c>
-      <c r="V25" s="7">
-        <f>IF(18&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,18),"ddd"),"")</f>
-        <v/>
-      </c>
-      <c r="W25" s="7">
-        <f>IF(19&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,19),"ddd"),"")</f>
-        <v/>
-      </c>
-      <c r="X25" s="7">
-        <f>IF(20&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,20),"ddd"),"")</f>
-        <v/>
-      </c>
-      <c r="Y25" s="7">
-        <f>IF(21&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,21),"ddd"),"")</f>
-        <v/>
-      </c>
-      <c r="Z25" s="7">
-        <f>IF(22&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,22),"ddd"),"")</f>
-        <v/>
-      </c>
-      <c r="AA25" s="7">
-        <f>IF(23&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,23),"ddd"),"")</f>
-        <v/>
-      </c>
-      <c r="AB25" s="7">
-        <f>IF(24&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,24),"ddd"),"")</f>
-        <v/>
-      </c>
-      <c r="AC25" s="7">
-        <f>IF(25&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,25),"ddd"),"")</f>
-        <v/>
-      </c>
-      <c r="AD25" s="7">
-        <f>IF(26&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,26),"ddd"),"")</f>
-        <v/>
-      </c>
-      <c r="AE25" s="7">
-        <f>IF(27&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,27),"ddd"),"")</f>
-        <v/>
-      </c>
-      <c r="AF25" s="7">
-        <f>IF(28&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,28),"ddd"),"")</f>
-        <v/>
-      </c>
-      <c r="AG25" s="7">
-        <f>IF(29&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,29),"ddd"),"")</f>
-        <v/>
-      </c>
-      <c r="AH25" s="7">
-        <f>IF(30&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,30),"ddd"),"")</f>
-        <v/>
-      </c>
-      <c r="AI25" s="7">
-        <f>IF(31&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,31),"ddd"),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" ht="16" customHeight="1">
-      <c r="A26" s="8" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B26" s="8" t="inlineStr">
-        <is>
-          <t>PRN</t>
-        </is>
-      </c>
-      <c r="C26" s="8" t="inlineStr">
-        <is>
-          <t>NAME</t>
-        </is>
-      </c>
-      <c r="D26" s="8" t="inlineStr">
-        <is>
-          <t>Posn</t>
-        </is>
-      </c>
-      <c r="E26" s="9">
+      <c r="E25" s="9">
         <f>IF(1&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),1,"")</f>
         <v/>
       </c>
-      <c r="F26" s="9">
+      <c r="F25" s="9">
         <f>IF(2&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),2,"")</f>
         <v/>
       </c>
-      <c r="G26" s="9">
+      <c r="G25" s="9">
         <f>IF(3&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),3,"")</f>
         <v/>
       </c>
-      <c r="H26" s="9">
+      <c r="H25" s="9">
         <f>IF(4&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),4,"")</f>
         <v/>
       </c>
-      <c r="I26" s="9">
+      <c r="I25" s="9">
         <f>IF(5&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),5,"")</f>
         <v/>
       </c>
-      <c r="J26" s="9">
+      <c r="J25" s="9">
         <f>IF(6&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),6,"")</f>
         <v/>
       </c>
-      <c r="K26" s="9">
+      <c r="K25" s="9">
         <f>IF(7&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),7,"")</f>
         <v/>
       </c>
-      <c r="L26" s="9">
+      <c r="L25" s="9">
         <f>IF(8&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),8,"")</f>
         <v/>
       </c>
-      <c r="M26" s="9">
+      <c r="M25" s="9">
         <f>IF(9&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),9,"")</f>
         <v/>
       </c>
-      <c r="N26" s="9">
+      <c r="N25" s="9">
         <f>IF(10&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),10,"")</f>
         <v/>
       </c>
-      <c r="O26" s="9">
+      <c r="O25" s="9">
         <f>IF(11&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),11,"")</f>
         <v/>
       </c>
-      <c r="P26" s="9">
+      <c r="P25" s="9">
         <f>IF(12&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),12,"")</f>
         <v/>
       </c>
-      <c r="Q26" s="9">
+      <c r="Q25" s="9">
         <f>IF(13&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),13,"")</f>
         <v/>
       </c>
-      <c r="R26" s="9">
+      <c r="R25" s="9">
         <f>IF(14&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),14,"")</f>
         <v/>
       </c>
-      <c r="S26" s="9">
+      <c r="S25" s="9">
         <f>IF(15&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),15,"")</f>
         <v/>
       </c>
-      <c r="T26" s="9">
+      <c r="T25" s="9">
         <f>IF(16&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),16,"")</f>
         <v/>
       </c>
-      <c r="U26" s="9">
+      <c r="U25" s="9">
         <f>IF(17&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),17,"")</f>
         <v/>
       </c>
-      <c r="V26" s="9">
+      <c r="V25" s="9">
         <f>IF(18&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),18,"")</f>
         <v/>
       </c>
-      <c r="W26" s="9">
+      <c r="W25" s="9">
         <f>IF(19&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),19,"")</f>
         <v/>
       </c>
-      <c r="X26" s="9">
+      <c r="X25" s="9">
         <f>IF(20&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),20,"")</f>
         <v/>
       </c>
-      <c r="Y26" s="9">
+      <c r="Y25" s="9">
         <f>IF(21&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),21,"")</f>
         <v/>
       </c>
-      <c r="Z26" s="9">
+      <c r="Z25" s="9">
         <f>IF(22&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),22,"")</f>
         <v/>
       </c>
-      <c r="AA26" s="9">
+      <c r="AA25" s="9">
         <f>IF(23&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),23,"")</f>
         <v/>
       </c>
-      <c r="AB26" s="9">
+      <c r="AB25" s="9">
         <f>IF(24&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),24,"")</f>
         <v/>
       </c>
-      <c r="AC26" s="9">
+      <c r="AC25" s="9">
         <f>IF(25&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),25,"")</f>
         <v/>
       </c>
-      <c r="AD26" s="9">
+      <c r="AD25" s="9">
         <f>IF(26&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),26,"")</f>
         <v/>
       </c>
-      <c r="AE26" s="9">
+      <c r="AE25" s="9">
         <f>IF(27&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),27,"")</f>
         <v/>
       </c>
-      <c r="AF26" s="9">
+      <c r="AF25" s="9">
         <f>IF(28&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),28,"")</f>
         <v/>
       </c>
-      <c r="AG26" s="9">
+      <c r="AG25" s="9">
         <f>IF(29&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),29,"")</f>
         <v/>
       </c>
-      <c r="AH26" s="9">
+      <c r="AH25" s="9">
         <f>IF(30&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),30,"")</f>
         <v/>
       </c>
-      <c r="AI26" s="9">
+      <c r="AI25" s="9">
         <f>IF(31&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),31,"")</f>
         <v/>
       </c>
+    </row>
+    <row r="26" ht="17" customHeight="1">
+      <c r="A26" s="10">
+        <f>IF($C26="","",ROW()-25)</f>
+        <v/>
+      </c>
+      <c r="B26" s="11" t="n"/>
+      <c r="C26" s="12" t="n"/>
+      <c r="D26" s="11" t="n"/>
+      <c r="E26" s="13" t="n"/>
+      <c r="F26" s="13" t="n"/>
+      <c r="G26" s="13" t="n"/>
+      <c r="H26" s="13" t="n"/>
+      <c r="I26" s="13" t="n"/>
+      <c r="J26" s="13" t="n"/>
+      <c r="K26" s="13" t="n"/>
+      <c r="L26" s="13" t="n"/>
+      <c r="M26" s="13" t="n"/>
+      <c r="N26" s="13" t="n"/>
+      <c r="O26" s="13" t="n"/>
+      <c r="P26" s="13" t="n"/>
+      <c r="Q26" s="13" t="n"/>
+      <c r="R26" s="13" t="n"/>
+      <c r="S26" s="13" t="n"/>
+      <c r="T26" s="13" t="n"/>
+      <c r="U26" s="13" t="n"/>
+      <c r="V26" s="13" t="n"/>
+      <c r="W26" s="13" t="n"/>
+      <c r="X26" s="13" t="n"/>
+      <c r="Y26" s="13" t="n"/>
+      <c r="Z26" s="13" t="n"/>
+      <c r="AA26" s="13" t="n"/>
+      <c r="AB26" s="13" t="n"/>
+      <c r="AC26" s="13" t="n"/>
+      <c r="AD26" s="13" t="n"/>
+      <c r="AE26" s="13" t="n"/>
+      <c r="AF26" s="13" t="n"/>
+      <c r="AG26" s="13" t="n"/>
+      <c r="AH26" s="13" t="n"/>
+      <c r="AI26" s="13" t="n"/>
     </row>
     <row r="27" ht="17" customHeight="1">
       <c r="A27" s="10">
-        <f>IF($C27="","",ROW()-26)</f>
+        <f>IF($C27="","",ROW()-25)</f>
         <v/>
       </c>
       <c r="B27" s="11" t="n"/>
@@ -2439,7 +2454,7 @@
     </row>
     <row r="28" ht="17" customHeight="1">
       <c r="A28" s="10">
-        <f>IF($C28="","",ROW()-26)</f>
+        <f>IF($C28="","",ROW()-25)</f>
         <v/>
       </c>
       <c r="B28" s="11" t="n"/>
@@ -2479,7 +2494,7 @@
     </row>
     <row r="29" ht="17" customHeight="1">
       <c r="A29" s="10">
-        <f>IF($C29="","",ROW()-26)</f>
+        <f>IF($C29="","",ROW()-25)</f>
         <v/>
       </c>
       <c r="B29" s="11" t="n"/>
@@ -2519,7 +2534,7 @@
     </row>
     <row r="30" ht="17" customHeight="1">
       <c r="A30" s="10">
-        <f>IF($C30="","",ROW()-26)</f>
+        <f>IF($C30="","",ROW()-25)</f>
         <v/>
       </c>
       <c r="B30" s="11" t="n"/>
@@ -2559,7 +2574,7 @@
     </row>
     <row r="31" ht="17" customHeight="1">
       <c r="A31" s="10">
-        <f>IF($C31="","",ROW()-26)</f>
+        <f>IF($C31="","",ROW()-25)</f>
         <v/>
       </c>
       <c r="B31" s="11" t="n"/>
@@ -2599,7 +2614,7 @@
     </row>
     <row r="32" ht="17" customHeight="1">
       <c r="A32" s="10">
-        <f>IF($C32="","",ROW()-26)</f>
+        <f>IF($C32="","",ROW()-25)</f>
         <v/>
       </c>
       <c r="B32" s="11" t="n"/>
@@ -2639,7 +2654,7 @@
     </row>
     <row r="33" ht="17" customHeight="1">
       <c r="A33" s="10">
-        <f>IF($C33="","",ROW()-26)</f>
+        <f>IF($C33="","",ROW()-25)</f>
         <v/>
       </c>
       <c r="B33" s="11" t="n"/>
@@ -2679,7 +2694,7 @@
     </row>
     <row r="34" ht="17" customHeight="1">
       <c r="A34" s="10">
-        <f>IF($C34="","",ROW()-26)</f>
+        <f>IF($C34="","",ROW()-25)</f>
         <v/>
       </c>
       <c r="B34" s="11" t="n"/>
@@ -2719,7 +2734,7 @@
     </row>
     <row r="35" ht="17" customHeight="1">
       <c r="A35" s="10">
-        <f>IF($C35="","",ROW()-26)</f>
+        <f>IF($C35="","",ROW()-25)</f>
         <v/>
       </c>
       <c r="B35" s="11" t="n"/>
@@ -2759,7 +2774,7 @@
     </row>
     <row r="36" ht="17" customHeight="1">
       <c r="A36" s="10">
-        <f>IF($C36="","",ROW()-26)</f>
+        <f>IF($C36="","",ROW()-25)</f>
         <v/>
       </c>
       <c r="B36" s="11" t="n"/>
@@ -2799,7 +2814,7 @@
     </row>
     <row r="37" ht="17" customHeight="1">
       <c r="A37" s="10">
-        <f>IF($C37="","",ROW()-26)</f>
+        <f>IF($C37="","",ROW()-25)</f>
         <v/>
       </c>
       <c r="B37" s="11" t="n"/>
@@ -2839,7 +2854,7 @@
     </row>
     <row r="38" ht="17" customHeight="1">
       <c r="A38" s="10">
-        <f>IF($C38="","",ROW()-26)</f>
+        <f>IF($C38="","",ROW()-25)</f>
         <v/>
       </c>
       <c r="B38" s="11" t="n"/>
@@ -2879,7 +2894,7 @@
     </row>
     <row r="39" ht="17" customHeight="1">
       <c r="A39" s="10">
-        <f>IF($C39="","",ROW()-26)</f>
+        <f>IF($C39="","",ROW()-25)</f>
         <v/>
       </c>
       <c r="B39" s="11" t="n"/>
@@ -2919,7 +2934,7 @@
     </row>
     <row r="40" ht="17" customHeight="1">
       <c r="A40" s="10">
-        <f>IF($C40="","",ROW()-26)</f>
+        <f>IF($C40="","",ROW()-25)</f>
         <v/>
       </c>
       <c r="B40" s="11" t="n"/>
@@ -2959,7 +2974,7 @@
     </row>
     <row r="41" ht="17" customHeight="1">
       <c r="A41" s="10">
-        <f>IF($C41="","",ROW()-26)</f>
+        <f>IF($C41="","",ROW()-25)</f>
         <v/>
       </c>
       <c r="B41" s="11" t="n"/>
@@ -2999,7 +3014,7 @@
     </row>
     <row r="42" ht="17" customHeight="1">
       <c r="A42" s="10">
-        <f>IF($C42="","",ROW()-26)</f>
+        <f>IF($C42="","",ROW()-25)</f>
         <v/>
       </c>
       <c r="B42" s="11" t="n"/>
@@ -3039,7 +3054,7 @@
     </row>
     <row r="43" ht="17" customHeight="1">
       <c r="A43" s="10">
-        <f>IF($C43="","",ROW()-26)</f>
+        <f>IF($C43="","",ROW()-25)</f>
         <v/>
       </c>
       <c r="B43" s="11" t="n"/>
@@ -3077,328 +3092,326 @@
       <c r="AH43" s="13" t="n"/>
       <c r="AI43" s="13" t="n"/>
     </row>
-    <row r="44" ht="17" customHeight="1">
-      <c r="A44" s="10">
-        <f>IF($C44="","",ROW()-26)</f>
-        <v/>
-      </c>
-      <c r="B44" s="11" t="n"/>
-      <c r="C44" s="12" t="n"/>
-      <c r="D44" s="11" t="n"/>
-      <c r="E44" s="13" t="n"/>
-      <c r="F44" s="13" t="n"/>
-      <c r="G44" s="13" t="n"/>
-      <c r="H44" s="13" t="n"/>
-      <c r="I44" s="13" t="n"/>
-      <c r="J44" s="13" t="n"/>
-      <c r="K44" s="13" t="n"/>
-      <c r="L44" s="13" t="n"/>
-      <c r="M44" s="13" t="n"/>
-      <c r="N44" s="13" t="n"/>
-      <c r="O44" s="13" t="n"/>
-      <c r="P44" s="13" t="n"/>
-      <c r="Q44" s="13" t="n"/>
-      <c r="R44" s="13" t="n"/>
-      <c r="S44" s="13" t="n"/>
-      <c r="T44" s="13" t="n"/>
-      <c r="U44" s="13" t="n"/>
-      <c r="V44" s="13" t="n"/>
-      <c r="W44" s="13" t="n"/>
-      <c r="X44" s="13" t="n"/>
-      <c r="Y44" s="13" t="n"/>
-      <c r="Z44" s="13" t="n"/>
-      <c r="AA44" s="13" t="n"/>
-      <c r="AB44" s="13" t="n"/>
-      <c r="AC44" s="13" t="n"/>
-      <c r="AD44" s="13" t="n"/>
-      <c r="AE44" s="13" t="n"/>
-      <c r="AF44" s="13" t="n"/>
-      <c r="AG44" s="13" t="n"/>
-      <c r="AH44" s="13" t="n"/>
-      <c r="AI44" s="13" t="n"/>
-    </row>
-    <row r="45" ht="17" customHeight="1">
-      <c r="A45" s="14" t="inlineStr">
+    <row r="45" ht="16" customHeight="1">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>PRN</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>NAME</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>Posn</t>
+        </is>
+      </c>
+      <c r="E45" s="7">
+        <f>IF(1&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,1),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="F45" s="7">
+        <f>IF(2&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,2),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="G45" s="7">
+        <f>IF(3&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,3),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="H45" s="7">
+        <f>IF(4&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,4),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="I45" s="7">
+        <f>IF(5&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,5),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="J45" s="7">
+        <f>IF(6&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,6),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="K45" s="7">
+        <f>IF(7&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,7),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="L45" s="7">
+        <f>IF(8&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,8),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="M45" s="7">
+        <f>IF(9&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,9),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="N45" s="7">
+        <f>IF(10&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,10),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="O45" s="7">
+        <f>IF(11&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,11),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="P45" s="7">
+        <f>IF(12&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,12),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="Q45" s="7">
+        <f>IF(13&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,13),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="R45" s="7">
+        <f>IF(14&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,14),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="S45" s="7">
+        <f>IF(15&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,15),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="T45" s="7">
+        <f>IF(16&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,16),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="U45" s="7">
+        <f>IF(17&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,17),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="V45" s="7">
+        <f>IF(18&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,18),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="W45" s="7">
+        <f>IF(19&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,19),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="X45" s="7">
+        <f>IF(20&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,20),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="Y45" s="7">
+        <f>IF(21&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,21),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="Z45" s="7">
+        <f>IF(22&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,22),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="AA45" s="7">
+        <f>IF(23&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,23),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="AB45" s="7">
+        <f>IF(24&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,24),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="AC45" s="7">
+        <f>IF(25&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,25),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="AD45" s="7">
+        <f>IF(26&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,26),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="AE45" s="7">
+        <f>IF(27&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,27),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="AF45" s="7">
+        <f>IF(28&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,28),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="AG45" s="7">
+        <f>IF(29&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,29),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="AH45" s="7">
+        <f>IF(30&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,30),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="AI45" s="7">
+        <f>IF(31&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,31),"ddd"),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46" ht="18" customHeight="1">
+      <c r="A46" s="8" t="inlineStr">
         <is>
           <t>SPECIAL SHIFTING</t>
         </is>
       </c>
-    </row>
-    <row r="46" ht="13" customHeight="1">
-      <c r="E46" s="7">
-        <f>IF(1&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,1),"ddd"),"")</f>
-        <v/>
-      </c>
-      <c r="F46" s="7">
-        <f>IF(2&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,2),"ddd"),"")</f>
-        <v/>
-      </c>
-      <c r="G46" s="7">
-        <f>IF(3&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,3),"ddd"),"")</f>
-        <v/>
-      </c>
-      <c r="H46" s="7">
-        <f>IF(4&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,4),"ddd"),"")</f>
-        <v/>
-      </c>
-      <c r="I46" s="7">
-        <f>IF(5&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,5),"ddd"),"")</f>
-        <v/>
-      </c>
-      <c r="J46" s="7">
-        <f>IF(6&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,6),"ddd"),"")</f>
-        <v/>
-      </c>
-      <c r="K46" s="7">
-        <f>IF(7&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,7),"ddd"),"")</f>
-        <v/>
-      </c>
-      <c r="L46" s="7">
-        <f>IF(8&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,8),"ddd"),"")</f>
-        <v/>
-      </c>
-      <c r="M46" s="7">
-        <f>IF(9&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,9),"ddd"),"")</f>
-        <v/>
-      </c>
-      <c r="N46" s="7">
-        <f>IF(10&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,10),"ddd"),"")</f>
-        <v/>
-      </c>
-      <c r="O46" s="7">
-        <f>IF(11&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,11),"ddd"),"")</f>
-        <v/>
-      </c>
-      <c r="P46" s="7">
-        <f>IF(12&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,12),"ddd"),"")</f>
-        <v/>
-      </c>
-      <c r="Q46" s="7">
-        <f>IF(13&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,13),"ddd"),"")</f>
-        <v/>
-      </c>
-      <c r="R46" s="7">
-        <f>IF(14&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,14),"ddd"),"")</f>
-        <v/>
-      </c>
-      <c r="S46" s="7">
-        <f>IF(15&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,15),"ddd"),"")</f>
-        <v/>
-      </c>
-      <c r="T46" s="7">
-        <f>IF(16&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,16),"ddd"),"")</f>
-        <v/>
-      </c>
-      <c r="U46" s="7">
-        <f>IF(17&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,17),"ddd"),"")</f>
-        <v/>
-      </c>
-      <c r="V46" s="7">
-        <f>IF(18&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,18),"ddd"),"")</f>
-        <v/>
-      </c>
-      <c r="W46" s="7">
-        <f>IF(19&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,19),"ddd"),"")</f>
-        <v/>
-      </c>
-      <c r="X46" s="7">
-        <f>IF(20&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,20),"ddd"),"")</f>
-        <v/>
-      </c>
-      <c r="Y46" s="7">
-        <f>IF(21&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,21),"ddd"),"")</f>
-        <v/>
-      </c>
-      <c r="Z46" s="7">
-        <f>IF(22&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,22),"ddd"),"")</f>
-        <v/>
-      </c>
-      <c r="AA46" s="7">
-        <f>IF(23&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,23),"ddd"),"")</f>
-        <v/>
-      </c>
-      <c r="AB46" s="7">
-        <f>IF(24&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,24),"ddd"),"")</f>
-        <v/>
-      </c>
-      <c r="AC46" s="7">
-        <f>IF(25&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,25),"ddd"),"")</f>
-        <v/>
-      </c>
-      <c r="AD46" s="7">
-        <f>IF(26&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,26),"ddd"),"")</f>
-        <v/>
-      </c>
-      <c r="AE46" s="7">
-        <f>IF(27&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,27),"ddd"),"")</f>
-        <v/>
-      </c>
-      <c r="AF46" s="7">
-        <f>IF(28&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,28),"ddd"),"")</f>
-        <v/>
-      </c>
-      <c r="AG46" s="7">
-        <f>IF(29&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,29),"ddd"),"")</f>
-        <v/>
-      </c>
-      <c r="AH46" s="7">
-        <f>IF(30&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,30),"ddd"),"")</f>
-        <v/>
-      </c>
-      <c r="AI46" s="7">
-        <f>IF(31&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),TEXT(DATE($D$2,$AK$2,31),"ddd"),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47" ht="16" customHeight="1">
-      <c r="A47" s="8" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B47" s="8" t="inlineStr">
-        <is>
-          <t>PRN</t>
-        </is>
-      </c>
-      <c r="C47" s="8" t="inlineStr">
-        <is>
-          <t>NAME</t>
-        </is>
-      </c>
-      <c r="D47" s="8" t="inlineStr">
-        <is>
-          <t>Posn</t>
-        </is>
-      </c>
-      <c r="E47" s="9">
+      <c r="E46" s="9">
         <f>IF(1&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),1,"")</f>
         <v/>
       </c>
-      <c r="F47" s="9">
+      <c r="F46" s="9">
         <f>IF(2&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),2,"")</f>
         <v/>
       </c>
-      <c r="G47" s="9">
+      <c r="G46" s="9">
         <f>IF(3&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),3,"")</f>
         <v/>
       </c>
-      <c r="H47" s="9">
+      <c r="H46" s="9">
         <f>IF(4&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),4,"")</f>
         <v/>
       </c>
-      <c r="I47" s="9">
+      <c r="I46" s="9">
         <f>IF(5&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),5,"")</f>
         <v/>
       </c>
-      <c r="J47" s="9">
+      <c r="J46" s="9">
         <f>IF(6&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),6,"")</f>
         <v/>
       </c>
-      <c r="K47" s="9">
+      <c r="K46" s="9">
         <f>IF(7&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),7,"")</f>
         <v/>
       </c>
-      <c r="L47" s="9">
+      <c r="L46" s="9">
         <f>IF(8&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),8,"")</f>
         <v/>
       </c>
-      <c r="M47" s="9">
+      <c r="M46" s="9">
         <f>IF(9&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),9,"")</f>
         <v/>
       </c>
-      <c r="N47" s="9">
+      <c r="N46" s="9">
         <f>IF(10&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),10,"")</f>
         <v/>
       </c>
-      <c r="O47" s="9">
+      <c r="O46" s="9">
         <f>IF(11&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),11,"")</f>
         <v/>
       </c>
-      <c r="P47" s="9">
+      <c r="P46" s="9">
         <f>IF(12&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),12,"")</f>
         <v/>
       </c>
-      <c r="Q47" s="9">
+      <c r="Q46" s="9">
         <f>IF(13&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),13,"")</f>
         <v/>
       </c>
-      <c r="R47" s="9">
+      <c r="R46" s="9">
         <f>IF(14&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),14,"")</f>
         <v/>
       </c>
-      <c r="S47" s="9">
+      <c r="S46" s="9">
         <f>IF(15&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),15,"")</f>
         <v/>
       </c>
-      <c r="T47" s="9">
+      <c r="T46" s="9">
         <f>IF(16&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),16,"")</f>
         <v/>
       </c>
-      <c r="U47" s="9">
+      <c r="U46" s="9">
         <f>IF(17&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),17,"")</f>
         <v/>
       </c>
-      <c r="V47" s="9">
+      <c r="V46" s="9">
         <f>IF(18&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),18,"")</f>
         <v/>
       </c>
-      <c r="W47" s="9">
+      <c r="W46" s="9">
         <f>IF(19&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),19,"")</f>
         <v/>
       </c>
-      <c r="X47" s="9">
+      <c r="X46" s="9">
         <f>IF(20&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),20,"")</f>
         <v/>
       </c>
-      <c r="Y47" s="9">
+      <c r="Y46" s="9">
         <f>IF(21&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),21,"")</f>
         <v/>
       </c>
-      <c r="Z47" s="9">
+      <c r="Z46" s="9">
         <f>IF(22&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),22,"")</f>
         <v/>
       </c>
-      <c r="AA47" s="9">
+      <c r="AA46" s="9">
         <f>IF(23&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),23,"")</f>
         <v/>
       </c>
-      <c r="AB47" s="9">
+      <c r="AB46" s="9">
         <f>IF(24&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),24,"")</f>
         <v/>
       </c>
-      <c r="AC47" s="9">
+      <c r="AC46" s="9">
         <f>IF(25&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),25,"")</f>
         <v/>
       </c>
-      <c r="AD47" s="9">
+      <c r="AD46" s="9">
         <f>IF(26&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),26,"")</f>
         <v/>
       </c>
-      <c r="AE47" s="9">
+      <c r="AE46" s="9">
         <f>IF(27&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),27,"")</f>
         <v/>
       </c>
-      <c r="AF47" s="9">
+      <c r="AF46" s="9">
         <f>IF(28&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),28,"")</f>
         <v/>
       </c>
-      <c r="AG47" s="9">
+      <c r="AG46" s="9">
         <f>IF(29&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),29,"")</f>
         <v/>
       </c>
-      <c r="AH47" s="9">
+      <c r="AH46" s="9">
         <f>IF(30&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),30,"")</f>
         <v/>
       </c>
-      <c r="AI47" s="9">
+      <c r="AI46" s="9">
         <f>IF(31&lt;=DAY(EOMONTH(DATE($D$2,$AK$2,1),0)),31,"")</f>
         <v/>
       </c>
+    </row>
+    <row r="47" ht="17" customHeight="1">
+      <c r="A47" s="10">
+        <f>IF($C47="","",ROW()-46)</f>
+        <v/>
+      </c>
+      <c r="B47" s="11" t="n"/>
+      <c r="C47" s="12" t="n"/>
+      <c r="D47" s="11" t="n"/>
+      <c r="E47" s="13" t="n"/>
+      <c r="F47" s="13" t="n"/>
+      <c r="G47" s="13" t="n"/>
+      <c r="H47" s="13" t="n"/>
+      <c r="I47" s="13" t="n"/>
+      <c r="J47" s="13" t="n"/>
+      <c r="K47" s="13" t="n"/>
+      <c r="L47" s="13" t="n"/>
+      <c r="M47" s="13" t="n"/>
+      <c r="N47" s="13" t="n"/>
+      <c r="O47" s="13" t="n"/>
+      <c r="P47" s="13" t="n"/>
+      <c r="Q47" s="13" t="n"/>
+      <c r="R47" s="13" t="n"/>
+      <c r="S47" s="13" t="n"/>
+      <c r="T47" s="13" t="n"/>
+      <c r="U47" s="13" t="n"/>
+      <c r="V47" s="13" t="n"/>
+      <c r="W47" s="13" t="n"/>
+      <c r="X47" s="13" t="n"/>
+      <c r="Y47" s="13" t="n"/>
+      <c r="Z47" s="13" t="n"/>
+      <c r="AA47" s="13" t="n"/>
+      <c r="AB47" s="13" t="n"/>
+      <c r="AC47" s="13" t="n"/>
+      <c r="AD47" s="13" t="n"/>
+      <c r="AE47" s="13" t="n"/>
+      <c r="AF47" s="13" t="n"/>
+      <c r="AG47" s="13" t="n"/>
+      <c r="AH47" s="13" t="n"/>
+      <c r="AI47" s="13" t="n"/>
     </row>
     <row r="48" ht="17" customHeight="1">
       <c r="A48" s="10">
-        <f>IF($C48="","",ROW()-47)</f>
+        <f>IF($C48="","",ROW()-46)</f>
         <v/>
       </c>
       <c r="B48" s="11" t="n"/>
@@ -3438,7 +3451,7 @@
     </row>
     <row r="49" ht="17" customHeight="1">
       <c r="A49" s="10">
-        <f>IF($C49="","",ROW()-47)</f>
+        <f>IF($C49="","",ROW()-46)</f>
         <v/>
       </c>
       <c r="B49" s="11" t="n"/>
@@ -3478,7 +3491,7 @@
     </row>
     <row r="50" ht="17" customHeight="1">
       <c r="A50" s="10">
-        <f>IF($C50="","",ROW()-47)</f>
+        <f>IF($C50="","",ROW()-46)</f>
         <v/>
       </c>
       <c r="B50" s="11" t="n"/>
@@ -3518,7 +3531,7 @@
     </row>
     <row r="51" ht="17" customHeight="1">
       <c r="A51" s="10">
-        <f>IF($C51="","",ROW()-47)</f>
+        <f>IF($C51="","",ROW()-46)</f>
         <v/>
       </c>
       <c r="B51" s="11" t="n"/>
@@ -3558,7 +3571,7 @@
     </row>
     <row r="52" ht="17" customHeight="1">
       <c r="A52" s="10">
-        <f>IF($C52="","",ROW()-47)</f>
+        <f>IF($C52="","",ROW()-46)</f>
         <v/>
       </c>
       <c r="B52" s="11" t="n"/>
@@ -3598,7 +3611,7 @@
     </row>
     <row r="53" ht="17" customHeight="1">
       <c r="A53" s="10">
-        <f>IF($C53="","",ROW()-47)</f>
+        <f>IF($C53="","",ROW()-46)</f>
         <v/>
       </c>
       <c r="B53" s="11" t="n"/>
@@ -3638,7 +3651,7 @@
     </row>
     <row r="54" ht="17" customHeight="1">
       <c r="A54" s="10">
-        <f>IF($C54="","",ROW()-47)</f>
+        <f>IF($C54="","",ROW()-46)</f>
         <v/>
       </c>
       <c r="B54" s="11" t="n"/>
@@ -3678,7 +3691,7 @@
     </row>
     <row r="55" ht="17" customHeight="1">
       <c r="A55" s="10">
-        <f>IF($C55="","",ROW()-47)</f>
+        <f>IF($C55="","",ROW()-46)</f>
         <v/>
       </c>
       <c r="B55" s="11" t="n"/>
@@ -3718,7 +3731,7 @@
     </row>
     <row r="56" ht="17" customHeight="1">
       <c r="A56" s="10">
-        <f>IF($C56="","",ROW()-47)</f>
+        <f>IF($C56="","",ROW()-46)</f>
         <v/>
       </c>
       <c r="B56" s="11" t="n"/>
@@ -3758,7 +3771,7 @@
     </row>
     <row r="57" ht="17" customHeight="1">
       <c r="A57" s="10">
-        <f>IF($C57="","",ROW()-47)</f>
+        <f>IF($C57="","",ROW()-46)</f>
         <v/>
       </c>
       <c r="B57" s="11" t="n"/>
@@ -3798,7 +3811,7 @@
     </row>
     <row r="58" ht="17" customHeight="1">
       <c r="A58" s="10">
-        <f>IF($C58="","",ROW()-47)</f>
+        <f>IF($C58="","",ROW()-46)</f>
         <v/>
       </c>
       <c r="B58" s="11" t="n"/>
@@ -3836,964 +3849,944 @@
       <c r="AH58" s="13" t="n"/>
       <c r="AI58" s="13" t="n"/>
     </row>
-    <row r="59" ht="17" customHeight="1">
-      <c r="A59" s="10">
-        <f>IF($C59="","",ROW()-47)</f>
-        <v/>
-      </c>
-      <c r="B59" s="11" t="n"/>
-      <c r="C59" s="12" t="n"/>
-      <c r="D59" s="11" t="n"/>
-      <c r="E59" s="13" t="n"/>
-      <c r="F59" s="13" t="n"/>
-      <c r="G59" s="13" t="n"/>
-      <c r="H59" s="13" t="n"/>
-      <c r="I59" s="13" t="n"/>
-      <c r="J59" s="13" t="n"/>
-      <c r="K59" s="13" t="n"/>
-      <c r="L59" s="13" t="n"/>
-      <c r="M59" s="13" t="n"/>
-      <c r="N59" s="13" t="n"/>
-      <c r="O59" s="13" t="n"/>
-      <c r="P59" s="13" t="n"/>
-      <c r="Q59" s="13" t="n"/>
-      <c r="R59" s="13" t="n"/>
-      <c r="S59" s="13" t="n"/>
-      <c r="T59" s="13" t="n"/>
-      <c r="U59" s="13" t="n"/>
-      <c r="V59" s="13" t="n"/>
-      <c r="W59" s="13" t="n"/>
-      <c r="X59" s="13" t="n"/>
-      <c r="Y59" s="13" t="n"/>
-      <c r="Z59" s="13" t="n"/>
-      <c r="AA59" s="13" t="n"/>
-      <c r="AB59" s="13" t="n"/>
-      <c r="AC59" s="13" t="n"/>
-      <c r="AD59" s="13" t="n"/>
-      <c r="AE59" s="13" t="n"/>
-      <c r="AF59" s="13" t="n"/>
-      <c r="AG59" s="13" t="n"/>
-      <c r="AH59" s="13" t="n"/>
-      <c r="AI59" s="13" t="n"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="15" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="14" t="inlineStr">
         <is>
           <t>TOTAL DAILY
 CREWS MANPOWER</t>
         </is>
       </c>
-      <c r="B61" s="16" t="n"/>
-      <c r="C61" s="16" t="n"/>
+      <c r="B60" s="15" t="n"/>
+      <c r="C60" s="15" t="n"/>
+      <c r="D60" s="16" t="inlineStr">
+        <is>
+          <t>SHIFT</t>
+        </is>
+      </c>
+      <c r="E60" s="7">
+        <f>E4</f>
+        <v/>
+      </c>
+      <c r="F60" s="7">
+        <f>F4</f>
+        <v/>
+      </c>
+      <c r="G60" s="7">
+        <f>G4</f>
+        <v/>
+      </c>
+      <c r="H60" s="7">
+        <f>H4</f>
+        <v/>
+      </c>
+      <c r="I60" s="7">
+        <f>I4</f>
+        <v/>
+      </c>
+      <c r="J60" s="7">
+        <f>J4</f>
+        <v/>
+      </c>
+      <c r="K60" s="7">
+        <f>K4</f>
+        <v/>
+      </c>
+      <c r="L60" s="7">
+        <f>L4</f>
+        <v/>
+      </c>
+      <c r="M60" s="7">
+        <f>M4</f>
+        <v/>
+      </c>
+      <c r="N60" s="7">
+        <f>N4</f>
+        <v/>
+      </c>
+      <c r="O60" s="7">
+        <f>O4</f>
+        <v/>
+      </c>
+      <c r="P60" s="7">
+        <f>P4</f>
+        <v/>
+      </c>
+      <c r="Q60" s="7">
+        <f>Q4</f>
+        <v/>
+      </c>
+      <c r="R60" s="7">
+        <f>R4</f>
+        <v/>
+      </c>
+      <c r="S60" s="7">
+        <f>S4</f>
+        <v/>
+      </c>
+      <c r="T60" s="7">
+        <f>T4</f>
+        <v/>
+      </c>
+      <c r="U60" s="7">
+        <f>U4</f>
+        <v/>
+      </c>
+      <c r="V60" s="7">
+        <f>V4</f>
+        <v/>
+      </c>
+      <c r="W60" s="7">
+        <f>W4</f>
+        <v/>
+      </c>
+      <c r="X60" s="7">
+        <f>X4</f>
+        <v/>
+      </c>
+      <c r="Y60" s="7">
+        <f>Y4</f>
+        <v/>
+      </c>
+      <c r="Z60" s="7">
+        <f>Z4</f>
+        <v/>
+      </c>
+      <c r="AA60" s="7">
+        <f>AA4</f>
+        <v/>
+      </c>
+      <c r="AB60" s="7">
+        <f>AB4</f>
+        <v/>
+      </c>
+      <c r="AC60" s="7">
+        <f>AC4</f>
+        <v/>
+      </c>
+      <c r="AD60" s="7">
+        <f>AD4</f>
+        <v/>
+      </c>
+      <c r="AE60" s="7">
+        <f>AE4</f>
+        <v/>
+      </c>
+      <c r="AF60" s="7">
+        <f>AF4</f>
+        <v/>
+      </c>
+      <c r="AG60" s="7">
+        <f>AG4</f>
+        <v/>
+      </c>
+      <c r="AH60" s="7">
+        <f>AH4</f>
+        <v/>
+      </c>
+      <c r="AI60" s="7">
+        <f>AI4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61" ht="15" customHeight="1">
+      <c r="A61" s="15" t="n"/>
+      <c r="B61" s="15" t="n"/>
+      <c r="C61" s="15" t="n"/>
       <c r="D61" s="17" t="inlineStr">
         <is>
-          <t>SHIFT</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E61" s="18">
-        <f>E5</f>
+        <f>IF(E$4="","",COUNTIF(E5:E58,"D"))</f>
         <v/>
       </c>
       <c r="F61" s="18">
-        <f>F5</f>
+        <f>IF(F$4="","",COUNTIF(F5:F58,"D"))</f>
         <v/>
       </c>
       <c r="G61" s="18">
-        <f>G5</f>
+        <f>IF(G$4="","",COUNTIF(G5:G58,"D"))</f>
         <v/>
       </c>
       <c r="H61" s="18">
-        <f>H5</f>
+        <f>IF(H$4="","",COUNTIF(H5:H58,"D"))</f>
         <v/>
       </c>
       <c r="I61" s="18">
-        <f>I5</f>
+        <f>IF(I$4="","",COUNTIF(I5:I58,"D"))</f>
         <v/>
       </c>
       <c r="J61" s="18">
-        <f>J5</f>
+        <f>IF(J$4="","",COUNTIF(J5:J58,"D"))</f>
         <v/>
       </c>
       <c r="K61" s="18">
-        <f>K5</f>
+        <f>IF(K$4="","",COUNTIF(K5:K58,"D"))</f>
         <v/>
       </c>
       <c r="L61" s="18">
-        <f>L5</f>
+        <f>IF(L$4="","",COUNTIF(L5:L58,"D"))</f>
         <v/>
       </c>
       <c r="M61" s="18">
-        <f>M5</f>
+        <f>IF(M$4="","",COUNTIF(M5:M58,"D"))</f>
         <v/>
       </c>
       <c r="N61" s="18">
-        <f>N5</f>
+        <f>IF(N$4="","",COUNTIF(N5:N58,"D"))</f>
         <v/>
       </c>
       <c r="O61" s="18">
-        <f>O5</f>
+        <f>IF(O$4="","",COUNTIF(O5:O58,"D"))</f>
         <v/>
       </c>
       <c r="P61" s="18">
-        <f>P5</f>
+        <f>IF(P$4="","",COUNTIF(P5:P58,"D"))</f>
         <v/>
       </c>
       <c r="Q61" s="18">
-        <f>Q5</f>
+        <f>IF(Q$4="","",COUNTIF(Q5:Q58,"D"))</f>
         <v/>
       </c>
       <c r="R61" s="18">
-        <f>R5</f>
+        <f>IF(R$4="","",COUNTIF(R5:R58,"D"))</f>
         <v/>
       </c>
       <c r="S61" s="18">
-        <f>S5</f>
+        <f>IF(S$4="","",COUNTIF(S5:S58,"D"))</f>
         <v/>
       </c>
       <c r="T61" s="18">
-        <f>T5</f>
+        <f>IF(T$4="","",COUNTIF(T5:T58,"D"))</f>
         <v/>
       </c>
       <c r="U61" s="18">
-        <f>U5</f>
+        <f>IF(U$4="","",COUNTIF(U5:U58,"D"))</f>
         <v/>
       </c>
       <c r="V61" s="18">
-        <f>V5</f>
+        <f>IF(V$4="","",COUNTIF(V5:V58,"D"))</f>
         <v/>
       </c>
       <c r="W61" s="18">
-        <f>W5</f>
+        <f>IF(W$4="","",COUNTIF(W5:W58,"D"))</f>
         <v/>
       </c>
       <c r="X61" s="18">
-        <f>X5</f>
+        <f>IF(X$4="","",COUNTIF(X5:X58,"D"))</f>
         <v/>
       </c>
       <c r="Y61" s="18">
-        <f>Y5</f>
+        <f>IF(Y$4="","",COUNTIF(Y5:Y58,"D"))</f>
         <v/>
       </c>
       <c r="Z61" s="18">
-        <f>Z5</f>
+        <f>IF(Z$4="","",COUNTIF(Z5:Z58,"D"))</f>
         <v/>
       </c>
       <c r="AA61" s="18">
-        <f>AA5</f>
+        <f>IF(AA$4="","",COUNTIF(AA5:AA58,"D"))</f>
         <v/>
       </c>
       <c r="AB61" s="18">
-        <f>AB5</f>
+        <f>IF(AB$4="","",COUNTIF(AB5:AB58,"D"))</f>
         <v/>
       </c>
       <c r="AC61" s="18">
-        <f>AC5</f>
+        <f>IF(AC$4="","",COUNTIF(AC5:AC58,"D"))</f>
         <v/>
       </c>
       <c r="AD61" s="18">
-        <f>AD5</f>
+        <f>IF(AD$4="","",COUNTIF(AD5:AD58,"D"))</f>
         <v/>
       </c>
       <c r="AE61" s="18">
-        <f>AE5</f>
+        <f>IF(AE$4="","",COUNTIF(AE5:AE58,"D"))</f>
         <v/>
       </c>
       <c r="AF61" s="18">
-        <f>AF5</f>
+        <f>IF(AF$4="","",COUNTIF(AF5:AF58,"D"))</f>
         <v/>
       </c>
       <c r="AG61" s="18">
-        <f>AG5</f>
+        <f>IF(AG$4="","",COUNTIF(AG5:AG58,"D"))</f>
         <v/>
       </c>
       <c r="AH61" s="18">
-        <f>AH5</f>
+        <f>IF(AH$4="","",COUNTIF(AH5:AH58,"D"))</f>
         <v/>
       </c>
       <c r="AI61" s="18">
-        <f>AI5</f>
+        <f>IF(AI$4="","",COUNTIF(AI5:AI58,"D"))</f>
         <v/>
       </c>
     </row>
     <row r="62" ht="15" customHeight="1">
-      <c r="A62" s="16" t="n"/>
-      <c r="B62" s="16" t="n"/>
-      <c r="C62" s="16" t="n"/>
+      <c r="A62" s="15" t="n"/>
+      <c r="B62" s="15" t="n"/>
+      <c r="C62" s="15" t="n"/>
       <c r="D62" s="19" t="inlineStr">
         <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="E62" s="20">
+        <f>IF(E$4="","",COUNTIF(E5:E58,"T"))</f>
+        <v/>
+      </c>
+      <c r="F62" s="20">
+        <f>IF(F$4="","",COUNTIF(F5:F58,"T"))</f>
+        <v/>
+      </c>
+      <c r="G62" s="20">
+        <f>IF(G$4="","",COUNTIF(G5:G58,"T"))</f>
+        <v/>
+      </c>
+      <c r="H62" s="20">
+        <f>IF(H$4="","",COUNTIF(H5:H58,"T"))</f>
+        <v/>
+      </c>
+      <c r="I62" s="20">
+        <f>IF(I$4="","",COUNTIF(I5:I58,"T"))</f>
+        <v/>
+      </c>
+      <c r="J62" s="20">
+        <f>IF(J$4="","",COUNTIF(J5:J58,"T"))</f>
+        <v/>
+      </c>
+      <c r="K62" s="20">
+        <f>IF(K$4="","",COUNTIF(K5:K58,"T"))</f>
+        <v/>
+      </c>
+      <c r="L62" s="20">
+        <f>IF(L$4="","",COUNTIF(L5:L58,"T"))</f>
+        <v/>
+      </c>
+      <c r="M62" s="20">
+        <f>IF(M$4="","",COUNTIF(M5:M58,"T"))</f>
+        <v/>
+      </c>
+      <c r="N62" s="20">
+        <f>IF(N$4="","",COUNTIF(N5:N58,"T"))</f>
+        <v/>
+      </c>
+      <c r="O62" s="20">
+        <f>IF(O$4="","",COUNTIF(O5:O58,"T"))</f>
+        <v/>
+      </c>
+      <c r="P62" s="20">
+        <f>IF(P$4="","",COUNTIF(P5:P58,"T"))</f>
+        <v/>
+      </c>
+      <c r="Q62" s="20">
+        <f>IF(Q$4="","",COUNTIF(Q5:Q58,"T"))</f>
+        <v/>
+      </c>
+      <c r="R62" s="20">
+        <f>IF(R$4="","",COUNTIF(R5:R58,"T"))</f>
+        <v/>
+      </c>
+      <c r="S62" s="20">
+        <f>IF(S$4="","",COUNTIF(S5:S58,"T"))</f>
+        <v/>
+      </c>
+      <c r="T62" s="20">
+        <f>IF(T$4="","",COUNTIF(T5:T58,"T"))</f>
+        <v/>
+      </c>
+      <c r="U62" s="20">
+        <f>IF(U$4="","",COUNTIF(U5:U58,"T"))</f>
+        <v/>
+      </c>
+      <c r="V62" s="20">
+        <f>IF(V$4="","",COUNTIF(V5:V58,"T"))</f>
+        <v/>
+      </c>
+      <c r="W62" s="20">
+        <f>IF(W$4="","",COUNTIF(W5:W58,"T"))</f>
+        <v/>
+      </c>
+      <c r="X62" s="20">
+        <f>IF(X$4="","",COUNTIF(X5:X58,"T"))</f>
+        <v/>
+      </c>
+      <c r="Y62" s="20">
+        <f>IF(Y$4="","",COUNTIF(Y5:Y58,"T"))</f>
+        <v/>
+      </c>
+      <c r="Z62" s="20">
+        <f>IF(Z$4="","",COUNTIF(Z5:Z58,"T"))</f>
+        <v/>
+      </c>
+      <c r="AA62" s="20">
+        <f>IF(AA$4="","",COUNTIF(AA5:AA58,"T"))</f>
+        <v/>
+      </c>
+      <c r="AB62" s="20">
+        <f>IF(AB$4="","",COUNTIF(AB5:AB58,"T"))</f>
+        <v/>
+      </c>
+      <c r="AC62" s="20">
+        <f>IF(AC$4="","",COUNTIF(AC5:AC58,"T"))</f>
+        <v/>
+      </c>
+      <c r="AD62" s="20">
+        <f>IF(AD$4="","",COUNTIF(AD5:AD58,"T"))</f>
+        <v/>
+      </c>
+      <c r="AE62" s="20">
+        <f>IF(AE$4="","",COUNTIF(AE5:AE58,"T"))</f>
+        <v/>
+      </c>
+      <c r="AF62" s="20">
+        <f>IF(AF$4="","",COUNTIF(AF5:AF58,"T"))</f>
+        <v/>
+      </c>
+      <c r="AG62" s="20">
+        <f>IF(AG$4="","",COUNTIF(AG5:AG58,"T"))</f>
+        <v/>
+      </c>
+      <c r="AH62" s="20">
+        <f>IF(AH$4="","",COUNTIF(AH5:AH58,"T"))</f>
+        <v/>
+      </c>
+      <c r="AI62" s="20">
+        <f>IF(AI$4="","",COUNTIF(AI5:AI58,"T"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63" ht="15" customHeight="1">
+      <c r="A63" s="15" t="n"/>
+      <c r="B63" s="15" t="n"/>
+      <c r="C63" s="15" t="n"/>
+      <c r="D63" s="21" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="E63" s="22">
+        <f>IF(E$4="","",COUNTIF(E5:E58,"G"))</f>
+        <v/>
+      </c>
+      <c r="F63" s="22">
+        <f>IF(F$4="","",COUNTIF(F5:F58,"G"))</f>
+        <v/>
+      </c>
+      <c r="G63" s="22">
+        <f>IF(G$4="","",COUNTIF(G5:G58,"G"))</f>
+        <v/>
+      </c>
+      <c r="H63" s="22">
+        <f>IF(H$4="","",COUNTIF(H5:H58,"G"))</f>
+        <v/>
+      </c>
+      <c r="I63" s="22">
+        <f>IF(I$4="","",COUNTIF(I5:I58,"G"))</f>
+        <v/>
+      </c>
+      <c r="J63" s="22">
+        <f>IF(J$4="","",COUNTIF(J5:J58,"G"))</f>
+        <v/>
+      </c>
+      <c r="K63" s="22">
+        <f>IF(K$4="","",COUNTIF(K5:K58,"G"))</f>
+        <v/>
+      </c>
+      <c r="L63" s="22">
+        <f>IF(L$4="","",COUNTIF(L5:L58,"G"))</f>
+        <v/>
+      </c>
+      <c r="M63" s="22">
+        <f>IF(M$4="","",COUNTIF(M5:M58,"G"))</f>
+        <v/>
+      </c>
+      <c r="N63" s="22">
+        <f>IF(N$4="","",COUNTIF(N5:N58,"G"))</f>
+        <v/>
+      </c>
+      <c r="O63" s="22">
+        <f>IF(O$4="","",COUNTIF(O5:O58,"G"))</f>
+        <v/>
+      </c>
+      <c r="P63" s="22">
+        <f>IF(P$4="","",COUNTIF(P5:P58,"G"))</f>
+        <v/>
+      </c>
+      <c r="Q63" s="22">
+        <f>IF(Q$4="","",COUNTIF(Q5:Q58,"G"))</f>
+        <v/>
+      </c>
+      <c r="R63" s="22">
+        <f>IF(R$4="","",COUNTIF(R5:R58,"G"))</f>
+        <v/>
+      </c>
+      <c r="S63" s="22">
+        <f>IF(S$4="","",COUNTIF(S5:S58,"G"))</f>
+        <v/>
+      </c>
+      <c r="T63" s="22">
+        <f>IF(T$4="","",COUNTIF(T5:T58,"G"))</f>
+        <v/>
+      </c>
+      <c r="U63" s="22">
+        <f>IF(U$4="","",COUNTIF(U5:U58,"G"))</f>
+        <v/>
+      </c>
+      <c r="V63" s="22">
+        <f>IF(V$4="","",COUNTIF(V5:V58,"G"))</f>
+        <v/>
+      </c>
+      <c r="W63" s="22">
+        <f>IF(W$4="","",COUNTIF(W5:W58,"G"))</f>
+        <v/>
+      </c>
+      <c r="X63" s="22">
+        <f>IF(X$4="","",COUNTIF(X5:X58,"G"))</f>
+        <v/>
+      </c>
+      <c r="Y63" s="22">
+        <f>IF(Y$4="","",COUNTIF(Y5:Y58,"G"))</f>
+        <v/>
+      </c>
+      <c r="Z63" s="22">
+        <f>IF(Z$4="","",COUNTIF(Z5:Z58,"G"))</f>
+        <v/>
+      </c>
+      <c r="AA63" s="22">
+        <f>IF(AA$4="","",COUNTIF(AA5:AA58,"G"))</f>
+        <v/>
+      </c>
+      <c r="AB63" s="22">
+        <f>IF(AB$4="","",COUNTIF(AB5:AB58,"G"))</f>
+        <v/>
+      </c>
+      <c r="AC63" s="22">
+        <f>IF(AC$4="","",COUNTIF(AC5:AC58,"G"))</f>
+        <v/>
+      </c>
+      <c r="AD63" s="22">
+        <f>IF(AD$4="","",COUNTIF(AD5:AD58,"G"))</f>
+        <v/>
+      </c>
+      <c r="AE63" s="22">
+        <f>IF(AE$4="","",COUNTIF(AE5:AE58,"G"))</f>
+        <v/>
+      </c>
+      <c r="AF63" s="22">
+        <f>IF(AF$4="","",COUNTIF(AF5:AF58,"G"))</f>
+        <v/>
+      </c>
+      <c r="AG63" s="22">
+        <f>IF(AG$4="","",COUNTIF(AG5:AG58,"G"))</f>
+        <v/>
+      </c>
+      <c r="AH63" s="22">
+        <f>IF(AH$4="","",COUNTIF(AH5:AH58,"G"))</f>
+        <v/>
+      </c>
+      <c r="AI63" s="22">
+        <f>IF(AI$4="","",COUNTIF(AI5:AI58,"G"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64" ht="15" customHeight="1">
+      <c r="A64" s="15" t="n"/>
+      <c r="B64" s="15" t="n"/>
+      <c r="C64" s="15" t="n"/>
+      <c r="D64" s="23" t="inlineStr">
+        <is>
+          <t>TOT</t>
+        </is>
+      </c>
+      <c r="E64" s="24">
+        <f>IF(E$4="","",SUM(E61:E63))</f>
+        <v/>
+      </c>
+      <c r="F64" s="24">
+        <f>IF(F$4="","",SUM(F61:F63))</f>
+        <v/>
+      </c>
+      <c r="G64" s="24">
+        <f>IF(G$4="","",SUM(G61:G63))</f>
+        <v/>
+      </c>
+      <c r="H64" s="24">
+        <f>IF(H$4="","",SUM(H61:H63))</f>
+        <v/>
+      </c>
+      <c r="I64" s="24">
+        <f>IF(I$4="","",SUM(I61:I63))</f>
+        <v/>
+      </c>
+      <c r="J64" s="24">
+        <f>IF(J$4="","",SUM(J61:J63))</f>
+        <v/>
+      </c>
+      <c r="K64" s="24">
+        <f>IF(K$4="","",SUM(K61:K63))</f>
+        <v/>
+      </c>
+      <c r="L64" s="24">
+        <f>IF(L$4="","",SUM(L61:L63))</f>
+        <v/>
+      </c>
+      <c r="M64" s="24">
+        <f>IF(M$4="","",SUM(M61:M63))</f>
+        <v/>
+      </c>
+      <c r="N64" s="24">
+        <f>IF(N$4="","",SUM(N61:N63))</f>
+        <v/>
+      </c>
+      <c r="O64" s="24">
+        <f>IF(O$4="","",SUM(O61:O63))</f>
+        <v/>
+      </c>
+      <c r="P64" s="24">
+        <f>IF(P$4="","",SUM(P61:P63))</f>
+        <v/>
+      </c>
+      <c r="Q64" s="24">
+        <f>IF(Q$4="","",SUM(Q61:Q63))</f>
+        <v/>
+      </c>
+      <c r="R64" s="24">
+        <f>IF(R$4="","",SUM(R61:R63))</f>
+        <v/>
+      </c>
+      <c r="S64" s="24">
+        <f>IF(S$4="","",SUM(S61:S63))</f>
+        <v/>
+      </c>
+      <c r="T64" s="24">
+        <f>IF(T$4="","",SUM(T61:T63))</f>
+        <v/>
+      </c>
+      <c r="U64" s="24">
+        <f>IF(U$4="","",SUM(U61:U63))</f>
+        <v/>
+      </c>
+      <c r="V64" s="24">
+        <f>IF(V$4="","",SUM(V61:V63))</f>
+        <v/>
+      </c>
+      <c r="W64" s="24">
+        <f>IF(W$4="","",SUM(W61:W63))</f>
+        <v/>
+      </c>
+      <c r="X64" s="24">
+        <f>IF(X$4="","",SUM(X61:X63))</f>
+        <v/>
+      </c>
+      <c r="Y64" s="24">
+        <f>IF(Y$4="","",SUM(Y61:Y63))</f>
+        <v/>
+      </c>
+      <c r="Z64" s="24">
+        <f>IF(Z$4="","",SUM(Z61:Z63))</f>
+        <v/>
+      </c>
+      <c r="AA64" s="24">
+        <f>IF(AA$4="","",SUM(AA61:AA63))</f>
+        <v/>
+      </c>
+      <c r="AB64" s="24">
+        <f>IF(AB$4="","",SUM(AB61:AB63))</f>
+        <v/>
+      </c>
+      <c r="AC64" s="24">
+        <f>IF(AC$4="","",SUM(AC61:AC63))</f>
+        <v/>
+      </c>
+      <c r="AD64" s="24">
+        <f>IF(AD$4="","",SUM(AD61:AD63))</f>
+        <v/>
+      </c>
+      <c r="AE64" s="24">
+        <f>IF(AE$4="","",SUM(AE61:AE63))</f>
+        <v/>
+      </c>
+      <c r="AF64" s="24">
+        <f>IF(AF$4="","",SUM(AF61:AF63))</f>
+        <v/>
+      </c>
+      <c r="AG64" s="24">
+        <f>IF(AG$4="","",SUM(AG61:AG63))</f>
+        <v/>
+      </c>
+      <c r="AH64" s="24">
+        <f>IF(AH$4="","",SUM(AH61:AH63))</f>
+        <v/>
+      </c>
+      <c r="AI64" s="24">
+        <f>IF(AI$4="","",SUM(AI61:AI63))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="25" t="inlineStr">
+        <is>
+          <t>SHIFT TIMES</t>
+        </is>
+      </c>
+      <c r="F66" s="25" t="inlineStr">
+        <is>
+          <t>CODE LEGEND</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="16" customHeight="1">
+      <c r="B67" s="26" t="inlineStr">
+        <is>
           <t>D</t>
         </is>
       </c>
-      <c r="E62" s="20">
-        <f>IF(E$5="","",COUNTIF(E6:E59,"D"))</f>
-        <v/>
-      </c>
-      <c r="F62" s="20">
-        <f>IF(F$5="","",COUNTIF(F6:F59,"D"))</f>
-        <v/>
-      </c>
-      <c r="G62" s="20">
-        <f>IF(G$5="","",COUNTIF(G6:G59,"D"))</f>
-        <v/>
-      </c>
-      <c r="H62" s="20">
-        <f>IF(H$5="","",COUNTIF(H6:H59,"D"))</f>
-        <v/>
-      </c>
-      <c r="I62" s="20">
-        <f>IF(I$5="","",COUNTIF(I6:I59,"D"))</f>
-        <v/>
-      </c>
-      <c r="J62" s="20">
-        <f>IF(J$5="","",COUNTIF(J6:J59,"D"))</f>
-        <v/>
-      </c>
-      <c r="K62" s="20">
-        <f>IF(K$5="","",COUNTIF(K6:K59,"D"))</f>
-        <v/>
-      </c>
-      <c r="L62" s="20">
-        <f>IF(L$5="","",COUNTIF(L6:L59,"D"))</f>
-        <v/>
-      </c>
-      <c r="M62" s="20">
-        <f>IF(M$5="","",COUNTIF(M6:M59,"D"))</f>
-        <v/>
-      </c>
-      <c r="N62" s="20">
-        <f>IF(N$5="","",COUNTIF(N6:N59,"D"))</f>
-        <v/>
-      </c>
-      <c r="O62" s="20">
-        <f>IF(O$5="","",COUNTIF(O6:O59,"D"))</f>
-        <v/>
-      </c>
-      <c r="P62" s="20">
-        <f>IF(P$5="","",COUNTIF(P6:P59,"D"))</f>
-        <v/>
-      </c>
-      <c r="Q62" s="20">
-        <f>IF(Q$5="","",COUNTIF(Q6:Q59,"D"))</f>
-        <v/>
-      </c>
-      <c r="R62" s="20">
-        <f>IF(R$5="","",COUNTIF(R6:R59,"D"))</f>
-        <v/>
-      </c>
-      <c r="S62" s="20">
-        <f>IF(S$5="","",COUNTIF(S6:S59,"D"))</f>
-        <v/>
-      </c>
-      <c r="T62" s="20">
-        <f>IF(T$5="","",COUNTIF(T6:T59,"D"))</f>
-        <v/>
-      </c>
-      <c r="U62" s="20">
-        <f>IF(U$5="","",COUNTIF(U6:U59,"D"))</f>
-        <v/>
-      </c>
-      <c r="V62" s="20">
-        <f>IF(V$5="","",COUNTIF(V6:V59,"D"))</f>
-        <v/>
-      </c>
-      <c r="W62" s="20">
-        <f>IF(W$5="","",COUNTIF(W6:W59,"D"))</f>
-        <v/>
-      </c>
-      <c r="X62" s="20">
-        <f>IF(X$5="","",COUNTIF(X6:X59,"D"))</f>
-        <v/>
-      </c>
-      <c r="Y62" s="20">
-        <f>IF(Y$5="","",COUNTIF(Y6:Y59,"D"))</f>
-        <v/>
-      </c>
-      <c r="Z62" s="20">
-        <f>IF(Z$5="","",COUNTIF(Z6:Z59,"D"))</f>
-        <v/>
-      </c>
-      <c r="AA62" s="20">
-        <f>IF(AA$5="","",COUNTIF(AA6:AA59,"D"))</f>
-        <v/>
-      </c>
-      <c r="AB62" s="20">
-        <f>IF(AB$5="","",COUNTIF(AB6:AB59,"D"))</f>
-        <v/>
-      </c>
-      <c r="AC62" s="20">
-        <f>IF(AC$5="","",COUNTIF(AC6:AC59,"D"))</f>
-        <v/>
-      </c>
-      <c r="AD62" s="20">
-        <f>IF(AD$5="","",COUNTIF(AD6:AD59,"D"))</f>
-        <v/>
-      </c>
-      <c r="AE62" s="20">
-        <f>IF(AE$5="","",COUNTIF(AE6:AE59,"D"))</f>
-        <v/>
-      </c>
-      <c r="AF62" s="20">
-        <f>IF(AF$5="","",COUNTIF(AF6:AF59,"D"))</f>
-        <v/>
-      </c>
-      <c r="AG62" s="20">
-        <f>IF(AG$5="","",COUNTIF(AG6:AG59,"D"))</f>
-        <v/>
-      </c>
-      <c r="AH62" s="20">
-        <f>IF(AH$5="","",COUNTIF(AH6:AH59,"D"))</f>
-        <v/>
-      </c>
-      <c r="AI62" s="20">
-        <f>IF(AI$5="","",COUNTIF(AI6:AI59,"D"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="63" ht="15" customHeight="1">
-      <c r="A63" s="16" t="n"/>
-      <c r="B63" s="16" t="n"/>
-      <c r="C63" s="16" t="n"/>
-      <c r="D63" s="21" t="inlineStr">
+      <c r="C67" s="27" t="inlineStr">
+        <is>
+          <t>DAY (07:00 - 15:00)</t>
+        </is>
+      </c>
+      <c r="F67" s="28" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G67" s="15" t="n"/>
+      <c r="H67" s="29" t="inlineStr">
+        <is>
+          <t>DAY</t>
+        </is>
+      </c>
+      <c r="L67" s="30" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="E63" s="22">
-        <f>IF(E$5="","",COUNTIF(E6:E59,"T"))</f>
-        <v/>
-      </c>
-      <c r="F63" s="22">
-        <f>IF(F$5="","",COUNTIF(F6:F59,"T"))</f>
-        <v/>
-      </c>
-      <c r="G63" s="22">
-        <f>IF(G$5="","",COUNTIF(G6:G59,"T"))</f>
-        <v/>
-      </c>
-      <c r="H63" s="22">
-        <f>IF(H$5="","",COUNTIF(H6:H59,"T"))</f>
-        <v/>
-      </c>
-      <c r="I63" s="22">
-        <f>IF(I$5="","",COUNTIF(I6:I59,"T"))</f>
-        <v/>
-      </c>
-      <c r="J63" s="22">
-        <f>IF(J$5="","",COUNTIF(J6:J59,"T"))</f>
-        <v/>
-      </c>
-      <c r="K63" s="22">
-        <f>IF(K$5="","",COUNTIF(K6:K59,"T"))</f>
-        <v/>
-      </c>
-      <c r="L63" s="22">
-        <f>IF(L$5="","",COUNTIF(L6:L59,"T"))</f>
-        <v/>
-      </c>
-      <c r="M63" s="22">
-        <f>IF(M$5="","",COUNTIF(M6:M59,"T"))</f>
-        <v/>
-      </c>
-      <c r="N63" s="22">
-        <f>IF(N$5="","",COUNTIF(N6:N59,"T"))</f>
-        <v/>
-      </c>
-      <c r="O63" s="22">
-        <f>IF(O$5="","",COUNTIF(O6:O59,"T"))</f>
-        <v/>
-      </c>
-      <c r="P63" s="22">
-        <f>IF(P$5="","",COUNTIF(P6:P59,"T"))</f>
-        <v/>
-      </c>
-      <c r="Q63" s="22">
-        <f>IF(Q$5="","",COUNTIF(Q6:Q59,"T"))</f>
-        <v/>
-      </c>
-      <c r="R63" s="22">
-        <f>IF(R$5="","",COUNTIF(R6:R59,"T"))</f>
-        <v/>
-      </c>
-      <c r="S63" s="22">
-        <f>IF(S$5="","",COUNTIF(S6:S59,"T"))</f>
-        <v/>
-      </c>
-      <c r="T63" s="22">
-        <f>IF(T$5="","",COUNTIF(T6:T59,"T"))</f>
-        <v/>
-      </c>
-      <c r="U63" s="22">
-        <f>IF(U$5="","",COUNTIF(U6:U59,"T"))</f>
-        <v/>
-      </c>
-      <c r="V63" s="22">
-        <f>IF(V$5="","",COUNTIF(V6:V59,"T"))</f>
-        <v/>
-      </c>
-      <c r="W63" s="22">
-        <f>IF(W$5="","",COUNTIF(W6:W59,"T"))</f>
-        <v/>
-      </c>
-      <c r="X63" s="22">
-        <f>IF(X$5="","",COUNTIF(X6:X59,"T"))</f>
-        <v/>
-      </c>
-      <c r="Y63" s="22">
-        <f>IF(Y$5="","",COUNTIF(Y6:Y59,"T"))</f>
-        <v/>
-      </c>
-      <c r="Z63" s="22">
-        <f>IF(Z$5="","",COUNTIF(Z6:Z59,"T"))</f>
-        <v/>
-      </c>
-      <c r="AA63" s="22">
-        <f>IF(AA$5="","",COUNTIF(AA6:AA59,"T"))</f>
-        <v/>
-      </c>
-      <c r="AB63" s="22">
-        <f>IF(AB$5="","",COUNTIF(AB6:AB59,"T"))</f>
-        <v/>
-      </c>
-      <c r="AC63" s="22">
-        <f>IF(AC$5="","",COUNTIF(AC6:AC59,"T"))</f>
-        <v/>
-      </c>
-      <c r="AD63" s="22">
-        <f>IF(AD$5="","",COUNTIF(AD6:AD59,"T"))</f>
-        <v/>
-      </c>
-      <c r="AE63" s="22">
-        <f>IF(AE$5="","",COUNTIF(AE6:AE59,"T"))</f>
-        <v/>
-      </c>
-      <c r="AF63" s="22">
-        <f>IF(AF$5="","",COUNTIF(AF6:AF59,"T"))</f>
-        <v/>
-      </c>
-      <c r="AG63" s="22">
-        <f>IF(AG$5="","",COUNTIF(AG6:AG59,"T"))</f>
-        <v/>
-      </c>
-      <c r="AH63" s="22">
-        <f>IF(AH$5="","",COUNTIF(AH6:AH59,"T"))</f>
-        <v/>
-      </c>
-      <c r="AI63" s="22">
-        <f>IF(AI$5="","",COUNTIF(AI6:AI59,"T"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="64" ht="15" customHeight="1">
-      <c r="A64" s="16" t="n"/>
-      <c r="B64" s="16" t="n"/>
-      <c r="C64" s="16" t="n"/>
-      <c r="D64" s="23" t="inlineStr">
+      <c r="M67" s="15" t="n"/>
+      <c r="N67" s="29" t="inlineStr">
+        <is>
+          <t>TWILIGHT</t>
+        </is>
+      </c>
+      <c r="R67" s="31" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
-      <c r="E64" s="24">
-        <f>IF(E$5="","",COUNTIF(E6:E59,"G"))</f>
-        <v/>
-      </c>
-      <c r="F64" s="24">
-        <f>IF(F$5="","",COUNTIF(F6:F59,"G"))</f>
-        <v/>
-      </c>
-      <c r="G64" s="24">
-        <f>IF(G$5="","",COUNTIF(G6:G59,"G"))</f>
-        <v/>
-      </c>
-      <c r="H64" s="24">
-        <f>IF(H$5="","",COUNTIF(H6:H59,"G"))</f>
-        <v/>
-      </c>
-      <c r="I64" s="24">
-        <f>IF(I$5="","",COUNTIF(I6:I59,"G"))</f>
-        <v/>
-      </c>
-      <c r="J64" s="24">
-        <f>IF(J$5="","",COUNTIF(J6:J59,"G"))</f>
-        <v/>
-      </c>
-      <c r="K64" s="24">
-        <f>IF(K$5="","",COUNTIF(K6:K59,"G"))</f>
-        <v/>
-      </c>
-      <c r="L64" s="24">
-        <f>IF(L$5="","",COUNTIF(L6:L59,"G"))</f>
-        <v/>
-      </c>
-      <c r="M64" s="24">
-        <f>IF(M$5="","",COUNTIF(M6:M59,"G"))</f>
-        <v/>
-      </c>
-      <c r="N64" s="24">
-        <f>IF(N$5="","",COUNTIF(N6:N59,"G"))</f>
-        <v/>
-      </c>
-      <c r="O64" s="24">
-        <f>IF(O$5="","",COUNTIF(O6:O59,"G"))</f>
-        <v/>
-      </c>
-      <c r="P64" s="24">
-        <f>IF(P$5="","",COUNTIF(P6:P59,"G"))</f>
-        <v/>
-      </c>
-      <c r="Q64" s="24">
-        <f>IF(Q$5="","",COUNTIF(Q6:Q59,"G"))</f>
-        <v/>
-      </c>
-      <c r="R64" s="24">
-        <f>IF(R$5="","",COUNTIF(R6:R59,"G"))</f>
-        <v/>
-      </c>
-      <c r="S64" s="24">
-        <f>IF(S$5="","",COUNTIF(S6:S59,"G"))</f>
-        <v/>
-      </c>
-      <c r="T64" s="24">
-        <f>IF(T$5="","",COUNTIF(T6:T59,"G"))</f>
-        <v/>
-      </c>
-      <c r="U64" s="24">
-        <f>IF(U$5="","",COUNTIF(U6:U59,"G"))</f>
-        <v/>
-      </c>
-      <c r="V64" s="24">
-        <f>IF(V$5="","",COUNTIF(V6:V59,"G"))</f>
-        <v/>
-      </c>
-      <c r="W64" s="24">
-        <f>IF(W$5="","",COUNTIF(W6:W59,"G"))</f>
-        <v/>
-      </c>
-      <c r="X64" s="24">
-        <f>IF(X$5="","",COUNTIF(X6:X59,"G"))</f>
-        <v/>
-      </c>
-      <c r="Y64" s="24">
-        <f>IF(Y$5="","",COUNTIF(Y6:Y59,"G"))</f>
-        <v/>
-      </c>
-      <c r="Z64" s="24">
-        <f>IF(Z$5="","",COUNTIF(Z6:Z59,"G"))</f>
-        <v/>
-      </c>
-      <c r="AA64" s="24">
-        <f>IF(AA$5="","",COUNTIF(AA6:AA59,"G"))</f>
-        <v/>
-      </c>
-      <c r="AB64" s="24">
-        <f>IF(AB$5="","",COUNTIF(AB6:AB59,"G"))</f>
-        <v/>
-      </c>
-      <c r="AC64" s="24">
-        <f>IF(AC$5="","",COUNTIF(AC6:AC59,"G"))</f>
-        <v/>
-      </c>
-      <c r="AD64" s="24">
-        <f>IF(AD$5="","",COUNTIF(AD6:AD59,"G"))</f>
-        <v/>
-      </c>
-      <c r="AE64" s="24">
-        <f>IF(AE$5="","",COUNTIF(AE6:AE59,"G"))</f>
-        <v/>
-      </c>
-      <c r="AF64" s="24">
-        <f>IF(AF$5="","",COUNTIF(AF6:AF59,"G"))</f>
-        <v/>
-      </c>
-      <c r="AG64" s="24">
-        <f>IF(AG$5="","",COUNTIF(AG6:AG59,"G"))</f>
-        <v/>
-      </c>
-      <c r="AH64" s="24">
-        <f>IF(AH$5="","",COUNTIF(AH6:AH59,"G"))</f>
-        <v/>
-      </c>
-      <c r="AI64" s="24">
-        <f>IF(AI$5="","",COUNTIF(AI6:AI59,"G"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="65" ht="15" customHeight="1">
-      <c r="A65" s="16" t="n"/>
-      <c r="B65" s="16" t="n"/>
-      <c r="C65" s="16" t="n"/>
-      <c r="D65" s="25" t="inlineStr">
-        <is>
-          <t>TOT</t>
-        </is>
-      </c>
-      <c r="E65" s="26">
-        <f>IF(E$5="","",SUM(E62:E64))</f>
-        <v/>
-      </c>
-      <c r="F65" s="26">
-        <f>IF(F$5="","",SUM(F62:F64))</f>
-        <v/>
-      </c>
-      <c r="G65" s="26">
-        <f>IF(G$5="","",SUM(G62:G64))</f>
-        <v/>
-      </c>
-      <c r="H65" s="26">
-        <f>IF(H$5="","",SUM(H62:H64))</f>
-        <v/>
-      </c>
-      <c r="I65" s="26">
-        <f>IF(I$5="","",SUM(I62:I64))</f>
-        <v/>
-      </c>
-      <c r="J65" s="26">
-        <f>IF(J$5="","",SUM(J62:J64))</f>
-        <v/>
-      </c>
-      <c r="K65" s="26">
-        <f>IF(K$5="","",SUM(K62:K64))</f>
-        <v/>
-      </c>
-      <c r="L65" s="26">
-        <f>IF(L$5="","",SUM(L62:L64))</f>
-        <v/>
-      </c>
-      <c r="M65" s="26">
-        <f>IF(M$5="","",SUM(M62:M64))</f>
-        <v/>
-      </c>
-      <c r="N65" s="26">
-        <f>IF(N$5="","",SUM(N62:N64))</f>
-        <v/>
-      </c>
-      <c r="O65" s="26">
-        <f>IF(O$5="","",SUM(O62:O64))</f>
-        <v/>
-      </c>
-      <c r="P65" s="26">
-        <f>IF(P$5="","",SUM(P62:P64))</f>
-        <v/>
-      </c>
-      <c r="Q65" s="26">
-        <f>IF(Q$5="","",SUM(Q62:Q64))</f>
-        <v/>
-      </c>
-      <c r="R65" s="26">
-        <f>IF(R$5="","",SUM(R62:R64))</f>
-        <v/>
-      </c>
-      <c r="S65" s="26">
-        <f>IF(S$5="","",SUM(S62:S64))</f>
-        <v/>
-      </c>
-      <c r="T65" s="26">
-        <f>IF(T$5="","",SUM(T62:T64))</f>
-        <v/>
-      </c>
-      <c r="U65" s="26">
-        <f>IF(U$5="","",SUM(U62:U64))</f>
-        <v/>
-      </c>
-      <c r="V65" s="26">
-        <f>IF(V$5="","",SUM(V62:V64))</f>
-        <v/>
-      </c>
-      <c r="W65" s="26">
-        <f>IF(W$5="","",SUM(W62:W64))</f>
-        <v/>
-      </c>
-      <c r="X65" s="26">
-        <f>IF(X$5="","",SUM(X62:X64))</f>
-        <v/>
-      </c>
-      <c r="Y65" s="26">
-        <f>IF(Y$5="","",SUM(Y62:Y64))</f>
-        <v/>
-      </c>
-      <c r="Z65" s="26">
-        <f>IF(Z$5="","",SUM(Z62:Z64))</f>
-        <v/>
-      </c>
-      <c r="AA65" s="26">
-        <f>IF(AA$5="","",SUM(AA62:AA64))</f>
-        <v/>
-      </c>
-      <c r="AB65" s="26">
-        <f>IF(AB$5="","",SUM(AB62:AB64))</f>
-        <v/>
-      </c>
-      <c r="AC65" s="26">
-        <f>IF(AC$5="","",SUM(AC62:AC64))</f>
-        <v/>
-      </c>
-      <c r="AD65" s="26">
-        <f>IF(AD$5="","",SUM(AD62:AD64))</f>
-        <v/>
-      </c>
-      <c r="AE65" s="26">
-        <f>IF(AE$5="","",SUM(AE62:AE64))</f>
-        <v/>
-      </c>
-      <c r="AF65" s="26">
-        <f>IF(AF$5="","",SUM(AF62:AF64))</f>
-        <v/>
-      </c>
-      <c r="AG65" s="26">
-        <f>IF(AG$5="","",SUM(AG62:AG64))</f>
-        <v/>
-      </c>
-      <c r="AH65" s="26">
-        <f>IF(AH$5="","",SUM(AH62:AH64))</f>
-        <v/>
-      </c>
-      <c r="AI65" s="26">
-        <f>IF(AI$5="","",SUM(AI62:AI64))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="27" t="inlineStr">
-        <is>
-          <t>SHIFT TIMES</t>
-        </is>
-      </c>
-      <c r="F67" s="27" t="inlineStr">
-        <is>
-          <t>CODE LEGEND</t>
+      <c r="S67" s="15" t="n"/>
+      <c r="T67" s="29" t="inlineStr">
+        <is>
+          <t>GRAVEYARD</t>
+        </is>
+      </c>
+      <c r="X67" s="32" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
+      <c r="Y67" s="15" t="n"/>
+      <c r="Z67" s="29" t="inlineStr">
+        <is>
+          <t>TRAINING</t>
+        </is>
+      </c>
+      <c r="AD67" s="33" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="AE67" s="15" t="n"/>
+      <c r="AF67" s="29" t="inlineStr">
+        <is>
+          <t>VACATION</t>
         </is>
       </c>
     </row>
     <row r="68" ht="16" customHeight="1">
-      <c r="B68" s="28" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C68" s="29" t="inlineStr">
-        <is>
-          <t>DAY (07:00 - 15:00)</t>
-        </is>
-      </c>
-      <c r="F68" s="30" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="G68" s="16" t="n"/>
-      <c r="H68" s="31" t="inlineStr">
-        <is>
-          <t>DAY</t>
-        </is>
-      </c>
-      <c r="L68" s="32" t="inlineStr">
+      <c r="B68" s="34" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="M68" s="16" t="n"/>
-      <c r="N68" s="31" t="inlineStr">
-        <is>
-          <t>TWILIGHT</t>
-        </is>
-      </c>
-      <c r="R68" s="33" t="inlineStr">
+      <c r="C68" s="27" t="inlineStr">
+        <is>
+          <t>TWI (15:00 - 23:00)</t>
+        </is>
+      </c>
+      <c r="F68" s="35" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="G68" s="15" t="n"/>
+      <c r="H68" s="29" t="inlineStr">
+        <is>
+          <t>REST/RDO</t>
+        </is>
+      </c>
+      <c r="L68" s="36" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="M68" s="15" t="n"/>
+      <c r="N68" s="29" t="inlineStr">
+        <is>
+          <t>ABSENT</t>
+        </is>
+      </c>
+      <c r="R68" s="37" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="S68" s="15" t="n"/>
+      <c r="T68" s="29" t="inlineStr">
+        <is>
+          <t>HOLIDAY</t>
+        </is>
+      </c>
+      <c r="X68" s="38" t="inlineStr">
+        <is>
+          <t>OT</t>
+        </is>
+      </c>
+      <c r="Y68" s="15" t="n"/>
+      <c r="Z68" s="29" t="inlineStr">
+        <is>
+          <t>OVERTIME</t>
+        </is>
+      </c>
+      <c r="AD68" s="39" t="inlineStr">
+        <is>
+          <t>OS</t>
+        </is>
+      </c>
+      <c r="AE68" s="15" t="n"/>
+      <c r="AF68" s="29" t="inlineStr">
+        <is>
+          <t>OUTSTATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="16" customHeight="1">
+      <c r="B69" s="40" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
-      <c r="S68" s="16" t="n"/>
-      <c r="T68" s="31" t="inlineStr">
-        <is>
-          <t>GRAVEYARD</t>
-        </is>
-      </c>
-      <c r="X68" s="34" t="inlineStr">
-        <is>
-          <t>TR</t>
-        </is>
-      </c>
-      <c r="Y68" s="16" t="n"/>
-      <c r="Z68" s="31" t="inlineStr">
-        <is>
-          <t>TRAINING</t>
-        </is>
-      </c>
-      <c r="AD68" s="35" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="AE68" s="16" t="n"/>
-      <c r="AF68" s="31" t="inlineStr">
-        <is>
-          <t>VACATION</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="16" customHeight="1">
-      <c r="B69" s="36" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="C69" s="29" t="inlineStr">
-        <is>
-          <t>TWI (15:00 - 23:00)</t>
-        </is>
-      </c>
-      <c r="F69" s="37" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="G69" s="16" t="n"/>
-      <c r="H69" s="31" t="inlineStr">
-        <is>
-          <t>REST/RDO</t>
-        </is>
-      </c>
-      <c r="L69" s="38" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="M69" s="16" t="n"/>
-      <c r="N69" s="31" t="inlineStr">
-        <is>
-          <t>ABSENT</t>
-        </is>
-      </c>
-      <c r="R69" s="39" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="S69" s="16" t="n"/>
-      <c r="T69" s="31" t="inlineStr">
-        <is>
-          <t>HOLIDAY</t>
-        </is>
-      </c>
-      <c r="X69" s="40" t="inlineStr">
-        <is>
-          <t>OT</t>
-        </is>
-      </c>
-      <c r="Y69" s="16" t="n"/>
-      <c r="Z69" s="31" t="inlineStr">
-        <is>
-          <t>OVERTIME</t>
-        </is>
-      </c>
-      <c r="AD69" s="41" t="inlineStr">
-        <is>
-          <t>OS</t>
-        </is>
-      </c>
-      <c r="AE69" s="16" t="n"/>
-      <c r="AF69" s="31" t="inlineStr">
-        <is>
-          <t>OUTSTATION</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="16" customHeight="1">
-      <c r="B70" s="42" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="C70" s="29" t="inlineStr">
+      <c r="C69" s="27" t="inlineStr">
         <is>
           <t>GRV (23:00 - 07:00)</t>
         </is>
       </c>
-      <c r="F70" s="43" t="inlineStr">
+      <c r="F69" s="41" t="inlineStr">
         <is>
           <t>S/L</t>
         </is>
       </c>
-      <c r="G70" s="16" t="n"/>
-      <c r="H70" s="31" t="inlineStr">
+      <c r="G69" s="15" t="n"/>
+      <c r="H69" s="29" t="inlineStr">
         <is>
           <t>SICK LEAVE</t>
         </is>
       </c>
-      <c r="L70" s="44" t="inlineStr">
+      <c r="L69" s="42" t="inlineStr">
         <is>
           <t>C/T</t>
         </is>
       </c>
-      <c r="M70" s="16" t="n"/>
-      <c r="N70" s="31" t="inlineStr">
+      <c r="M69" s="15" t="n"/>
+      <c r="N69" s="29" t="inlineStr">
         <is>
           <t>COMP TIME</t>
         </is>
       </c>
-      <c r="R70" s="45" t="inlineStr">
+      <c r="R69" s="43" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="S70" s="16" t="n"/>
-      <c r="T70" s="31" t="inlineStr">
+      <c r="S69" s="15" t="n"/>
+      <c r="T69" s="29" t="inlineStr">
         <is>
           <t>LATE/LEAVE</t>
         </is>
       </c>
-      <c r="X70" s="46" t="inlineStr">
+      <c r="X69" s="44" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="Y70" s="16" t="n"/>
-      <c r="Z70" s="31" t="inlineStr">
+      <c r="Y69" s="15" t="n"/>
+      <c r="Z69" s="29" t="inlineStr">
         <is>
           <t>NOTE</t>
         </is>
       </c>
     </row>
+    <row r="71">
+      <c r="A71" s="45" t="inlineStr">
+        <is>
+          <t>STAFF LIST — copy into crews above (excluded from print)</t>
+        </is>
+      </c>
+    </row>
     <row r="72">
-      <c r="A72" s="47" t="inlineStr">
-        <is>
-          <t>STAFF LIST — copy into crews above (excluded from print)</t>
+      <c r="A72" s="46" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B72" s="46" t="inlineStr">
+        <is>
+          <t>PRN</t>
+        </is>
+      </c>
+      <c r="C72" s="46" t="inlineStr">
+        <is>
+          <t>NAME</t>
+        </is>
+      </c>
+      <c r="D72" s="46" t="inlineStr">
+        <is>
+          <t>Posn</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="8" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B73" s="8" t="inlineStr">
-        <is>
-          <t>PRN</t>
-        </is>
-      </c>
-      <c r="C73" s="8" t="inlineStr">
-        <is>
-          <t>NAME</t>
-        </is>
-      </c>
-      <c r="D73" s="8" t="inlineStr">
-        <is>
-          <t>Posn</t>
+      <c r="A73" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="B73" s="11" t="inlineStr">
+        <is>
+          <t>13006435</t>
+        </is>
+      </c>
+      <c r="C73" s="47" t="inlineStr">
+        <is>
+          <t>HOMAID ALJAHDALI</t>
+        </is>
+      </c>
+      <c r="D73" s="10" t="inlineStr">
+        <is>
+          <t>ACT/SUPV</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B74" s="11" t="inlineStr">
         <is>
-          <t>13006435</t>
-        </is>
-      </c>
-      <c r="C74" s="48" t="inlineStr">
-        <is>
-          <t>HOMAID ALJAHDALI</t>
+          <t>13008931</t>
+        </is>
+      </c>
+      <c r="C74" s="47" t="inlineStr">
+        <is>
+          <t>RONILO NOGADAS AMEN</t>
         </is>
       </c>
       <c r="D74" s="10" t="inlineStr">
@@ -4804,16 +4797,16 @@
     </row>
     <row r="75">
       <c r="A75" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B75" s="11" t="inlineStr">
         <is>
-          <t>13008931</t>
-        </is>
-      </c>
-      <c r="C75" s="48" t="inlineStr">
-        <is>
-          <t>RONILO NOGADAS AMEN</t>
+          <t>13010279</t>
+        </is>
+      </c>
+      <c r="C75" s="47" t="inlineStr">
+        <is>
+          <t>AHMED M. ALWAHBI</t>
         </is>
       </c>
       <c r="D75" s="10" t="inlineStr">
@@ -4824,16 +4817,16 @@
     </row>
     <row r="76">
       <c r="A76" s="10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B76" s="11" t="inlineStr">
         <is>
-          <t>13010279</t>
-        </is>
-      </c>
-      <c r="C76" s="48" t="inlineStr">
-        <is>
-          <t>AHMED M. ALWAHBI</t>
+          <t>13007568</t>
+        </is>
+      </c>
+      <c r="C76" s="47" t="inlineStr">
+        <is>
+          <t>NAIF ALANEZI</t>
         </is>
       </c>
       <c r="D76" s="10" t="inlineStr">
@@ -4844,56 +4837,56 @@
     </row>
     <row r="77">
       <c r="A77" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B77" s="11" t="inlineStr">
         <is>
-          <t>13007568</t>
-        </is>
-      </c>
-      <c r="C77" s="48" t="inlineStr">
-        <is>
-          <t>NAIF ALANEZI</t>
+          <t>30005295</t>
+        </is>
+      </c>
+      <c r="C77" s="47" t="inlineStr">
+        <is>
+          <t>RODEL CLEMENTE</t>
         </is>
       </c>
       <c r="D77" s="10" t="inlineStr">
         <is>
-          <t>ACT/SUPV</t>
+          <t>TECH</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B78" s="11" t="inlineStr">
         <is>
-          <t>30005295</t>
-        </is>
-      </c>
-      <c r="C78" s="48" t="inlineStr">
-        <is>
-          <t>RODEL CLEMENTE</t>
+          <t>30001593</t>
+        </is>
+      </c>
+      <c r="C78" s="47" t="inlineStr">
+        <is>
+          <t>FYSAL M. ALEDAINI</t>
         </is>
       </c>
       <c r="D78" s="10" t="inlineStr">
         <is>
-          <t>TECH</t>
+          <t>OJT</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B79" s="11" t="inlineStr">
         <is>
-          <t>30001593</t>
-        </is>
-      </c>
-      <c r="C79" s="48" t="inlineStr">
-        <is>
-          <t>FYSAL M. ALEDAINI</t>
+          <t>30001338</t>
+        </is>
+      </c>
+      <c r="C79" s="47" t="inlineStr">
+        <is>
+          <t>MASHHOUR ALSULAIMANI</t>
         </is>
       </c>
       <c r="D79" s="10" t="inlineStr">
@@ -4904,16 +4897,16 @@
     </row>
     <row r="80">
       <c r="A80" s="10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B80" s="11" t="inlineStr">
         <is>
-          <t>30001338</t>
-        </is>
-      </c>
-      <c r="C80" s="48" t="inlineStr">
-        <is>
-          <t>MASHHOUR ALSULAIMANI</t>
+          <t>30001573</t>
+        </is>
+      </c>
+      <c r="C80" s="47" t="inlineStr">
+        <is>
+          <t>JEHAD M. HAKAMI</t>
         </is>
       </c>
       <c r="D80" s="10" t="inlineStr">
@@ -4924,16 +4917,16 @@
     </row>
     <row r="81">
       <c r="A81" s="10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B81" s="11" t="inlineStr">
         <is>
-          <t>30001573</t>
-        </is>
-      </c>
-      <c r="C81" s="48" t="inlineStr">
-        <is>
-          <t>JEHAD M. HAKAMI</t>
+          <t>30001366</t>
+        </is>
+      </c>
+      <c r="C81" s="47" t="inlineStr">
+        <is>
+          <t>ABDULAZIZ ZAKOUR</t>
         </is>
       </c>
       <c r="D81" s="10" t="inlineStr">
@@ -4944,16 +4937,16 @@
     </row>
     <row r="82">
       <c r="A82" s="10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B82" s="11" t="inlineStr">
         <is>
-          <t>30001366</t>
-        </is>
-      </c>
-      <c r="C82" s="48" t="inlineStr">
-        <is>
-          <t>ABDULAZIZ ZAKOUR</t>
+          <t>30001450</t>
+        </is>
+      </c>
+      <c r="C82" s="47" t="inlineStr">
+        <is>
+          <t>MUHAMMED ALSHAIKH</t>
         </is>
       </c>
       <c r="D82" s="10" t="inlineStr">
@@ -4964,16 +4957,16 @@
     </row>
     <row r="83">
       <c r="A83" s="10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B83" s="11" t="inlineStr">
         <is>
-          <t>30001450</t>
-        </is>
-      </c>
-      <c r="C83" s="48" t="inlineStr">
-        <is>
-          <t>MUHAMMED ALSHAIKH</t>
+          <t>30001602</t>
+        </is>
+      </c>
+      <c r="C83" s="47" t="inlineStr">
+        <is>
+          <t>AHMED M. ALYAMANI</t>
         </is>
       </c>
       <c r="D83" s="10" t="inlineStr">
@@ -4984,36 +4977,36 @@
     </row>
     <row r="84">
       <c r="A84" s="10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B84" s="11" t="inlineStr">
         <is>
-          <t>30001602</t>
-        </is>
-      </c>
-      <c r="C84" s="48" t="inlineStr">
-        <is>
-          <t>AHMED M. ALYAMANI</t>
+          <t>40001135</t>
+        </is>
+      </c>
+      <c r="C84" s="47" t="inlineStr">
+        <is>
+          <t>SYAHLENDRA SYAMSOE</t>
         </is>
       </c>
       <c r="D84" s="10" t="inlineStr">
         <is>
-          <t>OJT</t>
+          <t>FITTER</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B85" s="11" t="inlineStr">
         <is>
-          <t>40001135</t>
-        </is>
-      </c>
-      <c r="C85" s="48" t="inlineStr">
-        <is>
-          <t>SYAHLENDRA SYAMSOE</t>
+          <t>70010082</t>
+        </is>
+      </c>
+      <c r="C85" s="47" t="inlineStr">
+        <is>
+          <t>MOHAMMAD KAIFI</t>
         </is>
       </c>
       <c r="D85" s="10" t="inlineStr">
@@ -5024,16 +5017,16 @@
     </row>
     <row r="86">
       <c r="A86" s="10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B86" s="11" t="inlineStr">
         <is>
-          <t>70010082</t>
-        </is>
-      </c>
-      <c r="C86" s="48" t="inlineStr">
-        <is>
-          <t>MOHAMMAD KAIFI</t>
+          <t>13009258</t>
+        </is>
+      </c>
+      <c r="C86" s="47" t="inlineStr">
+        <is>
+          <t>ALI ALAHMADI</t>
         </is>
       </c>
       <c r="D86" s="10" t="inlineStr">
@@ -5044,16 +5037,16 @@
     </row>
     <row r="87">
       <c r="A87" s="10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B87" s="11" t="inlineStr">
         <is>
-          <t>13009258</t>
-        </is>
-      </c>
-      <c r="C87" s="48" t="inlineStr">
-        <is>
-          <t>ALI ALAHMADI</t>
+          <t>13009255</t>
+        </is>
+      </c>
+      <c r="C87" s="47" t="inlineStr">
+        <is>
+          <t>HOSSAM ALGHAMDI</t>
         </is>
       </c>
       <c r="D87" s="10" t="inlineStr">
@@ -5064,16 +5057,16 @@
     </row>
     <row r="88">
       <c r="A88" s="10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B88" s="11" t="inlineStr">
         <is>
-          <t>13009255</t>
-        </is>
-      </c>
-      <c r="C88" s="48" t="inlineStr">
-        <is>
-          <t>HOSSAM ALGHAMDI</t>
+          <t>13009047</t>
+        </is>
+      </c>
+      <c r="C88" s="47" t="inlineStr">
+        <is>
+          <t>JIMRICKS AQINO</t>
         </is>
       </c>
       <c r="D88" s="10" t="inlineStr">
@@ -5084,36 +5077,36 @@
     </row>
     <row r="89">
       <c r="A89" s="10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B89" s="11" t="inlineStr">
         <is>
-          <t>13009047</t>
-        </is>
-      </c>
-      <c r="C89" s="48" t="inlineStr">
-        <is>
-          <t>JIMRICKS AQINO</t>
+          <t>13006567</t>
+        </is>
+      </c>
+      <c r="C89" s="47" t="inlineStr">
+        <is>
+          <t>AHMED AL-GHAMDI</t>
         </is>
       </c>
       <c r="D89" s="10" t="inlineStr">
         <is>
-          <t>FITTER</t>
+          <t>ACT/SUPV</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="10" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B90" s="11" t="inlineStr">
         <is>
-          <t>13006567</t>
-        </is>
-      </c>
-      <c r="C90" s="48" t="inlineStr">
-        <is>
-          <t>AHMED AL-GHAMDI</t>
+          <t>13010253</t>
+        </is>
+      </c>
+      <c r="C90" s="47" t="inlineStr">
+        <is>
+          <t>AHMED S. ALGHAMDI</t>
         </is>
       </c>
       <c r="D90" s="10" t="inlineStr">
@@ -5124,36 +5117,36 @@
     </row>
     <row r="91">
       <c r="A91" s="10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B91" s="11" t="inlineStr">
         <is>
-          <t>13010253</t>
-        </is>
-      </c>
-      <c r="C91" s="48" t="inlineStr">
-        <is>
-          <t>AHMED S. ALGHAMDI</t>
+          <t>13007276</t>
+        </is>
+      </c>
+      <c r="C91" s="47" t="inlineStr">
+        <is>
+          <t>MOHAMMED BAROOM</t>
         </is>
       </c>
       <c r="D91" s="10" t="inlineStr">
         <is>
-          <t>ACT/SUPV</t>
+          <t>TECH</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B92" s="11" t="inlineStr">
         <is>
-          <t>13007276</t>
-        </is>
-      </c>
-      <c r="C92" s="48" t="inlineStr">
-        <is>
-          <t>MOHAMMED BAROOM</t>
+          <t>13010286</t>
+        </is>
+      </c>
+      <c r="C92" s="47" t="inlineStr">
+        <is>
+          <t>ABDULAZIZ F. ALBOUQ</t>
         </is>
       </c>
       <c r="D92" s="10" t="inlineStr">
@@ -5164,16 +5157,16 @@
     </row>
     <row r="93">
       <c r="A93" s="10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B93" s="11" t="inlineStr">
         <is>
-          <t>13010286</t>
-        </is>
-      </c>
-      <c r="C93" s="48" t="inlineStr">
-        <is>
-          <t>ABDULAZIZ F. ALBOUQ</t>
+          <t>30004221</t>
+        </is>
+      </c>
+      <c r="C93" s="47" t="inlineStr">
+        <is>
+          <t>YOUSEF BARIFAH</t>
         </is>
       </c>
       <c r="D93" s="10" t="inlineStr">
@@ -5184,36 +5177,36 @@
     </row>
     <row r="94">
       <c r="A94" s="10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B94" s="11" t="inlineStr">
         <is>
-          <t>30004221</t>
-        </is>
-      </c>
-      <c r="C94" s="48" t="inlineStr">
-        <is>
-          <t>YOUSEF BARIFAH</t>
+          <t>30001345</t>
+        </is>
+      </c>
+      <c r="C94" s="47" t="inlineStr">
+        <is>
+          <t>AHMED ALSHARIF</t>
         </is>
       </c>
       <c r="D94" s="10" t="inlineStr">
         <is>
-          <t>TECH</t>
+          <t>OJT</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="10" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B95" s="11" t="inlineStr">
         <is>
-          <t>30001345</t>
-        </is>
-      </c>
-      <c r="C95" s="48" t="inlineStr">
-        <is>
-          <t>AHMED ALSHARIF</t>
+          <t>30001351</t>
+        </is>
+      </c>
+      <c r="C95" s="47" t="inlineStr">
+        <is>
+          <t>KHALID ALSHUBRAMI</t>
         </is>
       </c>
       <c r="D95" s="10" t="inlineStr">
@@ -5224,16 +5217,16 @@
     </row>
     <row r="96">
       <c r="A96" s="10" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B96" s="11" t="inlineStr">
         <is>
-          <t>30001351</t>
-        </is>
-      </c>
-      <c r="C96" s="48" t="inlineStr">
-        <is>
-          <t>KHALID ALSHUBRAMI</t>
+          <t>30001451</t>
+        </is>
+      </c>
+      <c r="C96" s="47" t="inlineStr">
+        <is>
+          <t>MUHAMMED ALHARBI</t>
         </is>
       </c>
       <c r="D96" s="10" t="inlineStr">
@@ -5244,16 +5237,16 @@
     </row>
     <row r="97">
       <c r="A97" s="10" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B97" s="11" t="inlineStr">
         <is>
-          <t>30001451</t>
-        </is>
-      </c>
-      <c r="C97" s="48" t="inlineStr">
-        <is>
-          <t>MUHAMMED ALHARBI</t>
+          <t>30001452</t>
+        </is>
+      </c>
+      <c r="C97" s="47" t="inlineStr">
+        <is>
+          <t>SAAD ALDOSARI</t>
         </is>
       </c>
       <c r="D97" s="10" t="inlineStr">
@@ -5264,16 +5257,16 @@
     </row>
     <row r="98">
       <c r="A98" s="10" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B98" s="11" t="inlineStr">
         <is>
-          <t>30001452</t>
-        </is>
-      </c>
-      <c r="C98" s="48" t="inlineStr">
-        <is>
-          <t>SAAD ALDOSARI</t>
+          <t>30001461</t>
+        </is>
+      </c>
+      <c r="C98" s="47" t="inlineStr">
+        <is>
+          <t>HUSSAM ALTHUBAITI</t>
         </is>
       </c>
       <c r="D98" s="10" t="inlineStr">
@@ -5284,16 +5277,16 @@
     </row>
     <row r="99">
       <c r="A99" s="10" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B99" s="11" t="inlineStr">
         <is>
-          <t>30001461</t>
-        </is>
-      </c>
-      <c r="C99" s="48" t="inlineStr">
-        <is>
-          <t>HUSSAM ALTHUBAITI</t>
+          <t>30001575</t>
+        </is>
+      </c>
+      <c r="C99" s="47" t="inlineStr">
+        <is>
+          <t>FADUL A. FADUL</t>
         </is>
       </c>
       <c r="D99" s="10" t="inlineStr">
@@ -5304,16 +5297,16 @@
     </row>
     <row r="100">
       <c r="A100" s="10" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B100" s="11" t="inlineStr">
         <is>
-          <t>30001575</t>
-        </is>
-      </c>
-      <c r="C100" s="48" t="inlineStr">
-        <is>
-          <t>FADUL A. FADUL</t>
+          <t>30001577</t>
+        </is>
+      </c>
+      <c r="C100" s="47" t="inlineStr">
+        <is>
+          <t>FOUAD A. MOJALLY</t>
         </is>
       </c>
       <c r="D100" s="10" t="inlineStr">
@@ -5324,16 +5317,16 @@
     </row>
     <row r="101">
       <c r="A101" s="10" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B101" s="11" t="inlineStr">
         <is>
-          <t>30001577</t>
-        </is>
-      </c>
-      <c r="C101" s="48" t="inlineStr">
-        <is>
-          <t>FOUAD A. MOJALLY</t>
+          <t>30001774</t>
+        </is>
+      </c>
+      <c r="C101" s="47" t="inlineStr">
+        <is>
+          <t>SAAD A. ALQAHTANI</t>
         </is>
       </c>
       <c r="D101" s="10" t="inlineStr">
@@ -5344,36 +5337,36 @@
     </row>
     <row r="102">
       <c r="A102" s="10" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B102" s="11" t="inlineStr">
         <is>
-          <t>30001774</t>
-        </is>
-      </c>
-      <c r="C102" s="48" t="inlineStr">
-        <is>
-          <t>SAAD A. ALQAHTANI</t>
+          <t>40000188</t>
+        </is>
+      </c>
+      <c r="C102" s="47" t="inlineStr">
+        <is>
+          <t>RAKAN AGILY</t>
         </is>
       </c>
       <c r="D102" s="10" t="inlineStr">
         <is>
-          <t>OJT</t>
+          <t>FITTER</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="10" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B103" s="11" t="inlineStr">
         <is>
-          <t>40000188</t>
-        </is>
-      </c>
-      <c r="C103" s="48" t="inlineStr">
-        <is>
-          <t>RAKAN AGILY</t>
+          <t>13009042</t>
+        </is>
+      </c>
+      <c r="C103" s="47" t="inlineStr">
+        <is>
+          <t>OLANDRES JR BEINVENIDO</t>
         </is>
       </c>
       <c r="D103" s="10" t="inlineStr">
@@ -5384,16 +5377,16 @@
     </row>
     <row r="104">
       <c r="A104" s="10" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B104" s="11" t="inlineStr">
         <is>
-          <t>13009042</t>
-        </is>
-      </c>
-      <c r="C104" s="48" t="inlineStr">
-        <is>
-          <t>OLANDRES JR BEINVENIDO</t>
+          <t>40000706</t>
+        </is>
+      </c>
+      <c r="C104" s="47" t="inlineStr">
+        <is>
+          <t>JASON C. GUEVARRA</t>
         </is>
       </c>
       <c r="D104" s="10" t="inlineStr">
@@ -5404,16 +5397,16 @@
     </row>
     <row r="105">
       <c r="A105" s="10" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B105" s="11" t="inlineStr">
         <is>
-          <t>40000706</t>
-        </is>
-      </c>
-      <c r="C105" s="48" t="inlineStr">
-        <is>
-          <t>JASON C. GUEVARRA</t>
+          <t>13009023</t>
+        </is>
+      </c>
+      <c r="C105" s="47" t="inlineStr">
+        <is>
+          <t>SAMEER ALDUSUQI</t>
         </is>
       </c>
       <c r="D105" s="10" t="inlineStr">
@@ -5424,56 +5417,56 @@
     </row>
     <row r="106">
       <c r="A106" s="10" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B106" s="11" t="inlineStr">
         <is>
-          <t>13009023</t>
-        </is>
-      </c>
-      <c r="C106" s="48" t="inlineStr">
-        <is>
-          <t>SAMEER ALDUSUQI</t>
+          <t>13004037</t>
+        </is>
+      </c>
+      <c r="C106" s="47" t="inlineStr">
+        <is>
+          <t>KHALID FAISAL AL-ALAWI</t>
         </is>
       </c>
       <c r="D106" s="10" t="inlineStr">
         <is>
-          <t>FITTER</t>
+          <t>SUPV</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="10" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B107" s="11" t="inlineStr">
         <is>
-          <t>13004037</t>
-        </is>
-      </c>
-      <c r="C107" s="48" t="inlineStr">
-        <is>
-          <t>KHALID FAISAL AL-ALAWI</t>
+          <t>13010931</t>
+        </is>
+      </c>
+      <c r="C107" s="47" t="inlineStr">
+        <is>
+          <t>SULTAN ALMASRI</t>
         </is>
       </c>
       <c r="D107" s="10" t="inlineStr">
         <is>
-          <t>SUPV</t>
+          <t>TECH</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="10" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B108" s="11" t="inlineStr">
         <is>
-          <t>13010931</t>
-        </is>
-      </c>
-      <c r="C108" s="48" t="inlineStr">
-        <is>
-          <t>SULTAN ALMASRI</t>
+          <t>30003319</t>
+        </is>
+      </c>
+      <c r="C108" s="47" t="inlineStr">
+        <is>
+          <t>MANSOUR ALHARBI</t>
         </is>
       </c>
       <c r="D108" s="10" t="inlineStr">
@@ -5484,16 +5477,16 @@
     </row>
     <row r="109">
       <c r="A109" s="10" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B109" s="11" t="inlineStr">
         <is>
-          <t>30003319</t>
-        </is>
-      </c>
-      <c r="C109" s="48" t="inlineStr">
-        <is>
-          <t>MANSOUR ALHARBI</t>
+          <t>30003362</t>
+        </is>
+      </c>
+      <c r="C109" s="47" t="inlineStr">
+        <is>
+          <t>AYMAN HAMED</t>
         </is>
       </c>
       <c r="D109" s="10" t="inlineStr">
@@ -5504,16 +5497,16 @@
     </row>
     <row r="110">
       <c r="A110" s="10" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B110" s="11" t="inlineStr">
         <is>
-          <t>30003362</t>
-        </is>
-      </c>
-      <c r="C110" s="48" t="inlineStr">
-        <is>
-          <t>AYMAN HAMED</t>
+          <t>30003449</t>
+        </is>
+      </c>
+      <c r="C110" s="47" t="inlineStr">
+        <is>
+          <t>HAZEM ALSUBHI</t>
         </is>
       </c>
       <c r="D110" s="10" t="inlineStr">
@@ -5524,16 +5517,16 @@
     </row>
     <row r="111">
       <c r="A111" s="10" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B111" s="11" t="inlineStr">
         <is>
-          <t>30003449</t>
-        </is>
-      </c>
-      <c r="C111" s="48" t="inlineStr">
-        <is>
-          <t>HAZEM ALSUBHI</t>
+          <t>30003471</t>
+        </is>
+      </c>
+      <c r="C111" s="47" t="inlineStr">
+        <is>
+          <t>MOHAMMED ALOQBA</t>
         </is>
       </c>
       <c r="D111" s="10" t="inlineStr">
@@ -5544,16 +5537,16 @@
     </row>
     <row r="112">
       <c r="A112" s="10" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B112" s="11" t="inlineStr">
         <is>
-          <t>30003471</t>
-        </is>
-      </c>
-      <c r="C112" s="48" t="inlineStr">
-        <is>
-          <t>MOHAMMED ALOQBA</t>
+          <t>30003607</t>
+        </is>
+      </c>
+      <c r="C112" s="47" t="inlineStr">
+        <is>
+          <t>SIRAJ KHAYAT</t>
         </is>
       </c>
       <c r="D112" s="10" t="inlineStr">
@@ -5564,16 +5557,16 @@
     </row>
     <row r="113">
       <c r="A113" s="10" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B113" s="11" t="inlineStr">
         <is>
-          <t>30003607</t>
-        </is>
-      </c>
-      <c r="C113" s="48" t="inlineStr">
-        <is>
-          <t>SIRAJ KHAYAT</t>
+          <t>30004358</t>
+        </is>
+      </c>
+      <c r="C113" s="47" t="inlineStr">
+        <is>
+          <t>SALMAN ALJAADANI</t>
         </is>
       </c>
       <c r="D113" s="10" t="inlineStr">
@@ -5584,16 +5577,16 @@
     </row>
     <row r="114">
       <c r="A114" s="10" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B114" s="11" t="inlineStr">
         <is>
-          <t>30004358</t>
-        </is>
-      </c>
-      <c r="C114" s="48" t="inlineStr">
-        <is>
-          <t>SALMAN ALJAADANI</t>
+          <t>30004434</t>
+        </is>
+      </c>
+      <c r="C114" s="47" t="inlineStr">
+        <is>
+          <t>EID ALRIFAI</t>
         </is>
       </c>
       <c r="D114" s="10" t="inlineStr">
@@ -5604,39 +5597,19 @@
     </row>
     <row r="115">
       <c r="A115" s="10" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B115" s="11" t="inlineStr">
         <is>
-          <t>30004434</t>
-        </is>
-      </c>
-      <c r="C115" s="48" t="inlineStr">
-        <is>
-          <t>EID ALRIFAI</t>
+          <t>30004838</t>
+        </is>
+      </c>
+      <c r="C115" s="47" t="inlineStr">
+        <is>
+          <t>MUAED MEERA</t>
         </is>
       </c>
       <c r="D115" s="10" t="inlineStr">
-        <is>
-          <t>TECH</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="10" t="n">
-        <v>43</v>
-      </c>
-      <c r="B116" s="11" t="inlineStr">
-        <is>
-          <t>30004838</t>
-        </is>
-      </c>
-      <c r="C116" s="48" t="inlineStr">
-        <is>
-          <t>MUAED MEERA</t>
-        </is>
-      </c>
-      <c r="D116" s="10" t="inlineStr">
         <is>
           <t>TECH</t>
         </is>
@@ -5644,46 +5617,46 @@
     </row>
   </sheetData>
   <mergeCells count="38">
-    <mergeCell ref="X70:Y70"/>
-    <mergeCell ref="T70:W70"/>
     <mergeCell ref="F69:G69"/>
     <mergeCell ref="C68:D68"/>
     <mergeCell ref="AD68:AE68"/>
     <mergeCell ref="N69:Q69"/>
+    <mergeCell ref="L67:M67"/>
+    <mergeCell ref="R67:S67"/>
+    <mergeCell ref="E2:AI2"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="F68:G68"/>
     <mergeCell ref="T69:W69"/>
-    <mergeCell ref="E2:AI2"/>
-    <mergeCell ref="F68:G68"/>
     <mergeCell ref="Z69:AC69"/>
-    <mergeCell ref="A72:J72"/>
-    <mergeCell ref="A24:AI24"/>
+    <mergeCell ref="X67:Y67"/>
+    <mergeCell ref="AD67:AE67"/>
     <mergeCell ref="R69:S69"/>
     <mergeCell ref="L68:M68"/>
-    <mergeCell ref="AD69:AE69"/>
-    <mergeCell ref="N70:Q70"/>
-    <mergeCell ref="A45:AI45"/>
+    <mergeCell ref="T67:W67"/>
     <mergeCell ref="A1:AI1"/>
-    <mergeCell ref="F70:G70"/>
+    <mergeCell ref="H67:K67"/>
+    <mergeCell ref="AF67:AI67"/>
     <mergeCell ref="X68:Y68"/>
-    <mergeCell ref="R70:S70"/>
-    <mergeCell ref="Z70:AC70"/>
-    <mergeCell ref="A3:AI3"/>
+    <mergeCell ref="A25:D25"/>
     <mergeCell ref="H68:K68"/>
     <mergeCell ref="T68:W68"/>
-    <mergeCell ref="AF69:AI69"/>
-    <mergeCell ref="C70:D70"/>
     <mergeCell ref="L69:M69"/>
+    <mergeCell ref="A46:D46"/>
     <mergeCell ref="N68:Q68"/>
+    <mergeCell ref="F67:G67"/>
     <mergeCell ref="AF68:AI68"/>
     <mergeCell ref="X69:Y69"/>
-    <mergeCell ref="H70:K70"/>
+    <mergeCell ref="A71:J71"/>
+    <mergeCell ref="C67:D67"/>
     <mergeCell ref="R68:S68"/>
     <mergeCell ref="H69:K69"/>
     <mergeCell ref="Z68:AC68"/>
-    <mergeCell ref="A61:C65"/>
+    <mergeCell ref="N67:Q67"/>
+    <mergeCell ref="Z67:AC67"/>
     <mergeCell ref="C69:D69"/>
-    <mergeCell ref="L70:M70"/>
+    <mergeCell ref="A60:C64"/>
   </mergeCells>
-  <conditionalFormatting sqref="E6:AI59">
+  <conditionalFormatting sqref="E5:AI58">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"D"</formula>
     </cfRule>
@@ -5727,12 +5700,12 @@
       <formula>"N"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A6:D116">
+  <conditionalFormatting sqref="A5:D115">
     <cfRule type="expression" priority="15" dxfId="14">
-      <formula>$D6="OJT"</formula>
+      <formula>$D5="OJT"</formula>
     </cfRule>
     <cfRule type="expression" priority="16" dxfId="15">
-      <formula>$D6="ACT/SUPV"</formula>
+      <formula>$D5="ACT/SUPV"</formula>
     </cfRule>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>

--- a/uploads/inbox/SPV_ROSTER_TEMPLATE_AVISUITE_COLORS.xlsx
+++ b/uploads/inbox/SPV_ROSTER_TEMPLATE_AVISUITE_COLORS.xlsx
@@ -9,7 +9,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ROSTER" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'ROSTER'!$A$1:$AI$88</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'ROSTER'!$A$1:$AI$89</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -20,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mmmm\ yyyy"/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="36">
     <font>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -118,7 +118,75 @@
     <font>
       <name val="Times New Roman"/>
       <b val="1"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <b val="1"/>
+      <color rgb="0092400E"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <b val="1"/>
+      <color rgb="001A56DB"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <b val="1"/>
+      <color rgb="00065F46"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <b val="1"/>
       <color rgb="00196B24"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <b val="1"/>
+      <color rgb="0092400E"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <b val="1"/>
+      <color rgb="001A56DB"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <b val="1"/>
+      <color rgb="00065F46"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <b val="1"/>
+      <color rgb="005521B5"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <b val="1"/>
+      <color rgb="000E7490"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
       <sz val="10"/>
     </font>
     <font>
@@ -126,10 +194,6 @@
       <b val="1"/>
       <color rgb="00F9FAFB"/>
       <sz val="10"/>
-    </font>
-    <font>
-      <name val="Times New Roman"/>
-      <sz val="9"/>
     </font>
     <font>
       <name val="Times New Roman"/>
@@ -174,7 +238,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="21">
+  <fills count="28">
     <fill>
       <patternFill/>
     </fill>
@@ -243,6 +307,41 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF8E1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D0CECE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEF3C7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DBEAFE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D1FAE5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EDEBFE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00CFFAFE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
     <fill>
@@ -747,7 +846,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="138">
+  <cellXfs count="149">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -1063,10 +1162,16 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1093,32 +1198,59 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="13" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="19" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="20" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="21" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="22" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="23" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="24" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="25" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="26" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="27" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="37" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1130,76 +1262,46 @@
   <cellStyles count="1">
     <cellStyle name="عادي" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="20">
+  <dxfs count="27">
     <dxf>
-      <font>
-        <name val="Times New Roman"/>
-        <b val="1"/>
-        <color rgb="0092400E"/>
-      </font>
       <fill>
         <patternFill>
-          <bgColor rgb="00FEF3C7"/>
+          <bgColor rgb="FFFFFF99"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <name val="Times New Roman"/>
-        <b val="1"/>
-        <color rgb="001A56DB"/>
-      </font>
       <fill>
         <patternFill>
-          <bgColor rgb="00DBEAFE"/>
+          <bgColor theme="4" tint="0.7999816888943144"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <name val="Times New Roman"/>
-        <b val="1"/>
-        <color rgb="00065F46"/>
-      </font>
       <fill>
         <patternFill>
-          <bgColor rgb="00D1FAE5"/>
+          <bgColor theme="3" tint="0.499984740745262"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <name val="Times New Roman"/>
-        <b val="1"/>
-        <color rgb="006B7280"/>
-      </font>
       <fill>
         <patternFill>
-          <bgColor rgb="00F3F4F6"/>
+          <bgColor theme="0" tint="-0.249946592608417"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <name val="Times New Roman"/>
-        <b val="1"/>
-        <color rgb="000E7490"/>
-      </font>
       <fill>
         <patternFill>
-          <bgColor rgb="00CFFAFE"/>
+          <bgColor theme="9" tint="0.3999450666829432"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <name val="Times New Roman"/>
-        <b val="1"/>
-        <color rgb="005521B5"/>
-      </font>
       <fill>
         <patternFill>
-          <bgColor rgb="00EDEBFE"/>
+          <bgColor theme="8" tint="0.5999633777886288"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1242,6 +1344,66 @@
       <fill>
         <patternFill>
           <bgColor theme="8" tint="0.5999633777886288"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Times New Roman"/>
+        <b val="1"/>
+        <color rgb="0092400E"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="00FEF3C7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Times New Roman"/>
+        <b val="1"/>
+        <color rgb="001A56DB"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="00DBEAFE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Times New Roman"/>
+        <b val="1"/>
+        <color rgb="00065F46"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="00D1FAE5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Times New Roman"/>
+        <b val="1"/>
+        <color rgb="005521B5"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="00EDEBFE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Times New Roman"/>
+        <b val="1"/>
+        <color rgb="000E7490"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="00CFFAFE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1338,6 +1500,20 @@
       <fill>
         <patternFill>
           <bgColor rgb="00FEF9C3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="00DBEDD5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="00A1BFCC"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1735,7 +1911,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AP87"/>
+  <dimension ref="A1:AP88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1856,282 +2032,282 @@
           <t>CREW 1</t>
         </is>
       </c>
-      <c r="E3" s="1">
+      <c r="E3" s="109">
         <f>IF(1&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="F3" s="1">
+      <c r="F3" s="109">
         <f>IF(2&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,2),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="G3" s="1">
+      <c r="G3" s="109">
         <f>IF(3&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,3),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="H3" s="1">
+      <c r="H3" s="109">
         <f>IF(4&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,4),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="I3" s="1">
+      <c r="I3" s="109">
         <f>IF(5&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,5),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="J3" s="1">
+      <c r="J3" s="109">
         <f>IF(6&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,6),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="K3" s="1">
+      <c r="K3" s="109">
         <f>IF(7&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,7),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="L3" s="1">
+      <c r="L3" s="109">
         <f>IF(8&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,8),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="M3" s="1">
+      <c r="M3" s="109">
         <f>IF(9&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,9),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="N3" s="1">
+      <c r="N3" s="109">
         <f>IF(10&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,10),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="O3" s="1">
+      <c r="O3" s="109">
         <f>IF(11&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,11),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="P3" s="1">
+      <c r="P3" s="109">
         <f>IF(12&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,12),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="Q3" s="1">
+      <c r="Q3" s="109">
         <f>IF(13&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,13),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="R3" s="1">
+      <c r="R3" s="109">
         <f>IF(14&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,14),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="S3" s="1">
+      <c r="S3" s="109">
         <f>IF(15&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,15),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="T3" s="1">
+      <c r="T3" s="109">
         <f>IF(16&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,16),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="U3" s="1">
+      <c r="U3" s="109">
         <f>IF(17&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,17),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="V3" s="1">
+      <c r="V3" s="109">
         <f>IF(18&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,18),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="W3" s="1">
+      <c r="W3" s="109">
         <f>IF(19&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,19),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="X3" s="1">
+      <c r="X3" s="109">
         <f>IF(20&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,20),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="Y3" s="1">
+      <c r="Y3" s="109">
         <f>IF(21&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,21),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="Z3" s="1">
+      <c r="Z3" s="109">
         <f>IF(22&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,22),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="AA3" s="1">
+      <c r="AA3" s="109">
         <f>IF(23&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,23),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="AB3" s="1">
+      <c r="AB3" s="109">
         <f>IF(24&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,24),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="AC3" s="1">
+      <c r="AC3" s="109">
         <f>IF(25&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,25),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="AD3" s="1">
+      <c r="AD3" s="109">
         <f>IF(26&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,26),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="AE3" s="1">
+      <c r="AE3" s="109">
         <f>IF(27&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,27),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="AF3" s="1">
+      <c r="AF3" s="109">
         <f>IF(28&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,28),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="AG3" s="1">
+      <c r="AG3" s="109">
         <f>IF(29&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,29),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="AH3" s="24">
+      <c r="AH3" s="109">
         <f>IF(30&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,30),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="AI3" s="21">
+      <c r="AI3" s="109">
         <f>IF(31&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,31),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="AK3" s="109" t="inlineStr">
+      <c r="AK3" s="110" t="inlineStr">
         <is>
           <t>ROSTER PERIOD</t>
         </is>
       </c>
     </row>
     <row r="4" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A4" s="110" t="n"/>
-      <c r="E4" s="2">
+      <c r="A4" s="111" t="n"/>
+      <c r="E4" s="112">
         <f>IF(1&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),1,"")</f>
         <v/>
       </c>
-      <c r="F4" s="2">
+      <c r="F4" s="112">
         <f>IF(2&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),2,"")</f>
         <v/>
       </c>
-      <c r="G4" s="2">
+      <c r="G4" s="112">
         <f>IF(3&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),3,"")</f>
         <v/>
       </c>
-      <c r="H4" s="2">
+      <c r="H4" s="112">
         <f>IF(4&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),4,"")</f>
         <v/>
       </c>
-      <c r="I4" s="3">
+      <c r="I4" s="112">
         <f>IF(5&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),5,"")</f>
         <v/>
       </c>
-      <c r="J4" s="4">
+      <c r="J4" s="112">
         <f>IF(6&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),6,"")</f>
         <v/>
       </c>
-      <c r="K4" s="4">
+      <c r="K4" s="112">
         <f>IF(7&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),7,"")</f>
         <v/>
       </c>
-      <c r="L4" s="3">
+      <c r="L4" s="112">
         <f>IF(8&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),8,"")</f>
         <v/>
       </c>
-      <c r="M4" s="4">
+      <c r="M4" s="112">
         <f>IF(9&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),9,"")</f>
         <v/>
       </c>
-      <c r="N4" s="2">
+      <c r="N4" s="112">
         <f>IF(10&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),10,"")</f>
         <v/>
       </c>
-      <c r="O4" s="2">
+      <c r="O4" s="112">
         <f>IF(11&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),11,"")</f>
         <v/>
       </c>
-      <c r="P4" s="2">
+      <c r="P4" s="112">
         <f>IF(12&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),12,"")</f>
         <v/>
       </c>
-      <c r="Q4" s="2">
+      <c r="Q4" s="112">
         <f>IF(13&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),13,"")</f>
         <v/>
       </c>
-      <c r="R4" s="2">
+      <c r="R4" s="112">
         <f>IF(14&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),14,"")</f>
         <v/>
       </c>
-      <c r="S4" s="2">
+      <c r="S4" s="112">
         <f>IF(15&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),15,"")</f>
         <v/>
       </c>
-      <c r="T4" s="2">
+      <c r="T4" s="112">
         <f>IF(16&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),16,"")</f>
         <v/>
       </c>
-      <c r="U4" s="2">
+      <c r="U4" s="112">
         <f>IF(17&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),17,"")</f>
         <v/>
       </c>
-      <c r="V4" s="2">
+      <c r="V4" s="112">
         <f>IF(18&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),18,"")</f>
         <v/>
       </c>
-      <c r="W4" s="2">
+      <c r="W4" s="112">
         <f>IF(19&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),19,"")</f>
         <v/>
       </c>
-      <c r="X4" s="2">
+      <c r="X4" s="112">
         <f>IF(20&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),20,"")</f>
         <v/>
       </c>
-      <c r="Y4" s="2">
+      <c r="Y4" s="112">
         <f>IF(21&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),21,"")</f>
         <v/>
       </c>
-      <c r="Z4" s="2">
+      <c r="Z4" s="112">
         <f>IF(22&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),22,"")</f>
         <v/>
       </c>
-      <c r="AA4" s="2">
+      <c r="AA4" s="112">
         <f>IF(23&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),23,"")</f>
         <v/>
       </c>
-      <c r="AB4" s="2">
+      <c r="AB4" s="112">
         <f>IF(24&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),24,"")</f>
         <v/>
       </c>
-      <c r="AC4" s="2">
+      <c r="AC4" s="112">
         <f>IF(25&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),25,"")</f>
         <v/>
       </c>
-      <c r="AD4" s="2">
+      <c r="AD4" s="112">
         <f>IF(26&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),26,"")</f>
         <v/>
       </c>
-      <c r="AE4" s="2">
+      <c r="AE4" s="112">
         <f>IF(27&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),27,"")</f>
         <v/>
       </c>
-      <c r="AF4" s="2">
+      <c r="AF4" s="112">
         <f>IF(28&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),28,"")</f>
         <v/>
       </c>
-      <c r="AG4" s="2">
+      <c r="AG4" s="112">
         <f>IF(29&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),29,"")</f>
         <v/>
       </c>
-      <c r="AH4" s="25">
+      <c r="AH4" s="112">
         <f>IF(30&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),30,"")</f>
         <v/>
       </c>
-      <c r="AI4" s="22">
+      <c r="AI4" s="112">
         <f>IF(31&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),31,"")</f>
         <v/>
       </c>
-      <c r="AK4" s="111" t="inlineStr">
+      <c r="AK4" s="113" t="inlineStr">
         <is>
           <t>MONTH</t>
         </is>
       </c>
-      <c r="AL4" s="112" t="inlineStr">
+      <c r="AL4" s="114" t="inlineStr">
         <is>
           <t>JUL</t>
         </is>
       </c>
-      <c r="AM4" s="135" t="n"/>
-      <c r="AN4" s="136" t="n"/>
+      <c r="AM4" s="146" t="n"/>
+      <c r="AN4" s="147" t="n"/>
     </row>
     <row r="5" ht="16.2" customHeight="1" thickBot="1">
       <c r="A5" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="33" t="n"/>
-      <c r="C5" s="33" t="n"/>
-      <c r="D5" s="34" t="n"/>
+      <c r="B5" s="37" t="n"/>
+      <c r="C5" s="37" t="n"/>
+      <c r="D5" s="40" t="n"/>
       <c r="E5" s="6" t="n"/>
       <c r="F5" s="6" t="n"/>
       <c r="G5" s="7" t="n"/>
@@ -2163,24 +2339,24 @@
       <c r="AG5" s="6" t="n"/>
       <c r="AH5" s="26" t="n"/>
       <c r="AI5" s="23" t="n"/>
-      <c r="AK5" s="111" t="inlineStr">
+      <c r="AK5" s="113" t="inlineStr">
         <is>
           <t>YEAR</t>
         </is>
       </c>
-      <c r="AL5" s="112" t="n">
+      <c r="AL5" s="114" t="n">
         <v>2026</v>
       </c>
-      <c r="AM5" s="135" t="n"/>
-      <c r="AN5" s="136" t="n"/>
+      <c r="AM5" s="146" t="n"/>
+      <c r="AN5" s="147" t="n"/>
     </row>
     <row r="6" ht="16.2" customHeight="1" thickBot="1">
       <c r="A6" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="33" t="n"/>
-      <c r="C6" s="33" t="n"/>
-      <c r="D6" s="33" t="n"/>
+      <c r="B6" s="37" t="n"/>
+      <c r="C6" s="37" t="n"/>
+      <c r="D6" s="37" t="n"/>
       <c r="E6" s="6" t="n"/>
       <c r="F6" s="6" t="n"/>
       <c r="G6" s="7" t="n"/>
@@ -2212,7 +2388,7 @@
       <c r="AG6" s="6" t="n"/>
       <c r="AH6" s="26" t="n"/>
       <c r="AI6" s="23" t="n"/>
-      <c r="AK6" s="113" t="inlineStr">
+      <c r="AK6" s="115" t="inlineStr">
         <is>
           <t>type JUL / JULY / 7</t>
         </is>
@@ -2222,9 +2398,9 @@
       <c r="A7" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="35" t="n"/>
-      <c r="C7" s="33" t="n"/>
-      <c r="D7" s="33" t="n"/>
+      <c r="B7" s="36" t="n"/>
+      <c r="C7" s="37" t="n"/>
+      <c r="D7" s="37" t="n"/>
       <c r="E7" s="6" t="n"/>
       <c r="F7" s="6" t="n"/>
       <c r="G7" s="7" t="n"/>
@@ -2261,9 +2437,9 @@
       <c r="A8" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="33" t="n"/>
-      <c r="C8" s="33" t="n"/>
-      <c r="D8" s="33" t="n"/>
+      <c r="B8" s="37" t="n"/>
+      <c r="C8" s="37" t="n"/>
+      <c r="D8" s="37" t="n"/>
       <c r="E8" s="6" t="n"/>
       <c r="F8" s="6" t="n"/>
       <c r="G8" s="7" t="n"/>
@@ -2339,9 +2515,9 @@
       <c r="A10" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="38" t="n"/>
-      <c r="C10" s="38" t="n"/>
-      <c r="D10" s="38" t="n"/>
+      <c r="B10" s="37" t="n"/>
+      <c r="C10" s="37" t="n"/>
+      <c r="D10" s="37" t="n"/>
       <c r="E10" s="6" t="n"/>
       <c r="F10" s="6" t="n"/>
       <c r="G10" s="7" t="n"/>
@@ -2378,9 +2554,9 @@
       <c r="A11" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="38" t="n"/>
-      <c r="C11" s="38" t="n"/>
-      <c r="D11" s="38" t="n"/>
+      <c r="B11" s="37" t="n"/>
+      <c r="C11" s="37" t="n"/>
+      <c r="D11" s="37" t="n"/>
       <c r="E11" s="6" t="n"/>
       <c r="F11" s="6" t="n"/>
       <c r="G11" s="7" t="n"/>
@@ -2417,9 +2593,9 @@
       <c r="A12" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="38" t="n"/>
-      <c r="C12" s="38" t="n"/>
-      <c r="D12" s="38" t="n"/>
+      <c r="B12" s="37" t="n"/>
+      <c r="C12" s="37" t="n"/>
+      <c r="D12" s="37" t="n"/>
       <c r="E12" s="6" t="n"/>
       <c r="F12" s="6" t="n"/>
       <c r="G12" s="7" t="n"/>
@@ -2456,9 +2632,9 @@
       <c r="A13" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="38" t="n"/>
-      <c r="C13" s="38" t="n"/>
-      <c r="D13" s="38" t="n"/>
+      <c r="B13" s="37" t="n"/>
+      <c r="C13" s="37" t="n"/>
+      <c r="D13" s="37" t="n"/>
       <c r="E13" s="6" t="n"/>
       <c r="F13" s="6" t="n"/>
       <c r="G13" s="7" t="n"/>
@@ -2495,9 +2671,9 @@
       <c r="A14" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="38" t="n"/>
-      <c r="C14" s="38" t="n"/>
-      <c r="D14" s="38" t="n"/>
+      <c r="B14" s="37" t="n"/>
+      <c r="C14" s="37" t="n"/>
+      <c r="D14" s="37" t="n"/>
       <c r="E14" s="11" t="n"/>
       <c r="F14" s="11" t="n"/>
       <c r="G14" s="11" t="n"/>
@@ -2534,9 +2710,9 @@
       <c r="A15" s="10" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="38" t="n"/>
-      <c r="C15" s="38" t="n"/>
-      <c r="D15" s="38" t="n"/>
+      <c r="B15" s="37" t="n"/>
+      <c r="C15" s="37" t="n"/>
+      <c r="D15" s="37" t="n"/>
       <c r="E15" s="6" t="n"/>
       <c r="F15" s="6" t="n"/>
       <c r="G15" s="7" t="n"/>
@@ -2786,85 +2962,271 @@
           <t>CREW 2</t>
         </is>
       </c>
-      <c r="B22" s="114" t="n"/>
-      <c r="C22" s="114" t="n"/>
-      <c r="D22" s="114" t="n"/>
-      <c r="E22" s="30" t="n"/>
-      <c r="F22" s="30" t="n"/>
-      <c r="G22" s="30" t="n"/>
-      <c r="H22" s="30" t="n"/>
-      <c r="I22" s="30" t="n"/>
-      <c r="J22" s="30" t="n"/>
-      <c r="K22" s="30" t="n"/>
-      <c r="L22" s="30" t="n"/>
-      <c r="M22" s="30" t="n"/>
-      <c r="N22" s="30" t="n"/>
-      <c r="O22" s="30" t="n"/>
-      <c r="P22" s="30" t="n"/>
-      <c r="Q22" s="30" t="n"/>
-      <c r="R22" s="30" t="n"/>
-      <c r="S22" s="30" t="n"/>
-      <c r="T22" s="30" t="n"/>
-      <c r="U22" s="30" t="n"/>
-      <c r="V22" s="30" t="n"/>
-      <c r="W22" s="30" t="n"/>
-      <c r="X22" s="30" t="n"/>
-      <c r="Y22" s="30" t="n"/>
-      <c r="Z22" s="30" t="n"/>
-      <c r="AA22" s="30" t="n"/>
-      <c r="AB22" s="30" t="n"/>
-      <c r="AC22" s="30" t="n"/>
-      <c r="AD22" s="30" t="n"/>
-      <c r="AE22" s="30" t="n"/>
-      <c r="AF22" s="30" t="n"/>
-      <c r="AG22" s="30" t="n"/>
-      <c r="AH22" s="30" t="n"/>
-      <c r="AI22" s="31" t="n"/>
+      <c r="B22" s="116" t="n"/>
+      <c r="C22" s="116" t="n"/>
+      <c r="D22" s="116" t="n"/>
+      <c r="E22" s="109">
+        <f>IF(1&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="F22" s="109">
+        <f>IF(2&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,2),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="G22" s="109">
+        <f>IF(3&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,3),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="H22" s="109">
+        <f>IF(4&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,4),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="I22" s="109">
+        <f>IF(5&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,5),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="J22" s="109">
+        <f>IF(6&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,6),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="K22" s="109">
+        <f>IF(7&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,7),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="L22" s="109">
+        <f>IF(8&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,8),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="M22" s="109">
+        <f>IF(9&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,9),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="N22" s="109">
+        <f>IF(10&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,10),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="O22" s="109">
+        <f>IF(11&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,11),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="P22" s="109">
+        <f>IF(12&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,12),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="Q22" s="109">
+        <f>IF(13&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,13),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="R22" s="109">
+        <f>IF(14&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,14),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="S22" s="109">
+        <f>IF(15&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,15),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="T22" s="109">
+        <f>IF(16&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,16),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="U22" s="109">
+        <f>IF(17&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,17),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="V22" s="109">
+        <f>IF(18&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,18),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="W22" s="109">
+        <f>IF(19&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,19),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="X22" s="109">
+        <f>IF(20&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,20),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="Y22" s="109">
+        <f>IF(21&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,21),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="Z22" s="109">
+        <f>IF(22&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,22),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="AA22" s="109">
+        <f>IF(23&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,23),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="AB22" s="109">
+        <f>IF(24&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,24),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="AC22" s="109">
+        <f>IF(25&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,25),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="AD22" s="109">
+        <f>IF(26&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,26),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="AE22" s="109">
+        <f>IF(27&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,27),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="AF22" s="109">
+        <f>IF(28&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,28),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="AG22" s="109">
+        <f>IF(29&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,29),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="AH22" s="109">
+        <f>IF(30&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,30),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="AI22" s="109">
+        <f>IF(31&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,31),"ddd"),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="23" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A23" s="115" t="n"/>
-      <c r="B23" s="116" t="n"/>
-      <c r="C23" s="116" t="n"/>
-      <c r="D23" s="116" t="n"/>
-      <c r="E23" s="2" t="n"/>
-      <c r="F23" s="2" t="n"/>
-      <c r="G23" s="2" t="n"/>
-      <c r="H23" s="2" t="n"/>
-      <c r="I23" s="3" t="n"/>
-      <c r="J23" s="4" t="n"/>
-      <c r="K23" s="4" t="n"/>
-      <c r="L23" s="3" t="n"/>
-      <c r="M23" s="4" t="n"/>
-      <c r="N23" s="2" t="n"/>
-      <c r="O23" s="2" t="n"/>
-      <c r="P23" s="2" t="n"/>
-      <c r="Q23" s="2" t="n"/>
-      <c r="R23" s="2" t="n"/>
-      <c r="S23" s="2" t="n"/>
-      <c r="T23" s="2" t="n"/>
-      <c r="U23" s="2" t="n"/>
-      <c r="V23" s="2" t="n"/>
-      <c r="W23" s="2" t="n"/>
-      <c r="X23" s="2" t="n"/>
-      <c r="Y23" s="2" t="n"/>
-      <c r="Z23" s="2" t="n"/>
-      <c r="AA23" s="2" t="n"/>
-      <c r="AB23" s="2" t="n"/>
-      <c r="AC23" s="2" t="n"/>
-      <c r="AD23" s="2" t="n"/>
-      <c r="AE23" s="2" t="n"/>
-      <c r="AF23" s="2" t="n"/>
-      <c r="AG23" s="2" t="n"/>
-      <c r="AH23" s="2" t="n"/>
-      <c r="AI23" s="25" t="n"/>
+      <c r="A23" s="117" t="n"/>
+      <c r="B23" s="118" t="n"/>
+      <c r="C23" s="118" t="n"/>
+      <c r="D23" s="118" t="n"/>
+      <c r="E23" s="112">
+        <f>IF(1&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),1,"")</f>
+        <v/>
+      </c>
+      <c r="F23" s="112">
+        <f>IF(2&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),2,"")</f>
+        <v/>
+      </c>
+      <c r="G23" s="112">
+        <f>IF(3&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),3,"")</f>
+        <v/>
+      </c>
+      <c r="H23" s="112">
+        <f>IF(4&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),4,"")</f>
+        <v/>
+      </c>
+      <c r="I23" s="112">
+        <f>IF(5&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),5,"")</f>
+        <v/>
+      </c>
+      <c r="J23" s="112">
+        <f>IF(6&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),6,"")</f>
+        <v/>
+      </c>
+      <c r="K23" s="112">
+        <f>IF(7&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),7,"")</f>
+        <v/>
+      </c>
+      <c r="L23" s="112">
+        <f>IF(8&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),8,"")</f>
+        <v/>
+      </c>
+      <c r="M23" s="112">
+        <f>IF(9&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),9,"")</f>
+        <v/>
+      </c>
+      <c r="N23" s="112">
+        <f>IF(10&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),10,"")</f>
+        <v/>
+      </c>
+      <c r="O23" s="112">
+        <f>IF(11&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),11,"")</f>
+        <v/>
+      </c>
+      <c r="P23" s="112">
+        <f>IF(12&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),12,"")</f>
+        <v/>
+      </c>
+      <c r="Q23" s="112">
+        <f>IF(13&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),13,"")</f>
+        <v/>
+      </c>
+      <c r="R23" s="112">
+        <f>IF(14&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),14,"")</f>
+        <v/>
+      </c>
+      <c r="S23" s="112">
+        <f>IF(15&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),15,"")</f>
+        <v/>
+      </c>
+      <c r="T23" s="112">
+        <f>IF(16&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),16,"")</f>
+        <v/>
+      </c>
+      <c r="U23" s="112">
+        <f>IF(17&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),17,"")</f>
+        <v/>
+      </c>
+      <c r="V23" s="112">
+        <f>IF(18&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),18,"")</f>
+        <v/>
+      </c>
+      <c r="W23" s="112">
+        <f>IF(19&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),19,"")</f>
+        <v/>
+      </c>
+      <c r="X23" s="112">
+        <f>IF(20&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),20,"")</f>
+        <v/>
+      </c>
+      <c r="Y23" s="112">
+        <f>IF(21&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),21,"")</f>
+        <v/>
+      </c>
+      <c r="Z23" s="112">
+        <f>IF(22&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),22,"")</f>
+        <v/>
+      </c>
+      <c r="AA23" s="112">
+        <f>IF(23&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),23,"")</f>
+        <v/>
+      </c>
+      <c r="AB23" s="112">
+        <f>IF(24&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),24,"")</f>
+        <v/>
+      </c>
+      <c r="AC23" s="112">
+        <f>IF(25&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),25,"")</f>
+        <v/>
+      </c>
+      <c r="AD23" s="112">
+        <f>IF(26&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),26,"")</f>
+        <v/>
+      </c>
+      <c r="AE23" s="112">
+        <f>IF(27&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),27,"")</f>
+        <v/>
+      </c>
+      <c r="AF23" s="112">
+        <f>IF(28&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),28,"")</f>
+        <v/>
+      </c>
+      <c r="AG23" s="112">
+        <f>IF(29&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),29,"")</f>
+        <v/>
+      </c>
+      <c r="AH23" s="112">
+        <f>IF(30&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),30,"")</f>
+        <v/>
+      </c>
+      <c r="AI23" s="112">
+        <f>IF(31&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),31,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="24" ht="16.2" customHeight="1" thickBot="1">
       <c r="A24" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B24" s="33" t="n"/>
-      <c r="C24" s="33" t="n"/>
-      <c r="D24" s="33" t="n"/>
+      <c r="B24" s="37" t="n"/>
+      <c r="C24" s="37" t="n"/>
+      <c r="D24" s="37" t="n"/>
       <c r="E24" s="6" t="n"/>
       <c r="F24" s="6" t="n"/>
       <c r="G24" s="6" t="n"/>
@@ -2901,9 +3263,9 @@
       <c r="A25" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B25" s="33" t="n"/>
-      <c r="C25" s="33" t="n"/>
-      <c r="D25" s="33" t="n"/>
+      <c r="B25" s="37" t="n"/>
+      <c r="C25" s="37" t="n"/>
+      <c r="D25" s="37" t="n"/>
       <c r="E25" s="6" t="n"/>
       <c r="F25" s="6" t="n"/>
       <c r="G25" s="6" t="n"/>
@@ -3057,9 +3419,9 @@
       <c r="A29" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="B29" s="38" t="n"/>
-      <c r="C29" s="38" t="n"/>
-      <c r="D29" s="38" t="n"/>
+      <c r="B29" s="37" t="n"/>
+      <c r="C29" s="37" t="n"/>
+      <c r="D29" s="37" t="n"/>
       <c r="E29" s="6" t="n"/>
       <c r="F29" s="6" t="n"/>
       <c r="G29" s="6" t="n"/>
@@ -3096,9 +3458,9 @@
       <c r="A30" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="B30" s="38" t="n"/>
-      <c r="C30" s="38" t="n"/>
-      <c r="D30" s="38" t="n"/>
+      <c r="B30" s="37" t="n"/>
+      <c r="C30" s="37" t="n"/>
+      <c r="D30" s="37" t="n"/>
       <c r="E30" s="6" t="n"/>
       <c r="F30" s="6" t="n"/>
       <c r="G30" s="6" t="n"/>
@@ -3135,9 +3497,9 @@
       <c r="A31" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="B31" s="38" t="n"/>
-      <c r="C31" s="38" t="n"/>
-      <c r="D31" s="38" t="n"/>
+      <c r="B31" s="37" t="n"/>
+      <c r="C31" s="37" t="n"/>
+      <c r="D31" s="37" t="n"/>
       <c r="E31" s="6" t="n"/>
       <c r="F31" s="6" t="n"/>
       <c r="G31" s="6" t="n"/>
@@ -3174,9 +3536,9 @@
       <c r="A32" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="B32" s="38" t="n"/>
-      <c r="C32" s="38" t="n"/>
-      <c r="D32" s="38" t="n"/>
+      <c r="B32" s="37" t="n"/>
+      <c r="C32" s="37" t="n"/>
+      <c r="D32" s="37" t="n"/>
       <c r="E32" s="6" t="n"/>
       <c r="F32" s="6" t="n"/>
       <c r="G32" s="6" t="n"/>
@@ -3213,9 +3575,9 @@
       <c r="A33" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="B33" s="38" t="n"/>
-      <c r="C33" s="38" t="n"/>
-      <c r="D33" s="38" t="n"/>
+      <c r="B33" s="37" t="n"/>
+      <c r="C33" s="37" t="n"/>
+      <c r="D33" s="37" t="n"/>
       <c r="E33" s="6" t="n"/>
       <c r="F33" s="6" t="n"/>
       <c r="G33" s="6" t="n"/>
@@ -3252,9 +3614,9 @@
       <c r="A34" s="10" t="n">
         <v>11</v>
       </c>
-      <c r="B34" s="38" t="n"/>
-      <c r="C34" s="38" t="n"/>
-      <c r="D34" s="38" t="n"/>
+      <c r="B34" s="37" t="n"/>
+      <c r="C34" s="37" t="n"/>
+      <c r="D34" s="37" t="n"/>
       <c r="E34" s="6" t="n"/>
       <c r="F34" s="6" t="n"/>
       <c r="G34" s="6" t="n"/>
@@ -3291,9 +3653,9 @@
       <c r="A35" s="10" t="n">
         <v>12</v>
       </c>
-      <c r="B35" s="38" t="n"/>
-      <c r="C35" s="38" t="n"/>
-      <c r="D35" s="38" t="n"/>
+      <c r="B35" s="37" t="n"/>
+      <c r="C35" s="37" t="n"/>
+      <c r="D35" s="37" t="n"/>
       <c r="E35" s="6" t="n"/>
       <c r="F35" s="6" t="n"/>
       <c r="G35" s="6" t="n"/>
@@ -3330,9 +3692,9 @@
       <c r="A36" s="10" t="n">
         <v>13</v>
       </c>
-      <c r="B36" s="38" t="n"/>
-      <c r="C36" s="38" t="n"/>
-      <c r="D36" s="38" t="n"/>
+      <c r="B36" s="37" t="n"/>
+      <c r="C36" s="37" t="n"/>
+      <c r="D36" s="37" t="n"/>
       <c r="E36" s="6" t="n"/>
       <c r="F36" s="6" t="n"/>
       <c r="G36" s="6" t="n"/>
@@ -3523,82 +3885,268 @@
     </row>
     <row r="41" ht="15" customHeight="1" thickBot="1"/>
     <row r="42" ht="15" customHeight="1" thickBot="1">
-      <c r="A42" s="117" t="inlineStr">
+      <c r="A42" s="119" t="inlineStr">
         <is>
           <t>SPECIAL SHIFTING</t>
         </is>
       </c>
-      <c r="B42" s="114" t="n"/>
-      <c r="C42" s="114" t="n"/>
-      <c r="D42" s="118" t="n"/>
-      <c r="E42" s="1" t="n"/>
-      <c r="F42" s="1" t="n"/>
-      <c r="G42" s="1" t="n"/>
-      <c r="H42" s="1" t="n"/>
-      <c r="I42" s="1" t="n"/>
-      <c r="J42" s="1" t="n"/>
-      <c r="K42" s="1" t="n"/>
-      <c r="L42" s="1" t="n"/>
-      <c r="M42" s="1" t="n"/>
-      <c r="N42" s="1" t="n"/>
-      <c r="O42" s="1" t="n"/>
-      <c r="P42" s="1" t="n"/>
-      <c r="Q42" s="1" t="n"/>
-      <c r="R42" s="1" t="n"/>
-      <c r="S42" s="1" t="n"/>
-      <c r="T42" s="1" t="n"/>
-      <c r="U42" s="1" t="n"/>
-      <c r="V42" s="1" t="n"/>
-      <c r="W42" s="1" t="n"/>
-      <c r="X42" s="1" t="n"/>
-      <c r="Y42" s="1" t="n"/>
-      <c r="Z42" s="1" t="n"/>
-      <c r="AA42" s="1" t="n"/>
-      <c r="AB42" s="1" t="n"/>
-      <c r="AC42" s="1" t="n"/>
-      <c r="AD42" s="1" t="n"/>
-      <c r="AE42" s="1" t="n"/>
-      <c r="AF42" s="1" t="n"/>
-      <c r="AG42" s="1" t="n"/>
-      <c r="AH42" s="1" t="n"/>
-      <c r="AI42" s="1" t="n"/>
+      <c r="B42" s="116" t="n"/>
+      <c r="C42" s="116" t="n"/>
+      <c r="D42" s="120" t="n"/>
+      <c r="E42" s="109">
+        <f>IF(1&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="F42" s="109">
+        <f>IF(2&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,2),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="G42" s="109">
+        <f>IF(3&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,3),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="H42" s="109">
+        <f>IF(4&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,4),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="I42" s="109">
+        <f>IF(5&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,5),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="J42" s="109">
+        <f>IF(6&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,6),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="K42" s="109">
+        <f>IF(7&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,7),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="L42" s="109">
+        <f>IF(8&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,8),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="M42" s="109">
+        <f>IF(9&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,9),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="N42" s="109">
+        <f>IF(10&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,10),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="O42" s="109">
+        <f>IF(11&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,11),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="P42" s="109">
+        <f>IF(12&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,12),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="Q42" s="109">
+        <f>IF(13&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,13),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="R42" s="109">
+        <f>IF(14&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,14),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="S42" s="109">
+        <f>IF(15&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,15),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="T42" s="109">
+        <f>IF(16&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,16),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="U42" s="109">
+        <f>IF(17&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,17),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="V42" s="109">
+        <f>IF(18&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,18),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="W42" s="109">
+        <f>IF(19&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,19),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="X42" s="109">
+        <f>IF(20&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,20),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="Y42" s="109">
+        <f>IF(21&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,21),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="Z42" s="109">
+        <f>IF(22&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,22),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="AA42" s="109">
+        <f>IF(23&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,23),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="AB42" s="109">
+        <f>IF(24&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,24),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="AC42" s="109">
+        <f>IF(25&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,25),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="AD42" s="109">
+        <f>IF(26&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,26),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="AE42" s="109">
+        <f>IF(27&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,27),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="AF42" s="109">
+        <f>IF(28&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,28),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="AG42" s="109">
+        <f>IF(29&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,29),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="AH42" s="109">
+        <f>IF(30&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,30),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="AI42" s="109">
+        <f>IF(31&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,31),"ddd"),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="43" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A43" s="115" t="n"/>
-      <c r="B43" s="116" t="n"/>
-      <c r="C43" s="116" t="n"/>
-      <c r="D43" s="119" t="n"/>
-      <c r="E43" s="2" t="n"/>
-      <c r="F43" s="2" t="n"/>
-      <c r="G43" s="2" t="n"/>
-      <c r="H43" s="2" t="n"/>
-      <c r="I43" s="3" t="n"/>
-      <c r="J43" s="4" t="n"/>
-      <c r="K43" s="4" t="n"/>
-      <c r="L43" s="3" t="n"/>
-      <c r="M43" s="4" t="n"/>
-      <c r="N43" s="2" t="n"/>
-      <c r="O43" s="2" t="n"/>
-      <c r="P43" s="2" t="n"/>
-      <c r="Q43" s="2" t="n"/>
-      <c r="R43" s="2" t="n"/>
-      <c r="S43" s="2" t="n"/>
-      <c r="T43" s="2" t="n"/>
-      <c r="U43" s="2" t="n"/>
-      <c r="V43" s="2" t="n"/>
-      <c r="W43" s="2" t="n"/>
-      <c r="X43" s="2" t="n"/>
-      <c r="Y43" s="2" t="n"/>
-      <c r="Z43" s="2" t="n"/>
-      <c r="AA43" s="2" t="n"/>
-      <c r="AB43" s="2" t="n"/>
-      <c r="AC43" s="2" t="n"/>
-      <c r="AD43" s="2" t="n"/>
-      <c r="AE43" s="2" t="n"/>
-      <c r="AF43" s="2" t="n"/>
-      <c r="AG43" s="2" t="n"/>
-      <c r="AH43" s="2" t="n"/>
-      <c r="AI43" s="2" t="n"/>
+      <c r="A43" s="117" t="n"/>
+      <c r="B43" s="118" t="n"/>
+      <c r="C43" s="118" t="n"/>
+      <c r="D43" s="121" t="n"/>
+      <c r="E43" s="112">
+        <f>IF(1&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),1,"")</f>
+        <v/>
+      </c>
+      <c r="F43" s="112">
+        <f>IF(2&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),2,"")</f>
+        <v/>
+      </c>
+      <c r="G43" s="112">
+        <f>IF(3&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),3,"")</f>
+        <v/>
+      </c>
+      <c r="H43" s="112">
+        <f>IF(4&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),4,"")</f>
+        <v/>
+      </c>
+      <c r="I43" s="112">
+        <f>IF(5&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),5,"")</f>
+        <v/>
+      </c>
+      <c r="J43" s="112">
+        <f>IF(6&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),6,"")</f>
+        <v/>
+      </c>
+      <c r="K43" s="112">
+        <f>IF(7&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),7,"")</f>
+        <v/>
+      </c>
+      <c r="L43" s="112">
+        <f>IF(8&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),8,"")</f>
+        <v/>
+      </c>
+      <c r="M43" s="112">
+        <f>IF(9&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),9,"")</f>
+        <v/>
+      </c>
+      <c r="N43" s="112">
+        <f>IF(10&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),10,"")</f>
+        <v/>
+      </c>
+      <c r="O43" s="112">
+        <f>IF(11&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),11,"")</f>
+        <v/>
+      </c>
+      <c r="P43" s="112">
+        <f>IF(12&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),12,"")</f>
+        <v/>
+      </c>
+      <c r="Q43" s="112">
+        <f>IF(13&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),13,"")</f>
+        <v/>
+      </c>
+      <c r="R43" s="112">
+        <f>IF(14&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),14,"")</f>
+        <v/>
+      </c>
+      <c r="S43" s="112">
+        <f>IF(15&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),15,"")</f>
+        <v/>
+      </c>
+      <c r="T43" s="112">
+        <f>IF(16&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),16,"")</f>
+        <v/>
+      </c>
+      <c r="U43" s="112">
+        <f>IF(17&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),17,"")</f>
+        <v/>
+      </c>
+      <c r="V43" s="112">
+        <f>IF(18&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),18,"")</f>
+        <v/>
+      </c>
+      <c r="W43" s="112">
+        <f>IF(19&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),19,"")</f>
+        <v/>
+      </c>
+      <c r="X43" s="112">
+        <f>IF(20&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),20,"")</f>
+        <v/>
+      </c>
+      <c r="Y43" s="112">
+        <f>IF(21&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),21,"")</f>
+        <v/>
+      </c>
+      <c r="Z43" s="112">
+        <f>IF(22&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),22,"")</f>
+        <v/>
+      </c>
+      <c r="AA43" s="112">
+        <f>IF(23&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),23,"")</f>
+        <v/>
+      </c>
+      <c r="AB43" s="112">
+        <f>IF(24&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),24,"")</f>
+        <v/>
+      </c>
+      <c r="AC43" s="112">
+        <f>IF(25&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),25,"")</f>
+        <v/>
+      </c>
+      <c r="AD43" s="112">
+        <f>IF(26&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),26,"")</f>
+        <v/>
+      </c>
+      <c r="AE43" s="112">
+        <f>IF(27&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),27,"")</f>
+        <v/>
+      </c>
+      <c r="AF43" s="112">
+        <f>IF(28&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),28,"")</f>
+        <v/>
+      </c>
+      <c r="AG43" s="112">
+        <f>IF(29&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),29,"")</f>
+        <v/>
+      </c>
+      <c r="AH43" s="112">
+        <f>IF(30&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),30,"")</f>
+        <v/>
+      </c>
+      <c r="AI43" s="112">
+        <f>IF(31&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),31,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="44" ht="16.2" customHeight="1" thickBot="1">
       <c r="A44" s="5" t="n">
@@ -3657,82 +4205,268 @@
       <c r="O45" s="14" t="n"/>
     </row>
     <row r="46" ht="15" customHeight="1" thickBot="1">
-      <c r="A46" s="117" t="inlineStr">
+      <c r="A46" s="119" t="inlineStr">
         <is>
           <t>TRANSFERRED-IN MANPOWER</t>
         </is>
       </c>
-      <c r="B46" s="114" t="n"/>
-      <c r="C46" s="114" t="n"/>
-      <c r="D46" s="118" t="n"/>
-      <c r="E46" s="1" t="n"/>
-      <c r="F46" s="1" t="n"/>
-      <c r="G46" s="1" t="n"/>
-      <c r="H46" s="1" t="n"/>
-      <c r="I46" s="1" t="n"/>
-      <c r="J46" s="1" t="n"/>
-      <c r="K46" s="1" t="n"/>
-      <c r="L46" s="1" t="n"/>
-      <c r="M46" s="1" t="n"/>
-      <c r="N46" s="1" t="n"/>
-      <c r="O46" s="1" t="n"/>
-      <c r="P46" s="1" t="n"/>
-      <c r="Q46" s="1" t="n"/>
-      <c r="R46" s="1" t="n"/>
-      <c r="S46" s="1" t="n"/>
-      <c r="T46" s="1" t="n"/>
-      <c r="U46" s="1" t="n"/>
-      <c r="V46" s="1" t="n"/>
-      <c r="W46" s="1" t="n"/>
-      <c r="X46" s="1" t="n"/>
-      <c r="Y46" s="1" t="n"/>
-      <c r="Z46" s="1" t="n"/>
-      <c r="AA46" s="1" t="n"/>
-      <c r="AB46" s="1" t="n"/>
-      <c r="AC46" s="1" t="n"/>
-      <c r="AD46" s="1" t="n"/>
-      <c r="AE46" s="1" t="n"/>
-      <c r="AF46" s="1" t="n"/>
-      <c r="AG46" s="1" t="n"/>
-      <c r="AH46" s="1" t="n"/>
-      <c r="AI46" s="1" t="n"/>
+      <c r="B46" s="116" t="n"/>
+      <c r="C46" s="116" t="n"/>
+      <c r="D46" s="120" t="n"/>
+      <c r="E46" s="109">
+        <f>IF(1&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="F46" s="109">
+        <f>IF(2&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,2),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="G46" s="109">
+        <f>IF(3&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,3),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="H46" s="109">
+        <f>IF(4&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,4),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="I46" s="109">
+        <f>IF(5&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,5),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="J46" s="109">
+        <f>IF(6&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,6),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="K46" s="109">
+        <f>IF(7&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,7),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="L46" s="109">
+        <f>IF(8&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,8),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="M46" s="109">
+        <f>IF(9&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,9),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="N46" s="109">
+        <f>IF(10&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,10),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="O46" s="109">
+        <f>IF(11&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,11),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="P46" s="109">
+        <f>IF(12&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,12),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="Q46" s="109">
+        <f>IF(13&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,13),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="R46" s="109">
+        <f>IF(14&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,14),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="S46" s="109">
+        <f>IF(15&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,15),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="T46" s="109">
+        <f>IF(16&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,16),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="U46" s="109">
+        <f>IF(17&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,17),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="V46" s="109">
+        <f>IF(18&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,18),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="W46" s="109">
+        <f>IF(19&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,19),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="X46" s="109">
+        <f>IF(20&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,20),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="Y46" s="109">
+        <f>IF(21&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,21),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="Z46" s="109">
+        <f>IF(22&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,22),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="AA46" s="109">
+        <f>IF(23&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,23),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="AB46" s="109">
+        <f>IF(24&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,24),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="AC46" s="109">
+        <f>IF(25&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,25),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="AD46" s="109">
+        <f>IF(26&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,26),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="AE46" s="109">
+        <f>IF(27&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,27),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="AF46" s="109">
+        <f>IF(28&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,28),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="AG46" s="109">
+        <f>IF(29&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,29),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="AH46" s="109">
+        <f>IF(30&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,30),"ddd"),"")</f>
+        <v/>
+      </c>
+      <c r="AI46" s="109">
+        <f>IF(31&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,31),"ddd"),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="47" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A47" s="115" t="n"/>
-      <c r="B47" s="116" t="n"/>
-      <c r="C47" s="116" t="n"/>
-      <c r="D47" s="119" t="n"/>
-      <c r="E47" s="2" t="n"/>
-      <c r="F47" s="2" t="n"/>
-      <c r="G47" s="2" t="n"/>
-      <c r="H47" s="2" t="n"/>
-      <c r="I47" s="3" t="n"/>
-      <c r="J47" s="4" t="n"/>
-      <c r="K47" s="4" t="n"/>
-      <c r="L47" s="3" t="n"/>
-      <c r="M47" s="4" t="n"/>
-      <c r="N47" s="2" t="n"/>
-      <c r="O47" s="2" t="n"/>
-      <c r="P47" s="2" t="n"/>
-      <c r="Q47" s="2" t="n"/>
-      <c r="R47" s="2" t="n"/>
-      <c r="S47" s="2" t="n"/>
-      <c r="T47" s="2" t="n"/>
-      <c r="U47" s="2" t="n"/>
-      <c r="V47" s="2" t="n"/>
-      <c r="W47" s="2" t="n"/>
-      <c r="X47" s="2" t="n"/>
-      <c r="Y47" s="2" t="n"/>
-      <c r="Z47" s="2" t="n"/>
-      <c r="AA47" s="2" t="n"/>
-      <c r="AB47" s="2" t="n"/>
-      <c r="AC47" s="2" t="n"/>
-      <c r="AD47" s="2" t="n"/>
-      <c r="AE47" s="2" t="n"/>
-      <c r="AF47" s="2" t="n"/>
-      <c r="AG47" s="2" t="n"/>
-      <c r="AH47" s="2" t="n"/>
-      <c r="AI47" s="2" t="n"/>
+      <c r="A47" s="117" t="n"/>
+      <c r="B47" s="118" t="n"/>
+      <c r="C47" s="118" t="n"/>
+      <c r="D47" s="121" t="n"/>
+      <c r="E47" s="112">
+        <f>IF(1&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),1,"")</f>
+        <v/>
+      </c>
+      <c r="F47" s="112">
+        <f>IF(2&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),2,"")</f>
+        <v/>
+      </c>
+      <c r="G47" s="112">
+        <f>IF(3&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),3,"")</f>
+        <v/>
+      </c>
+      <c r="H47" s="112">
+        <f>IF(4&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),4,"")</f>
+        <v/>
+      </c>
+      <c r="I47" s="112">
+        <f>IF(5&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),5,"")</f>
+        <v/>
+      </c>
+      <c r="J47" s="112">
+        <f>IF(6&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),6,"")</f>
+        <v/>
+      </c>
+      <c r="K47" s="112">
+        <f>IF(7&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),7,"")</f>
+        <v/>
+      </c>
+      <c r="L47" s="112">
+        <f>IF(8&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),8,"")</f>
+        <v/>
+      </c>
+      <c r="M47" s="112">
+        <f>IF(9&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),9,"")</f>
+        <v/>
+      </c>
+      <c r="N47" s="112">
+        <f>IF(10&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),10,"")</f>
+        <v/>
+      </c>
+      <c r="O47" s="112">
+        <f>IF(11&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),11,"")</f>
+        <v/>
+      </c>
+      <c r="P47" s="112">
+        <f>IF(12&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),12,"")</f>
+        <v/>
+      </c>
+      <c r="Q47" s="112">
+        <f>IF(13&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),13,"")</f>
+        <v/>
+      </c>
+      <c r="R47" s="112">
+        <f>IF(14&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),14,"")</f>
+        <v/>
+      </c>
+      <c r="S47" s="112">
+        <f>IF(15&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),15,"")</f>
+        <v/>
+      </c>
+      <c r="T47" s="112">
+        <f>IF(16&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),16,"")</f>
+        <v/>
+      </c>
+      <c r="U47" s="112">
+        <f>IF(17&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),17,"")</f>
+        <v/>
+      </c>
+      <c r="V47" s="112">
+        <f>IF(18&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),18,"")</f>
+        <v/>
+      </c>
+      <c r="W47" s="112">
+        <f>IF(19&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),19,"")</f>
+        <v/>
+      </c>
+      <c r="X47" s="112">
+        <f>IF(20&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),20,"")</f>
+        <v/>
+      </c>
+      <c r="Y47" s="112">
+        <f>IF(21&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),21,"")</f>
+        <v/>
+      </c>
+      <c r="Z47" s="112">
+        <f>IF(22&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),22,"")</f>
+        <v/>
+      </c>
+      <c r="AA47" s="112">
+        <f>IF(23&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),23,"")</f>
+        <v/>
+      </c>
+      <c r="AB47" s="112">
+        <f>IF(24&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),24,"")</f>
+        <v/>
+      </c>
+      <c r="AC47" s="112">
+        <f>IF(25&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),25,"")</f>
+        <v/>
+      </c>
+      <c r="AD47" s="112">
+        <f>IF(26&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),26,"")</f>
+        <v/>
+      </c>
+      <c r="AE47" s="112">
+        <f>IF(27&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),27,"")</f>
+        <v/>
+      </c>
+      <c r="AF47" s="112">
+        <f>IF(28&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),28,"")</f>
+        <v/>
+      </c>
+      <c r="AG47" s="112">
+        <f>IF(29&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),29,"")</f>
+        <v/>
+      </c>
+      <c r="AH47" s="112">
+        <f>IF(30&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),30,"")</f>
+        <v/>
+      </c>
+      <c r="AI47" s="112">
+        <f>IF(31&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),31,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="48" ht="16.2" customHeight="1" thickBot="1">
       <c r="A48" s="9" t="n">
@@ -4165,9 +4899,9 @@
       <c r="C59" s="37" t="n"/>
       <c r="D59" s="40" t="n"/>
       <c r="E59" s="6" t="n"/>
-      <c r="F59" s="121" t="n"/>
-      <c r="G59" s="121" t="n"/>
-      <c r="H59" s="122" t="n"/>
+      <c r="F59" s="123" t="n"/>
+      <c r="G59" s="123" t="n"/>
+      <c r="H59" s="124" t="n"/>
       <c r="I59" s="23" t="n"/>
       <c r="J59" s="6" t="n"/>
       <c r="K59" s="6" t="n"/>
@@ -4204,9 +4938,9 @@
       <c r="C60" s="37" t="n"/>
       <c r="D60" s="40" t="n"/>
       <c r="E60" s="6" t="n"/>
-      <c r="F60" s="121" t="n"/>
-      <c r="G60" s="121" t="n"/>
-      <c r="H60" s="122" t="n"/>
+      <c r="F60" s="123" t="n"/>
+      <c r="G60" s="123" t="n"/>
+      <c r="H60" s="124" t="n"/>
       <c r="I60" s="23" t="n"/>
       <c r="J60" s="6" t="n"/>
       <c r="K60" s="6" t="n"/>
@@ -4279,9 +5013,9 @@
       <c r="C62" s="37" t="n"/>
       <c r="D62" s="40" t="n"/>
       <c r="E62" s="6" t="n"/>
-      <c r="F62" s="121" t="n"/>
-      <c r="G62" s="121" t="n"/>
-      <c r="H62" s="122" t="n"/>
+      <c r="F62" s="123" t="n"/>
+      <c r="G62" s="123" t="n"/>
+      <c r="H62" s="124" t="n"/>
       <c r="I62" s="23" t="n"/>
       <c r="J62" s="6" t="n"/>
       <c r="K62" s="6" t="n"/>
@@ -4318,9 +5052,9 @@
       <c r="C63" s="37" t="n"/>
       <c r="D63" s="40" t="n"/>
       <c r="E63" s="6" t="n"/>
-      <c r="F63" s="121" t="n"/>
-      <c r="G63" s="121" t="n"/>
-      <c r="H63" s="122" t="n"/>
+      <c r="F63" s="123" t="n"/>
+      <c r="G63" s="123" t="n"/>
+      <c r="H63" s="124" t="n"/>
       <c r="I63" s="23" t="n"/>
       <c r="J63" s="6" t="n"/>
       <c r="K63" s="6" t="n"/>
@@ -4357,9 +5091,9 @@
       <c r="C64" s="37" t="n"/>
       <c r="D64" s="40" t="n"/>
       <c r="E64" s="6" t="n"/>
-      <c r="F64" s="121" t="n"/>
-      <c r="G64" s="121" t="n"/>
-      <c r="H64" s="122" t="n"/>
+      <c r="F64" s="123" t="n"/>
+      <c r="G64" s="123" t="n"/>
+      <c r="H64" s="124" t="n"/>
       <c r="I64" s="23" t="n"/>
       <c r="J64" s="6" t="n"/>
       <c r="K64" s="6" t="n"/>
@@ -4396,9 +5130,9 @@
       <c r="C65" s="37" t="n"/>
       <c r="D65" s="40" t="n"/>
       <c r="E65" s="6" t="n"/>
-      <c r="F65" s="121" t="n"/>
-      <c r="G65" s="121" t="n"/>
-      <c r="H65" s="122" t="n"/>
+      <c r="F65" s="123" t="n"/>
+      <c r="G65" s="123" t="n"/>
+      <c r="H65" s="124" t="n"/>
       <c r="I65" s="23" t="n"/>
       <c r="J65" s="6" t="n"/>
       <c r="K65" s="6" t="n"/>
@@ -4434,7 +5168,7 @@
       <c r="B66" s="37" t="n"/>
       <c r="C66" s="37" t="n"/>
       <c r="D66" s="40" t="n"/>
-      <c r="E66" s="137" t="n"/>
+      <c r="E66" s="148" t="n"/>
       <c r="F66" s="7" t="n"/>
       <c r="G66" s="7" t="n"/>
       <c r="H66" s="23" t="n"/>
@@ -4473,7 +5207,7 @@
       <c r="B67" s="37" t="n"/>
       <c r="C67" s="37" t="n"/>
       <c r="D67" s="40" t="n"/>
-      <c r="E67" s="137" t="n"/>
+      <c r="E67" s="148" t="n"/>
       <c r="F67" s="7" t="n"/>
       <c r="G67" s="7" t="n"/>
       <c r="H67" s="23" t="n"/>
@@ -4512,7 +5246,7 @@
       <c r="B68" s="37" t="n"/>
       <c r="C68" s="37" t="n"/>
       <c r="D68" s="40" t="n"/>
-      <c r="E68" s="137" t="n"/>
+      <c r="E68" s="148" t="n"/>
       <c r="F68" s="7" t="n"/>
       <c r="G68" s="7" t="n"/>
       <c r="H68" s="23" t="n"/>
@@ -4551,7 +5285,7 @@
       <c r="B69" s="37" t="n"/>
       <c r="C69" s="37" t="n"/>
       <c r="D69" s="40" t="n"/>
-      <c r="E69" s="137" t="n"/>
+      <c r="E69" s="148" t="n"/>
       <c r="F69" s="7" t="n"/>
       <c r="G69" s="7" t="n"/>
       <c r="H69" s="23" t="n"/>
@@ -4590,7 +5324,7 @@
       <c r="B70" s="37" t="n"/>
       <c r="C70" s="37" t="n"/>
       <c r="D70" s="40" t="n"/>
-      <c r="E70" s="137" t="n"/>
+      <c r="E70" s="148" t="n"/>
       <c r="F70" s="7" t="n"/>
       <c r="G70" s="7" t="n"/>
       <c r="H70" s="23" t="n"/>
@@ -4629,7 +5363,7 @@
       <c r="B71" s="37" t="n"/>
       <c r="C71" s="37" t="n"/>
       <c r="D71" s="40" t="n"/>
-      <c r="E71" s="137" t="n"/>
+      <c r="E71" s="148" t="n"/>
       <c r="F71" s="7" t="n"/>
       <c r="G71" s="7" t="n"/>
       <c r="H71" s="23" t="n"/>
@@ -4715,275 +5449,275 @@
       <c r="O73" s="14" t="n"/>
     </row>
     <row r="74" ht="15" customHeight="1" thickBot="1">
-      <c r="A74" s="123" t="inlineStr">
+      <c r="A74" s="125" t="inlineStr">
         <is>
           <t>TOTAL DAILY CREWS MANPOWER</t>
         </is>
       </c>
-      <c r="B74" s="114" t="n"/>
-      <c r="C74" s="118" t="n"/>
-      <c r="D74" s="117" t="inlineStr">
+      <c r="B74" s="116" t="n"/>
+      <c r="C74" s="120" t="n"/>
+      <c r="D74" s="119" t="inlineStr">
         <is>
           <t>SHIFT</t>
         </is>
       </c>
-      <c r="E74" s="1">
+      <c r="E74" s="109">
         <f>IF(1&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="F74" s="1">
+      <c r="F74" s="109">
         <f>IF(2&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,2),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="G74" s="1">
+      <c r="G74" s="109">
         <f>IF(3&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,3),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="H74" s="1">
+      <c r="H74" s="109">
         <f>IF(4&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,4),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="I74" s="1">
+      <c r="I74" s="109">
         <f>IF(5&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,5),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="J74" s="1">
+      <c r="J74" s="109">
         <f>IF(6&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,6),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="K74" s="1">
+      <c r="K74" s="109">
         <f>IF(7&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,7),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="L74" s="1">
+      <c r="L74" s="109">
         <f>IF(8&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,8),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="M74" s="1">
+      <c r="M74" s="109">
         <f>IF(9&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,9),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="N74" s="1">
+      <c r="N74" s="109">
         <f>IF(10&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,10),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="O74" s="1">
+      <c r="O74" s="109">
         <f>IF(11&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,11),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="P74" s="1">
+      <c r="P74" s="109">
         <f>IF(12&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,12),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="Q74" s="1">
+      <c r="Q74" s="109">
         <f>IF(13&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,13),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="R74" s="1">
+      <c r="R74" s="109">
         <f>IF(14&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,14),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="S74" s="1">
+      <c r="S74" s="109">
         <f>IF(15&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,15),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="T74" s="1">
+      <c r="T74" s="109">
         <f>IF(16&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,16),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="U74" s="1">
+      <c r="U74" s="109">
         <f>IF(17&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,17),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="V74" s="1">
+      <c r="V74" s="109">
         <f>IF(18&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,18),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="W74" s="1">
+      <c r="W74" s="109">
         <f>IF(19&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,19),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="X74" s="1">
+      <c r="X74" s="109">
         <f>IF(20&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,20),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="Y74" s="1">
+      <c r="Y74" s="109">
         <f>IF(21&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,21),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="Z74" s="1">
+      <c r="Z74" s="109">
         <f>IF(22&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,22),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="AA74" s="1">
+      <c r="AA74" s="109">
         <f>IF(23&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,23),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="AB74" s="1">
+      <c r="AB74" s="109">
         <f>IF(24&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,24),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="AC74" s="1">
+      <c r="AC74" s="109">
         <f>IF(25&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,25),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="AD74" s="1">
+      <c r="AD74" s="109">
         <f>IF(26&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,26),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="AE74" s="1">
+      <c r="AE74" s="109">
         <f>IF(27&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,27),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="AF74" s="1">
+      <c r="AF74" s="109">
         <f>IF(28&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,28),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="AG74" s="1">
+      <c r="AG74" s="109">
         <f>IF(29&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,29),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="AH74" s="1">
+      <c r="AH74" s="109">
         <f>IF(30&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,30),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="AI74" s="1">
+      <c r="AI74" s="109">
         <f>IF(31&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,31),"ddd"),"")</f>
         <v/>
       </c>
     </row>
     <row r="75" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A75" s="110" t="n"/>
-      <c r="C75" s="124" t="n"/>
+      <c r="A75" s="111" t="n"/>
+      <c r="C75" s="126" t="n"/>
       <c r="D75" s="105" t="n"/>
-      <c r="E75" s="2">
+      <c r="E75" s="112">
         <f>IF(1&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),1,"")</f>
         <v/>
       </c>
-      <c r="F75" s="2">
+      <c r="F75" s="112">
         <f>IF(2&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),2,"")</f>
         <v/>
       </c>
-      <c r="G75" s="2">
+      <c r="G75" s="112">
         <f>IF(3&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),3,"")</f>
         <v/>
       </c>
-      <c r="H75" s="2">
+      <c r="H75" s="112">
         <f>IF(4&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),4,"")</f>
         <v/>
       </c>
-      <c r="I75" s="3">
+      <c r="I75" s="112">
         <f>IF(5&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),5,"")</f>
         <v/>
       </c>
-      <c r="J75" s="4">
+      <c r="J75" s="112">
         <f>IF(6&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),6,"")</f>
         <v/>
       </c>
-      <c r="K75" s="4">
+      <c r="K75" s="112">
         <f>IF(7&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),7,"")</f>
         <v/>
       </c>
-      <c r="L75" s="3">
+      <c r="L75" s="112">
         <f>IF(8&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),8,"")</f>
         <v/>
       </c>
-      <c r="M75" s="4">
+      <c r="M75" s="112">
         <f>IF(9&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),9,"")</f>
         <v/>
       </c>
-      <c r="N75" s="2">
+      <c r="N75" s="112">
         <f>IF(10&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),10,"")</f>
         <v/>
       </c>
-      <c r="O75" s="2">
+      <c r="O75" s="112">
         <f>IF(11&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),11,"")</f>
         <v/>
       </c>
-      <c r="P75" s="2">
+      <c r="P75" s="112">
         <f>IF(12&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),12,"")</f>
         <v/>
       </c>
-      <c r="Q75" s="2">
+      <c r="Q75" s="112">
         <f>IF(13&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),13,"")</f>
         <v/>
       </c>
-      <c r="R75" s="2">
+      <c r="R75" s="112">
         <f>IF(14&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),14,"")</f>
         <v/>
       </c>
-      <c r="S75" s="2">
+      <c r="S75" s="112">
         <f>IF(15&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),15,"")</f>
         <v/>
       </c>
-      <c r="T75" s="2">
+      <c r="T75" s="112">
         <f>IF(16&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),16,"")</f>
         <v/>
       </c>
-      <c r="U75" s="2">
+      <c r="U75" s="112">
         <f>IF(17&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),17,"")</f>
         <v/>
       </c>
-      <c r="V75" s="2">
+      <c r="V75" s="112">
         <f>IF(18&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),18,"")</f>
         <v/>
       </c>
-      <c r="W75" s="2">
+      <c r="W75" s="112">
         <f>IF(19&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),19,"")</f>
         <v/>
       </c>
-      <c r="X75" s="2">
+      <c r="X75" s="112">
         <f>IF(20&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),20,"")</f>
         <v/>
       </c>
-      <c r="Y75" s="2">
+      <c r="Y75" s="112">
         <f>IF(21&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),21,"")</f>
         <v/>
       </c>
-      <c r="Z75" s="2">
+      <c r="Z75" s="112">
         <f>IF(22&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),22,"")</f>
         <v/>
       </c>
-      <c r="AA75" s="2">
+      <c r="AA75" s="112">
         <f>IF(23&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),23,"")</f>
         <v/>
       </c>
-      <c r="AB75" s="2">
+      <c r="AB75" s="112">
         <f>IF(24&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),24,"")</f>
         <v/>
       </c>
-      <c r="AC75" s="2">
+      <c r="AC75" s="112">
         <f>IF(25&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),25,"")</f>
         <v/>
       </c>
-      <c r="AD75" s="2">
+      <c r="AD75" s="112">
         <f>IF(26&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),26,"")</f>
         <v/>
       </c>
-      <c r="AE75" s="2">
+      <c r="AE75" s="112">
         <f>IF(27&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),27,"")</f>
         <v/>
       </c>
-      <c r="AF75" s="2">
+      <c r="AF75" s="112">
         <f>IF(28&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),28,"")</f>
         <v/>
       </c>
-      <c r="AG75" s="2">
+      <c r="AG75" s="112">
         <f>IF(29&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),29,"")</f>
         <v/>
       </c>
-      <c r="AH75" s="2">
+      <c r="AH75" s="112">
         <f>IF(30&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),30,"")</f>
         <v/>
       </c>
-      <c r="AI75" s="2">
+      <c r="AI75" s="112">
         <f>IF(31&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),31,"")</f>
         <v/>
       </c>
     </row>
     <row r="76" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A76" s="110" t="n"/>
-      <c r="C76" s="124" t="n"/>
+      <c r="A76" s="111" t="n"/>
+      <c r="C76" s="126" t="n"/>
       <c r="D76" s="15" t="inlineStr">
         <is>
           <t>D</t>
@@ -5115,8 +5849,8 @@
       </c>
     </row>
     <row r="77" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A77" s="110" t="n"/>
-      <c r="C77" s="124" t="n"/>
+      <c r="A77" s="111" t="n"/>
+      <c r="C77" s="126" t="n"/>
       <c r="D77" s="17" t="inlineStr">
         <is>
           <t>T</t>
@@ -5248,9 +5982,9 @@
       </c>
     </row>
     <row r="78" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A78" s="115" t="n"/>
-      <c r="B78" s="116" t="n"/>
-      <c r="C78" s="119" t="n"/>
+      <c r="A78" s="117" t="n"/>
+      <c r="B78" s="118" t="n"/>
+      <c r="C78" s="121" t="n"/>
       <c r="D78" s="19" t="inlineStr">
         <is>
           <t>G</t>
@@ -5383,7 +6117,7 @@
     </row>
     <row r="79" ht="15" customHeight="1" thickBot="1"/>
     <row r="80" ht="21" customHeight="1" thickBot="1">
-      <c r="E80" s="117" t="inlineStr">
+      <c r="E80" s="119" t="inlineStr">
         <is>
           <t>SHIFT</t>
         </is>
@@ -5395,7 +6129,7 @@
       <c r="J80" s="104" t="n"/>
     </row>
     <row r="81" ht="16.2" customHeight="1" thickBot="1">
-      <c r="E81" s="44" t="inlineStr">
+      <c r="E81" s="127" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -5411,7 +6145,7 @@
       <c r="J81" s="104" t="n"/>
     </row>
     <row r="82" ht="16.2" customHeight="1" thickBot="1">
-      <c r="E82" s="45" t="inlineStr">
+      <c r="E82" s="128" t="inlineStr">
         <is>
           <t>T</t>
         </is>
@@ -5430,30 +6164,34 @@
           <t>ABDULLAH A. ALSHEHRY</t>
         </is>
       </c>
-      <c r="N82" s="116" t="n"/>
-      <c r="O82" s="116" t="n"/>
-      <c r="P82" s="116" t="n"/>
-      <c r="Q82" s="116" t="n"/>
-      <c r="R82" s="116" t="n"/>
-      <c r="S82" s="116" t="n"/>
+      <c r="N82" s="118" t="n"/>
+      <c r="O82" s="118" t="n"/>
+      <c r="P82" s="118" t="n"/>
+      <c r="Q82" s="118" t="n"/>
+      <c r="R82" s="118" t="n"/>
+      <c r="S82" s="118" t="n"/>
       <c r="W82" s="96">
         <f>UPPER(TEXT(TODAY(),"DDDD dd/mm/yyyy"))</f>
         <v/>
       </c>
-      <c r="X82" s="116" t="n"/>
-      <c r="Y82" s="116" t="n"/>
-      <c r="Z82" s="116" t="n"/>
-      <c r="AA82" s="116" t="n"/>
-      <c r="AB82" s="116" t="n"/>
-      <c r="AC82" s="116" t="n"/>
+      <c r="X82" s="118" t="n"/>
+      <c r="Y82" s="118" t="n"/>
+      <c r="Z82" s="118" t="n"/>
+      <c r="AA82" s="118" t="n"/>
+      <c r="AB82" s="118" t="n"/>
+      <c r="AC82" s="118" t="n"/>
     </row>
     <row r="83" ht="16.2" customHeight="1" thickBot="1">
-      <c r="E83" s="46" t="inlineStr">
+      <c r="E83" s="129" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
-      <c r="F83" s="20" t="n"/>
+      <c r="F83" s="20" t="inlineStr">
+        <is>
+          <t>GRV (23:00 - 07:00)</t>
+        </is>
+      </c>
       <c r="G83" s="103" t="n"/>
       <c r="H83" s="103" t="n"/>
       <c r="I83" s="103" t="n"/>
@@ -5470,120 +6208,184 @@
       </c>
     </row>
     <row r="85">
-      <c r="E85" s="125" t="inlineStr">
+      <c r="E85" s="130" t="inlineStr">
         <is>
-          <t>ADDITIONAL CODES</t>
+          <t>CODE LEGEND — ALL CODES</t>
         </is>
       </c>
     </row>
     <row r="86" ht="16" customHeight="1">
-      <c r="E86" s="126" t="inlineStr">
+      <c r="E86" s="131" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F86" s="132" t="inlineStr">
+        <is>
+          <t>DAY</t>
+        </is>
+      </c>
+      <c r="K86" s="133" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="L86" s="132" t="inlineStr">
+        <is>
+          <t>TWILIGHT</t>
+        </is>
+      </c>
+      <c r="Q86" s="134" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="R86" s="132" t="inlineStr">
+        <is>
+          <t>GRAVEYARD</t>
+        </is>
+      </c>
+      <c r="W86" s="135" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
+      <c r="X86" s="132" t="inlineStr">
+        <is>
+          <t>TRAINING</t>
+        </is>
+      </c>
+      <c r="AC86" s="136" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="AD86" s="132" t="inlineStr">
+        <is>
+          <t>VACATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="16" customHeight="1">
+      <c r="E87" s="137" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F87" s="132" t="inlineStr">
+        <is>
+          <t>REST/RDO</t>
+        </is>
+      </c>
+      <c r="K87" s="138" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="F86" s="127" t="inlineStr">
+      <c r="L87" s="132" t="inlineStr">
         <is>
           <t>ABSENT</t>
         </is>
       </c>
-      <c r="L86" s="128" t="inlineStr">
+      <c r="Q87" s="139" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="M86" s="127" t="inlineStr">
+      <c r="R87" s="132" t="inlineStr">
         <is>
           <t>HOLIDAY</t>
         </is>
       </c>
-      <c r="S86" s="129" t="inlineStr">
+      <c r="W87" s="140" t="inlineStr">
         <is>
           <t>OT</t>
         </is>
       </c>
-      <c r="T86" s="127" t="inlineStr">
+      <c r="X87" s="132" t="inlineStr">
         <is>
           <t>OVERTIME</t>
         </is>
       </c>
-      <c r="Z86" s="130" t="inlineStr">
+      <c r="AC87" s="141" t="inlineStr">
         <is>
           <t>OS</t>
         </is>
       </c>
-      <c r="AA86" s="127" t="inlineStr">
+      <c r="AD87" s="132" t="inlineStr">
         <is>
           <t>OUTSTATION</t>
         </is>
       </c>
     </row>
-    <row r="87" ht="16" customHeight="1">
-      <c r="E87" s="131" t="inlineStr">
+    <row r="88" ht="16" customHeight="1">
+      <c r="E88" s="142" t="inlineStr">
         <is>
           <t>S/L</t>
         </is>
       </c>
-      <c r="F87" s="127" t="inlineStr">
+      <c r="F88" s="132" t="inlineStr">
         <is>
           <t>SICK LEAVE</t>
         </is>
       </c>
-      <c r="L87" s="132" t="inlineStr">
+      <c r="K88" s="143" t="inlineStr">
         <is>
           <t>C/T</t>
         </is>
       </c>
-      <c r="M87" s="127" t="inlineStr">
+      <c r="L88" s="132" t="inlineStr">
         <is>
           <t>COMP TIME</t>
         </is>
       </c>
-      <c r="S87" s="133" t="inlineStr">
+      <c r="Q88" s="144" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="T87" s="127" t="inlineStr">
+      <c r="R88" s="132" t="inlineStr">
         <is>
           <t>LATE/LEAVE</t>
         </is>
       </c>
-      <c r="Z87" s="134" t="inlineStr">
+      <c r="W88" s="145" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="AA87" s="127" t="inlineStr">
+      <c r="X88" s="132" t="inlineStr">
         <is>
           <t>NOTE</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="39">
-    <mergeCell ref="M87:Q87"/>
-    <mergeCell ref="F87:J87"/>
+  <mergeCells count="45">
+    <mergeCell ref="X88:AA88"/>
     <mergeCell ref="E2:AC2"/>
     <mergeCell ref="C1:C2"/>
+    <mergeCell ref="AD87:AG87"/>
     <mergeCell ref="AK6:AN6"/>
     <mergeCell ref="A74:C78"/>
     <mergeCell ref="W82:AC82"/>
-    <mergeCell ref="AA87:AE87"/>
     <mergeCell ref="E80:J80"/>
     <mergeCell ref="F83:J83"/>
-    <mergeCell ref="AA86:AE86"/>
-    <mergeCell ref="T87:X87"/>
+    <mergeCell ref="F88:I88"/>
+    <mergeCell ref="L86:O86"/>
     <mergeCell ref="AL5:AN5"/>
     <mergeCell ref="A46:D47"/>
     <mergeCell ref="AD1:AI2"/>
     <mergeCell ref="A3:D4"/>
-    <mergeCell ref="F86:J86"/>
+    <mergeCell ref="F87:I87"/>
     <mergeCell ref="E62:H62"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="M83:S83"/>
+    <mergeCell ref="X86:AA86"/>
     <mergeCell ref="AL4:AN4"/>
+    <mergeCell ref="R88:U88"/>
     <mergeCell ref="E64:H64"/>
+    <mergeCell ref="R87:U87"/>
     <mergeCell ref="F81:J81"/>
     <mergeCell ref="A22:D23"/>
     <mergeCell ref="D74:D75"/>
@@ -5591,103 +6393,68 @@
     <mergeCell ref="A42:D43"/>
     <mergeCell ref="AK3:AN3"/>
     <mergeCell ref="M82:S82"/>
-    <mergeCell ref="M86:Q86"/>
+    <mergeCell ref="L87:O87"/>
+    <mergeCell ref="X87:AA87"/>
+    <mergeCell ref="F86:I86"/>
     <mergeCell ref="E63:H63"/>
     <mergeCell ref="E60:H60"/>
     <mergeCell ref="E1:AC1"/>
     <mergeCell ref="E65:H65"/>
-    <mergeCell ref="T86:X86"/>
+    <mergeCell ref="L88:O88"/>
     <mergeCell ref="F82:J82"/>
+    <mergeCell ref="R86:U86"/>
     <mergeCell ref="D1:D2"/>
     <mergeCell ref="E59:H59"/>
+    <mergeCell ref="AD86:AG86"/>
     <mergeCell ref="A1:A2"/>
   </mergeCells>
-  <conditionalFormatting sqref="E21:O21 E24:AI40 E44:AI44 E45:O45 E48:AI56 E57:E72 E73:O73 I57:AI72">
-    <cfRule type="containsText" priority="13" operator="containsText" dxfId="5" text="TR">
-      <formula>NOT(ISERROR(SEARCH("TR",E21)))</formula>
+  <conditionalFormatting sqref="E5:AI73">
+    <cfRule type="cellIs" priority="13" operator="equal" dxfId="12">
+      <formula>"D"</formula>
     </cfRule>
-    <cfRule type="containsText" priority="14" operator="containsText" dxfId="4" text="V">
-      <formula>NOT(ISERROR(SEARCH("V",E21)))</formula>
+    <cfRule type="cellIs" priority="14" operator="equal" dxfId="13">
+      <formula>"T"</formula>
     </cfRule>
-    <cfRule type="containsText" priority="15" operator="containsText" dxfId="3" text="R">
-      <formula>NOT(ISERROR(SEARCH("R",E21)))</formula>
+    <cfRule type="cellIs" priority="15" operator="equal" dxfId="14">
+      <formula>"G"</formula>
     </cfRule>
-    <cfRule type="containsText" priority="16" operator="containsText" dxfId="2" text="G">
-      <formula>NOT(ISERROR(SEARCH("G",E21)))</formula>
+    <cfRule type="cellIs" priority="16" operator="equal" dxfId="15">
+      <formula>"TR"</formula>
     </cfRule>
-    <cfRule type="containsText" priority="17" operator="containsText" dxfId="1" text="T">
-      <formula>NOT(ISERROR(SEARCH("T",E21)))</formula>
+    <cfRule type="cellIs" priority="17" operator="equal" dxfId="16">
+      <formula>"V"</formula>
     </cfRule>
-    <cfRule type="containsText" priority="18" operator="containsText" dxfId="0" text="D">
-      <formula>NOT(ISERROR(SEARCH("D",E21)))</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="13" operator="equal" dxfId="12">
+    <cfRule type="cellIs" priority="18" operator="equal" dxfId="17">
       <formula>"A"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="14" operator="equal" dxfId="13">
+    <cfRule type="cellIs" priority="19" operator="equal" dxfId="18">
       <formula>"H"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="15" operator="equal" dxfId="14">
+    <cfRule type="cellIs" priority="20" operator="equal" dxfId="19">
       <formula>"OT"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="16" operator="equal" dxfId="15">
+    <cfRule type="cellIs" priority="21" operator="equal" dxfId="20">
       <formula>"OS"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="17" operator="equal" dxfId="16">
+    <cfRule type="cellIs" priority="22" operator="equal" dxfId="21">
       <formula>"S/L"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="18" operator="equal" dxfId="17">
+    <cfRule type="cellIs" priority="23" operator="equal" dxfId="22">
       <formula>"C/T"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="19" operator="equal" dxfId="18">
+    <cfRule type="cellIs" priority="24" operator="equal" dxfId="23">
       <formula>"L"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="20" operator="equal" dxfId="19">
+    <cfRule type="cellIs" priority="25" operator="equal" dxfId="24">
       <formula>"N"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E5:AI20">
-    <cfRule type="containsText" priority="1" operator="containsText" dxfId="5" text="TR">
-      <formula>NOT(ISERROR(SEARCH("TR",E5)))</formula>
+  <conditionalFormatting sqref="A5:D73">
+    <cfRule type="expression" priority="26" dxfId="25">
+      <formula>$D5="OJT"</formula>
     </cfRule>
-    <cfRule type="containsText" priority="2" operator="containsText" dxfId="4" text="V">
-      <formula>NOT(ISERROR(SEARCH("V",E5)))</formula>
-    </cfRule>
-    <cfRule type="containsText" priority="3" operator="containsText" dxfId="3" text="R">
-      <formula>NOT(ISERROR(SEARCH("R",E5)))</formula>
-    </cfRule>
-    <cfRule type="containsText" priority="4" operator="containsText" dxfId="2" text="G">
-      <formula>NOT(ISERROR(SEARCH("G",E5)))</formula>
-    </cfRule>
-    <cfRule type="containsText" priority="5" operator="containsText" dxfId="1" text="T">
-      <formula>NOT(ISERROR(SEARCH("T",E5)))</formula>
-    </cfRule>
-    <cfRule type="containsText" priority="6" operator="containsText" dxfId="0" text="D">
-      <formula>NOT(ISERROR(SEARCH("D",E5)))</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="21" operator="equal" dxfId="12">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="22" operator="equal" dxfId="13">
-      <formula>"H"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="23" operator="equal" dxfId="14">
-      <formula>"OT"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="24" operator="equal" dxfId="15">
-      <formula>"OS"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="25" operator="equal" dxfId="16">
-      <formula>"S/L"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="26" operator="equal" dxfId="17">
-      <formula>"C/T"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="27" operator="equal" dxfId="18">
-      <formula>"L"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="28" operator="equal" dxfId="19">
-      <formula>"N"</formula>
+    <cfRule type="expression" priority="27" dxfId="26">
+      <formula>$D5="ACT/SUPV"</formula>
     </cfRule>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>

--- a/uploads/inbox/SPV_ROSTER_TEMPLATE_AVISUITE_COLORS.xlsx
+++ b/uploads/inbox/SPV_ROSTER_TEMPLATE_AVISUITE_COLORS.xlsx
@@ -20,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mmmm\ yyyy"/>
   </numFmts>
-  <fonts count="36">
+  <fonts count="37">
     <font>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -117,13 +117,15 @@
     </font>
     <font>
       <name val="Times New Roman"/>
-      <b val="1"/>
-      <sz val="8"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Times New Roman"/>
-      <b val="1"/>
-      <sz val="10"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <sz val="12"/>
     </font>
     <font>
       <name val="Times New Roman"/>
@@ -238,7 +240,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="28">
+  <fills count="27">
     <fill>
       <patternFill/>
     </fill>
@@ -307,11 +309,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF8E1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D0CECE"/>
       </patternFill>
     </fill>
     <fill>
@@ -385,7 +382,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="39">
+  <borders count="35">
     <border>
       <left/>
       <right/>
@@ -798,55 +795,11 @@
         <color rgb="007F8C8D"/>
       </bottom>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="007F8C8D"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="007F8C8D"/>
-      </right>
-      <top style="thin">
-        <color rgb="007F8C8D"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="007F8C8D"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="007F8C8D"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="007F8C8D"/>
-      </right>
-      <top style="thin">
-        <color rgb="007F8C8D"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="007F8C8D"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="149">
+  <cellXfs count="153">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -1162,23 +1115,35 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="13" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="12" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1189,73 +1154,77 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="17" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="18" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="19" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="20" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="21" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="22" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="23" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="24" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="25" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="26" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="27" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="17" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="18" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="19" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="20" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="21" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="22" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="23" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="24" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="25" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="26" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1506,14 +1475,14 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="00DBEDD5"/>
+          <bgColor rgb="00DAF2D0"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="00A1BFCC"/>
+          <bgColor rgb="0083CCEB"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2032,282 +2001,280 @@
           <t>CREW 1</t>
         </is>
       </c>
-      <c r="E3" s="109">
+      <c r="E3" s="1">
         <f>IF(1&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="F3" s="109">
+      <c r="F3" s="1">
         <f>IF(2&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,2),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="G3" s="109">
+      <c r="G3" s="1">
         <f>IF(3&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,3),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="H3" s="109">
+      <c r="H3" s="1">
         <f>IF(4&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,4),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="I3" s="109">
+      <c r="I3" s="1">
         <f>IF(5&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,5),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="J3" s="109">
+      <c r="J3" s="1">
         <f>IF(6&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,6),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="K3" s="109">
+      <c r="K3" s="1">
         <f>IF(7&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,7),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="L3" s="109">
+      <c r="L3" s="1">
         <f>IF(8&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,8),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="M3" s="109">
+      <c r="M3" s="1">
         <f>IF(9&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,9),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="N3" s="109">
+      <c r="N3" s="1">
         <f>IF(10&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,10),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="O3" s="109">
+      <c r="O3" s="1">
         <f>IF(11&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,11),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="P3" s="109">
+      <c r="P3" s="1">
         <f>IF(12&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,12),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="Q3" s="109">
+      <c r="Q3" s="1">
         <f>IF(13&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,13),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="R3" s="109">
+      <c r="R3" s="1">
         <f>IF(14&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,14),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="S3" s="109">
+      <c r="S3" s="1">
         <f>IF(15&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,15),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="T3" s="109">
+      <c r="T3" s="1">
         <f>IF(16&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,16),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="U3" s="109">
+      <c r="U3" s="1">
         <f>IF(17&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,17),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="V3" s="109">
+      <c r="V3" s="1">
         <f>IF(18&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,18),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="W3" s="109">
+      <c r="W3" s="1">
         <f>IF(19&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,19),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="X3" s="109">
+      <c r="X3" s="1">
         <f>IF(20&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,20),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="Y3" s="109">
+      <c r="Y3" s="1">
         <f>IF(21&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,21),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="Z3" s="109">
+      <c r="Z3" s="1">
         <f>IF(22&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,22),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="AA3" s="109">
+      <c r="AA3" s="1">
         <f>IF(23&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,23),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="AB3" s="109">
+      <c r="AB3" s="1">
         <f>IF(24&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,24),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="AC3" s="109">
+      <c r="AC3" s="1">
         <f>IF(25&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,25),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="AD3" s="109">
+      <c r="AD3" s="1">
         <f>IF(26&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,26),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="AE3" s="109">
+      <c r="AE3" s="1">
         <f>IF(27&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,27),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="AF3" s="109">
+      <c r="AF3" s="1">
         <f>IF(28&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,28),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="AG3" s="109">
+      <c r="AG3" s="1">
         <f>IF(29&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,29),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="AH3" s="109">
+      <c r="AH3" s="24">
         <f>IF(30&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,30),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="AI3" s="109">
+      <c r="AI3" s="21">
         <f>IF(31&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,31),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="AK3" s="110" t="inlineStr">
+      <c r="AK3" s="109" t="inlineStr">
         <is>
           <t>ROSTER PERIOD</t>
         </is>
       </c>
     </row>
     <row r="4" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A4" s="111" t="n"/>
-      <c r="E4" s="112">
+      <c r="A4" s="110" t="n"/>
+      <c r="E4" s="2">
         <f>IF(1&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),1,"")</f>
         <v/>
       </c>
-      <c r="F4" s="112">
+      <c r="F4" s="2">
         <f>IF(2&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),2,"")</f>
         <v/>
       </c>
-      <c r="G4" s="112">
+      <c r="G4" s="2">
         <f>IF(3&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),3,"")</f>
         <v/>
       </c>
-      <c r="H4" s="112">
+      <c r="H4" s="2">
         <f>IF(4&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),4,"")</f>
         <v/>
       </c>
-      <c r="I4" s="112">
+      <c r="I4" s="3">
         <f>IF(5&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),5,"")</f>
         <v/>
       </c>
-      <c r="J4" s="112">
+      <c r="J4" s="4">
         <f>IF(6&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),6,"")</f>
         <v/>
       </c>
-      <c r="K4" s="112">
+      <c r="K4" s="4">
         <f>IF(7&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),7,"")</f>
         <v/>
       </c>
-      <c r="L4" s="112">
+      <c r="L4" s="3">
         <f>IF(8&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),8,"")</f>
         <v/>
       </c>
-      <c r="M4" s="112">
+      <c r="M4" s="4">
         <f>IF(9&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),9,"")</f>
         <v/>
       </c>
-      <c r="N4" s="112">
+      <c r="N4" s="2">
         <f>IF(10&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),10,"")</f>
         <v/>
       </c>
-      <c r="O4" s="112">
+      <c r="O4" s="2">
         <f>IF(11&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),11,"")</f>
         <v/>
       </c>
-      <c r="P4" s="112">
+      <c r="P4" s="2">
         <f>IF(12&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),12,"")</f>
         <v/>
       </c>
-      <c r="Q4" s="112">
+      <c r="Q4" s="2">
         <f>IF(13&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),13,"")</f>
         <v/>
       </c>
-      <c r="R4" s="112">
+      <c r="R4" s="2">
         <f>IF(14&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),14,"")</f>
         <v/>
       </c>
-      <c r="S4" s="112">
+      <c r="S4" s="2">
         <f>IF(15&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),15,"")</f>
         <v/>
       </c>
-      <c r="T4" s="112">
+      <c r="T4" s="2">
         <f>IF(16&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),16,"")</f>
         <v/>
       </c>
-      <c r="U4" s="112">
+      <c r="U4" s="2">
         <f>IF(17&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),17,"")</f>
         <v/>
       </c>
-      <c r="V4" s="112">
+      <c r="V4" s="2">
         <f>IF(18&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),18,"")</f>
         <v/>
       </c>
-      <c r="W4" s="112">
+      <c r="W4" s="2">
         <f>IF(19&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),19,"")</f>
         <v/>
       </c>
-      <c r="X4" s="112">
+      <c r="X4" s="2">
         <f>IF(20&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),20,"")</f>
         <v/>
       </c>
-      <c r="Y4" s="112">
+      <c r="Y4" s="2">
         <f>IF(21&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),21,"")</f>
         <v/>
       </c>
-      <c r="Z4" s="112">
+      <c r="Z4" s="2">
         <f>IF(22&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),22,"")</f>
         <v/>
       </c>
-      <c r="AA4" s="112">
+      <c r="AA4" s="2">
         <f>IF(23&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),23,"")</f>
         <v/>
       </c>
-      <c r="AB4" s="112">
+      <c r="AB4" s="2">
         <f>IF(24&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),24,"")</f>
         <v/>
       </c>
-      <c r="AC4" s="112">
+      <c r="AC4" s="2">
         <f>IF(25&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),25,"")</f>
         <v/>
       </c>
-      <c r="AD4" s="112">
+      <c r="AD4" s="2">
         <f>IF(26&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),26,"")</f>
         <v/>
       </c>
-      <c r="AE4" s="112">
+      <c r="AE4" s="2">
         <f>IF(27&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),27,"")</f>
         <v/>
       </c>
-      <c r="AF4" s="112">
+      <c r="AF4" s="2">
         <f>IF(28&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),28,"")</f>
         <v/>
       </c>
-      <c r="AG4" s="112">
+      <c r="AG4" s="2">
         <f>IF(29&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),29,"")</f>
         <v/>
       </c>
-      <c r="AH4" s="112">
+      <c r="AH4" s="25">
         <f>IF(30&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),30,"")</f>
         <v/>
       </c>
-      <c r="AI4" s="112">
+      <c r="AI4" s="22">
         <f>IF(31&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),31,"")</f>
         <v/>
       </c>
-      <c r="AK4" s="113" t="inlineStr">
+      <c r="AK4" s="111" t="inlineStr">
         <is>
           <t>MONTH</t>
         </is>
       </c>
-      <c r="AL4" s="114" t="inlineStr">
+      <c r="AL4" s="112" t="inlineStr">
         <is>
           <t>JUL</t>
         </is>
       </c>
-      <c r="AM4" s="146" t="n"/>
-      <c r="AN4" s="147" t="n"/>
     </row>
     <row r="5" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="113" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="37" t="n"/>
-      <c r="C5" s="37" t="n"/>
-      <c r="D5" s="40" t="n"/>
+      <c r="B5" s="114" t="n"/>
+      <c r="C5" s="115" t="n"/>
+      <c r="D5" s="116" t="n"/>
       <c r="E5" s="6" t="n"/>
       <c r="F5" s="6" t="n"/>
       <c r="G5" s="7" t="n"/>
@@ -2339,24 +2306,22 @@
       <c r="AG5" s="6" t="n"/>
       <c r="AH5" s="26" t="n"/>
       <c r="AI5" s="23" t="n"/>
-      <c r="AK5" s="113" t="inlineStr">
+      <c r="AK5" s="111" t="inlineStr">
         <is>
           <t>YEAR</t>
         </is>
       </c>
-      <c r="AL5" s="114" t="n">
+      <c r="AL5" s="112" t="n">
         <v>2026</v>
       </c>
-      <c r="AM5" s="146" t="n"/>
-      <c r="AN5" s="147" t="n"/>
     </row>
     <row r="6" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="113" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="37" t="n"/>
-      <c r="C6" s="37" t="n"/>
-      <c r="D6" s="37" t="n"/>
+      <c r="B6" s="114" t="n"/>
+      <c r="C6" s="115" t="n"/>
+      <c r="D6" s="114" t="n"/>
       <c r="E6" s="6" t="n"/>
       <c r="F6" s="6" t="n"/>
       <c r="G6" s="7" t="n"/>
@@ -2388,19 +2353,19 @@
       <c r="AG6" s="6" t="n"/>
       <c r="AH6" s="26" t="n"/>
       <c r="AI6" s="23" t="n"/>
-      <c r="AK6" s="115" t="inlineStr">
+      <c r="AK6" s="117" t="inlineStr">
         <is>
           <t>type JUL / JULY / 7</t>
         </is>
       </c>
     </row>
     <row r="7" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A7" s="5" t="n">
+      <c r="A7" s="113" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="36" t="n"/>
-      <c r="C7" s="37" t="n"/>
-      <c r="D7" s="37" t="n"/>
+      <c r="B7" s="114" t="n"/>
+      <c r="C7" s="115" t="n"/>
+      <c r="D7" s="114" t="n"/>
       <c r="E7" s="6" t="n"/>
       <c r="F7" s="6" t="n"/>
       <c r="G7" s="7" t="n"/>
@@ -2434,12 +2399,12 @@
       <c r="AI7" s="23" t="n"/>
     </row>
     <row r="8" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A8" s="5" t="n">
+      <c r="A8" s="113" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="37" t="n"/>
-      <c r="C8" s="37" t="n"/>
-      <c r="D8" s="37" t="n"/>
+      <c r="B8" s="114" t="n"/>
+      <c r="C8" s="115" t="n"/>
+      <c r="D8" s="114" t="n"/>
       <c r="E8" s="6" t="n"/>
       <c r="F8" s="6" t="n"/>
       <c r="G8" s="7" t="n"/>
@@ -2473,12 +2438,12 @@
       <c r="AI8" s="23" t="n"/>
     </row>
     <row r="9" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A9" s="5" t="n">
+      <c r="A9" s="113" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="36" t="n"/>
-      <c r="C9" s="36" t="n"/>
-      <c r="D9" s="37" t="n"/>
+      <c r="B9" s="114" t="n"/>
+      <c r="C9" s="115" t="n"/>
+      <c r="D9" s="114" t="n"/>
       <c r="E9" s="6" t="n"/>
       <c r="F9" s="6" t="n"/>
       <c r="G9" s="7" t="n"/>
@@ -2512,12 +2477,12 @@
       <c r="AI9" s="23" t="n"/>
     </row>
     <row r="10" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A10" s="10" t="n">
+      <c r="A10" s="118" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="37" t="n"/>
-      <c r="C10" s="37" t="n"/>
-      <c r="D10" s="37" t="n"/>
+      <c r="B10" s="114" t="n"/>
+      <c r="C10" s="115" t="n"/>
+      <c r="D10" s="114" t="n"/>
       <c r="E10" s="6" t="n"/>
       <c r="F10" s="6" t="n"/>
       <c r="G10" s="7" t="n"/>
@@ -2551,12 +2516,12 @@
       <c r="AI10" s="23" t="n"/>
     </row>
     <row r="11" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A11" s="10" t="n">
+      <c r="A11" s="118" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="37" t="n"/>
-      <c r="C11" s="37" t="n"/>
-      <c r="D11" s="37" t="n"/>
+      <c r="B11" s="114" t="n"/>
+      <c r="C11" s="115" t="n"/>
+      <c r="D11" s="114" t="n"/>
       <c r="E11" s="6" t="n"/>
       <c r="F11" s="6" t="n"/>
       <c r="G11" s="7" t="n"/>
@@ -2590,12 +2555,12 @@
       <c r="AI11" s="23" t="n"/>
     </row>
     <row r="12" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A12" s="10" t="n">
+      <c r="A12" s="118" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="37" t="n"/>
-      <c r="C12" s="37" t="n"/>
-      <c r="D12" s="37" t="n"/>
+      <c r="B12" s="114" t="n"/>
+      <c r="C12" s="115" t="n"/>
+      <c r="D12" s="114" t="n"/>
       <c r="E12" s="6" t="n"/>
       <c r="F12" s="6" t="n"/>
       <c r="G12" s="7" t="n"/>
@@ -2629,12 +2594,12 @@
       <c r="AI12" s="23" t="n"/>
     </row>
     <row r="13" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A13" s="10" t="n">
+      <c r="A13" s="118" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="37" t="n"/>
-      <c r="C13" s="37" t="n"/>
-      <c r="D13" s="37" t="n"/>
+      <c r="B13" s="114" t="n"/>
+      <c r="C13" s="115" t="n"/>
+      <c r="D13" s="114" t="n"/>
       <c r="E13" s="6" t="n"/>
       <c r="F13" s="6" t="n"/>
       <c r="G13" s="7" t="n"/>
@@ -2668,12 +2633,12 @@
       <c r="AI13" s="23" t="n"/>
     </row>
     <row r="14" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A14" s="10" t="n">
+      <c r="A14" s="118" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="37" t="n"/>
-      <c r="C14" s="37" t="n"/>
-      <c r="D14" s="37" t="n"/>
+      <c r="B14" s="114" t="n"/>
+      <c r="C14" s="115" t="n"/>
+      <c r="D14" s="114" t="n"/>
       <c r="E14" s="11" t="n"/>
       <c r="F14" s="11" t="n"/>
       <c r="G14" s="11" t="n"/>
@@ -2707,12 +2672,12 @@
       <c r="AI14" s="23" t="n"/>
     </row>
     <row r="15" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A15" s="10" t="n">
+      <c r="A15" s="118" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="37" t="n"/>
-      <c r="C15" s="37" t="n"/>
-      <c r="D15" s="37" t="n"/>
+      <c r="B15" s="114" t="n"/>
+      <c r="C15" s="115" t="n"/>
+      <c r="D15" s="114" t="n"/>
       <c r="E15" s="6" t="n"/>
       <c r="F15" s="6" t="n"/>
       <c r="G15" s="7" t="n"/>
@@ -2746,12 +2711,12 @@
       <c r="AI15" s="23" t="n"/>
     </row>
     <row r="16" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A16" s="8" t="n">
+      <c r="A16" s="113" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="36" t="n"/>
-      <c r="C16" s="36" t="n"/>
-      <c r="D16" s="39" t="n"/>
+      <c r="B16" s="114" t="n"/>
+      <c r="C16" s="115" t="n"/>
+      <c r="D16" s="119" t="n"/>
       <c r="E16" s="6" t="n"/>
       <c r="F16" s="6" t="n"/>
       <c r="G16" s="7" t="n"/>
@@ -2785,12 +2750,12 @@
       <c r="AI16" s="23" t="n"/>
     </row>
     <row r="17" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A17" s="8" t="n">
+      <c r="A17" s="113" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="36" t="n"/>
-      <c r="C17" s="36" t="n"/>
-      <c r="D17" s="37" t="n"/>
+      <c r="B17" s="114" t="n"/>
+      <c r="C17" s="115" t="n"/>
+      <c r="D17" s="114" t="n"/>
       <c r="E17" s="6" t="n"/>
       <c r="F17" s="6" t="n"/>
       <c r="G17" s="7" t="n"/>
@@ -2824,12 +2789,12 @@
       <c r="AI17" s="23" t="n"/>
     </row>
     <row r="18" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A18" s="8" t="n">
+      <c r="A18" s="113" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="36" t="n"/>
-      <c r="C18" s="36" t="n"/>
-      <c r="D18" s="39" t="n"/>
+      <c r="B18" s="114" t="n"/>
+      <c r="C18" s="115" t="n"/>
+      <c r="D18" s="119" t="n"/>
       <c r="E18" s="6" t="n"/>
       <c r="F18" s="6" t="n"/>
       <c r="G18" s="7" t="n"/>
@@ -2863,12 +2828,12 @@
       <c r="AI18" s="23" t="n"/>
     </row>
     <row r="19" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A19" s="8" t="n">
+      <c r="A19" s="113" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="36" t="n"/>
-      <c r="C19" s="36" t="n"/>
-      <c r="D19" s="37" t="n"/>
+      <c r="B19" s="114" t="n"/>
+      <c r="C19" s="115" t="n"/>
+      <c r="D19" s="114" t="n"/>
       <c r="E19" s="6" t="n"/>
       <c r="F19" s="6" t="n"/>
       <c r="G19" s="7" t="n"/>
@@ -2902,12 +2867,12 @@
       <c r="AI19" s="23" t="n"/>
     </row>
     <row r="20" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A20" s="8" t="n">
+      <c r="A20" s="113" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="36" t="n"/>
-      <c r="C20" s="36" t="n"/>
-      <c r="D20" s="37" t="n"/>
+      <c r="B20" s="114" t="n"/>
+      <c r="C20" s="115" t="n"/>
+      <c r="D20" s="114" t="n"/>
       <c r="E20" s="27" t="n"/>
       <c r="F20" s="27" t="n"/>
       <c r="G20" s="28" t="n"/>
@@ -2962,271 +2927,271 @@
           <t>CREW 2</t>
         </is>
       </c>
-      <c r="B22" s="116" t="n"/>
-      <c r="C22" s="116" t="n"/>
-      <c r="D22" s="116" t="n"/>
-      <c r="E22" s="109">
+      <c r="B22" s="120" t="n"/>
+      <c r="C22" s="120" t="n"/>
+      <c r="D22" s="120" t="n"/>
+      <c r="E22" s="30">
         <f>IF(1&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="F22" s="109">
+      <c r="F22" s="30">
         <f>IF(2&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,2),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="G22" s="109">
+      <c r="G22" s="30">
         <f>IF(3&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,3),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="H22" s="109">
+      <c r="H22" s="30">
         <f>IF(4&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,4),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="I22" s="109">
+      <c r="I22" s="30">
         <f>IF(5&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,5),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="J22" s="109">
+      <c r="J22" s="30">
         <f>IF(6&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,6),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="K22" s="109">
+      <c r="K22" s="30">
         <f>IF(7&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,7),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="L22" s="109">
+      <c r="L22" s="30">
         <f>IF(8&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,8),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="M22" s="109">
+      <c r="M22" s="30">
         <f>IF(9&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,9),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="N22" s="109">
+      <c r="N22" s="30">
         <f>IF(10&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,10),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="O22" s="109">
+      <c r="O22" s="30">
         <f>IF(11&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,11),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="P22" s="109">
+      <c r="P22" s="30">
         <f>IF(12&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,12),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="Q22" s="109">
+      <c r="Q22" s="30">
         <f>IF(13&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,13),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="R22" s="109">
+      <c r="R22" s="30">
         <f>IF(14&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,14),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="S22" s="109">
+      <c r="S22" s="30">
         <f>IF(15&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,15),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="T22" s="109">
+      <c r="T22" s="30">
         <f>IF(16&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,16),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="U22" s="109">
+      <c r="U22" s="30">
         <f>IF(17&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,17),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="V22" s="109">
+      <c r="V22" s="30">
         <f>IF(18&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,18),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="W22" s="109">
+      <c r="W22" s="30">
         <f>IF(19&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,19),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="X22" s="109">
+      <c r="X22" s="30">
         <f>IF(20&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,20),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="Y22" s="109">
+      <c r="Y22" s="30">
         <f>IF(21&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,21),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="Z22" s="109">
+      <c r="Z22" s="30">
         <f>IF(22&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,22),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="AA22" s="109">
+      <c r="AA22" s="30">
         <f>IF(23&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,23),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="AB22" s="109">
+      <c r="AB22" s="30">
         <f>IF(24&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,24),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="AC22" s="109">
+      <c r="AC22" s="30">
         <f>IF(25&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,25),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="AD22" s="109">
+      <c r="AD22" s="30">
         <f>IF(26&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,26),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="AE22" s="109">
+      <c r="AE22" s="30">
         <f>IF(27&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,27),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="AF22" s="109">
+      <c r="AF22" s="30">
         <f>IF(28&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,28),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="AG22" s="109">
+      <c r="AG22" s="30">
         <f>IF(29&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,29),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="AH22" s="109">
+      <c r="AH22" s="30">
         <f>IF(30&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,30),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="AI22" s="109">
+      <c r="AI22" s="31">
         <f>IF(31&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,31),"ddd"),"")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A23" s="117" t="n"/>
-      <c r="B23" s="118" t="n"/>
-      <c r="C23" s="118" t="n"/>
-      <c r="D23" s="118" t="n"/>
-      <c r="E23" s="112">
+      <c r="A23" s="121" t="n"/>
+      <c r="B23" s="122" t="n"/>
+      <c r="C23" s="122" t="n"/>
+      <c r="D23" s="122" t="n"/>
+      <c r="E23" s="2">
         <f>IF(1&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),1,"")</f>
         <v/>
       </c>
-      <c r="F23" s="112">
+      <c r="F23" s="2">
         <f>IF(2&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),2,"")</f>
         <v/>
       </c>
-      <c r="G23" s="112">
+      <c r="G23" s="2">
         <f>IF(3&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),3,"")</f>
         <v/>
       </c>
-      <c r="H23" s="112">
+      <c r="H23" s="2">
         <f>IF(4&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),4,"")</f>
         <v/>
       </c>
-      <c r="I23" s="112">
+      <c r="I23" s="3">
         <f>IF(5&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),5,"")</f>
         <v/>
       </c>
-      <c r="J23" s="112">
+      <c r="J23" s="4">
         <f>IF(6&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),6,"")</f>
         <v/>
       </c>
-      <c r="K23" s="112">
+      <c r="K23" s="4">
         <f>IF(7&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),7,"")</f>
         <v/>
       </c>
-      <c r="L23" s="112">
+      <c r="L23" s="3">
         <f>IF(8&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),8,"")</f>
         <v/>
       </c>
-      <c r="M23" s="112">
+      <c r="M23" s="4">
         <f>IF(9&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),9,"")</f>
         <v/>
       </c>
-      <c r="N23" s="112">
+      <c r="N23" s="2">
         <f>IF(10&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),10,"")</f>
         <v/>
       </c>
-      <c r="O23" s="112">
+      <c r="O23" s="2">
         <f>IF(11&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),11,"")</f>
         <v/>
       </c>
-      <c r="P23" s="112">
+      <c r="P23" s="2">
         <f>IF(12&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),12,"")</f>
         <v/>
       </c>
-      <c r="Q23" s="112">
+      <c r="Q23" s="2">
         <f>IF(13&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),13,"")</f>
         <v/>
       </c>
-      <c r="R23" s="112">
+      <c r="R23" s="2">
         <f>IF(14&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),14,"")</f>
         <v/>
       </c>
-      <c r="S23" s="112">
+      <c r="S23" s="2">
         <f>IF(15&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),15,"")</f>
         <v/>
       </c>
-      <c r="T23" s="112">
+      <c r="T23" s="2">
         <f>IF(16&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),16,"")</f>
         <v/>
       </c>
-      <c r="U23" s="112">
+      <c r="U23" s="2">
         <f>IF(17&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),17,"")</f>
         <v/>
       </c>
-      <c r="V23" s="112">
+      <c r="V23" s="2">
         <f>IF(18&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),18,"")</f>
         <v/>
       </c>
-      <c r="W23" s="112">
+      <c r="W23" s="2">
         <f>IF(19&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),19,"")</f>
         <v/>
       </c>
-      <c r="X23" s="112">
+      <c r="X23" s="2">
         <f>IF(20&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),20,"")</f>
         <v/>
       </c>
-      <c r="Y23" s="112">
+      <c r="Y23" s="2">
         <f>IF(21&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),21,"")</f>
         <v/>
       </c>
-      <c r="Z23" s="112">
+      <c r="Z23" s="2">
         <f>IF(22&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),22,"")</f>
         <v/>
       </c>
-      <c r="AA23" s="112">
+      <c r="AA23" s="2">
         <f>IF(23&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),23,"")</f>
         <v/>
       </c>
-      <c r="AB23" s="112">
+      <c r="AB23" s="2">
         <f>IF(24&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),24,"")</f>
         <v/>
       </c>
-      <c r="AC23" s="112">
+      <c r="AC23" s="2">
         <f>IF(25&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),25,"")</f>
         <v/>
       </c>
-      <c r="AD23" s="112">
+      <c r="AD23" s="2">
         <f>IF(26&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),26,"")</f>
         <v/>
       </c>
-      <c r="AE23" s="112">
+      <c r="AE23" s="2">
         <f>IF(27&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),27,"")</f>
         <v/>
       </c>
-      <c r="AF23" s="112">
+      <c r="AF23" s="2">
         <f>IF(28&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),28,"")</f>
         <v/>
       </c>
-      <c r="AG23" s="112">
+      <c r="AG23" s="2">
         <f>IF(29&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),29,"")</f>
         <v/>
       </c>
-      <c r="AH23" s="112">
+      <c r="AH23" s="2">
         <f>IF(30&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),30,"")</f>
         <v/>
       </c>
-      <c r="AI23" s="112">
+      <c r="AI23" s="25">
         <f>IF(31&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),31,"")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A24" s="5" t="n">
+      <c r="A24" s="113" t="n">
         <v>1</v>
       </c>
-      <c r="B24" s="37" t="n"/>
-      <c r="C24" s="37" t="n"/>
-      <c r="D24" s="37" t="n"/>
+      <c r="B24" s="114" t="n"/>
+      <c r="C24" s="115" t="n"/>
+      <c r="D24" s="114" t="n"/>
       <c r="E24" s="6" t="n"/>
       <c r="F24" s="6" t="n"/>
       <c r="G24" s="6" t="n"/>
@@ -3260,12 +3225,12 @@
       <c r="AI24" s="26" t="n"/>
     </row>
     <row r="25" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A25" s="5" t="n">
+      <c r="A25" s="113" t="n">
         <v>2</v>
       </c>
-      <c r="B25" s="37" t="n"/>
-      <c r="C25" s="37" t="n"/>
-      <c r="D25" s="37" t="n"/>
+      <c r="B25" s="114" t="n"/>
+      <c r="C25" s="115" t="n"/>
+      <c r="D25" s="114" t="n"/>
       <c r="E25" s="6" t="n"/>
       <c r="F25" s="6" t="n"/>
       <c r="G25" s="6" t="n"/>
@@ -3299,12 +3264,12 @@
       <c r="AI25" s="26" t="n"/>
     </row>
     <row r="26" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A26" s="5" t="n">
+      <c r="A26" s="113" t="n">
         <v>3</v>
       </c>
-      <c r="B26" s="36" t="n"/>
-      <c r="C26" s="36" t="n"/>
-      <c r="D26" s="40" t="n"/>
+      <c r="B26" s="114" t="n"/>
+      <c r="C26" s="115" t="n"/>
+      <c r="D26" s="116" t="n"/>
       <c r="E26" s="6" t="n"/>
       <c r="F26" s="6" t="n"/>
       <c r="G26" s="6" t="n"/>
@@ -3338,12 +3303,12 @@
       <c r="AI26" s="26" t="n"/>
     </row>
     <row r="27" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A27" s="5" t="n">
+      <c r="A27" s="113" t="n">
         <v>4</v>
       </c>
-      <c r="B27" s="36" t="n"/>
-      <c r="C27" s="36" t="n"/>
-      <c r="D27" s="40" t="n"/>
+      <c r="B27" s="114" t="n"/>
+      <c r="C27" s="115" t="n"/>
+      <c r="D27" s="116" t="n"/>
       <c r="E27" s="6" t="n"/>
       <c r="F27" s="6" t="n"/>
       <c r="G27" s="6" t="n"/>
@@ -3377,12 +3342,12 @@
       <c r="AI27" s="26" t="n"/>
     </row>
     <row r="28" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A28" s="5" t="n">
+      <c r="A28" s="113" t="n">
         <v>5</v>
       </c>
-      <c r="B28" s="36" t="n"/>
-      <c r="C28" s="36" t="n"/>
-      <c r="D28" s="40" t="n"/>
+      <c r="B28" s="114" t="n"/>
+      <c r="C28" s="115" t="n"/>
+      <c r="D28" s="116" t="n"/>
       <c r="E28" s="6" t="n"/>
       <c r="F28" s="6" t="n"/>
       <c r="G28" s="6" t="n"/>
@@ -3416,12 +3381,12 @@
       <c r="AI28" s="26" t="n"/>
     </row>
     <row r="29" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A29" s="10" t="n">
+      <c r="A29" s="118" t="n">
         <v>6</v>
       </c>
-      <c r="B29" s="37" t="n"/>
-      <c r="C29" s="37" t="n"/>
-      <c r="D29" s="37" t="n"/>
+      <c r="B29" s="114" t="n"/>
+      <c r="C29" s="115" t="n"/>
+      <c r="D29" s="114" t="n"/>
       <c r="E29" s="6" t="n"/>
       <c r="F29" s="6" t="n"/>
       <c r="G29" s="6" t="n"/>
@@ -3455,12 +3420,12 @@
       <c r="AI29" s="26" t="n"/>
     </row>
     <row r="30" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A30" s="10" t="n">
+      <c r="A30" s="118" t="n">
         <v>7</v>
       </c>
-      <c r="B30" s="37" t="n"/>
-      <c r="C30" s="37" t="n"/>
-      <c r="D30" s="37" t="n"/>
+      <c r="B30" s="114" t="n"/>
+      <c r="C30" s="115" t="n"/>
+      <c r="D30" s="114" t="n"/>
       <c r="E30" s="6" t="n"/>
       <c r="F30" s="6" t="n"/>
       <c r="G30" s="6" t="n"/>
@@ -3494,12 +3459,12 @@
       <c r="AI30" s="26" t="n"/>
     </row>
     <row r="31" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A31" s="10" t="n">
+      <c r="A31" s="118" t="n">
         <v>8</v>
       </c>
-      <c r="B31" s="37" t="n"/>
-      <c r="C31" s="37" t="n"/>
-      <c r="D31" s="37" t="n"/>
+      <c r="B31" s="114" t="n"/>
+      <c r="C31" s="115" t="n"/>
+      <c r="D31" s="114" t="n"/>
       <c r="E31" s="6" t="n"/>
       <c r="F31" s="6" t="n"/>
       <c r="G31" s="6" t="n"/>
@@ -3533,12 +3498,12 @@
       <c r="AI31" s="26" t="n"/>
     </row>
     <row r="32" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A32" s="10" t="n">
+      <c r="A32" s="118" t="n">
         <v>9</v>
       </c>
-      <c r="B32" s="37" t="n"/>
-      <c r="C32" s="37" t="n"/>
-      <c r="D32" s="37" t="n"/>
+      <c r="B32" s="114" t="n"/>
+      <c r="C32" s="115" t="n"/>
+      <c r="D32" s="114" t="n"/>
       <c r="E32" s="6" t="n"/>
       <c r="F32" s="6" t="n"/>
       <c r="G32" s="6" t="n"/>
@@ -3572,12 +3537,12 @@
       <c r="AI32" s="26" t="n"/>
     </row>
     <row r="33" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A33" s="10" t="n">
+      <c r="A33" s="118" t="n">
         <v>10</v>
       </c>
-      <c r="B33" s="37" t="n"/>
-      <c r="C33" s="37" t="n"/>
-      <c r="D33" s="37" t="n"/>
+      <c r="B33" s="114" t="n"/>
+      <c r="C33" s="115" t="n"/>
+      <c r="D33" s="114" t="n"/>
       <c r="E33" s="6" t="n"/>
       <c r="F33" s="6" t="n"/>
       <c r="G33" s="6" t="n"/>
@@ -3611,12 +3576,12 @@
       <c r="AI33" s="26" t="n"/>
     </row>
     <row r="34" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A34" s="10" t="n">
+      <c r="A34" s="118" t="n">
         <v>11</v>
       </c>
-      <c r="B34" s="37" t="n"/>
-      <c r="C34" s="37" t="n"/>
-      <c r="D34" s="37" t="n"/>
+      <c r="B34" s="114" t="n"/>
+      <c r="C34" s="115" t="n"/>
+      <c r="D34" s="114" t="n"/>
       <c r="E34" s="6" t="n"/>
       <c r="F34" s="6" t="n"/>
       <c r="G34" s="6" t="n"/>
@@ -3650,12 +3615,12 @@
       <c r="AI34" s="26" t="n"/>
     </row>
     <row r="35" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A35" s="10" t="n">
+      <c r="A35" s="118" t="n">
         <v>12</v>
       </c>
-      <c r="B35" s="37" t="n"/>
-      <c r="C35" s="37" t="n"/>
-      <c r="D35" s="37" t="n"/>
+      <c r="B35" s="114" t="n"/>
+      <c r="C35" s="115" t="n"/>
+      <c r="D35" s="114" t="n"/>
       <c r="E35" s="6" t="n"/>
       <c r="F35" s="6" t="n"/>
       <c r="G35" s="6" t="n"/>
@@ -3689,12 +3654,12 @@
       <c r="AI35" s="26" t="n"/>
     </row>
     <row r="36" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A36" s="10" t="n">
+      <c r="A36" s="118" t="n">
         <v>13</v>
       </c>
-      <c r="B36" s="37" t="n"/>
-      <c r="C36" s="37" t="n"/>
-      <c r="D36" s="37" t="n"/>
+      <c r="B36" s="114" t="n"/>
+      <c r="C36" s="115" t="n"/>
+      <c r="D36" s="114" t="n"/>
       <c r="E36" s="6" t="n"/>
       <c r="F36" s="6" t="n"/>
       <c r="G36" s="6" t="n"/>
@@ -3728,12 +3693,12 @@
       <c r="AI36" s="26" t="n"/>
     </row>
     <row r="37" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A37" s="8" t="n">
+      <c r="A37" s="113" t="n">
         <v>14</v>
       </c>
-      <c r="B37" s="36" t="n"/>
-      <c r="C37" s="36" t="n"/>
-      <c r="D37" s="36" t="n"/>
+      <c r="B37" s="114" t="n"/>
+      <c r="C37" s="115" t="n"/>
+      <c r="D37" s="114" t="n"/>
       <c r="E37" s="6" t="n"/>
       <c r="F37" s="6" t="n"/>
       <c r="G37" s="6" t="n"/>
@@ -3767,12 +3732,12 @@
       <c r="AI37" s="26" t="n"/>
     </row>
     <row r="38" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A38" s="8" t="n">
+      <c r="A38" s="113" t="n">
         <v>15</v>
       </c>
-      <c r="B38" s="36" t="n"/>
-      <c r="C38" s="36" t="n"/>
-      <c r="D38" s="36" t="n"/>
+      <c r="B38" s="114" t="n"/>
+      <c r="C38" s="115" t="n"/>
+      <c r="D38" s="114" t="n"/>
       <c r="E38" s="6" t="n"/>
       <c r="F38" s="6" t="n"/>
       <c r="G38" s="6" t="n"/>
@@ -3806,12 +3771,12 @@
       <c r="AI38" s="26" t="n"/>
     </row>
     <row r="39" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A39" s="8" t="n">
+      <c r="A39" s="113" t="n">
         <v>16</v>
       </c>
-      <c r="B39" s="36" t="n"/>
-      <c r="C39" s="36" t="n"/>
-      <c r="D39" s="36" t="n"/>
+      <c r="B39" s="114" t="n"/>
+      <c r="C39" s="115" t="n"/>
+      <c r="D39" s="114" t="n"/>
       <c r="E39" s="6" t="n"/>
       <c r="F39" s="6" t="n"/>
       <c r="G39" s="6" t="n"/>
@@ -3845,12 +3810,12 @@
       <c r="AI39" s="26" t="n"/>
     </row>
     <row r="40" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A40" s="8" t="n">
+      <c r="A40" s="113" t="n">
         <v>17</v>
       </c>
-      <c r="B40" s="36" t="n"/>
-      <c r="C40" s="36" t="n"/>
-      <c r="D40" s="36" t="n"/>
+      <c r="B40" s="114" t="n"/>
+      <c r="C40" s="115" t="n"/>
+      <c r="D40" s="114" t="n"/>
       <c r="E40" s="27" t="n"/>
       <c r="F40" s="27" t="n"/>
       <c r="G40" s="27" t="n"/>
@@ -3885,276 +3850,276 @@
     </row>
     <row r="41" ht="15" customHeight="1" thickBot="1"/>
     <row r="42" ht="15" customHeight="1" thickBot="1">
-      <c r="A42" s="119" t="inlineStr">
+      <c r="A42" s="123" t="inlineStr">
         <is>
           <t>SPECIAL SHIFTING</t>
         </is>
       </c>
-      <c r="B42" s="116" t="n"/>
-      <c r="C42" s="116" t="n"/>
-      <c r="D42" s="120" t="n"/>
-      <c r="E42" s="109">
+      <c r="B42" s="120" t="n"/>
+      <c r="C42" s="120" t="n"/>
+      <c r="D42" s="124" t="n"/>
+      <c r="E42" s="1">
         <f>IF(1&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="F42" s="109">
+      <c r="F42" s="1">
         <f>IF(2&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,2),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="G42" s="109">
+      <c r="G42" s="1">
         <f>IF(3&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,3),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="H42" s="109">
+      <c r="H42" s="1">
         <f>IF(4&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,4),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="I42" s="109">
+      <c r="I42" s="1">
         <f>IF(5&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,5),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="J42" s="109">
+      <c r="J42" s="1">
         <f>IF(6&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,6),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="K42" s="109">
+      <c r="K42" s="1">
         <f>IF(7&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,7),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="L42" s="109">
+      <c r="L42" s="1">
         <f>IF(8&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,8),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="M42" s="109">
+      <c r="M42" s="1">
         <f>IF(9&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,9),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="N42" s="109">
+      <c r="N42" s="1">
         <f>IF(10&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,10),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="O42" s="109">
+      <c r="O42" s="1">
         <f>IF(11&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,11),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="P42" s="109">
+      <c r="P42" s="1">
         <f>IF(12&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,12),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="Q42" s="109">
+      <c r="Q42" s="1">
         <f>IF(13&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,13),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="R42" s="109">
+      <c r="R42" s="1">
         <f>IF(14&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,14),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="S42" s="109">
+      <c r="S42" s="1">
         <f>IF(15&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,15),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="T42" s="109">
+      <c r="T42" s="1">
         <f>IF(16&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,16),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="U42" s="109">
+      <c r="U42" s="1">
         <f>IF(17&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,17),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="V42" s="109">
+      <c r="V42" s="1">
         <f>IF(18&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,18),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="W42" s="109">
+      <c r="W42" s="1">
         <f>IF(19&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,19),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="X42" s="109">
+      <c r="X42" s="1">
         <f>IF(20&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,20),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="Y42" s="109">
+      <c r="Y42" s="1">
         <f>IF(21&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,21),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="Z42" s="109">
+      <c r="Z42" s="1">
         <f>IF(22&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,22),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="AA42" s="109">
+      <c r="AA42" s="1">
         <f>IF(23&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,23),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="AB42" s="109">
+      <c r="AB42" s="1">
         <f>IF(24&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,24),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="AC42" s="109">
+      <c r="AC42" s="1">
         <f>IF(25&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,25),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="AD42" s="109">
+      <c r="AD42" s="1">
         <f>IF(26&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,26),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="AE42" s="109">
+      <c r="AE42" s="1">
         <f>IF(27&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,27),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="AF42" s="109">
+      <c r="AF42" s="1">
         <f>IF(28&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,28),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="AG42" s="109">
+      <c r="AG42" s="1">
         <f>IF(29&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,29),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="AH42" s="109">
+      <c r="AH42" s="1">
         <f>IF(30&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,30),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="AI42" s="109">
+      <c r="AI42" s="1">
         <f>IF(31&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,31),"ddd"),"")</f>
         <v/>
       </c>
     </row>
     <row r="43" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A43" s="117" t="n"/>
-      <c r="B43" s="118" t="n"/>
-      <c r="C43" s="118" t="n"/>
-      <c r="D43" s="121" t="n"/>
-      <c r="E43" s="112">
+      <c r="A43" s="121" t="n"/>
+      <c r="B43" s="122" t="n"/>
+      <c r="C43" s="122" t="n"/>
+      <c r="D43" s="125" t="n"/>
+      <c r="E43" s="2">
         <f>IF(1&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),1,"")</f>
         <v/>
       </c>
-      <c r="F43" s="112">
+      <c r="F43" s="2">
         <f>IF(2&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),2,"")</f>
         <v/>
       </c>
-      <c r="G43" s="112">
+      <c r="G43" s="2">
         <f>IF(3&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),3,"")</f>
         <v/>
       </c>
-      <c r="H43" s="112">
+      <c r="H43" s="2">
         <f>IF(4&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),4,"")</f>
         <v/>
       </c>
-      <c r="I43" s="112">
+      <c r="I43" s="3">
         <f>IF(5&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),5,"")</f>
         <v/>
       </c>
-      <c r="J43" s="112">
+      <c r="J43" s="4">
         <f>IF(6&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),6,"")</f>
         <v/>
       </c>
-      <c r="K43" s="112">
+      <c r="K43" s="4">
         <f>IF(7&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),7,"")</f>
         <v/>
       </c>
-      <c r="L43" s="112">
+      <c r="L43" s="3">
         <f>IF(8&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),8,"")</f>
         <v/>
       </c>
-      <c r="M43" s="112">
+      <c r="M43" s="4">
         <f>IF(9&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),9,"")</f>
         <v/>
       </c>
-      <c r="N43" s="112">
+      <c r="N43" s="2">
         <f>IF(10&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),10,"")</f>
         <v/>
       </c>
-      <c r="O43" s="112">
+      <c r="O43" s="2">
         <f>IF(11&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),11,"")</f>
         <v/>
       </c>
-      <c r="P43" s="112">
+      <c r="P43" s="2">
         <f>IF(12&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),12,"")</f>
         <v/>
       </c>
-      <c r="Q43" s="112">
+      <c r="Q43" s="2">
         <f>IF(13&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),13,"")</f>
         <v/>
       </c>
-      <c r="R43" s="112">
+      <c r="R43" s="2">
         <f>IF(14&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),14,"")</f>
         <v/>
       </c>
-      <c r="S43" s="112">
+      <c r="S43" s="2">
         <f>IF(15&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),15,"")</f>
         <v/>
       </c>
-      <c r="T43" s="112">
+      <c r="T43" s="2">
         <f>IF(16&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),16,"")</f>
         <v/>
       </c>
-      <c r="U43" s="112">
+      <c r="U43" s="2">
         <f>IF(17&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),17,"")</f>
         <v/>
       </c>
-      <c r="V43" s="112">
+      <c r="V43" s="2">
         <f>IF(18&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),18,"")</f>
         <v/>
       </c>
-      <c r="W43" s="112">
+      <c r="W43" s="2">
         <f>IF(19&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),19,"")</f>
         <v/>
       </c>
-      <c r="X43" s="112">
+      <c r="X43" s="2">
         <f>IF(20&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),20,"")</f>
         <v/>
       </c>
-      <c r="Y43" s="112">
+      <c r="Y43" s="2">
         <f>IF(21&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),21,"")</f>
         <v/>
       </c>
-      <c r="Z43" s="112">
+      <c r="Z43" s="2">
         <f>IF(22&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),22,"")</f>
         <v/>
       </c>
-      <c r="AA43" s="112">
+      <c r="AA43" s="2">
         <f>IF(23&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),23,"")</f>
         <v/>
       </c>
-      <c r="AB43" s="112">
+      <c r="AB43" s="2">
         <f>IF(24&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),24,"")</f>
         <v/>
       </c>
-      <c r="AC43" s="112">
+      <c r="AC43" s="2">
         <f>IF(25&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),25,"")</f>
         <v/>
       </c>
-      <c r="AD43" s="112">
+      <c r="AD43" s="2">
         <f>IF(26&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),26,"")</f>
         <v/>
       </c>
-      <c r="AE43" s="112">
+      <c r="AE43" s="2">
         <f>IF(27&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),27,"")</f>
         <v/>
       </c>
-      <c r="AF43" s="112">
+      <c r="AF43" s="2">
         <f>IF(28&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),28,"")</f>
         <v/>
       </c>
-      <c r="AG43" s="112">
+      <c r="AG43" s="2">
         <f>IF(29&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),29,"")</f>
         <v/>
       </c>
-      <c r="AH43" s="112">
+      <c r="AH43" s="2">
         <f>IF(30&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),30,"")</f>
         <v/>
       </c>
-      <c r="AI43" s="112">
+      <c r="AI43" s="2">
         <f>IF(31&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),31,"")</f>
         <v/>
       </c>
     </row>
     <row r="44" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A44" s="5" t="n">
+      <c r="A44" s="113" t="n">
         <v>1</v>
       </c>
-      <c r="B44" s="37" t="n"/>
-      <c r="C44" s="37" t="n"/>
-      <c r="D44" s="37" t="n"/>
+      <c r="B44" s="114" t="n"/>
+      <c r="C44" s="115" t="n"/>
+      <c r="D44" s="114" t="n"/>
       <c r="E44" s="6" t="n"/>
       <c r="F44" s="6" t="n"/>
       <c r="G44" s="6" t="n"/>
@@ -4188,10 +4153,12 @@
       <c r="AI44" s="29" t="n"/>
     </row>
     <row r="45" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A45" s="12" t="n"/>
-      <c r="B45" s="13" t="n"/>
-      <c r="C45" s="13" t="n"/>
-      <c r="D45" s="13" t="n"/>
+      <c r="A45" s="126" t="n">
+        <v>2</v>
+      </c>
+      <c r="B45" s="127" t="n"/>
+      <c r="C45" s="128" t="n"/>
+      <c r="D45" s="127" t="n"/>
       <c r="E45" s="14" t="n"/>
       <c r="F45" s="14" t="n"/>
       <c r="G45" s="14" t="n"/>
@@ -4205,276 +4172,276 @@
       <c r="O45" s="14" t="n"/>
     </row>
     <row r="46" ht="15" customHeight="1" thickBot="1">
-      <c r="A46" s="119" t="inlineStr">
+      <c r="A46" s="123" t="inlineStr">
         <is>
           <t>TRANSFERRED-IN MANPOWER</t>
         </is>
       </c>
-      <c r="B46" s="116" t="n"/>
-      <c r="C46" s="116" t="n"/>
-      <c r="D46" s="120" t="n"/>
-      <c r="E46" s="109">
+      <c r="B46" s="120" t="n"/>
+      <c r="C46" s="120" t="n"/>
+      <c r="D46" s="124" t="n"/>
+      <c r="E46" s="1">
         <f>IF(1&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="F46" s="109">
+      <c r="F46" s="1">
         <f>IF(2&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,2),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="G46" s="109">
+      <c r="G46" s="1">
         <f>IF(3&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,3),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="H46" s="109">
+      <c r="H46" s="1">
         <f>IF(4&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,4),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="I46" s="109">
+      <c r="I46" s="1">
         <f>IF(5&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,5),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="J46" s="109">
+      <c r="J46" s="1">
         <f>IF(6&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,6),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="K46" s="109">
+      <c r="K46" s="1">
         <f>IF(7&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,7),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="L46" s="109">
+      <c r="L46" s="1">
         <f>IF(8&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,8),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="M46" s="109">
+      <c r="M46" s="1">
         <f>IF(9&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,9),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="N46" s="109">
+      <c r="N46" s="1">
         <f>IF(10&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,10),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="O46" s="109">
+      <c r="O46" s="1">
         <f>IF(11&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,11),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="P46" s="109">
+      <c r="P46" s="1">
         <f>IF(12&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,12),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="Q46" s="109">
+      <c r="Q46" s="1">
         <f>IF(13&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,13),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="R46" s="109">
+      <c r="R46" s="1">
         <f>IF(14&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,14),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="S46" s="109">
+      <c r="S46" s="1">
         <f>IF(15&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,15),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="T46" s="109">
+      <c r="T46" s="1">
         <f>IF(16&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,16),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="U46" s="109">
+      <c r="U46" s="1">
         <f>IF(17&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,17),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="V46" s="109">
+      <c r="V46" s="1">
         <f>IF(18&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,18),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="W46" s="109">
+      <c r="W46" s="1">
         <f>IF(19&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,19),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="X46" s="109">
+      <c r="X46" s="1">
         <f>IF(20&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,20),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="Y46" s="109">
+      <c r="Y46" s="1">
         <f>IF(21&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,21),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="Z46" s="109">
+      <c r="Z46" s="1">
         <f>IF(22&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,22),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="AA46" s="109">
+      <c r="AA46" s="1">
         <f>IF(23&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,23),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="AB46" s="109">
+      <c r="AB46" s="1">
         <f>IF(24&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,24),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="AC46" s="109">
+      <c r="AC46" s="1">
         <f>IF(25&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,25),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="AD46" s="109">
+      <c r="AD46" s="1">
         <f>IF(26&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,26),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="AE46" s="109">
+      <c r="AE46" s="1">
         <f>IF(27&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,27),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="AF46" s="109">
+      <c r="AF46" s="1">
         <f>IF(28&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,28),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="AG46" s="109">
+      <c r="AG46" s="1">
         <f>IF(29&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,29),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="AH46" s="109">
+      <c r="AH46" s="1">
         <f>IF(30&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,30),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="AI46" s="109">
+      <c r="AI46" s="1">
         <f>IF(31&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,31),"ddd"),"")</f>
         <v/>
       </c>
     </row>
     <row r="47" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A47" s="117" t="n"/>
-      <c r="B47" s="118" t="n"/>
-      <c r="C47" s="118" t="n"/>
-      <c r="D47" s="121" t="n"/>
-      <c r="E47" s="112">
+      <c r="A47" s="121" t="n"/>
+      <c r="B47" s="122" t="n"/>
+      <c r="C47" s="122" t="n"/>
+      <c r="D47" s="125" t="n"/>
+      <c r="E47" s="2">
         <f>IF(1&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),1,"")</f>
         <v/>
       </c>
-      <c r="F47" s="112">
+      <c r="F47" s="2">
         <f>IF(2&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),2,"")</f>
         <v/>
       </c>
-      <c r="G47" s="112">
+      <c r="G47" s="2">
         <f>IF(3&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),3,"")</f>
         <v/>
       </c>
-      <c r="H47" s="112">
+      <c r="H47" s="2">
         <f>IF(4&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),4,"")</f>
         <v/>
       </c>
-      <c r="I47" s="112">
+      <c r="I47" s="3">
         <f>IF(5&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),5,"")</f>
         <v/>
       </c>
-      <c r="J47" s="112">
+      <c r="J47" s="4">
         <f>IF(6&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),6,"")</f>
         <v/>
       </c>
-      <c r="K47" s="112">
+      <c r="K47" s="4">
         <f>IF(7&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),7,"")</f>
         <v/>
       </c>
-      <c r="L47" s="112">
+      <c r="L47" s="3">
         <f>IF(8&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),8,"")</f>
         <v/>
       </c>
-      <c r="M47" s="112">
+      <c r="M47" s="4">
         <f>IF(9&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),9,"")</f>
         <v/>
       </c>
-      <c r="N47" s="112">
+      <c r="N47" s="2">
         <f>IF(10&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),10,"")</f>
         <v/>
       </c>
-      <c r="O47" s="112">
+      <c r="O47" s="2">
         <f>IF(11&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),11,"")</f>
         <v/>
       </c>
-      <c r="P47" s="112">
+      <c r="P47" s="2">
         <f>IF(12&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),12,"")</f>
         <v/>
       </c>
-      <c r="Q47" s="112">
+      <c r="Q47" s="2">
         <f>IF(13&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),13,"")</f>
         <v/>
       </c>
-      <c r="R47" s="112">
+      <c r="R47" s="2">
         <f>IF(14&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),14,"")</f>
         <v/>
       </c>
-      <c r="S47" s="112">
+      <c r="S47" s="2">
         <f>IF(15&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),15,"")</f>
         <v/>
       </c>
-      <c r="T47" s="112">
+      <c r="T47" s="2">
         <f>IF(16&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),16,"")</f>
         <v/>
       </c>
-      <c r="U47" s="112">
+      <c r="U47" s="2">
         <f>IF(17&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),17,"")</f>
         <v/>
       </c>
-      <c r="V47" s="112">
+      <c r="V47" s="2">
         <f>IF(18&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),18,"")</f>
         <v/>
       </c>
-      <c r="W47" s="112">
+      <c r="W47" s="2">
         <f>IF(19&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),19,"")</f>
         <v/>
       </c>
-      <c r="X47" s="112">
+      <c r="X47" s="2">
         <f>IF(20&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),20,"")</f>
         <v/>
       </c>
-      <c r="Y47" s="112">
+      <c r="Y47" s="2">
         <f>IF(21&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),21,"")</f>
         <v/>
       </c>
-      <c r="Z47" s="112">
+      <c r="Z47" s="2">
         <f>IF(22&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),22,"")</f>
         <v/>
       </c>
-      <c r="AA47" s="112">
+      <c r="AA47" s="2">
         <f>IF(23&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),23,"")</f>
         <v/>
       </c>
-      <c r="AB47" s="112">
+      <c r="AB47" s="2">
         <f>IF(24&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),24,"")</f>
         <v/>
       </c>
-      <c r="AC47" s="112">
+      <c r="AC47" s="2">
         <f>IF(25&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),25,"")</f>
         <v/>
       </c>
-      <c r="AD47" s="112">
+      <c r="AD47" s="2">
         <f>IF(26&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),26,"")</f>
         <v/>
       </c>
-      <c r="AE47" s="112">
+      <c r="AE47" s="2">
         <f>IF(27&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),27,"")</f>
         <v/>
       </c>
-      <c r="AF47" s="112">
+      <c r="AF47" s="2">
         <f>IF(28&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),28,"")</f>
         <v/>
       </c>
-      <c r="AG47" s="112">
+      <c r="AG47" s="2">
         <f>IF(29&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),29,"")</f>
         <v/>
       </c>
-      <c r="AH47" s="112">
+      <c r="AH47" s="2">
         <f>IF(30&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),30,"")</f>
         <v/>
       </c>
-      <c r="AI47" s="112">
+      <c r="AI47" s="2">
         <f>IF(31&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),31,"")</f>
         <v/>
       </c>
     </row>
     <row r="48" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A48" s="9" t="n">
+      <c r="A48" s="113" t="n">
         <v>1</v>
       </c>
-      <c r="B48" s="37" t="n"/>
-      <c r="C48" s="37" t="n"/>
-      <c r="D48" s="37" t="n"/>
+      <c r="B48" s="114" t="n"/>
+      <c r="C48" s="115" t="n"/>
+      <c r="D48" s="114" t="n"/>
       <c r="E48" s="6" t="n"/>
       <c r="F48" s="6" t="n"/>
       <c r="G48" s="6" t="n"/>
@@ -4508,12 +4475,12 @@
       <c r="AI48" s="6" t="n"/>
     </row>
     <row r="49" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A49" s="9" t="n">
+      <c r="A49" s="113" t="n">
         <v>2</v>
       </c>
-      <c r="B49" s="37" t="n"/>
-      <c r="C49" s="37" t="n"/>
-      <c r="D49" s="37" t="n"/>
+      <c r="B49" s="114" t="n"/>
+      <c r="C49" s="115" t="n"/>
+      <c r="D49" s="114" t="n"/>
       <c r="E49" s="6" t="n"/>
       <c r="F49" s="6" t="n"/>
       <c r="G49" s="6" t="n"/>
@@ -4547,12 +4514,12 @@
       <c r="AI49" s="6" t="n"/>
     </row>
     <row r="50" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A50" s="9" t="n">
+      <c r="A50" s="113" t="n">
         <v>3</v>
       </c>
-      <c r="B50" s="37" t="n"/>
-      <c r="C50" s="37" t="n"/>
-      <c r="D50" s="37" t="n"/>
+      <c r="B50" s="114" t="n"/>
+      <c r="C50" s="115" t="n"/>
+      <c r="D50" s="114" t="n"/>
       <c r="E50" s="6" t="n"/>
       <c r="F50" s="6" t="n"/>
       <c r="G50" s="6" t="n"/>
@@ -4586,12 +4553,12 @@
       <c r="AI50" s="6" t="n"/>
     </row>
     <row r="51" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A51" s="9" t="n">
+      <c r="A51" s="113" t="n">
         <v>4</v>
       </c>
-      <c r="B51" s="37" t="n"/>
-      <c r="C51" s="37" t="n"/>
-      <c r="D51" s="37" t="n"/>
+      <c r="B51" s="114" t="n"/>
+      <c r="C51" s="115" t="n"/>
+      <c r="D51" s="114" t="n"/>
       <c r="E51" s="6" t="n"/>
       <c r="F51" s="6" t="n"/>
       <c r="G51" s="6" t="n"/>
@@ -4625,12 +4592,12 @@
       <c r="AI51" s="6" t="n"/>
     </row>
     <row r="52" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A52" s="9" t="n">
+      <c r="A52" s="113" t="n">
         <v>5</v>
       </c>
-      <c r="B52" s="37" t="n"/>
-      <c r="C52" s="37" t="n"/>
-      <c r="D52" s="37" t="n"/>
+      <c r="B52" s="114" t="n"/>
+      <c r="C52" s="115" t="n"/>
+      <c r="D52" s="114" t="n"/>
       <c r="E52" s="6" t="n"/>
       <c r="F52" s="6" t="n"/>
       <c r="G52" s="6" t="n"/>
@@ -4664,12 +4631,12 @@
       <c r="AI52" s="6" t="n"/>
     </row>
     <row r="53" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A53" s="9" t="n">
+      <c r="A53" s="113" t="n">
         <v>6</v>
       </c>
-      <c r="B53" s="37" t="n"/>
-      <c r="C53" s="37" t="n"/>
-      <c r="D53" s="37" t="n"/>
+      <c r="B53" s="114" t="n"/>
+      <c r="C53" s="115" t="n"/>
+      <c r="D53" s="114" t="n"/>
       <c r="E53" s="6" t="n"/>
       <c r="F53" s="6" t="n"/>
       <c r="G53" s="6" t="n"/>
@@ -4703,12 +4670,12 @@
       <c r="AI53" s="6" t="n"/>
     </row>
     <row r="54" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A54" s="9" t="n">
+      <c r="A54" s="113" t="n">
         <v>7</v>
       </c>
-      <c r="B54" s="37" t="n"/>
-      <c r="C54" s="37" t="n"/>
-      <c r="D54" s="37" t="n"/>
+      <c r="B54" s="114" t="n"/>
+      <c r="C54" s="115" t="n"/>
+      <c r="D54" s="114" t="n"/>
       <c r="E54" s="6" t="n"/>
       <c r="F54" s="6" t="n"/>
       <c r="G54" s="6" t="n"/>
@@ -4742,12 +4709,12 @@
       <c r="AI54" s="6" t="n"/>
     </row>
     <row r="55" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A55" s="9" t="n">
+      <c r="A55" s="113" t="n">
         <v>8</v>
       </c>
-      <c r="B55" s="37" t="n"/>
-      <c r="C55" s="37" t="n"/>
-      <c r="D55" s="37" t="n"/>
+      <c r="B55" s="114" t="n"/>
+      <c r="C55" s="115" t="n"/>
+      <c r="D55" s="114" t="n"/>
       <c r="E55" s="6" t="n"/>
       <c r="F55" s="6" t="n"/>
       <c r="G55" s="6" t="n"/>
@@ -4781,12 +4748,12 @@
       <c r="AI55" s="6" t="n"/>
     </row>
     <row r="56" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A56" s="9" t="n">
+      <c r="A56" s="113" t="n">
         <v>9</v>
       </c>
-      <c r="B56" s="37" t="n"/>
-      <c r="C56" s="37" t="n"/>
-      <c r="D56" s="37" t="n"/>
+      <c r="B56" s="114" t="n"/>
+      <c r="C56" s="115" t="n"/>
+      <c r="D56" s="114" t="n"/>
       <c r="E56" s="32" t="n"/>
       <c r="F56" s="32" t="n"/>
       <c r="G56" s="32" t="n"/>
@@ -4820,12 +4787,12 @@
       <c r="AI56" s="6" t="n"/>
     </row>
     <row r="57" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A57" s="9" t="n">
+      <c r="A57" s="113" t="n">
         <v>10</v>
       </c>
-      <c r="B57" s="37" t="n"/>
-      <c r="C57" s="37" t="n"/>
-      <c r="D57" s="40" t="n"/>
+      <c r="B57" s="114" t="n"/>
+      <c r="C57" s="115" t="n"/>
+      <c r="D57" s="116" t="n"/>
       <c r="E57" s="6" t="n"/>
       <c r="I57" s="23" t="n"/>
       <c r="J57" s="6" t="n"/>
@@ -4856,12 +4823,12 @@
       <c r="AI57" s="6" t="n"/>
     </row>
     <row r="58" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A58" s="9" t="n">
+      <c r="A58" s="113" t="n">
         <v>11</v>
       </c>
-      <c r="B58" s="37" t="n"/>
-      <c r="C58" s="37" t="n"/>
-      <c r="D58" s="40" t="n"/>
+      <c r="B58" s="114" t="n"/>
+      <c r="C58" s="115" t="n"/>
+      <c r="D58" s="116" t="n"/>
       <c r="E58" s="6" t="n"/>
       <c r="I58" s="23" t="n"/>
       <c r="J58" s="6" t="n"/>
@@ -4892,16 +4859,16 @@
       <c r="AI58" s="6" t="n"/>
     </row>
     <row r="59" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A59" s="9" t="n">
+      <c r="A59" s="113" t="n">
         <v>12</v>
       </c>
-      <c r="B59" s="37" t="n"/>
-      <c r="C59" s="37" t="n"/>
-      <c r="D59" s="40" t="n"/>
+      <c r="B59" s="114" t="n"/>
+      <c r="C59" s="115" t="n"/>
+      <c r="D59" s="116" t="n"/>
       <c r="E59" s="6" t="n"/>
-      <c r="F59" s="123" t="n"/>
-      <c r="G59" s="123" t="n"/>
-      <c r="H59" s="124" t="n"/>
+      <c r="F59" s="129" t="n"/>
+      <c r="G59" s="129" t="n"/>
+      <c r="H59" s="130" t="n"/>
       <c r="I59" s="23" t="n"/>
       <c r="J59" s="6" t="n"/>
       <c r="K59" s="6" t="n"/>
@@ -4931,16 +4898,16 @@
       <c r="AI59" s="6" t="n"/>
     </row>
     <row r="60" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A60" s="9" t="n">
+      <c r="A60" s="113" t="n">
         <v>13</v>
       </c>
-      <c r="B60" s="37" t="n"/>
-      <c r="C60" s="37" t="n"/>
-      <c r="D60" s="40" t="n"/>
+      <c r="B60" s="114" t="n"/>
+      <c r="C60" s="115" t="n"/>
+      <c r="D60" s="116" t="n"/>
       <c r="E60" s="6" t="n"/>
-      <c r="F60" s="123" t="n"/>
-      <c r="G60" s="123" t="n"/>
-      <c r="H60" s="124" t="n"/>
+      <c r="F60" s="129" t="n"/>
+      <c r="G60" s="129" t="n"/>
+      <c r="H60" s="130" t="n"/>
       <c r="I60" s="23" t="n"/>
       <c r="J60" s="6" t="n"/>
       <c r="K60" s="6" t="n"/>
@@ -4970,12 +4937,12 @@
       <c r="AI60" s="6" t="n"/>
     </row>
     <row r="61" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A61" s="9" t="n">
+      <c r="A61" s="113" t="n">
         <v>14</v>
       </c>
-      <c r="B61" s="37" t="n"/>
-      <c r="C61" s="37" t="n"/>
-      <c r="D61" s="40" t="n"/>
+      <c r="B61" s="114" t="n"/>
+      <c r="C61" s="115" t="n"/>
+      <c r="D61" s="116" t="n"/>
       <c r="E61" s="6" t="n"/>
       <c r="I61" s="23" t="n"/>
       <c r="J61" s="6" t="n"/>
@@ -5006,16 +4973,16 @@
       <c r="AI61" s="6" t="n"/>
     </row>
     <row r="62" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A62" s="9" t="n">
+      <c r="A62" s="113" t="n">
         <v>15</v>
       </c>
-      <c r="B62" s="37" t="n"/>
-      <c r="C62" s="37" t="n"/>
-      <c r="D62" s="40" t="n"/>
+      <c r="B62" s="114" t="n"/>
+      <c r="C62" s="115" t="n"/>
+      <c r="D62" s="116" t="n"/>
       <c r="E62" s="6" t="n"/>
-      <c r="F62" s="123" t="n"/>
-      <c r="G62" s="123" t="n"/>
-      <c r="H62" s="124" t="n"/>
+      <c r="F62" s="129" t="n"/>
+      <c r="G62" s="129" t="n"/>
+      <c r="H62" s="130" t="n"/>
       <c r="I62" s="23" t="n"/>
       <c r="J62" s="6" t="n"/>
       <c r="K62" s="6" t="n"/>
@@ -5045,16 +5012,16 @@
       <c r="AI62" s="6" t="n"/>
     </row>
     <row r="63" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A63" s="9" t="n">
+      <c r="A63" s="113" t="n">
         <v>16</v>
       </c>
-      <c r="B63" s="37" t="n"/>
-      <c r="C63" s="37" t="n"/>
-      <c r="D63" s="40" t="n"/>
+      <c r="B63" s="114" t="n"/>
+      <c r="C63" s="115" t="n"/>
+      <c r="D63" s="116" t="n"/>
       <c r="E63" s="6" t="n"/>
-      <c r="F63" s="123" t="n"/>
-      <c r="G63" s="123" t="n"/>
-      <c r="H63" s="124" t="n"/>
+      <c r="F63" s="129" t="n"/>
+      <c r="G63" s="129" t="n"/>
+      <c r="H63" s="130" t="n"/>
       <c r="I63" s="23" t="n"/>
       <c r="J63" s="6" t="n"/>
       <c r="K63" s="6" t="n"/>
@@ -5084,16 +5051,16 @@
       <c r="AI63" s="6" t="n"/>
     </row>
     <row r="64" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A64" s="9" t="n">
+      <c r="A64" s="113" t="n">
         <v>17</v>
       </c>
-      <c r="B64" s="37" t="n"/>
-      <c r="C64" s="37" t="n"/>
-      <c r="D64" s="40" t="n"/>
+      <c r="B64" s="114" t="n"/>
+      <c r="C64" s="115" t="n"/>
+      <c r="D64" s="116" t="n"/>
       <c r="E64" s="6" t="n"/>
-      <c r="F64" s="123" t="n"/>
-      <c r="G64" s="123" t="n"/>
-      <c r="H64" s="124" t="n"/>
+      <c r="F64" s="129" t="n"/>
+      <c r="G64" s="129" t="n"/>
+      <c r="H64" s="130" t="n"/>
       <c r="I64" s="23" t="n"/>
       <c r="J64" s="6" t="n"/>
       <c r="K64" s="6" t="n"/>
@@ -5123,16 +5090,16 @@
       <c r="AI64" s="6" t="n"/>
     </row>
     <row r="65" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A65" s="9" t="n">
+      <c r="A65" s="113" t="n">
         <v>18</v>
       </c>
-      <c r="B65" s="37" t="n"/>
-      <c r="C65" s="37" t="n"/>
-      <c r="D65" s="40" t="n"/>
+      <c r="B65" s="114" t="n"/>
+      <c r="C65" s="115" t="n"/>
+      <c r="D65" s="116" t="n"/>
       <c r="E65" s="6" t="n"/>
-      <c r="F65" s="123" t="n"/>
-      <c r="G65" s="123" t="n"/>
-      <c r="H65" s="124" t="n"/>
+      <c r="F65" s="129" t="n"/>
+      <c r="G65" s="129" t="n"/>
+      <c r="H65" s="130" t="n"/>
       <c r="I65" s="23" t="n"/>
       <c r="J65" s="6" t="n"/>
       <c r="K65" s="6" t="n"/>
@@ -5162,13 +5129,13 @@
       <c r="AI65" s="6" t="n"/>
     </row>
     <row r="66" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A66" s="9" t="n">
+      <c r="A66" s="113" t="n">
         <v>19</v>
       </c>
-      <c r="B66" s="37" t="n"/>
-      <c r="C66" s="37" t="n"/>
-      <c r="D66" s="40" t="n"/>
-      <c r="E66" s="148" t="n"/>
+      <c r="B66" s="114" t="n"/>
+      <c r="C66" s="115" t="n"/>
+      <c r="D66" s="116" t="n"/>
+      <c r="E66" s="131" t="n"/>
       <c r="F66" s="7" t="n"/>
       <c r="G66" s="7" t="n"/>
       <c r="H66" s="23" t="n"/>
@@ -5201,13 +5168,13 @@
       <c r="AI66" s="6" t="n"/>
     </row>
     <row r="67" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A67" s="9" t="n">
+      <c r="A67" s="113" t="n">
         <v>20</v>
       </c>
-      <c r="B67" s="37" t="n"/>
-      <c r="C67" s="37" t="n"/>
-      <c r="D67" s="40" t="n"/>
-      <c r="E67" s="148" t="n"/>
+      <c r="B67" s="114" t="n"/>
+      <c r="C67" s="115" t="n"/>
+      <c r="D67" s="116" t="n"/>
+      <c r="E67" s="131" t="n"/>
       <c r="F67" s="7" t="n"/>
       <c r="G67" s="7" t="n"/>
       <c r="H67" s="23" t="n"/>
@@ -5240,13 +5207,13 @@
       <c r="AI67" s="6" t="n"/>
     </row>
     <row r="68" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A68" s="9" t="n">
+      <c r="A68" s="113" t="n">
         <v>21</v>
       </c>
-      <c r="B68" s="37" t="n"/>
-      <c r="C68" s="37" t="n"/>
-      <c r="D68" s="40" t="n"/>
-      <c r="E68" s="148" t="n"/>
+      <c r="B68" s="114" t="n"/>
+      <c r="C68" s="115" t="n"/>
+      <c r="D68" s="116" t="n"/>
+      <c r="E68" s="131" t="n"/>
       <c r="F68" s="7" t="n"/>
       <c r="G68" s="7" t="n"/>
       <c r="H68" s="23" t="n"/>
@@ -5279,13 +5246,13 @@
       <c r="AI68" s="6" t="n"/>
     </row>
     <row r="69" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A69" s="9" t="n">
+      <c r="A69" s="113" t="n">
         <v>22</v>
       </c>
-      <c r="B69" s="37" t="n"/>
-      <c r="C69" s="37" t="n"/>
-      <c r="D69" s="40" t="n"/>
-      <c r="E69" s="148" t="n"/>
+      <c r="B69" s="114" t="n"/>
+      <c r="C69" s="115" t="n"/>
+      <c r="D69" s="116" t="n"/>
+      <c r="E69" s="131" t="n"/>
       <c r="F69" s="7" t="n"/>
       <c r="G69" s="7" t="n"/>
       <c r="H69" s="23" t="n"/>
@@ -5318,13 +5285,13 @@
       <c r="AI69" s="6" t="n"/>
     </row>
     <row r="70" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A70" s="9" t="n">
+      <c r="A70" s="113" t="n">
         <v>23</v>
       </c>
-      <c r="B70" s="37" t="n"/>
-      <c r="C70" s="37" t="n"/>
-      <c r="D70" s="40" t="n"/>
-      <c r="E70" s="148" t="n"/>
+      <c r="B70" s="114" t="n"/>
+      <c r="C70" s="115" t="n"/>
+      <c r="D70" s="116" t="n"/>
+      <c r="E70" s="131" t="n"/>
       <c r="F70" s="7" t="n"/>
       <c r="G70" s="7" t="n"/>
       <c r="H70" s="23" t="n"/>
@@ -5357,13 +5324,13 @@
       <c r="AI70" s="6" t="n"/>
     </row>
     <row r="71" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A71" s="9" t="n">
+      <c r="A71" s="113" t="n">
         <v>24</v>
       </c>
-      <c r="B71" s="37" t="n"/>
-      <c r="C71" s="37" t="n"/>
-      <c r="D71" s="40" t="n"/>
-      <c r="E71" s="148" t="n"/>
+      <c r="B71" s="114" t="n"/>
+      <c r="C71" s="115" t="n"/>
+      <c r="D71" s="116" t="n"/>
+      <c r="E71" s="131" t="n"/>
       <c r="F71" s="7" t="n"/>
       <c r="G71" s="7" t="n"/>
       <c r="H71" s="23" t="n"/>
@@ -5396,12 +5363,12 @@
       <c r="AI71" s="6" t="n"/>
     </row>
     <row r="72" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A72" s="9" t="n">
+      <c r="A72" s="113" t="n">
         <v>25</v>
       </c>
-      <c r="B72" s="37" t="n"/>
-      <c r="C72" s="37" t="n"/>
-      <c r="D72" s="40" t="n"/>
+      <c r="B72" s="114" t="n"/>
+      <c r="C72" s="115" t="n"/>
+      <c r="D72" s="116" t="n"/>
       <c r="E72" s="6" t="n"/>
       <c r="I72" s="23" t="n"/>
       <c r="J72" s="6" t="n"/>
@@ -5432,10 +5399,12 @@
       <c r="AI72" s="6" t="n"/>
     </row>
     <row r="73" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A73" s="13" t="n"/>
-      <c r="B73" s="13" t="n"/>
-      <c r="C73" s="13" t="n"/>
-      <c r="D73" s="13" t="n"/>
+      <c r="A73" s="126" t="n">
+        <v>26</v>
+      </c>
+      <c r="B73" s="127" t="n"/>
+      <c r="C73" s="128" t="n"/>
+      <c r="D73" s="127" t="n"/>
       <c r="E73" s="14" t="n"/>
       <c r="F73" s="14" t="n"/>
       <c r="G73" s="14" t="n"/>
@@ -5449,275 +5418,275 @@
       <c r="O73" s="14" t="n"/>
     </row>
     <row r="74" ht="15" customHeight="1" thickBot="1">
-      <c r="A74" s="125" t="inlineStr">
+      <c r="A74" s="132" t="inlineStr">
         <is>
           <t>TOTAL DAILY CREWS MANPOWER</t>
         </is>
       </c>
-      <c r="B74" s="116" t="n"/>
-      <c r="C74" s="120" t="n"/>
-      <c r="D74" s="119" t="inlineStr">
+      <c r="B74" s="120" t="n"/>
+      <c r="C74" s="124" t="n"/>
+      <c r="D74" s="123" t="inlineStr">
         <is>
           <t>SHIFT</t>
         </is>
       </c>
-      <c r="E74" s="109">
+      <c r="E74" s="1">
         <f>IF(1&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="F74" s="109">
+      <c r="F74" s="1">
         <f>IF(2&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,2),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="G74" s="109">
+      <c r="G74" s="1">
         <f>IF(3&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,3),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="H74" s="109">
+      <c r="H74" s="1">
         <f>IF(4&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,4),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="I74" s="109">
+      <c r="I74" s="1">
         <f>IF(5&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,5),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="J74" s="109">
+      <c r="J74" s="1">
         <f>IF(6&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,6),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="K74" s="109">
+      <c r="K74" s="1">
         <f>IF(7&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,7),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="L74" s="109">
+      <c r="L74" s="1">
         <f>IF(8&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,8),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="M74" s="109">
+      <c r="M74" s="1">
         <f>IF(9&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,9),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="N74" s="109">
+      <c r="N74" s="1">
         <f>IF(10&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,10),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="O74" s="109">
+      <c r="O74" s="1">
         <f>IF(11&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,11),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="P74" s="109">
+      <c r="P74" s="1">
         <f>IF(12&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,12),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="Q74" s="109">
+      <c r="Q74" s="1">
         <f>IF(13&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,13),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="R74" s="109">
+      <c r="R74" s="1">
         <f>IF(14&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,14),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="S74" s="109">
+      <c r="S74" s="1">
         <f>IF(15&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,15),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="T74" s="109">
+      <c r="T74" s="1">
         <f>IF(16&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,16),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="U74" s="109">
+      <c r="U74" s="1">
         <f>IF(17&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,17),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="V74" s="109">
+      <c r="V74" s="1">
         <f>IF(18&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,18),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="W74" s="109">
+      <c r="W74" s="1">
         <f>IF(19&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,19),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="X74" s="109">
+      <c r="X74" s="1">
         <f>IF(20&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,20),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="Y74" s="109">
+      <c r="Y74" s="1">
         <f>IF(21&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,21),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="Z74" s="109">
+      <c r="Z74" s="1">
         <f>IF(22&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,22),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="AA74" s="109">
+      <c r="AA74" s="1">
         <f>IF(23&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,23),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="AB74" s="109">
+      <c r="AB74" s="1">
         <f>IF(24&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,24),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="AC74" s="109">
+      <c r="AC74" s="1">
         <f>IF(25&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,25),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="AD74" s="109">
+      <c r="AD74" s="1">
         <f>IF(26&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,26),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="AE74" s="109">
+      <c r="AE74" s="1">
         <f>IF(27&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,27),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="AF74" s="109">
+      <c r="AF74" s="1">
         <f>IF(28&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,28),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="AG74" s="109">
+      <c r="AG74" s="1">
         <f>IF(29&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,29),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="AH74" s="109">
+      <c r="AH74" s="1">
         <f>IF(30&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,30),"ddd"),"")</f>
         <v/>
       </c>
-      <c r="AI74" s="109">
+      <c r="AI74" s="1">
         <f>IF(31&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,31),"ddd"),"")</f>
         <v/>
       </c>
     </row>
     <row r="75" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A75" s="111" t="n"/>
-      <c r="C75" s="126" t="n"/>
+      <c r="A75" s="110" t="n"/>
+      <c r="C75" s="133" t="n"/>
       <c r="D75" s="105" t="n"/>
-      <c r="E75" s="112">
+      <c r="E75" s="2">
         <f>IF(1&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),1,"")</f>
         <v/>
       </c>
-      <c r="F75" s="112">
+      <c r="F75" s="2">
         <f>IF(2&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),2,"")</f>
         <v/>
       </c>
-      <c r="G75" s="112">
+      <c r="G75" s="2">
         <f>IF(3&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),3,"")</f>
         <v/>
       </c>
-      <c r="H75" s="112">
+      <c r="H75" s="2">
         <f>IF(4&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),4,"")</f>
         <v/>
       </c>
-      <c r="I75" s="112">
+      <c r="I75" s="3">
         <f>IF(5&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),5,"")</f>
         <v/>
       </c>
-      <c r="J75" s="112">
+      <c r="J75" s="4">
         <f>IF(6&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),6,"")</f>
         <v/>
       </c>
-      <c r="K75" s="112">
+      <c r="K75" s="4">
         <f>IF(7&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),7,"")</f>
         <v/>
       </c>
-      <c r="L75" s="112">
+      <c r="L75" s="3">
         <f>IF(8&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),8,"")</f>
         <v/>
       </c>
-      <c r="M75" s="112">
+      <c r="M75" s="4">
         <f>IF(9&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),9,"")</f>
         <v/>
       </c>
-      <c r="N75" s="112">
+      <c r="N75" s="2">
         <f>IF(10&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),10,"")</f>
         <v/>
       </c>
-      <c r="O75" s="112">
+      <c r="O75" s="2">
         <f>IF(11&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),11,"")</f>
         <v/>
       </c>
-      <c r="P75" s="112">
+      <c r="P75" s="2">
         <f>IF(12&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),12,"")</f>
         <v/>
       </c>
-      <c r="Q75" s="112">
+      <c r="Q75" s="2">
         <f>IF(13&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),13,"")</f>
         <v/>
       </c>
-      <c r="R75" s="112">
+      <c r="R75" s="2">
         <f>IF(14&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),14,"")</f>
         <v/>
       </c>
-      <c r="S75" s="112">
+      <c r="S75" s="2">
         <f>IF(15&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),15,"")</f>
         <v/>
       </c>
-      <c r="T75" s="112">
+      <c r="T75" s="2">
         <f>IF(16&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),16,"")</f>
         <v/>
       </c>
-      <c r="U75" s="112">
+      <c r="U75" s="2">
         <f>IF(17&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),17,"")</f>
         <v/>
       </c>
-      <c r="V75" s="112">
+      <c r="V75" s="2">
         <f>IF(18&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),18,"")</f>
         <v/>
       </c>
-      <c r="W75" s="112">
+      <c r="W75" s="2">
         <f>IF(19&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),19,"")</f>
         <v/>
       </c>
-      <c r="X75" s="112">
+      <c r="X75" s="2">
         <f>IF(20&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),20,"")</f>
         <v/>
       </c>
-      <c r="Y75" s="112">
+      <c r="Y75" s="2">
         <f>IF(21&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),21,"")</f>
         <v/>
       </c>
-      <c r="Z75" s="112">
+      <c r="Z75" s="2">
         <f>IF(22&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),22,"")</f>
         <v/>
       </c>
-      <c r="AA75" s="112">
+      <c r="AA75" s="2">
         <f>IF(23&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),23,"")</f>
         <v/>
       </c>
-      <c r="AB75" s="112">
+      <c r="AB75" s="2">
         <f>IF(24&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),24,"")</f>
         <v/>
       </c>
-      <c r="AC75" s="112">
+      <c r="AC75" s="2">
         <f>IF(25&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),25,"")</f>
         <v/>
       </c>
-      <c r="AD75" s="112">
+      <c r="AD75" s="2">
         <f>IF(26&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),26,"")</f>
         <v/>
       </c>
-      <c r="AE75" s="112">
+      <c r="AE75" s="2">
         <f>IF(27&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),27,"")</f>
         <v/>
       </c>
-      <c r="AF75" s="112">
+      <c r="AF75" s="2">
         <f>IF(28&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),28,"")</f>
         <v/>
       </c>
-      <c r="AG75" s="112">
+      <c r="AG75" s="2">
         <f>IF(29&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),29,"")</f>
         <v/>
       </c>
-      <c r="AH75" s="112">
+      <c r="AH75" s="2">
         <f>IF(30&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),30,"")</f>
         <v/>
       </c>
-      <c r="AI75" s="112">
+      <c r="AI75" s="2">
         <f>IF(31&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),31,"")</f>
         <v/>
       </c>
     </row>
     <row r="76" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A76" s="111" t="n"/>
-      <c r="C76" s="126" t="n"/>
+      <c r="A76" s="110" t="n"/>
+      <c r="C76" s="133" t="n"/>
       <c r="D76" s="15" t="inlineStr">
         <is>
           <t>D</t>
@@ -5849,8 +5818,8 @@
       </c>
     </row>
     <row r="77" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A77" s="111" t="n"/>
-      <c r="C77" s="126" t="n"/>
+      <c r="A77" s="110" t="n"/>
+      <c r="C77" s="133" t="n"/>
       <c r="D77" s="17" t="inlineStr">
         <is>
           <t>T</t>
@@ -5982,9 +5951,9 @@
       </c>
     </row>
     <row r="78" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A78" s="117" t="n"/>
-      <c r="B78" s="118" t="n"/>
-      <c r="C78" s="121" t="n"/>
+      <c r="A78" s="121" t="n"/>
+      <c r="B78" s="122" t="n"/>
+      <c r="C78" s="125" t="n"/>
       <c r="D78" s="19" t="inlineStr">
         <is>
           <t>G</t>
@@ -6117,7 +6086,7 @@
     </row>
     <row r="79" ht="15" customHeight="1" thickBot="1"/>
     <row r="80" ht="21" customHeight="1" thickBot="1">
-      <c r="E80" s="119" t="inlineStr">
+      <c r="E80" s="123" t="inlineStr">
         <is>
           <t>SHIFT</t>
         </is>
@@ -6129,7 +6098,7 @@
       <c r="J80" s="104" t="n"/>
     </row>
     <row r="81" ht="16.2" customHeight="1" thickBot="1">
-      <c r="E81" s="127" t="inlineStr">
+      <c r="E81" s="134" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -6145,7 +6114,7 @@
       <c r="J81" s="104" t="n"/>
     </row>
     <row r="82" ht="16.2" customHeight="1" thickBot="1">
-      <c r="E82" s="128" t="inlineStr">
+      <c r="E82" s="135" t="inlineStr">
         <is>
           <t>T</t>
         </is>
@@ -6164,25 +6133,25 @@
           <t>ABDULLAH A. ALSHEHRY</t>
         </is>
       </c>
-      <c r="N82" s="118" t="n"/>
-      <c r="O82" s="118" t="n"/>
-      <c r="P82" s="118" t="n"/>
-      <c r="Q82" s="118" t="n"/>
-      <c r="R82" s="118" t="n"/>
-      <c r="S82" s="118" t="n"/>
+      <c r="N82" s="122" t="n"/>
+      <c r="O82" s="122" t="n"/>
+      <c r="P82" s="122" t="n"/>
+      <c r="Q82" s="122" t="n"/>
+      <c r="R82" s="122" t="n"/>
+      <c r="S82" s="122" t="n"/>
       <c r="W82" s="96">
         <f>UPPER(TEXT(TODAY(),"DDDD dd/mm/yyyy"))</f>
         <v/>
       </c>
-      <c r="X82" s="118" t="n"/>
-      <c r="Y82" s="118" t="n"/>
-      <c r="Z82" s="118" t="n"/>
-      <c r="AA82" s="118" t="n"/>
-      <c r="AB82" s="118" t="n"/>
-      <c r="AC82" s="118" t="n"/>
+      <c r="X82" s="122" t="n"/>
+      <c r="Y82" s="122" t="n"/>
+      <c r="Z82" s="122" t="n"/>
+      <c r="AA82" s="122" t="n"/>
+      <c r="AB82" s="122" t="n"/>
+      <c r="AC82" s="122" t="n"/>
     </row>
     <row r="83" ht="16.2" customHeight="1" thickBot="1">
-      <c r="E83" s="129" t="inlineStr">
+      <c r="E83" s="136" t="inlineStr">
         <is>
           <t>G</t>
         </is>
@@ -6208,153 +6177,153 @@
       </c>
     </row>
     <row r="85">
-      <c r="E85" s="130" t="inlineStr">
+      <c r="E85" s="137" t="inlineStr">
         <is>
           <t>CODE LEGEND — ALL CODES</t>
         </is>
       </c>
     </row>
     <row r="86" ht="16" customHeight="1">
-      <c r="E86" s="131" t="inlineStr">
+      <c r="E86" s="138" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="F86" s="132" t="inlineStr">
+      <c r="F86" s="139" t="inlineStr">
         <is>
           <t>DAY</t>
         </is>
       </c>
-      <c r="K86" s="133" t="inlineStr">
+      <c r="K86" s="140" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="L86" s="132" t="inlineStr">
+      <c r="L86" s="139" t="inlineStr">
         <is>
           <t>TWILIGHT</t>
         </is>
       </c>
-      <c r="Q86" s="134" t="inlineStr">
+      <c r="Q86" s="141" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
-      <c r="R86" s="132" t="inlineStr">
+      <c r="R86" s="139" t="inlineStr">
         <is>
           <t>GRAVEYARD</t>
         </is>
       </c>
-      <c r="W86" s="135" t="inlineStr">
+      <c r="W86" s="142" t="inlineStr">
         <is>
           <t>TR</t>
         </is>
       </c>
-      <c r="X86" s="132" t="inlineStr">
+      <c r="X86" s="139" t="inlineStr">
         <is>
           <t>TRAINING</t>
         </is>
       </c>
-      <c r="AC86" s="136" t="inlineStr">
+      <c r="AC86" s="143" t="inlineStr">
         <is>
           <t>V</t>
         </is>
       </c>
-      <c r="AD86" s="132" t="inlineStr">
+      <c r="AD86" s="139" t="inlineStr">
         <is>
           <t>VACATION</t>
         </is>
       </c>
     </row>
     <row r="87" ht="16" customHeight="1">
-      <c r="E87" s="137" t="inlineStr">
+      <c r="E87" s="144" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="F87" s="132" t="inlineStr">
+      <c r="F87" s="139" t="inlineStr">
         <is>
           <t>REST/RDO</t>
         </is>
       </c>
-      <c r="K87" s="138" t="inlineStr">
+      <c r="K87" s="145" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="L87" s="132" t="inlineStr">
+      <c r="L87" s="139" t="inlineStr">
         <is>
           <t>ABSENT</t>
         </is>
       </c>
-      <c r="Q87" s="139" t="inlineStr">
+      <c r="Q87" s="146" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="R87" s="132" t="inlineStr">
+      <c r="R87" s="139" t="inlineStr">
         <is>
           <t>HOLIDAY</t>
         </is>
       </c>
-      <c r="W87" s="140" t="inlineStr">
+      <c r="W87" s="147" t="inlineStr">
         <is>
           <t>OT</t>
         </is>
       </c>
-      <c r="X87" s="132" t="inlineStr">
+      <c r="X87" s="139" t="inlineStr">
         <is>
           <t>OVERTIME</t>
         </is>
       </c>
-      <c r="AC87" s="141" t="inlineStr">
+      <c r="AC87" s="148" t="inlineStr">
         <is>
           <t>OS</t>
         </is>
       </c>
-      <c r="AD87" s="132" t="inlineStr">
+      <c r="AD87" s="139" t="inlineStr">
         <is>
           <t>OUTSTATION</t>
         </is>
       </c>
     </row>
     <row r="88" ht="16" customHeight="1">
-      <c r="E88" s="142" t="inlineStr">
+      <c r="E88" s="149" t="inlineStr">
         <is>
           <t>S/L</t>
         </is>
       </c>
-      <c r="F88" s="132" t="inlineStr">
+      <c r="F88" s="139" t="inlineStr">
         <is>
           <t>SICK LEAVE</t>
         </is>
       </c>
-      <c r="K88" s="143" t="inlineStr">
+      <c r="K88" s="150" t="inlineStr">
         <is>
           <t>C/T</t>
         </is>
       </c>
-      <c r="L88" s="132" t="inlineStr">
+      <c r="L88" s="139" t="inlineStr">
         <is>
           <t>COMP TIME</t>
         </is>
       </c>
-      <c r="Q88" s="144" t="inlineStr">
+      <c r="Q88" s="151" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="R88" s="132" t="inlineStr">
+      <c r="R88" s="139" t="inlineStr">
         <is>
           <t>LATE/LEAVE</t>
         </is>
       </c>
-      <c r="W88" s="145" t="inlineStr">
+      <c r="W88" s="152" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="X88" s="132" t="inlineStr">
+      <c r="X88" s="139" t="inlineStr">
         <is>
           <t>NOTE</t>
         </is>
@@ -6365,8 +6334,8 @@
     <mergeCell ref="X88:AA88"/>
     <mergeCell ref="E2:AC2"/>
     <mergeCell ref="C1:C2"/>
+    <mergeCell ref="AK6:AN6"/>
     <mergeCell ref="AD87:AG87"/>
-    <mergeCell ref="AK6:AN6"/>
     <mergeCell ref="A74:C78"/>
     <mergeCell ref="W82:AC82"/>
     <mergeCell ref="E80:J80"/>

--- a/uploads/inbox/SPV_ROSTER_TEMPLATE_AVISUITE_COLORS.xlsx
+++ b/uploads/inbox/SPV_ROSTER_TEMPLATE_AVISUITE_COLORS.xlsx
@@ -799,7 +799,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="153">
+  <cellXfs count="164">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -1122,20 +1122,40 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="34" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="14" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="14" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="15" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -1143,8 +1163,25 @@
     <xf numFmtId="0" fontId="15" fillId="5" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1157,16 +1194,30 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1231,7 +1282,7 @@
   <cellStyles count="1">
     <cellStyle name="عادي" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="27">
+  <dxfs count="28">
     <dxf>
       <fill>
         <patternFill>
@@ -1483,6 +1534,18 @@
       <fill>
         <patternFill>
           <bgColor rgb="0083CCEB"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Times New Roman"/>
+        <b val="1"/>
+        <color rgb="00C00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="00FFE1E1"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2002,127 +2065,127 @@
         </is>
       </c>
       <c r="E3" s="1">
-        <f>IF(1&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1),"ddd"),"")</f>
+        <f>IF(1&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+0,"ddd"),"")</f>
         <v/>
       </c>
       <c r="F3" s="1">
-        <f>IF(2&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,2),"ddd"),"")</f>
+        <f>IF(2&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+1,"ddd"),"")</f>
         <v/>
       </c>
       <c r="G3" s="1">
-        <f>IF(3&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,3),"ddd"),"")</f>
+        <f>IF(3&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+2,"ddd"),"")</f>
         <v/>
       </c>
       <c r="H3" s="1">
-        <f>IF(4&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,4),"ddd"),"")</f>
+        <f>IF(4&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+3,"ddd"),"")</f>
         <v/>
       </c>
       <c r="I3" s="1">
-        <f>IF(5&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,5),"ddd"),"")</f>
+        <f>IF(5&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+4,"ddd"),"")</f>
         <v/>
       </c>
       <c r="J3" s="1">
-        <f>IF(6&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,6),"ddd"),"")</f>
+        <f>IF(6&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+5,"ddd"),"")</f>
         <v/>
       </c>
       <c r="K3" s="1">
-        <f>IF(7&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,7),"ddd"),"")</f>
+        <f>IF(7&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+6,"ddd"),"")</f>
         <v/>
       </c>
       <c r="L3" s="1">
-        <f>IF(8&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,8),"ddd"),"")</f>
+        <f>IF(8&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+7,"ddd"),"")</f>
         <v/>
       </c>
       <c r="M3" s="1">
-        <f>IF(9&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,9),"ddd"),"")</f>
+        <f>IF(9&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+8,"ddd"),"")</f>
         <v/>
       </c>
       <c r="N3" s="1">
-        <f>IF(10&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,10),"ddd"),"")</f>
+        <f>IF(10&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+9,"ddd"),"")</f>
         <v/>
       </c>
       <c r="O3" s="1">
-        <f>IF(11&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,11),"ddd"),"")</f>
+        <f>IF(11&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+10,"ddd"),"")</f>
         <v/>
       </c>
       <c r="P3" s="1">
-        <f>IF(12&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,12),"ddd"),"")</f>
+        <f>IF(12&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+11,"ddd"),"")</f>
         <v/>
       </c>
       <c r="Q3" s="1">
-        <f>IF(13&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,13),"ddd"),"")</f>
+        <f>IF(13&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+12,"ddd"),"")</f>
         <v/>
       </c>
       <c r="R3" s="1">
-        <f>IF(14&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,14),"ddd"),"")</f>
+        <f>IF(14&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+13,"ddd"),"")</f>
         <v/>
       </c>
       <c r="S3" s="1">
-        <f>IF(15&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,15),"ddd"),"")</f>
+        <f>IF(15&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+14,"ddd"),"")</f>
         <v/>
       </c>
       <c r="T3" s="1">
-        <f>IF(16&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,16),"ddd"),"")</f>
+        <f>IF(16&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+15,"ddd"),"")</f>
         <v/>
       </c>
       <c r="U3" s="1">
-        <f>IF(17&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,17),"ddd"),"")</f>
+        <f>IF(17&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+16,"ddd"),"")</f>
         <v/>
       </c>
       <c r="V3" s="1">
-        <f>IF(18&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,18),"ddd"),"")</f>
+        <f>IF(18&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+17,"ddd"),"")</f>
         <v/>
       </c>
       <c r="W3" s="1">
-        <f>IF(19&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,19),"ddd"),"")</f>
+        <f>IF(19&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+18,"ddd"),"")</f>
         <v/>
       </c>
       <c r="X3" s="1">
-        <f>IF(20&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,20),"ddd"),"")</f>
+        <f>IF(20&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+19,"ddd"),"")</f>
         <v/>
       </c>
       <c r="Y3" s="1">
-        <f>IF(21&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,21),"ddd"),"")</f>
+        <f>IF(21&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+20,"ddd"),"")</f>
         <v/>
       </c>
       <c r="Z3" s="1">
-        <f>IF(22&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,22),"ddd"),"")</f>
+        <f>IF(22&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+21,"ddd"),"")</f>
         <v/>
       </c>
       <c r="AA3" s="1">
-        <f>IF(23&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,23),"ddd"),"")</f>
+        <f>IF(23&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+22,"ddd"),"")</f>
         <v/>
       </c>
       <c r="AB3" s="1">
-        <f>IF(24&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,24),"ddd"),"")</f>
+        <f>IF(24&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+23,"ddd"),"")</f>
         <v/>
       </c>
       <c r="AC3" s="1">
-        <f>IF(25&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,25),"ddd"),"")</f>
+        <f>IF(25&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+24,"ddd"),"")</f>
         <v/>
       </c>
       <c r="AD3" s="1">
-        <f>IF(26&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,26),"ddd"),"")</f>
+        <f>IF(26&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+25,"ddd"),"")</f>
         <v/>
       </c>
       <c r="AE3" s="1">
-        <f>IF(27&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,27),"ddd"),"")</f>
+        <f>IF(27&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+26,"ddd"),"")</f>
         <v/>
       </c>
       <c r="AF3" s="1">
-        <f>IF(28&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,28),"ddd"),"")</f>
+        <f>IF(28&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+27,"ddd"),"")</f>
         <v/>
       </c>
       <c r="AG3" s="1">
-        <f>IF(29&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,29),"ddd"),"")</f>
+        <f>IF(29&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+28,"ddd"),"")</f>
         <v/>
       </c>
       <c r="AH3" s="24">
-        <f>IF(30&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,30),"ddd"),"")</f>
+        <f>IF(30&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+29,"ddd"),"")</f>
         <v/>
       </c>
       <c r="AI3" s="21">
-        <f>IF(31&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,31),"ddd"),"")</f>
+        <f>IF(31&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+30,"ddd"),"")</f>
         <v/>
       </c>
       <c r="AK3" s="109" t="inlineStr">
@@ -2269,43 +2332,44 @@
       </c>
     </row>
     <row r="5" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A5" s="113" t="n">
-        <v>1</v>
+      <c r="A5" s="113">
+        <f>IF($C5="","",ROW()-4)</f>
+        <v/>
       </c>
       <c r="B5" s="114" t="n"/>
       <c r="C5" s="115" t="n"/>
       <c r="D5" s="116" t="n"/>
-      <c r="E5" s="6" t="n"/>
-      <c r="F5" s="6" t="n"/>
-      <c r="G5" s="7" t="n"/>
-      <c r="H5" s="6" t="n"/>
-      <c r="I5" s="6" t="n"/>
-      <c r="J5" s="6" t="n"/>
-      <c r="K5" s="6" t="n"/>
-      <c r="L5" s="6" t="n"/>
-      <c r="M5" s="6" t="n"/>
-      <c r="N5" s="6" t="n"/>
-      <c r="O5" s="6" t="n"/>
-      <c r="P5" s="6" t="n"/>
-      <c r="Q5" s="6" t="n"/>
-      <c r="R5" s="6" t="n"/>
-      <c r="S5" s="6" t="n"/>
-      <c r="T5" s="6" t="n"/>
-      <c r="U5" s="6" t="n"/>
-      <c r="V5" s="6" t="n"/>
-      <c r="W5" s="6" t="n"/>
-      <c r="X5" s="6" t="n"/>
-      <c r="Y5" s="6" t="n"/>
-      <c r="Z5" s="6" t="n"/>
-      <c r="AA5" s="6" t="n"/>
-      <c r="AB5" s="6" t="n"/>
-      <c r="AC5" s="6" t="n"/>
-      <c r="AD5" s="6" t="n"/>
-      <c r="AE5" s="6" t="n"/>
-      <c r="AF5" s="6" t="n"/>
-      <c r="AG5" s="6" t="n"/>
-      <c r="AH5" s="26" t="n"/>
-      <c r="AI5" s="23" t="n"/>
+      <c r="E5" s="117" t="n"/>
+      <c r="F5" s="117" t="n"/>
+      <c r="G5" s="118" t="n"/>
+      <c r="H5" s="117" t="n"/>
+      <c r="I5" s="117" t="n"/>
+      <c r="J5" s="117" t="n"/>
+      <c r="K5" s="117" t="n"/>
+      <c r="L5" s="117" t="n"/>
+      <c r="M5" s="117" t="n"/>
+      <c r="N5" s="117" t="n"/>
+      <c r="O5" s="117" t="n"/>
+      <c r="P5" s="117" t="n"/>
+      <c r="Q5" s="117" t="n"/>
+      <c r="R5" s="117" t="n"/>
+      <c r="S5" s="117" t="n"/>
+      <c r="T5" s="117" t="n"/>
+      <c r="U5" s="117" t="n"/>
+      <c r="V5" s="117" t="n"/>
+      <c r="W5" s="117" t="n"/>
+      <c r="X5" s="117" t="n"/>
+      <c r="Y5" s="117" t="n"/>
+      <c r="Z5" s="117" t="n"/>
+      <c r="AA5" s="117" t="n"/>
+      <c r="AB5" s="117" t="n"/>
+      <c r="AC5" s="117" t="n"/>
+      <c r="AD5" s="117" t="n"/>
+      <c r="AE5" s="117" t="n"/>
+      <c r="AF5" s="117" t="n"/>
+      <c r="AG5" s="117" t="n"/>
+      <c r="AH5" s="119" t="n"/>
+      <c r="AI5" s="120" t="n"/>
       <c r="AK5" s="111" t="inlineStr">
         <is>
           <t>YEAR</t>
@@ -2316,594 +2380,609 @@
       </c>
     </row>
     <row r="6" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A6" s="113" t="n">
-        <v>2</v>
+      <c r="A6" s="113">
+        <f>IF($C6="","",ROW()-4)</f>
+        <v/>
       </c>
       <c r="B6" s="114" t="n"/>
       <c r="C6" s="115" t="n"/>
       <c r="D6" s="114" t="n"/>
-      <c r="E6" s="6" t="n"/>
-      <c r="F6" s="6" t="n"/>
-      <c r="G6" s="7" t="n"/>
-      <c r="H6" s="6" t="n"/>
-      <c r="I6" s="6" t="n"/>
-      <c r="J6" s="6" t="n"/>
-      <c r="K6" s="6" t="n"/>
-      <c r="L6" s="6" t="n"/>
-      <c r="M6" s="6" t="n"/>
-      <c r="N6" s="6" t="n"/>
-      <c r="O6" s="6" t="n"/>
-      <c r="P6" s="6" t="n"/>
-      <c r="Q6" s="6" t="n"/>
-      <c r="R6" s="6" t="n"/>
-      <c r="S6" s="6" t="n"/>
-      <c r="T6" s="6" t="n"/>
-      <c r="U6" s="6" t="n"/>
-      <c r="V6" s="6" t="n"/>
-      <c r="W6" s="6" t="n"/>
-      <c r="X6" s="6" t="n"/>
-      <c r="Y6" s="6" t="n"/>
-      <c r="Z6" s="6" t="n"/>
-      <c r="AA6" s="6" t="n"/>
-      <c r="AB6" s="6" t="n"/>
-      <c r="AC6" s="6" t="n"/>
-      <c r="AD6" s="6" t="n"/>
-      <c r="AE6" s="6" t="n"/>
-      <c r="AF6" s="6" t="n"/>
-      <c r="AG6" s="6" t="n"/>
-      <c r="AH6" s="26" t="n"/>
-      <c r="AI6" s="23" t="n"/>
-      <c r="AK6" s="117" t="inlineStr">
+      <c r="E6" s="117" t="n"/>
+      <c r="F6" s="117" t="n"/>
+      <c r="G6" s="118" t="n"/>
+      <c r="H6" s="117" t="n"/>
+      <c r="I6" s="117" t="n"/>
+      <c r="J6" s="117" t="n"/>
+      <c r="K6" s="117" t="n"/>
+      <c r="L6" s="117" t="n"/>
+      <c r="M6" s="117" t="n"/>
+      <c r="N6" s="117" t="n"/>
+      <c r="O6" s="117" t="n"/>
+      <c r="P6" s="117" t="n"/>
+      <c r="Q6" s="117" t="n"/>
+      <c r="R6" s="117" t="n"/>
+      <c r="S6" s="117" t="n"/>
+      <c r="T6" s="117" t="n"/>
+      <c r="U6" s="117" t="n"/>
+      <c r="V6" s="117" t="n"/>
+      <c r="W6" s="117" t="n"/>
+      <c r="X6" s="117" t="n"/>
+      <c r="Y6" s="117" t="n"/>
+      <c r="Z6" s="117" t="n"/>
+      <c r="AA6" s="117" t="n"/>
+      <c r="AB6" s="117" t="n"/>
+      <c r="AC6" s="117" t="n"/>
+      <c r="AD6" s="117" t="n"/>
+      <c r="AE6" s="117" t="n"/>
+      <c r="AF6" s="117" t="n"/>
+      <c r="AG6" s="117" t="n"/>
+      <c r="AH6" s="119" t="n"/>
+      <c r="AI6" s="120" t="n"/>
+      <c r="AK6" s="121" t="inlineStr">
         <is>
-          <t>type JUL / JULY / 7</t>
+          <t>month name or number</t>
         </is>
       </c>
     </row>
     <row r="7" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A7" s="113" t="n">
-        <v>3</v>
+      <c r="A7" s="113">
+        <f>IF($C7="","",ROW()-4)</f>
+        <v/>
       </c>
       <c r="B7" s="114" t="n"/>
       <c r="C7" s="115" t="n"/>
       <c r="D7" s="114" t="n"/>
-      <c r="E7" s="6" t="n"/>
-      <c r="F7" s="6" t="n"/>
-      <c r="G7" s="7" t="n"/>
-      <c r="H7" s="6" t="n"/>
-      <c r="I7" s="6" t="n"/>
-      <c r="J7" s="6" t="n"/>
-      <c r="K7" s="6" t="n"/>
-      <c r="L7" s="6" t="n"/>
-      <c r="M7" s="6" t="n"/>
-      <c r="N7" s="6" t="n"/>
-      <c r="O7" s="6" t="n"/>
-      <c r="P7" s="6" t="n"/>
-      <c r="Q7" s="6" t="n"/>
-      <c r="R7" s="6" t="n"/>
-      <c r="S7" s="6" t="n"/>
-      <c r="T7" s="6" t="n"/>
-      <c r="U7" s="6" t="n"/>
-      <c r="V7" s="6" t="n"/>
-      <c r="W7" s="6" t="n"/>
-      <c r="X7" s="6" t="n"/>
-      <c r="Y7" s="6" t="n"/>
-      <c r="Z7" s="6" t="n"/>
-      <c r="AA7" s="6" t="n"/>
-      <c r="AB7" s="6" t="n"/>
-      <c r="AC7" s="6" t="n"/>
-      <c r="AD7" s="6" t="n"/>
-      <c r="AE7" s="6" t="n"/>
-      <c r="AF7" s="6" t="n"/>
-      <c r="AG7" s="6" t="n"/>
-      <c r="AH7" s="26" t="n"/>
-      <c r="AI7" s="23" t="n"/>
+      <c r="E7" s="117" t="n"/>
+      <c r="F7" s="117" t="n"/>
+      <c r="G7" s="118" t="n"/>
+      <c r="H7" s="117" t="n"/>
+      <c r="I7" s="117" t="n"/>
+      <c r="J7" s="117" t="n"/>
+      <c r="K7" s="117" t="n"/>
+      <c r="L7" s="117" t="n"/>
+      <c r="M7" s="117" t="n"/>
+      <c r="N7" s="117" t="n"/>
+      <c r="O7" s="117" t="n"/>
+      <c r="P7" s="117" t="n"/>
+      <c r="Q7" s="117" t="n"/>
+      <c r="R7" s="117" t="n"/>
+      <c r="S7" s="117" t="n"/>
+      <c r="T7" s="117" t="n"/>
+      <c r="U7" s="117" t="n"/>
+      <c r="V7" s="117" t="n"/>
+      <c r="W7" s="117" t="n"/>
+      <c r="X7" s="117" t="n"/>
+      <c r="Y7" s="117" t="n"/>
+      <c r="Z7" s="117" t="n"/>
+      <c r="AA7" s="117" t="n"/>
+      <c r="AB7" s="117" t="n"/>
+      <c r="AC7" s="117" t="n"/>
+      <c r="AD7" s="117" t="n"/>
+      <c r="AE7" s="117" t="n"/>
+      <c r="AF7" s="117" t="n"/>
+      <c r="AG7" s="117" t="n"/>
+      <c r="AH7" s="119" t="n"/>
+      <c r="AI7" s="120" t="n"/>
     </row>
     <row r="8" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A8" s="113" t="n">
-        <v>4</v>
+      <c r="A8" s="113">
+        <f>IF($C8="","",ROW()-4)</f>
+        <v/>
       </c>
       <c r="B8" s="114" t="n"/>
       <c r="C8" s="115" t="n"/>
       <c r="D8" s="114" t="n"/>
-      <c r="E8" s="6" t="n"/>
-      <c r="F8" s="6" t="n"/>
-      <c r="G8" s="7" t="n"/>
-      <c r="H8" s="6" t="n"/>
-      <c r="I8" s="6" t="n"/>
-      <c r="J8" s="6" t="n"/>
-      <c r="K8" s="6" t="n"/>
-      <c r="L8" s="6" t="n"/>
-      <c r="M8" s="6" t="n"/>
-      <c r="N8" s="6" t="n"/>
-      <c r="O8" s="6" t="n"/>
-      <c r="P8" s="6" t="n"/>
-      <c r="Q8" s="6" t="n"/>
-      <c r="R8" s="6" t="n"/>
-      <c r="S8" s="6" t="n"/>
-      <c r="T8" s="6" t="n"/>
-      <c r="U8" s="6" t="n"/>
-      <c r="V8" s="6" t="n"/>
-      <c r="W8" s="6" t="n"/>
-      <c r="X8" s="6" t="n"/>
-      <c r="Y8" s="6" t="n"/>
-      <c r="Z8" s="6" t="n"/>
-      <c r="AA8" s="6" t="n"/>
-      <c r="AB8" s="6" t="n"/>
-      <c r="AC8" s="6" t="n"/>
-      <c r="AD8" s="6" t="n"/>
-      <c r="AE8" s="6" t="n"/>
-      <c r="AF8" s="6" t="n"/>
-      <c r="AG8" s="6" t="n"/>
-      <c r="AH8" s="26" t="n"/>
-      <c r="AI8" s="23" t="n"/>
+      <c r="E8" s="117" t="n"/>
+      <c r="F8" s="117" t="n"/>
+      <c r="G8" s="118" t="n"/>
+      <c r="H8" s="117" t="n"/>
+      <c r="I8" s="117" t="n"/>
+      <c r="J8" s="117" t="n"/>
+      <c r="K8" s="117" t="n"/>
+      <c r="L8" s="117" t="n"/>
+      <c r="M8" s="117" t="n"/>
+      <c r="N8" s="117" t="n"/>
+      <c r="O8" s="117" t="n"/>
+      <c r="P8" s="117" t="n"/>
+      <c r="Q8" s="117" t="n"/>
+      <c r="R8" s="117" t="n"/>
+      <c r="S8" s="117" t="n"/>
+      <c r="T8" s="117" t="n"/>
+      <c r="U8" s="117" t="n"/>
+      <c r="V8" s="117" t="n"/>
+      <c r="W8" s="117" t="n"/>
+      <c r="X8" s="117" t="n"/>
+      <c r="Y8" s="117" t="n"/>
+      <c r="Z8" s="117" t="n"/>
+      <c r="AA8" s="117" t="n"/>
+      <c r="AB8" s="117" t="n"/>
+      <c r="AC8" s="117" t="n"/>
+      <c r="AD8" s="117" t="n"/>
+      <c r="AE8" s="117" t="n"/>
+      <c r="AF8" s="117" t="n"/>
+      <c r="AG8" s="117" t="n"/>
+      <c r="AH8" s="119" t="n"/>
+      <c r="AI8" s="120" t="n"/>
     </row>
     <row r="9" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A9" s="113" t="n">
-        <v>5</v>
+      <c r="A9" s="113">
+        <f>IF($C9="","",ROW()-4)</f>
+        <v/>
       </c>
       <c r="B9" s="114" t="n"/>
       <c r="C9" s="115" t="n"/>
       <c r="D9" s="114" t="n"/>
-      <c r="E9" s="6" t="n"/>
-      <c r="F9" s="6" t="n"/>
-      <c r="G9" s="7" t="n"/>
-      <c r="H9" s="6" t="n"/>
-      <c r="I9" s="6" t="n"/>
-      <c r="J9" s="6" t="n"/>
-      <c r="K9" s="6" t="n"/>
-      <c r="L9" s="6" t="n"/>
-      <c r="M9" s="6" t="n"/>
-      <c r="N9" s="6" t="n"/>
-      <c r="O9" s="6" t="n"/>
-      <c r="P9" s="6" t="n"/>
-      <c r="Q9" s="6" t="n"/>
-      <c r="R9" s="6" t="n"/>
-      <c r="S9" s="6" t="n"/>
-      <c r="T9" s="6" t="n"/>
-      <c r="U9" s="6" t="n"/>
-      <c r="V9" s="6" t="n"/>
-      <c r="W9" s="6" t="n"/>
-      <c r="X9" s="6" t="n"/>
-      <c r="Y9" s="6" t="n"/>
-      <c r="Z9" s="6" t="n"/>
-      <c r="AA9" s="6" t="n"/>
-      <c r="AB9" s="6" t="n"/>
-      <c r="AC9" s="6" t="n"/>
-      <c r="AD9" s="6" t="n"/>
-      <c r="AE9" s="6" t="n"/>
-      <c r="AF9" s="6" t="n"/>
-      <c r="AG9" s="6" t="n"/>
-      <c r="AH9" s="26" t="n"/>
-      <c r="AI9" s="23" t="n"/>
+      <c r="E9" s="117" t="n"/>
+      <c r="F9" s="117" t="n"/>
+      <c r="G9" s="118" t="n"/>
+      <c r="H9" s="117" t="n"/>
+      <c r="I9" s="117" t="n"/>
+      <c r="J9" s="117" t="n"/>
+      <c r="K9" s="117" t="n"/>
+      <c r="L9" s="117" t="n"/>
+      <c r="M9" s="117" t="n"/>
+      <c r="N9" s="117" t="n"/>
+      <c r="O9" s="117" t="n"/>
+      <c r="P9" s="117" t="n"/>
+      <c r="Q9" s="117" t="n"/>
+      <c r="R9" s="117" t="n"/>
+      <c r="S9" s="117" t="n"/>
+      <c r="T9" s="117" t="n"/>
+      <c r="U9" s="117" t="n"/>
+      <c r="V9" s="117" t="n"/>
+      <c r="W9" s="117" t="n"/>
+      <c r="X9" s="117" t="n"/>
+      <c r="Y9" s="117" t="n"/>
+      <c r="Z9" s="117" t="n"/>
+      <c r="AA9" s="117" t="n"/>
+      <c r="AB9" s="117" t="n"/>
+      <c r="AC9" s="117" t="n"/>
+      <c r="AD9" s="117" t="n"/>
+      <c r="AE9" s="117" t="n"/>
+      <c r="AF9" s="117" t="n"/>
+      <c r="AG9" s="117" t="n"/>
+      <c r="AH9" s="119" t="n"/>
+      <c r="AI9" s="120" t="n"/>
     </row>
     <row r="10" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A10" s="118" t="n">
-        <v>6</v>
+      <c r="A10" s="122">
+        <f>IF($C10="","",ROW()-4)</f>
+        <v/>
       </c>
       <c r="B10" s="114" t="n"/>
       <c r="C10" s="115" t="n"/>
       <c r="D10" s="114" t="n"/>
-      <c r="E10" s="6" t="n"/>
-      <c r="F10" s="6" t="n"/>
-      <c r="G10" s="7" t="n"/>
-      <c r="H10" s="6" t="n"/>
-      <c r="I10" s="6" t="n"/>
-      <c r="J10" s="6" t="n"/>
-      <c r="K10" s="6" t="n"/>
-      <c r="L10" s="6" t="n"/>
-      <c r="M10" s="6" t="n"/>
-      <c r="N10" s="6" t="n"/>
-      <c r="O10" s="6" t="n"/>
-      <c r="P10" s="6" t="n"/>
-      <c r="Q10" s="6" t="n"/>
-      <c r="R10" s="6" t="n"/>
-      <c r="S10" s="6" t="n"/>
-      <c r="T10" s="6" t="n"/>
-      <c r="U10" s="6" t="n"/>
-      <c r="V10" s="6" t="n"/>
-      <c r="W10" s="6" t="n"/>
-      <c r="X10" s="6" t="n"/>
-      <c r="Y10" s="6" t="n"/>
-      <c r="Z10" s="6" t="n"/>
-      <c r="AA10" s="6" t="n"/>
-      <c r="AB10" s="6" t="n"/>
-      <c r="AC10" s="6" t="n"/>
-      <c r="AD10" s="6" t="n"/>
-      <c r="AE10" s="6" t="n"/>
-      <c r="AF10" s="6" t="n"/>
-      <c r="AG10" s="6" t="n"/>
-      <c r="AH10" s="26" t="n"/>
-      <c r="AI10" s="23" t="n"/>
+      <c r="E10" s="117" t="n"/>
+      <c r="F10" s="117" t="n"/>
+      <c r="G10" s="118" t="n"/>
+      <c r="H10" s="117" t="n"/>
+      <c r="I10" s="117" t="n"/>
+      <c r="J10" s="117" t="n"/>
+      <c r="K10" s="117" t="n"/>
+      <c r="L10" s="117" t="n"/>
+      <c r="M10" s="117" t="n"/>
+      <c r="N10" s="117" t="n"/>
+      <c r="O10" s="117" t="n"/>
+      <c r="P10" s="117" t="n"/>
+      <c r="Q10" s="117" t="n"/>
+      <c r="R10" s="117" t="n"/>
+      <c r="S10" s="117" t="n"/>
+      <c r="T10" s="117" t="n"/>
+      <c r="U10" s="117" t="n"/>
+      <c r="V10" s="117" t="n"/>
+      <c r="W10" s="117" t="n"/>
+      <c r="X10" s="117" t="n"/>
+      <c r="Y10" s="117" t="n"/>
+      <c r="Z10" s="117" t="n"/>
+      <c r="AA10" s="117" t="n"/>
+      <c r="AB10" s="117" t="n"/>
+      <c r="AC10" s="117" t="n"/>
+      <c r="AD10" s="117" t="n"/>
+      <c r="AE10" s="117" t="n"/>
+      <c r="AF10" s="117" t="n"/>
+      <c r="AG10" s="117" t="n"/>
+      <c r="AH10" s="119" t="n"/>
+      <c r="AI10" s="120" t="n"/>
     </row>
     <row r="11" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A11" s="118" t="n">
-        <v>7</v>
+      <c r="A11" s="122">
+        <f>IF($C11="","",ROW()-4)</f>
+        <v/>
       </c>
       <c r="B11" s="114" t="n"/>
       <c r="C11" s="115" t="n"/>
       <c r="D11" s="114" t="n"/>
-      <c r="E11" s="6" t="n"/>
-      <c r="F11" s="6" t="n"/>
-      <c r="G11" s="7" t="n"/>
-      <c r="H11" s="6" t="n"/>
-      <c r="I11" s="6" t="n"/>
-      <c r="J11" s="6" t="n"/>
-      <c r="K11" s="6" t="n"/>
-      <c r="L11" s="6" t="n"/>
-      <c r="M11" s="6" t="n"/>
-      <c r="N11" s="6" t="n"/>
-      <c r="O11" s="6" t="n"/>
-      <c r="P11" s="6" t="n"/>
-      <c r="Q11" s="6" t="n"/>
-      <c r="R11" s="6" t="n"/>
-      <c r="S11" s="6" t="n"/>
-      <c r="T11" s="6" t="n"/>
-      <c r="U11" s="6" t="n"/>
-      <c r="V11" s="6" t="n"/>
-      <c r="W11" s="6" t="n"/>
-      <c r="X11" s="6" t="n"/>
-      <c r="Y11" s="6" t="n"/>
-      <c r="Z11" s="6" t="n"/>
-      <c r="AA11" s="6" t="n"/>
-      <c r="AB11" s="6" t="n"/>
-      <c r="AC11" s="6" t="n"/>
-      <c r="AD11" s="6" t="n"/>
-      <c r="AE11" s="6" t="n"/>
-      <c r="AF11" s="6" t="n"/>
-      <c r="AG11" s="6" t="n"/>
-      <c r="AH11" s="26" t="n"/>
-      <c r="AI11" s="23" t="n"/>
+      <c r="E11" s="117" t="n"/>
+      <c r="F11" s="117" t="n"/>
+      <c r="G11" s="118" t="n"/>
+      <c r="H11" s="117" t="n"/>
+      <c r="I11" s="117" t="n"/>
+      <c r="J11" s="117" t="n"/>
+      <c r="K11" s="117" t="n"/>
+      <c r="L11" s="117" t="n"/>
+      <c r="M11" s="117" t="n"/>
+      <c r="N11" s="117" t="n"/>
+      <c r="O11" s="117" t="n"/>
+      <c r="P11" s="117" t="n"/>
+      <c r="Q11" s="117" t="n"/>
+      <c r="R11" s="117" t="n"/>
+      <c r="S11" s="117" t="n"/>
+      <c r="T11" s="117" t="n"/>
+      <c r="U11" s="117" t="n"/>
+      <c r="V11" s="117" t="n"/>
+      <c r="W11" s="117" t="n"/>
+      <c r="X11" s="117" t="n"/>
+      <c r="Y11" s="117" t="n"/>
+      <c r="Z11" s="117" t="n"/>
+      <c r="AA11" s="117" t="n"/>
+      <c r="AB11" s="117" t="n"/>
+      <c r="AC11" s="117" t="n"/>
+      <c r="AD11" s="117" t="n"/>
+      <c r="AE11" s="117" t="n"/>
+      <c r="AF11" s="117" t="n"/>
+      <c r="AG11" s="117" t="n"/>
+      <c r="AH11" s="119" t="n"/>
+      <c r="AI11" s="120" t="n"/>
     </row>
     <row r="12" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A12" s="118" t="n">
-        <v>8</v>
+      <c r="A12" s="122">
+        <f>IF($C12="","",ROW()-4)</f>
+        <v/>
       </c>
       <c r="B12" s="114" t="n"/>
       <c r="C12" s="115" t="n"/>
       <c r="D12" s="114" t="n"/>
-      <c r="E12" s="6" t="n"/>
-      <c r="F12" s="6" t="n"/>
-      <c r="G12" s="7" t="n"/>
-      <c r="H12" s="6" t="n"/>
-      <c r="I12" s="6" t="n"/>
-      <c r="J12" s="6" t="n"/>
-      <c r="K12" s="6" t="n"/>
-      <c r="L12" s="6" t="n"/>
-      <c r="M12" s="6" t="n"/>
-      <c r="N12" s="6" t="n"/>
-      <c r="O12" s="6" t="n"/>
-      <c r="P12" s="6" t="n"/>
-      <c r="Q12" s="6" t="n"/>
-      <c r="R12" s="6" t="n"/>
-      <c r="S12" s="6" t="n"/>
-      <c r="T12" s="6" t="n"/>
-      <c r="U12" s="6" t="n"/>
-      <c r="V12" s="6" t="n"/>
-      <c r="W12" s="6" t="n"/>
-      <c r="X12" s="6" t="n"/>
-      <c r="Y12" s="6" t="n"/>
-      <c r="Z12" s="6" t="n"/>
-      <c r="AA12" s="6" t="n"/>
-      <c r="AB12" s="6" t="n"/>
-      <c r="AC12" s="6" t="n"/>
-      <c r="AD12" s="6" t="n"/>
-      <c r="AE12" s="6" t="n"/>
-      <c r="AF12" s="6" t="n"/>
-      <c r="AG12" s="6" t="n"/>
-      <c r="AH12" s="26" t="n"/>
-      <c r="AI12" s="23" t="n"/>
+      <c r="E12" s="117" t="n"/>
+      <c r="F12" s="117" t="n"/>
+      <c r="G12" s="118" t="n"/>
+      <c r="H12" s="117" t="n"/>
+      <c r="I12" s="117" t="n"/>
+      <c r="J12" s="117" t="n"/>
+      <c r="K12" s="117" t="n"/>
+      <c r="L12" s="117" t="n"/>
+      <c r="M12" s="117" t="n"/>
+      <c r="N12" s="117" t="n"/>
+      <c r="O12" s="117" t="n"/>
+      <c r="P12" s="117" t="n"/>
+      <c r="Q12" s="117" t="n"/>
+      <c r="R12" s="117" t="n"/>
+      <c r="S12" s="117" t="n"/>
+      <c r="T12" s="117" t="n"/>
+      <c r="U12" s="117" t="n"/>
+      <c r="V12" s="117" t="n"/>
+      <c r="W12" s="117" t="n"/>
+      <c r="X12" s="117" t="n"/>
+      <c r="Y12" s="117" t="n"/>
+      <c r="Z12" s="117" t="n"/>
+      <c r="AA12" s="117" t="n"/>
+      <c r="AB12" s="117" t="n"/>
+      <c r="AC12" s="117" t="n"/>
+      <c r="AD12" s="117" t="n"/>
+      <c r="AE12" s="117" t="n"/>
+      <c r="AF12" s="117" t="n"/>
+      <c r="AG12" s="117" t="n"/>
+      <c r="AH12" s="119" t="n"/>
+      <c r="AI12" s="120" t="n"/>
     </row>
     <row r="13" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A13" s="118" t="n">
-        <v>9</v>
+      <c r="A13" s="122">
+        <f>IF($C13="","",ROW()-4)</f>
+        <v/>
       </c>
       <c r="B13" s="114" t="n"/>
       <c r="C13" s="115" t="n"/>
       <c r="D13" s="114" t="n"/>
-      <c r="E13" s="6" t="n"/>
-      <c r="F13" s="6" t="n"/>
-      <c r="G13" s="7" t="n"/>
-      <c r="H13" s="6" t="n"/>
-      <c r="I13" s="6" t="n"/>
-      <c r="J13" s="6" t="n"/>
-      <c r="K13" s="6" t="n"/>
-      <c r="L13" s="6" t="n"/>
-      <c r="M13" s="6" t="n"/>
-      <c r="N13" s="6" t="n"/>
-      <c r="O13" s="6" t="n"/>
-      <c r="P13" s="6" t="n"/>
-      <c r="Q13" s="6" t="n"/>
-      <c r="R13" s="6" t="n"/>
-      <c r="S13" s="6" t="n"/>
-      <c r="T13" s="6" t="n"/>
-      <c r="U13" s="6" t="n"/>
-      <c r="V13" s="6" t="n"/>
-      <c r="W13" s="6" t="n"/>
-      <c r="X13" s="6" t="n"/>
-      <c r="Y13" s="6" t="n"/>
-      <c r="Z13" s="6" t="n"/>
-      <c r="AA13" s="6" t="n"/>
-      <c r="AB13" s="6" t="n"/>
-      <c r="AC13" s="6" t="n"/>
-      <c r="AD13" s="6" t="n"/>
-      <c r="AE13" s="6" t="n"/>
-      <c r="AF13" s="6" t="n"/>
-      <c r="AG13" s="6" t="n"/>
-      <c r="AH13" s="26" t="n"/>
-      <c r="AI13" s="23" t="n"/>
+      <c r="E13" s="117" t="n"/>
+      <c r="F13" s="117" t="n"/>
+      <c r="G13" s="118" t="n"/>
+      <c r="H13" s="117" t="n"/>
+      <c r="I13" s="117" t="n"/>
+      <c r="J13" s="117" t="n"/>
+      <c r="K13" s="117" t="n"/>
+      <c r="L13" s="117" t="n"/>
+      <c r="M13" s="117" t="n"/>
+      <c r="N13" s="117" t="n"/>
+      <c r="O13" s="117" t="n"/>
+      <c r="P13" s="117" t="n"/>
+      <c r="Q13" s="117" t="n"/>
+      <c r="R13" s="117" t="n"/>
+      <c r="S13" s="117" t="n"/>
+      <c r="T13" s="117" t="n"/>
+      <c r="U13" s="117" t="n"/>
+      <c r="V13" s="117" t="n"/>
+      <c r="W13" s="117" t="n"/>
+      <c r="X13" s="117" t="n"/>
+      <c r="Y13" s="117" t="n"/>
+      <c r="Z13" s="117" t="n"/>
+      <c r="AA13" s="117" t="n"/>
+      <c r="AB13" s="117" t="n"/>
+      <c r="AC13" s="117" t="n"/>
+      <c r="AD13" s="117" t="n"/>
+      <c r="AE13" s="117" t="n"/>
+      <c r="AF13" s="117" t="n"/>
+      <c r="AG13" s="117" t="n"/>
+      <c r="AH13" s="119" t="n"/>
+      <c r="AI13" s="120" t="n"/>
     </row>
     <row r="14" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A14" s="118" t="n">
-        <v>10</v>
+      <c r="A14" s="122">
+        <f>IF($C14="","",ROW()-4)</f>
+        <v/>
       </c>
       <c r="B14" s="114" t="n"/>
       <c r="C14" s="115" t="n"/>
       <c r="D14" s="114" t="n"/>
-      <c r="E14" s="11" t="n"/>
-      <c r="F14" s="11" t="n"/>
-      <c r="G14" s="11" t="n"/>
-      <c r="H14" s="11" t="n"/>
-      <c r="I14" s="11" t="n"/>
-      <c r="J14" s="11" t="n"/>
-      <c r="K14" s="11" t="n"/>
-      <c r="L14" s="11" t="n"/>
-      <c r="M14" s="11" t="n"/>
-      <c r="N14" s="11" t="n"/>
-      <c r="O14" s="11" t="n"/>
-      <c r="P14" s="11" t="n"/>
-      <c r="Q14" s="11" t="n"/>
-      <c r="R14" s="11" t="n"/>
-      <c r="S14" s="11" t="n"/>
-      <c r="T14" s="11" t="n"/>
-      <c r="U14" s="11" t="n"/>
-      <c r="V14" s="11" t="n"/>
-      <c r="W14" s="11" t="n"/>
-      <c r="X14" s="11" t="n"/>
-      <c r="Y14" s="11" t="n"/>
-      <c r="Z14" s="11" t="n"/>
-      <c r="AA14" s="11" t="n"/>
-      <c r="AB14" s="11" t="n"/>
-      <c r="AC14" s="11" t="n"/>
-      <c r="AD14" s="11" t="n"/>
-      <c r="AE14" s="11" t="n"/>
-      <c r="AF14" s="11" t="n"/>
-      <c r="AG14" s="11" t="n"/>
-      <c r="AH14" s="11" t="n"/>
-      <c r="AI14" s="23" t="n"/>
+      <c r="E14" s="123" t="n"/>
+      <c r="F14" s="123" t="n"/>
+      <c r="G14" s="123" t="n"/>
+      <c r="H14" s="123" t="n"/>
+      <c r="I14" s="123" t="n"/>
+      <c r="J14" s="123" t="n"/>
+      <c r="K14" s="123" t="n"/>
+      <c r="L14" s="123" t="n"/>
+      <c r="M14" s="123" t="n"/>
+      <c r="N14" s="123" t="n"/>
+      <c r="O14" s="123" t="n"/>
+      <c r="P14" s="123" t="n"/>
+      <c r="Q14" s="123" t="n"/>
+      <c r="R14" s="123" t="n"/>
+      <c r="S14" s="123" t="n"/>
+      <c r="T14" s="123" t="n"/>
+      <c r="U14" s="123" t="n"/>
+      <c r="V14" s="123" t="n"/>
+      <c r="W14" s="123" t="n"/>
+      <c r="X14" s="123" t="n"/>
+      <c r="Y14" s="123" t="n"/>
+      <c r="Z14" s="123" t="n"/>
+      <c r="AA14" s="123" t="n"/>
+      <c r="AB14" s="123" t="n"/>
+      <c r="AC14" s="123" t="n"/>
+      <c r="AD14" s="123" t="n"/>
+      <c r="AE14" s="123" t="n"/>
+      <c r="AF14" s="123" t="n"/>
+      <c r="AG14" s="123" t="n"/>
+      <c r="AH14" s="123" t="n"/>
+      <c r="AI14" s="120" t="n"/>
     </row>
     <row r="15" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A15" s="118" t="n">
-        <v>11</v>
+      <c r="A15" s="122">
+        <f>IF($C15="","",ROW()-4)</f>
+        <v/>
       </c>
       <c r="B15" s="114" t="n"/>
       <c r="C15" s="115" t="n"/>
       <c r="D15" s="114" t="n"/>
-      <c r="E15" s="6" t="n"/>
-      <c r="F15" s="6" t="n"/>
-      <c r="G15" s="7" t="n"/>
-      <c r="H15" s="6" t="n"/>
-      <c r="I15" s="6" t="n"/>
-      <c r="J15" s="6" t="n"/>
-      <c r="K15" s="6" t="n"/>
-      <c r="L15" s="6" t="n"/>
-      <c r="M15" s="6" t="n"/>
-      <c r="N15" s="6" t="n"/>
-      <c r="O15" s="6" t="n"/>
-      <c r="P15" s="6" t="n"/>
-      <c r="Q15" s="6" t="n"/>
-      <c r="R15" s="6" t="n"/>
-      <c r="S15" s="6" t="n"/>
-      <c r="T15" s="6" t="n"/>
-      <c r="U15" s="6" t="n"/>
-      <c r="V15" s="6" t="n"/>
-      <c r="W15" s="6" t="n"/>
-      <c r="X15" s="6" t="n"/>
-      <c r="Y15" s="6" t="n"/>
-      <c r="Z15" s="6" t="n"/>
-      <c r="AA15" s="6" t="n"/>
-      <c r="AB15" s="6" t="n"/>
-      <c r="AC15" s="6" t="n"/>
-      <c r="AD15" s="6" t="n"/>
-      <c r="AE15" s="6" t="n"/>
-      <c r="AF15" s="6" t="n"/>
-      <c r="AG15" s="6" t="n"/>
-      <c r="AH15" s="26" t="n"/>
-      <c r="AI15" s="23" t="n"/>
+      <c r="E15" s="117" t="n"/>
+      <c r="F15" s="117" t="n"/>
+      <c r="G15" s="118" t="n"/>
+      <c r="H15" s="117" t="n"/>
+      <c r="I15" s="117" t="n"/>
+      <c r="J15" s="117" t="n"/>
+      <c r="K15" s="117" t="n"/>
+      <c r="L15" s="117" t="n"/>
+      <c r="M15" s="117" t="n"/>
+      <c r="N15" s="117" t="n"/>
+      <c r="O15" s="117" t="n"/>
+      <c r="P15" s="117" t="n"/>
+      <c r="Q15" s="117" t="n"/>
+      <c r="R15" s="117" t="n"/>
+      <c r="S15" s="117" t="n"/>
+      <c r="T15" s="117" t="n"/>
+      <c r="U15" s="117" t="n"/>
+      <c r="V15" s="117" t="n"/>
+      <c r="W15" s="117" t="n"/>
+      <c r="X15" s="117" t="n"/>
+      <c r="Y15" s="117" t="n"/>
+      <c r="Z15" s="117" t="n"/>
+      <c r="AA15" s="117" t="n"/>
+      <c r="AB15" s="117" t="n"/>
+      <c r="AC15" s="117" t="n"/>
+      <c r="AD15" s="117" t="n"/>
+      <c r="AE15" s="117" t="n"/>
+      <c r="AF15" s="117" t="n"/>
+      <c r="AG15" s="117" t="n"/>
+      <c r="AH15" s="119" t="n"/>
+      <c r="AI15" s="120" t="n"/>
     </row>
     <row r="16" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A16" s="113" t="n">
-        <v>12</v>
+      <c r="A16" s="113">
+        <f>IF($C16="","",ROW()-4)</f>
+        <v/>
       </c>
       <c r="B16" s="114" t="n"/>
       <c r="C16" s="115" t="n"/>
-      <c r="D16" s="119" t="n"/>
-      <c r="E16" s="6" t="n"/>
-      <c r="F16" s="6" t="n"/>
-      <c r="G16" s="7" t="n"/>
-      <c r="H16" s="6" t="n"/>
-      <c r="I16" s="6" t="n"/>
-      <c r="J16" s="6" t="n"/>
-      <c r="K16" s="6" t="n"/>
-      <c r="L16" s="6" t="n"/>
-      <c r="M16" s="6" t="n"/>
-      <c r="N16" s="6" t="n"/>
-      <c r="O16" s="6" t="n"/>
-      <c r="P16" s="6" t="n"/>
-      <c r="Q16" s="6" t="n"/>
-      <c r="R16" s="6" t="n"/>
-      <c r="S16" s="6" t="n"/>
-      <c r="T16" s="6" t="n"/>
-      <c r="U16" s="6" t="n"/>
-      <c r="V16" s="6" t="n"/>
-      <c r="W16" s="6" t="n"/>
-      <c r="X16" s="6" t="n"/>
-      <c r="Y16" s="6" t="n"/>
-      <c r="Z16" s="6" t="n"/>
-      <c r="AA16" s="6" t="n"/>
-      <c r="AB16" s="6" t="n"/>
-      <c r="AC16" s="6" t="n"/>
-      <c r="AD16" s="6" t="n"/>
-      <c r="AE16" s="6" t="n"/>
-      <c r="AF16" s="6" t="n"/>
-      <c r="AG16" s="6" t="n"/>
-      <c r="AH16" s="26" t="n"/>
-      <c r="AI16" s="23" t="n"/>
+      <c r="D16" s="124" t="n"/>
+      <c r="E16" s="117" t="n"/>
+      <c r="F16" s="117" t="n"/>
+      <c r="G16" s="118" t="n"/>
+      <c r="H16" s="117" t="n"/>
+      <c r="I16" s="117" t="n"/>
+      <c r="J16" s="117" t="n"/>
+      <c r="K16" s="117" t="n"/>
+      <c r="L16" s="117" t="n"/>
+      <c r="M16" s="117" t="n"/>
+      <c r="N16" s="117" t="n"/>
+      <c r="O16" s="117" t="n"/>
+      <c r="P16" s="117" t="n"/>
+      <c r="Q16" s="117" t="n"/>
+      <c r="R16" s="117" t="n"/>
+      <c r="S16" s="117" t="n"/>
+      <c r="T16" s="117" t="n"/>
+      <c r="U16" s="117" t="n"/>
+      <c r="V16" s="117" t="n"/>
+      <c r="W16" s="117" t="n"/>
+      <c r="X16" s="117" t="n"/>
+      <c r="Y16" s="117" t="n"/>
+      <c r="Z16" s="117" t="n"/>
+      <c r="AA16" s="117" t="n"/>
+      <c r="AB16" s="117" t="n"/>
+      <c r="AC16" s="117" t="n"/>
+      <c r="AD16" s="117" t="n"/>
+      <c r="AE16" s="117" t="n"/>
+      <c r="AF16" s="117" t="n"/>
+      <c r="AG16" s="117" t="n"/>
+      <c r="AH16" s="119" t="n"/>
+      <c r="AI16" s="120" t="n"/>
     </row>
     <row r="17" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A17" s="113" t="n">
-        <v>13</v>
+      <c r="A17" s="113">
+        <f>IF($C17="","",ROW()-4)</f>
+        <v/>
       </c>
       <c r="B17" s="114" t="n"/>
       <c r="C17" s="115" t="n"/>
       <c r="D17" s="114" t="n"/>
-      <c r="E17" s="6" t="n"/>
-      <c r="F17" s="6" t="n"/>
-      <c r="G17" s="7" t="n"/>
-      <c r="H17" s="6" t="n"/>
-      <c r="I17" s="6" t="n"/>
-      <c r="J17" s="6" t="n"/>
-      <c r="K17" s="6" t="n"/>
-      <c r="L17" s="6" t="n"/>
-      <c r="M17" s="6" t="n"/>
-      <c r="N17" s="6" t="n"/>
-      <c r="O17" s="6" t="n"/>
-      <c r="P17" s="6" t="n"/>
-      <c r="Q17" s="6" t="n"/>
-      <c r="R17" s="6" t="n"/>
-      <c r="S17" s="6" t="n"/>
-      <c r="T17" s="6" t="n"/>
-      <c r="U17" s="6" t="n"/>
-      <c r="V17" s="6" t="n"/>
-      <c r="W17" s="6" t="n"/>
-      <c r="X17" s="6" t="n"/>
-      <c r="Y17" s="6" t="n"/>
-      <c r="Z17" s="6" t="n"/>
-      <c r="AA17" s="6" t="n"/>
-      <c r="AB17" s="6" t="n"/>
-      <c r="AC17" s="6" t="n"/>
-      <c r="AD17" s="6" t="n"/>
-      <c r="AE17" s="6" t="n"/>
-      <c r="AF17" s="6" t="n"/>
-      <c r="AG17" s="6" t="n"/>
-      <c r="AH17" s="26" t="n"/>
-      <c r="AI17" s="23" t="n"/>
+      <c r="E17" s="117" t="n"/>
+      <c r="F17" s="117" t="n"/>
+      <c r="G17" s="118" t="n"/>
+      <c r="H17" s="117" t="n"/>
+      <c r="I17" s="117" t="n"/>
+      <c r="J17" s="117" t="n"/>
+      <c r="K17" s="117" t="n"/>
+      <c r="L17" s="117" t="n"/>
+      <c r="M17" s="117" t="n"/>
+      <c r="N17" s="117" t="n"/>
+      <c r="O17" s="117" t="n"/>
+      <c r="P17" s="117" t="n"/>
+      <c r="Q17" s="117" t="n"/>
+      <c r="R17" s="117" t="n"/>
+      <c r="S17" s="117" t="n"/>
+      <c r="T17" s="117" t="n"/>
+      <c r="U17" s="117" t="n"/>
+      <c r="V17" s="117" t="n"/>
+      <c r="W17" s="117" t="n"/>
+      <c r="X17" s="117" t="n"/>
+      <c r="Y17" s="117" t="n"/>
+      <c r="Z17" s="117" t="n"/>
+      <c r="AA17" s="117" t="n"/>
+      <c r="AB17" s="117" t="n"/>
+      <c r="AC17" s="117" t="n"/>
+      <c r="AD17" s="117" t="n"/>
+      <c r="AE17" s="117" t="n"/>
+      <c r="AF17" s="117" t="n"/>
+      <c r="AG17" s="117" t="n"/>
+      <c r="AH17" s="119" t="n"/>
+      <c r="AI17" s="120" t="n"/>
     </row>
     <row r="18" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A18" s="113" t="n">
-        <v>14</v>
+      <c r="A18" s="113">
+        <f>IF($C18="","",ROW()-4)</f>
+        <v/>
       </c>
       <c r="B18" s="114" t="n"/>
       <c r="C18" s="115" t="n"/>
-      <c r="D18" s="119" t="n"/>
-      <c r="E18" s="6" t="n"/>
-      <c r="F18" s="6" t="n"/>
-      <c r="G18" s="7" t="n"/>
-      <c r="H18" s="6" t="n"/>
-      <c r="I18" s="6" t="n"/>
-      <c r="J18" s="6" t="n"/>
-      <c r="K18" s="6" t="n"/>
-      <c r="L18" s="6" t="n"/>
-      <c r="M18" s="6" t="n"/>
-      <c r="N18" s="6" t="n"/>
-      <c r="O18" s="6" t="n"/>
-      <c r="P18" s="6" t="n"/>
-      <c r="Q18" s="6" t="n"/>
-      <c r="R18" s="6" t="n"/>
-      <c r="S18" s="6" t="n"/>
-      <c r="T18" s="6" t="n"/>
-      <c r="U18" s="6" t="n"/>
-      <c r="V18" s="6" t="n"/>
-      <c r="W18" s="6" t="n"/>
-      <c r="X18" s="6" t="n"/>
-      <c r="Y18" s="6" t="n"/>
-      <c r="Z18" s="6" t="n"/>
-      <c r="AA18" s="6" t="n"/>
-      <c r="AB18" s="6" t="n"/>
-      <c r="AC18" s="6" t="n"/>
-      <c r="AD18" s="6" t="n"/>
-      <c r="AE18" s="6" t="n"/>
-      <c r="AF18" s="6" t="n"/>
-      <c r="AG18" s="6" t="n"/>
-      <c r="AH18" s="26" t="n"/>
-      <c r="AI18" s="23" t="n"/>
+      <c r="D18" s="124" t="n"/>
+      <c r="E18" s="117" t="n"/>
+      <c r="F18" s="117" t="n"/>
+      <c r="G18" s="118" t="n"/>
+      <c r="H18" s="117" t="n"/>
+      <c r="I18" s="117" t="n"/>
+      <c r="J18" s="117" t="n"/>
+      <c r="K18" s="117" t="n"/>
+      <c r="L18" s="117" t="n"/>
+      <c r="M18" s="117" t="n"/>
+      <c r="N18" s="117" t="n"/>
+      <c r="O18" s="117" t="n"/>
+      <c r="P18" s="117" t="n"/>
+      <c r="Q18" s="117" t="n"/>
+      <c r="R18" s="117" t="n"/>
+      <c r="S18" s="117" t="n"/>
+      <c r="T18" s="117" t="n"/>
+      <c r="U18" s="117" t="n"/>
+      <c r="V18" s="117" t="n"/>
+      <c r="W18" s="117" t="n"/>
+      <c r="X18" s="117" t="n"/>
+      <c r="Y18" s="117" t="n"/>
+      <c r="Z18" s="117" t="n"/>
+      <c r="AA18" s="117" t="n"/>
+      <c r="AB18" s="117" t="n"/>
+      <c r="AC18" s="117" t="n"/>
+      <c r="AD18" s="117" t="n"/>
+      <c r="AE18" s="117" t="n"/>
+      <c r="AF18" s="117" t="n"/>
+      <c r="AG18" s="117" t="n"/>
+      <c r="AH18" s="119" t="n"/>
+      <c r="AI18" s="120" t="n"/>
     </row>
     <row r="19" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A19" s="113" t="n">
-        <v>15</v>
+      <c r="A19" s="113">
+        <f>IF($C19="","",ROW()-4)</f>
+        <v/>
       </c>
       <c r="B19" s="114" t="n"/>
       <c r="C19" s="115" t="n"/>
       <c r="D19" s="114" t="n"/>
-      <c r="E19" s="6" t="n"/>
-      <c r="F19" s="6" t="n"/>
-      <c r="G19" s="7" t="n"/>
-      <c r="H19" s="6" t="n"/>
-      <c r="I19" s="6" t="n"/>
-      <c r="J19" s="6" t="n"/>
-      <c r="K19" s="6" t="n"/>
-      <c r="L19" s="6" t="n"/>
-      <c r="M19" s="6" t="n"/>
-      <c r="N19" s="6" t="n"/>
-      <c r="O19" s="6" t="n"/>
-      <c r="P19" s="6" t="n"/>
-      <c r="Q19" s="6" t="n"/>
-      <c r="R19" s="6" t="n"/>
-      <c r="S19" s="6" t="n"/>
-      <c r="T19" s="6" t="n"/>
-      <c r="U19" s="6" t="n"/>
-      <c r="V19" s="6" t="n"/>
-      <c r="W19" s="6" t="n"/>
-      <c r="X19" s="6" t="n"/>
-      <c r="Y19" s="6" t="n"/>
-      <c r="Z19" s="6" t="n"/>
-      <c r="AA19" s="6" t="n"/>
-      <c r="AB19" s="6" t="n"/>
-      <c r="AC19" s="6" t="n"/>
-      <c r="AD19" s="6" t="n"/>
-      <c r="AE19" s="6" t="n"/>
-      <c r="AF19" s="6" t="n"/>
-      <c r="AG19" s="6" t="n"/>
-      <c r="AH19" s="26" t="n"/>
-      <c r="AI19" s="23" t="n"/>
+      <c r="E19" s="117" t="n"/>
+      <c r="F19" s="117" t="n"/>
+      <c r="G19" s="118" t="n"/>
+      <c r="H19" s="117" t="n"/>
+      <c r="I19" s="117" t="n"/>
+      <c r="J19" s="117" t="n"/>
+      <c r="K19" s="117" t="n"/>
+      <c r="L19" s="117" t="n"/>
+      <c r="M19" s="117" t="n"/>
+      <c r="N19" s="117" t="n"/>
+      <c r="O19" s="117" t="n"/>
+      <c r="P19" s="117" t="n"/>
+      <c r="Q19" s="117" t="n"/>
+      <c r="R19" s="117" t="n"/>
+      <c r="S19" s="117" t="n"/>
+      <c r="T19" s="117" t="n"/>
+      <c r="U19" s="117" t="n"/>
+      <c r="V19" s="117" t="n"/>
+      <c r="W19" s="117" t="n"/>
+      <c r="X19" s="117" t="n"/>
+      <c r="Y19" s="117" t="n"/>
+      <c r="Z19" s="117" t="n"/>
+      <c r="AA19" s="117" t="n"/>
+      <c r="AB19" s="117" t="n"/>
+      <c r="AC19" s="117" t="n"/>
+      <c r="AD19" s="117" t="n"/>
+      <c r="AE19" s="117" t="n"/>
+      <c r="AF19" s="117" t="n"/>
+      <c r="AG19" s="117" t="n"/>
+      <c r="AH19" s="119" t="n"/>
+      <c r="AI19" s="120" t="n"/>
     </row>
     <row r="20" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A20" s="113" t="n">
-        <v>16</v>
+      <c r="A20" s="113">
+        <f>IF($C20="","",ROW()-4)</f>
+        <v/>
       </c>
       <c r="B20" s="114" t="n"/>
       <c r="C20" s="115" t="n"/>
       <c r="D20" s="114" t="n"/>
-      <c r="E20" s="27" t="n"/>
-      <c r="F20" s="27" t="n"/>
-      <c r="G20" s="28" t="n"/>
-      <c r="H20" s="27" t="n"/>
-      <c r="I20" s="27" t="n"/>
-      <c r="J20" s="27" t="n"/>
-      <c r="K20" s="27" t="n"/>
-      <c r="L20" s="27" t="n"/>
-      <c r="M20" s="27" t="n"/>
-      <c r="N20" s="27" t="n"/>
-      <c r="O20" s="27" t="n"/>
-      <c r="P20" s="27" t="n"/>
-      <c r="Q20" s="27" t="n"/>
-      <c r="R20" s="27" t="n"/>
-      <c r="S20" s="27" t="n"/>
-      <c r="T20" s="27" t="n"/>
-      <c r="U20" s="27" t="n"/>
-      <c r="V20" s="27" t="n"/>
-      <c r="W20" s="27" t="n"/>
-      <c r="X20" s="27" t="n"/>
-      <c r="Y20" s="27" t="n"/>
-      <c r="Z20" s="27" t="n"/>
-      <c r="AA20" s="27" t="n"/>
-      <c r="AB20" s="27" t="n"/>
-      <c r="AC20" s="27" t="n"/>
-      <c r="AD20" s="27" t="n"/>
-      <c r="AE20" s="27" t="n"/>
-      <c r="AF20" s="27" t="n"/>
-      <c r="AG20" s="27" t="n"/>
-      <c r="AH20" s="29" t="n"/>
-      <c r="AI20" s="23" t="n"/>
+      <c r="E20" s="125" t="n"/>
+      <c r="F20" s="125" t="n"/>
+      <c r="G20" s="126" t="n"/>
+      <c r="H20" s="125" t="n"/>
+      <c r="I20" s="125" t="n"/>
+      <c r="J20" s="125" t="n"/>
+      <c r="K20" s="125" t="n"/>
+      <c r="L20" s="125" t="n"/>
+      <c r="M20" s="125" t="n"/>
+      <c r="N20" s="125" t="n"/>
+      <c r="O20" s="125" t="n"/>
+      <c r="P20" s="125" t="n"/>
+      <c r="Q20" s="125" t="n"/>
+      <c r="R20" s="125" t="n"/>
+      <c r="S20" s="125" t="n"/>
+      <c r="T20" s="125" t="n"/>
+      <c r="U20" s="125" t="n"/>
+      <c r="V20" s="125" t="n"/>
+      <c r="W20" s="125" t="n"/>
+      <c r="X20" s="125" t="n"/>
+      <c r="Y20" s="125" t="n"/>
+      <c r="Z20" s="125" t="n"/>
+      <c r="AA20" s="125" t="n"/>
+      <c r="AB20" s="125" t="n"/>
+      <c r="AC20" s="125" t="n"/>
+      <c r="AD20" s="125" t="n"/>
+      <c r="AE20" s="125" t="n"/>
+      <c r="AF20" s="125" t="n"/>
+      <c r="AG20" s="125" t="n"/>
+      <c r="AH20" s="127" t="n"/>
+      <c r="AI20" s="120" t="n"/>
     </row>
     <row r="21" ht="16.2" customHeight="1" thickBot="1">
       <c r="A21" s="12" t="n"/>
@@ -2927,139 +3006,139 @@
           <t>CREW 2</t>
         </is>
       </c>
-      <c r="B22" s="120" t="n"/>
-      <c r="C22" s="120" t="n"/>
-      <c r="D22" s="120" t="n"/>
+      <c r="B22" s="128" t="n"/>
+      <c r="C22" s="128" t="n"/>
+      <c r="D22" s="128" t="n"/>
       <c r="E22" s="30">
-        <f>IF(1&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1),"ddd"),"")</f>
+        <f>IF(1&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+0,"ddd"),"")</f>
         <v/>
       </c>
       <c r="F22" s="30">
-        <f>IF(2&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,2),"ddd"),"")</f>
+        <f>IF(2&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+1,"ddd"),"")</f>
         <v/>
       </c>
       <c r="G22" s="30">
-        <f>IF(3&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,3),"ddd"),"")</f>
+        <f>IF(3&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+2,"ddd"),"")</f>
         <v/>
       </c>
       <c r="H22" s="30">
-        <f>IF(4&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,4),"ddd"),"")</f>
+        <f>IF(4&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+3,"ddd"),"")</f>
         <v/>
       </c>
       <c r="I22" s="30">
-        <f>IF(5&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,5),"ddd"),"")</f>
+        <f>IF(5&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+4,"ddd"),"")</f>
         <v/>
       </c>
       <c r="J22" s="30">
-        <f>IF(6&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,6),"ddd"),"")</f>
+        <f>IF(6&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+5,"ddd"),"")</f>
         <v/>
       </c>
       <c r="K22" s="30">
-        <f>IF(7&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,7),"ddd"),"")</f>
+        <f>IF(7&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+6,"ddd"),"")</f>
         <v/>
       </c>
       <c r="L22" s="30">
-        <f>IF(8&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,8),"ddd"),"")</f>
+        <f>IF(8&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+7,"ddd"),"")</f>
         <v/>
       </c>
       <c r="M22" s="30">
-        <f>IF(9&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,9),"ddd"),"")</f>
+        <f>IF(9&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+8,"ddd"),"")</f>
         <v/>
       </c>
       <c r="N22" s="30">
-        <f>IF(10&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,10),"ddd"),"")</f>
+        <f>IF(10&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+9,"ddd"),"")</f>
         <v/>
       </c>
       <c r="O22" s="30">
-        <f>IF(11&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,11),"ddd"),"")</f>
+        <f>IF(11&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+10,"ddd"),"")</f>
         <v/>
       </c>
       <c r="P22" s="30">
-        <f>IF(12&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,12),"ddd"),"")</f>
+        <f>IF(12&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+11,"ddd"),"")</f>
         <v/>
       </c>
       <c r="Q22" s="30">
-        <f>IF(13&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,13),"ddd"),"")</f>
+        <f>IF(13&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+12,"ddd"),"")</f>
         <v/>
       </c>
       <c r="R22" s="30">
-        <f>IF(14&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,14),"ddd"),"")</f>
+        <f>IF(14&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+13,"ddd"),"")</f>
         <v/>
       </c>
       <c r="S22" s="30">
-        <f>IF(15&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,15),"ddd"),"")</f>
+        <f>IF(15&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+14,"ddd"),"")</f>
         <v/>
       </c>
       <c r="T22" s="30">
-        <f>IF(16&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,16),"ddd"),"")</f>
+        <f>IF(16&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+15,"ddd"),"")</f>
         <v/>
       </c>
       <c r="U22" s="30">
-        <f>IF(17&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,17),"ddd"),"")</f>
+        <f>IF(17&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+16,"ddd"),"")</f>
         <v/>
       </c>
       <c r="V22" s="30">
-        <f>IF(18&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,18),"ddd"),"")</f>
+        <f>IF(18&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+17,"ddd"),"")</f>
         <v/>
       </c>
       <c r="W22" s="30">
-        <f>IF(19&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,19),"ddd"),"")</f>
+        <f>IF(19&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+18,"ddd"),"")</f>
         <v/>
       </c>
       <c r="X22" s="30">
-        <f>IF(20&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,20),"ddd"),"")</f>
+        <f>IF(20&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+19,"ddd"),"")</f>
         <v/>
       </c>
       <c r="Y22" s="30">
-        <f>IF(21&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,21),"ddd"),"")</f>
+        <f>IF(21&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+20,"ddd"),"")</f>
         <v/>
       </c>
       <c r="Z22" s="30">
-        <f>IF(22&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,22),"ddd"),"")</f>
+        <f>IF(22&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+21,"ddd"),"")</f>
         <v/>
       </c>
       <c r="AA22" s="30">
-        <f>IF(23&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,23),"ddd"),"")</f>
+        <f>IF(23&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+22,"ddd"),"")</f>
         <v/>
       </c>
       <c r="AB22" s="30">
-        <f>IF(24&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,24),"ddd"),"")</f>
+        <f>IF(24&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+23,"ddd"),"")</f>
         <v/>
       </c>
       <c r="AC22" s="30">
-        <f>IF(25&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,25),"ddd"),"")</f>
+        <f>IF(25&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+24,"ddd"),"")</f>
         <v/>
       </c>
       <c r="AD22" s="30">
-        <f>IF(26&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,26),"ddd"),"")</f>
+        <f>IF(26&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+25,"ddd"),"")</f>
         <v/>
       </c>
       <c r="AE22" s="30">
-        <f>IF(27&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,27),"ddd"),"")</f>
+        <f>IF(27&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+26,"ddd"),"")</f>
         <v/>
       </c>
       <c r="AF22" s="30">
-        <f>IF(28&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,28),"ddd"),"")</f>
+        <f>IF(28&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+27,"ddd"),"")</f>
         <v/>
       </c>
       <c r="AG22" s="30">
-        <f>IF(29&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,29),"ddd"),"")</f>
+        <f>IF(29&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+28,"ddd"),"")</f>
         <v/>
       </c>
       <c r="AH22" s="30">
-        <f>IF(30&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,30),"ddd"),"")</f>
+        <f>IF(30&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+29,"ddd"),"")</f>
         <v/>
       </c>
       <c r="AI22" s="31">
-        <f>IF(31&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,31),"ddd"),"")</f>
+        <f>IF(31&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+30,"ddd"),"")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A23" s="121" t="n"/>
-      <c r="B23" s="122" t="n"/>
-      <c r="C23" s="122" t="n"/>
-      <c r="D23" s="122" t="n"/>
+      <c r="A23" s="129" t="n"/>
+      <c r="B23" s="130" t="n"/>
+      <c r="C23" s="130" t="n"/>
+      <c r="D23" s="130" t="n"/>
       <c r="E23" s="2">
         <f>IF(1&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),1,"")</f>
         <v/>
@@ -3186,808 +3265,825 @@
       </c>
     </row>
     <row r="24" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A24" s="113" t="n">
-        <v>1</v>
+      <c r="A24" s="113">
+        <f>IF($C24="","",ROW()-23)</f>
+        <v/>
       </c>
       <c r="B24" s="114" t="n"/>
       <c r="C24" s="115" t="n"/>
       <c r="D24" s="114" t="n"/>
-      <c r="E24" s="6" t="n"/>
-      <c r="F24" s="6" t="n"/>
-      <c r="G24" s="6" t="n"/>
-      <c r="H24" s="6" t="n"/>
-      <c r="I24" s="6" t="n"/>
-      <c r="J24" s="6" t="n"/>
-      <c r="K24" s="6" t="n"/>
-      <c r="L24" s="6" t="n"/>
-      <c r="M24" s="6" t="n"/>
-      <c r="N24" s="6" t="n"/>
-      <c r="O24" s="6" t="n"/>
-      <c r="P24" s="6" t="n"/>
-      <c r="Q24" s="6" t="n"/>
-      <c r="R24" s="6" t="n"/>
-      <c r="S24" s="6" t="n"/>
-      <c r="T24" s="6" t="n"/>
-      <c r="U24" s="6" t="n"/>
-      <c r="V24" s="6" t="n"/>
-      <c r="W24" s="6" t="n"/>
-      <c r="X24" s="6" t="n"/>
-      <c r="Y24" s="6" t="n"/>
-      <c r="Z24" s="6" t="n"/>
-      <c r="AA24" s="6" t="n"/>
-      <c r="AB24" s="6" t="n"/>
-      <c r="AC24" s="6" t="n"/>
-      <c r="AD24" s="6" t="n"/>
-      <c r="AE24" s="6" t="n"/>
-      <c r="AF24" s="6" t="n"/>
-      <c r="AG24" s="6" t="n"/>
-      <c r="AH24" s="6" t="n"/>
-      <c r="AI24" s="26" t="n"/>
+      <c r="E24" s="117" t="n"/>
+      <c r="F24" s="117" t="n"/>
+      <c r="G24" s="117" t="n"/>
+      <c r="H24" s="117" t="n"/>
+      <c r="I24" s="117" t="n"/>
+      <c r="J24" s="117" t="n"/>
+      <c r="K24" s="117" t="n"/>
+      <c r="L24" s="117" t="n"/>
+      <c r="M24" s="117" t="n"/>
+      <c r="N24" s="117" t="n"/>
+      <c r="O24" s="117" t="n"/>
+      <c r="P24" s="117" t="n"/>
+      <c r="Q24" s="117" t="n"/>
+      <c r="R24" s="117" t="n"/>
+      <c r="S24" s="117" t="n"/>
+      <c r="T24" s="117" t="n"/>
+      <c r="U24" s="117" t="n"/>
+      <c r="V24" s="117" t="n"/>
+      <c r="W24" s="117" t="n"/>
+      <c r="X24" s="117" t="n"/>
+      <c r="Y24" s="117" t="n"/>
+      <c r="Z24" s="117" t="n"/>
+      <c r="AA24" s="117" t="n"/>
+      <c r="AB24" s="117" t="n"/>
+      <c r="AC24" s="117" t="n"/>
+      <c r="AD24" s="117" t="n"/>
+      <c r="AE24" s="117" t="n"/>
+      <c r="AF24" s="117" t="n"/>
+      <c r="AG24" s="117" t="n"/>
+      <c r="AH24" s="117" t="n"/>
+      <c r="AI24" s="119" t="n"/>
     </row>
     <row r="25" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A25" s="113" t="n">
-        <v>2</v>
+      <c r="A25" s="113">
+        <f>IF($C25="","",ROW()-23)</f>
+        <v/>
       </c>
       <c r="B25" s="114" t="n"/>
       <c r="C25" s="115" t="n"/>
       <c r="D25" s="114" t="n"/>
-      <c r="E25" s="6" t="n"/>
-      <c r="F25" s="6" t="n"/>
-      <c r="G25" s="6" t="n"/>
-      <c r="H25" s="6" t="n"/>
-      <c r="I25" s="6" t="n"/>
-      <c r="J25" s="6" t="n"/>
-      <c r="K25" s="6" t="n"/>
-      <c r="L25" s="6" t="n"/>
-      <c r="M25" s="6" t="n"/>
-      <c r="N25" s="6" t="n"/>
-      <c r="O25" s="6" t="n"/>
-      <c r="P25" s="6" t="n"/>
-      <c r="Q25" s="6" t="n"/>
-      <c r="R25" s="6" t="n"/>
-      <c r="S25" s="6" t="n"/>
-      <c r="T25" s="6" t="n"/>
-      <c r="U25" s="6" t="n"/>
-      <c r="V25" s="6" t="n"/>
-      <c r="W25" s="6" t="n"/>
-      <c r="X25" s="6" t="n"/>
-      <c r="Y25" s="6" t="n"/>
-      <c r="Z25" s="6" t="n"/>
-      <c r="AA25" s="6" t="n"/>
-      <c r="AB25" s="6" t="n"/>
-      <c r="AC25" s="6" t="n"/>
-      <c r="AD25" s="6" t="n"/>
-      <c r="AE25" s="6" t="n"/>
-      <c r="AF25" s="6" t="n"/>
-      <c r="AG25" s="6" t="n"/>
-      <c r="AH25" s="6" t="n"/>
-      <c r="AI25" s="26" t="n"/>
+      <c r="E25" s="117" t="n"/>
+      <c r="F25" s="117" t="n"/>
+      <c r="G25" s="117" t="n"/>
+      <c r="H25" s="117" t="n"/>
+      <c r="I25" s="117" t="n"/>
+      <c r="J25" s="117" t="n"/>
+      <c r="K25" s="117" t="n"/>
+      <c r="L25" s="117" t="n"/>
+      <c r="M25" s="117" t="n"/>
+      <c r="N25" s="117" t="n"/>
+      <c r="O25" s="117" t="n"/>
+      <c r="P25" s="117" t="n"/>
+      <c r="Q25" s="117" t="n"/>
+      <c r="R25" s="117" t="n"/>
+      <c r="S25" s="117" t="n"/>
+      <c r="T25" s="117" t="n"/>
+      <c r="U25" s="117" t="n"/>
+      <c r="V25" s="117" t="n"/>
+      <c r="W25" s="117" t="n"/>
+      <c r="X25" s="117" t="n"/>
+      <c r="Y25" s="117" t="n"/>
+      <c r="Z25" s="117" t="n"/>
+      <c r="AA25" s="117" t="n"/>
+      <c r="AB25" s="117" t="n"/>
+      <c r="AC25" s="117" t="n"/>
+      <c r="AD25" s="117" t="n"/>
+      <c r="AE25" s="117" t="n"/>
+      <c r="AF25" s="117" t="n"/>
+      <c r="AG25" s="117" t="n"/>
+      <c r="AH25" s="117" t="n"/>
+      <c r="AI25" s="119" t="n"/>
     </row>
     <row r="26" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A26" s="113" t="n">
-        <v>3</v>
+      <c r="A26" s="113">
+        <f>IF($C26="","",ROW()-23)</f>
+        <v/>
       </c>
       <c r="B26" s="114" t="n"/>
       <c r="C26" s="115" t="n"/>
       <c r="D26" s="116" t="n"/>
-      <c r="E26" s="6" t="n"/>
-      <c r="F26" s="6" t="n"/>
-      <c r="G26" s="6" t="n"/>
-      <c r="H26" s="6" t="n"/>
-      <c r="I26" s="6" t="n"/>
-      <c r="J26" s="6" t="n"/>
-      <c r="K26" s="6" t="n"/>
-      <c r="L26" s="6" t="n"/>
-      <c r="M26" s="6" t="n"/>
-      <c r="N26" s="6" t="n"/>
-      <c r="O26" s="6" t="n"/>
-      <c r="P26" s="6" t="n"/>
-      <c r="Q26" s="6" t="n"/>
-      <c r="R26" s="6" t="n"/>
-      <c r="S26" s="6" t="n"/>
-      <c r="T26" s="6" t="n"/>
-      <c r="U26" s="6" t="n"/>
-      <c r="V26" s="6" t="n"/>
-      <c r="W26" s="6" t="n"/>
-      <c r="X26" s="6" t="n"/>
-      <c r="Y26" s="6" t="n"/>
-      <c r="Z26" s="6" t="n"/>
-      <c r="AA26" s="6" t="n"/>
-      <c r="AB26" s="6" t="n"/>
-      <c r="AC26" s="6" t="n"/>
-      <c r="AD26" s="6" t="n"/>
-      <c r="AE26" s="6" t="n"/>
-      <c r="AF26" s="6" t="n"/>
-      <c r="AG26" s="6" t="n"/>
-      <c r="AH26" s="6" t="n"/>
-      <c r="AI26" s="26" t="n"/>
+      <c r="E26" s="117" t="n"/>
+      <c r="F26" s="117" t="n"/>
+      <c r="G26" s="117" t="n"/>
+      <c r="H26" s="117" t="n"/>
+      <c r="I26" s="117" t="n"/>
+      <c r="J26" s="117" t="n"/>
+      <c r="K26" s="117" t="n"/>
+      <c r="L26" s="117" t="n"/>
+      <c r="M26" s="117" t="n"/>
+      <c r="N26" s="117" t="n"/>
+      <c r="O26" s="117" t="n"/>
+      <c r="P26" s="117" t="n"/>
+      <c r="Q26" s="117" t="n"/>
+      <c r="R26" s="117" t="n"/>
+      <c r="S26" s="117" t="n"/>
+      <c r="T26" s="117" t="n"/>
+      <c r="U26" s="117" t="n"/>
+      <c r="V26" s="117" t="n"/>
+      <c r="W26" s="117" t="n"/>
+      <c r="X26" s="117" t="n"/>
+      <c r="Y26" s="117" t="n"/>
+      <c r="Z26" s="117" t="n"/>
+      <c r="AA26" s="117" t="n"/>
+      <c r="AB26" s="117" t="n"/>
+      <c r="AC26" s="117" t="n"/>
+      <c r="AD26" s="117" t="n"/>
+      <c r="AE26" s="117" t="n"/>
+      <c r="AF26" s="117" t="n"/>
+      <c r="AG26" s="117" t="n"/>
+      <c r="AH26" s="117" t="n"/>
+      <c r="AI26" s="119" t="n"/>
     </row>
     <row r="27" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A27" s="113" t="n">
-        <v>4</v>
+      <c r="A27" s="113">
+        <f>IF($C27="","",ROW()-23)</f>
+        <v/>
       </c>
       <c r="B27" s="114" t="n"/>
       <c r="C27" s="115" t="n"/>
       <c r="D27" s="116" t="n"/>
-      <c r="E27" s="6" t="n"/>
-      <c r="F27" s="6" t="n"/>
-      <c r="G27" s="6" t="n"/>
-      <c r="H27" s="6" t="n"/>
-      <c r="I27" s="6" t="n"/>
-      <c r="J27" s="6" t="n"/>
-      <c r="K27" s="6" t="n"/>
-      <c r="L27" s="6" t="n"/>
-      <c r="M27" s="6" t="n"/>
-      <c r="N27" s="6" t="n"/>
-      <c r="O27" s="6" t="n"/>
-      <c r="P27" s="6" t="n"/>
-      <c r="Q27" s="6" t="n"/>
-      <c r="R27" s="6" t="n"/>
-      <c r="S27" s="6" t="n"/>
-      <c r="T27" s="6" t="n"/>
-      <c r="U27" s="6" t="n"/>
-      <c r="V27" s="6" t="n"/>
-      <c r="W27" s="6" t="n"/>
-      <c r="X27" s="6" t="n"/>
-      <c r="Y27" s="6" t="n"/>
-      <c r="Z27" s="6" t="n"/>
-      <c r="AA27" s="6" t="n"/>
-      <c r="AB27" s="6" t="n"/>
-      <c r="AC27" s="6" t="n"/>
-      <c r="AD27" s="6" t="n"/>
-      <c r="AE27" s="6" t="n"/>
-      <c r="AF27" s="6" t="n"/>
-      <c r="AG27" s="6" t="n"/>
-      <c r="AH27" s="6" t="n"/>
-      <c r="AI27" s="26" t="n"/>
+      <c r="E27" s="117" t="n"/>
+      <c r="F27" s="117" t="n"/>
+      <c r="G27" s="117" t="n"/>
+      <c r="H27" s="117" t="n"/>
+      <c r="I27" s="117" t="n"/>
+      <c r="J27" s="117" t="n"/>
+      <c r="K27" s="117" t="n"/>
+      <c r="L27" s="117" t="n"/>
+      <c r="M27" s="117" t="n"/>
+      <c r="N27" s="117" t="n"/>
+      <c r="O27" s="117" t="n"/>
+      <c r="P27" s="117" t="n"/>
+      <c r="Q27" s="117" t="n"/>
+      <c r="R27" s="117" t="n"/>
+      <c r="S27" s="117" t="n"/>
+      <c r="T27" s="117" t="n"/>
+      <c r="U27" s="117" t="n"/>
+      <c r="V27" s="117" t="n"/>
+      <c r="W27" s="117" t="n"/>
+      <c r="X27" s="117" t="n"/>
+      <c r="Y27" s="117" t="n"/>
+      <c r="Z27" s="117" t="n"/>
+      <c r="AA27" s="117" t="n"/>
+      <c r="AB27" s="117" t="n"/>
+      <c r="AC27" s="117" t="n"/>
+      <c r="AD27" s="117" t="n"/>
+      <c r="AE27" s="117" t="n"/>
+      <c r="AF27" s="117" t="n"/>
+      <c r="AG27" s="117" t="n"/>
+      <c r="AH27" s="117" t="n"/>
+      <c r="AI27" s="119" t="n"/>
     </row>
     <row r="28" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A28" s="113" t="n">
-        <v>5</v>
+      <c r="A28" s="113">
+        <f>IF($C28="","",ROW()-23)</f>
+        <v/>
       </c>
       <c r="B28" s="114" t="n"/>
       <c r="C28" s="115" t="n"/>
       <c r="D28" s="116" t="n"/>
-      <c r="E28" s="6" t="n"/>
-      <c r="F28" s="6" t="n"/>
-      <c r="G28" s="6" t="n"/>
-      <c r="H28" s="6" t="n"/>
-      <c r="I28" s="6" t="n"/>
-      <c r="J28" s="6" t="n"/>
-      <c r="K28" s="6" t="n"/>
-      <c r="L28" s="6" t="n"/>
-      <c r="M28" s="6" t="n"/>
-      <c r="N28" s="6" t="n"/>
-      <c r="O28" s="6" t="n"/>
-      <c r="P28" s="6" t="n"/>
-      <c r="Q28" s="6" t="n"/>
-      <c r="R28" s="6" t="n"/>
-      <c r="S28" s="6" t="n"/>
-      <c r="T28" s="6" t="n"/>
-      <c r="U28" s="6" t="n"/>
-      <c r="V28" s="6" t="n"/>
-      <c r="W28" s="6" t="n"/>
-      <c r="X28" s="6" t="n"/>
-      <c r="Y28" s="6" t="n"/>
-      <c r="Z28" s="6" t="n"/>
-      <c r="AA28" s="6" t="n"/>
-      <c r="AB28" s="6" t="n"/>
-      <c r="AC28" s="6" t="n"/>
-      <c r="AD28" s="6" t="n"/>
-      <c r="AE28" s="6" t="n"/>
-      <c r="AF28" s="6" t="n"/>
-      <c r="AG28" s="6" t="n"/>
-      <c r="AH28" s="6" t="n"/>
-      <c r="AI28" s="26" t="n"/>
+      <c r="E28" s="117" t="n"/>
+      <c r="F28" s="117" t="n"/>
+      <c r="G28" s="117" t="n"/>
+      <c r="H28" s="117" t="n"/>
+      <c r="I28" s="117" t="n"/>
+      <c r="J28" s="117" t="n"/>
+      <c r="K28" s="117" t="n"/>
+      <c r="L28" s="117" t="n"/>
+      <c r="M28" s="117" t="n"/>
+      <c r="N28" s="117" t="n"/>
+      <c r="O28" s="117" t="n"/>
+      <c r="P28" s="117" t="n"/>
+      <c r="Q28" s="117" t="n"/>
+      <c r="R28" s="117" t="n"/>
+      <c r="S28" s="117" t="n"/>
+      <c r="T28" s="117" t="n"/>
+      <c r="U28" s="117" t="n"/>
+      <c r="V28" s="117" t="n"/>
+      <c r="W28" s="117" t="n"/>
+      <c r="X28" s="117" t="n"/>
+      <c r="Y28" s="117" t="n"/>
+      <c r="Z28" s="117" t="n"/>
+      <c r="AA28" s="117" t="n"/>
+      <c r="AB28" s="117" t="n"/>
+      <c r="AC28" s="117" t="n"/>
+      <c r="AD28" s="117" t="n"/>
+      <c r="AE28" s="117" t="n"/>
+      <c r="AF28" s="117" t="n"/>
+      <c r="AG28" s="117" t="n"/>
+      <c r="AH28" s="117" t="n"/>
+      <c r="AI28" s="119" t="n"/>
     </row>
     <row r="29" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A29" s="118" t="n">
-        <v>6</v>
+      <c r="A29" s="122">
+        <f>IF($C29="","",ROW()-23)</f>
+        <v/>
       </c>
       <c r="B29" s="114" t="n"/>
       <c r="C29" s="115" t="n"/>
       <c r="D29" s="114" t="n"/>
-      <c r="E29" s="6" t="n"/>
-      <c r="F29" s="6" t="n"/>
-      <c r="G29" s="6" t="n"/>
-      <c r="H29" s="6" t="n"/>
-      <c r="I29" s="6" t="n"/>
-      <c r="J29" s="6" t="n"/>
-      <c r="K29" s="6" t="n"/>
-      <c r="L29" s="6" t="n"/>
-      <c r="M29" s="6" t="n"/>
-      <c r="N29" s="6" t="n"/>
-      <c r="O29" s="6" t="n"/>
-      <c r="P29" s="6" t="n"/>
-      <c r="Q29" s="6" t="n"/>
-      <c r="R29" s="6" t="n"/>
-      <c r="S29" s="6" t="n"/>
-      <c r="T29" s="6" t="n"/>
-      <c r="U29" s="6" t="n"/>
-      <c r="V29" s="6" t="n"/>
-      <c r="W29" s="6" t="n"/>
-      <c r="X29" s="6" t="n"/>
-      <c r="Y29" s="6" t="n"/>
-      <c r="Z29" s="6" t="n"/>
-      <c r="AA29" s="6" t="n"/>
-      <c r="AB29" s="6" t="n"/>
-      <c r="AC29" s="6" t="n"/>
-      <c r="AD29" s="6" t="n"/>
-      <c r="AE29" s="6" t="n"/>
-      <c r="AF29" s="6" t="n"/>
-      <c r="AG29" s="6" t="n"/>
-      <c r="AH29" s="6" t="n"/>
-      <c r="AI29" s="26" t="n"/>
+      <c r="E29" s="117" t="n"/>
+      <c r="F29" s="117" t="n"/>
+      <c r="G29" s="117" t="n"/>
+      <c r="H29" s="117" t="n"/>
+      <c r="I29" s="117" t="n"/>
+      <c r="J29" s="117" t="n"/>
+      <c r="K29" s="117" t="n"/>
+      <c r="L29" s="117" t="n"/>
+      <c r="M29" s="117" t="n"/>
+      <c r="N29" s="117" t="n"/>
+      <c r="O29" s="117" t="n"/>
+      <c r="P29" s="117" t="n"/>
+      <c r="Q29" s="117" t="n"/>
+      <c r="R29" s="117" t="n"/>
+      <c r="S29" s="117" t="n"/>
+      <c r="T29" s="117" t="n"/>
+      <c r="U29" s="117" t="n"/>
+      <c r="V29" s="117" t="n"/>
+      <c r="W29" s="117" t="n"/>
+      <c r="X29" s="117" t="n"/>
+      <c r="Y29" s="117" t="n"/>
+      <c r="Z29" s="117" t="n"/>
+      <c r="AA29" s="117" t="n"/>
+      <c r="AB29" s="117" t="n"/>
+      <c r="AC29" s="117" t="n"/>
+      <c r="AD29" s="117" t="n"/>
+      <c r="AE29" s="117" t="n"/>
+      <c r="AF29" s="117" t="n"/>
+      <c r="AG29" s="117" t="n"/>
+      <c r="AH29" s="117" t="n"/>
+      <c r="AI29" s="119" t="n"/>
     </row>
     <row r="30" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A30" s="118" t="n">
-        <v>7</v>
+      <c r="A30" s="122">
+        <f>IF($C30="","",ROW()-23)</f>
+        <v/>
       </c>
       <c r="B30" s="114" t="n"/>
       <c r="C30" s="115" t="n"/>
       <c r="D30" s="114" t="n"/>
-      <c r="E30" s="6" t="n"/>
-      <c r="F30" s="6" t="n"/>
-      <c r="G30" s="6" t="n"/>
-      <c r="H30" s="6" t="n"/>
-      <c r="I30" s="6" t="n"/>
-      <c r="J30" s="6" t="n"/>
-      <c r="K30" s="6" t="n"/>
-      <c r="L30" s="6" t="n"/>
-      <c r="M30" s="6" t="n"/>
-      <c r="N30" s="6" t="n"/>
-      <c r="O30" s="6" t="n"/>
-      <c r="P30" s="6" t="n"/>
-      <c r="Q30" s="6" t="n"/>
-      <c r="R30" s="6" t="n"/>
-      <c r="S30" s="6" t="n"/>
-      <c r="T30" s="6" t="n"/>
-      <c r="U30" s="6" t="n"/>
-      <c r="V30" s="6" t="n"/>
-      <c r="W30" s="6" t="n"/>
-      <c r="X30" s="6" t="n"/>
-      <c r="Y30" s="6" t="n"/>
-      <c r="Z30" s="6" t="n"/>
-      <c r="AA30" s="6" t="n"/>
-      <c r="AB30" s="6" t="n"/>
-      <c r="AC30" s="6" t="n"/>
-      <c r="AD30" s="6" t="n"/>
-      <c r="AE30" s="6" t="n"/>
-      <c r="AF30" s="6" t="n"/>
-      <c r="AG30" s="6" t="n"/>
-      <c r="AH30" s="6" t="n"/>
-      <c r="AI30" s="26" t="n"/>
+      <c r="E30" s="117" t="n"/>
+      <c r="F30" s="117" t="n"/>
+      <c r="G30" s="117" t="n"/>
+      <c r="H30" s="117" t="n"/>
+      <c r="I30" s="117" t="n"/>
+      <c r="J30" s="117" t="n"/>
+      <c r="K30" s="117" t="n"/>
+      <c r="L30" s="117" t="n"/>
+      <c r="M30" s="117" t="n"/>
+      <c r="N30" s="117" t="n"/>
+      <c r="O30" s="117" t="n"/>
+      <c r="P30" s="117" t="n"/>
+      <c r="Q30" s="117" t="n"/>
+      <c r="R30" s="117" t="n"/>
+      <c r="S30" s="117" t="n"/>
+      <c r="T30" s="117" t="n"/>
+      <c r="U30" s="117" t="n"/>
+      <c r="V30" s="117" t="n"/>
+      <c r="W30" s="117" t="n"/>
+      <c r="X30" s="117" t="n"/>
+      <c r="Y30" s="117" t="n"/>
+      <c r="Z30" s="117" t="n"/>
+      <c r="AA30" s="117" t="n"/>
+      <c r="AB30" s="117" t="n"/>
+      <c r="AC30" s="117" t="n"/>
+      <c r="AD30" s="117" t="n"/>
+      <c r="AE30" s="117" t="n"/>
+      <c r="AF30" s="117" t="n"/>
+      <c r="AG30" s="117" t="n"/>
+      <c r="AH30" s="117" t="n"/>
+      <c r="AI30" s="119" t="n"/>
     </row>
     <row r="31" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A31" s="118" t="n">
-        <v>8</v>
+      <c r="A31" s="122">
+        <f>IF($C31="","",ROW()-23)</f>
+        <v/>
       </c>
       <c r="B31" s="114" t="n"/>
       <c r="C31" s="115" t="n"/>
       <c r="D31" s="114" t="n"/>
-      <c r="E31" s="6" t="n"/>
-      <c r="F31" s="6" t="n"/>
-      <c r="G31" s="6" t="n"/>
-      <c r="H31" s="6" t="n"/>
-      <c r="I31" s="6" t="n"/>
-      <c r="J31" s="6" t="n"/>
-      <c r="K31" s="6" t="n"/>
-      <c r="L31" s="6" t="n"/>
-      <c r="M31" s="6" t="n"/>
-      <c r="N31" s="6" t="n"/>
-      <c r="O31" s="6" t="n"/>
-      <c r="P31" s="6" t="n"/>
-      <c r="Q31" s="6" t="n"/>
-      <c r="R31" s="6" t="n"/>
-      <c r="S31" s="6" t="n"/>
-      <c r="T31" s="6" t="n"/>
-      <c r="U31" s="6" t="n"/>
-      <c r="V31" s="6" t="n"/>
-      <c r="W31" s="6" t="n"/>
-      <c r="X31" s="6" t="n"/>
-      <c r="Y31" s="6" t="n"/>
-      <c r="Z31" s="6" t="n"/>
-      <c r="AA31" s="6" t="n"/>
-      <c r="AB31" s="6" t="n"/>
-      <c r="AC31" s="6" t="n"/>
-      <c r="AD31" s="6" t="n"/>
-      <c r="AE31" s="6" t="n"/>
-      <c r="AF31" s="6" t="n"/>
-      <c r="AG31" s="6" t="n"/>
-      <c r="AH31" s="6" t="n"/>
-      <c r="AI31" s="26" t="n"/>
+      <c r="E31" s="117" t="n"/>
+      <c r="F31" s="117" t="n"/>
+      <c r="G31" s="117" t="n"/>
+      <c r="H31" s="117" t="n"/>
+      <c r="I31" s="117" t="n"/>
+      <c r="J31" s="117" t="n"/>
+      <c r="K31" s="117" t="n"/>
+      <c r="L31" s="117" t="n"/>
+      <c r="M31" s="117" t="n"/>
+      <c r="N31" s="117" t="n"/>
+      <c r="O31" s="117" t="n"/>
+      <c r="P31" s="117" t="n"/>
+      <c r="Q31" s="117" t="n"/>
+      <c r="R31" s="117" t="n"/>
+      <c r="S31" s="117" t="n"/>
+      <c r="T31" s="117" t="n"/>
+      <c r="U31" s="117" t="n"/>
+      <c r="V31" s="117" t="n"/>
+      <c r="W31" s="117" t="n"/>
+      <c r="X31" s="117" t="n"/>
+      <c r="Y31" s="117" t="n"/>
+      <c r="Z31" s="117" t="n"/>
+      <c r="AA31" s="117" t="n"/>
+      <c r="AB31" s="117" t="n"/>
+      <c r="AC31" s="117" t="n"/>
+      <c r="AD31" s="117" t="n"/>
+      <c r="AE31" s="117" t="n"/>
+      <c r="AF31" s="117" t="n"/>
+      <c r="AG31" s="117" t="n"/>
+      <c r="AH31" s="117" t="n"/>
+      <c r="AI31" s="119" t="n"/>
     </row>
     <row r="32" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A32" s="118" t="n">
-        <v>9</v>
+      <c r="A32" s="122">
+        <f>IF($C32="","",ROW()-23)</f>
+        <v/>
       </c>
       <c r="B32" s="114" t="n"/>
       <c r="C32" s="115" t="n"/>
       <c r="D32" s="114" t="n"/>
-      <c r="E32" s="6" t="n"/>
-      <c r="F32" s="6" t="n"/>
-      <c r="G32" s="6" t="n"/>
-      <c r="H32" s="6" t="n"/>
-      <c r="I32" s="6" t="n"/>
-      <c r="J32" s="6" t="n"/>
-      <c r="K32" s="6" t="n"/>
-      <c r="L32" s="6" t="n"/>
-      <c r="M32" s="6" t="n"/>
-      <c r="N32" s="6" t="n"/>
-      <c r="O32" s="6" t="n"/>
-      <c r="P32" s="6" t="n"/>
-      <c r="Q32" s="6" t="n"/>
-      <c r="R32" s="6" t="n"/>
-      <c r="S32" s="6" t="n"/>
-      <c r="T32" s="6" t="n"/>
-      <c r="U32" s="6" t="n"/>
-      <c r="V32" s="6" t="n"/>
-      <c r="W32" s="6" t="n"/>
-      <c r="X32" s="6" t="n"/>
-      <c r="Y32" s="6" t="n"/>
-      <c r="Z32" s="6" t="n"/>
-      <c r="AA32" s="6" t="n"/>
-      <c r="AB32" s="6" t="n"/>
-      <c r="AC32" s="6" t="n"/>
-      <c r="AD32" s="6" t="n"/>
-      <c r="AE32" s="6" t="n"/>
-      <c r="AF32" s="6" t="n"/>
-      <c r="AG32" s="6" t="n"/>
-      <c r="AH32" s="6" t="n"/>
-      <c r="AI32" s="26" t="n"/>
+      <c r="E32" s="117" t="n"/>
+      <c r="F32" s="117" t="n"/>
+      <c r="G32" s="117" t="n"/>
+      <c r="H32" s="117" t="n"/>
+      <c r="I32" s="117" t="n"/>
+      <c r="J32" s="117" t="n"/>
+      <c r="K32" s="117" t="n"/>
+      <c r="L32" s="117" t="n"/>
+      <c r="M32" s="117" t="n"/>
+      <c r="N32" s="117" t="n"/>
+      <c r="O32" s="117" t="n"/>
+      <c r="P32" s="117" t="n"/>
+      <c r="Q32" s="117" t="n"/>
+      <c r="R32" s="117" t="n"/>
+      <c r="S32" s="117" t="n"/>
+      <c r="T32" s="117" t="n"/>
+      <c r="U32" s="117" t="n"/>
+      <c r="V32" s="117" t="n"/>
+      <c r="W32" s="117" t="n"/>
+      <c r="X32" s="117" t="n"/>
+      <c r="Y32" s="117" t="n"/>
+      <c r="Z32" s="117" t="n"/>
+      <c r="AA32" s="117" t="n"/>
+      <c r="AB32" s="117" t="n"/>
+      <c r="AC32" s="117" t="n"/>
+      <c r="AD32" s="117" t="n"/>
+      <c r="AE32" s="117" t="n"/>
+      <c r="AF32" s="117" t="n"/>
+      <c r="AG32" s="117" t="n"/>
+      <c r="AH32" s="117" t="n"/>
+      <c r="AI32" s="119" t="n"/>
     </row>
     <row r="33" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A33" s="118" t="n">
-        <v>10</v>
+      <c r="A33" s="122">
+        <f>IF($C33="","",ROW()-23)</f>
+        <v/>
       </c>
       <c r="B33" s="114" t="n"/>
       <c r="C33" s="115" t="n"/>
       <c r="D33" s="114" t="n"/>
-      <c r="E33" s="6" t="n"/>
-      <c r="F33" s="6" t="n"/>
-      <c r="G33" s="6" t="n"/>
-      <c r="H33" s="6" t="n"/>
-      <c r="I33" s="6" t="n"/>
-      <c r="J33" s="6" t="n"/>
-      <c r="K33" s="6" t="n"/>
-      <c r="L33" s="6" t="n"/>
-      <c r="M33" s="6" t="n"/>
-      <c r="N33" s="6" t="n"/>
-      <c r="O33" s="6" t="n"/>
-      <c r="P33" s="6" t="n"/>
-      <c r="Q33" s="6" t="n"/>
-      <c r="R33" s="6" t="n"/>
-      <c r="S33" s="6" t="n"/>
-      <c r="T33" s="6" t="n"/>
-      <c r="U33" s="6" t="n"/>
-      <c r="V33" s="6" t="n"/>
-      <c r="W33" s="6" t="n"/>
-      <c r="X33" s="6" t="n"/>
-      <c r="Y33" s="6" t="n"/>
-      <c r="Z33" s="6" t="n"/>
-      <c r="AA33" s="6" t="n"/>
-      <c r="AB33" s="6" t="n"/>
-      <c r="AC33" s="6" t="n"/>
-      <c r="AD33" s="6" t="n"/>
-      <c r="AE33" s="6" t="n"/>
-      <c r="AF33" s="6" t="n"/>
-      <c r="AG33" s="6" t="n"/>
-      <c r="AH33" s="6" t="n"/>
-      <c r="AI33" s="26" t="n"/>
+      <c r="E33" s="117" t="n"/>
+      <c r="F33" s="117" t="n"/>
+      <c r="G33" s="117" t="n"/>
+      <c r="H33" s="117" t="n"/>
+      <c r="I33" s="117" t="n"/>
+      <c r="J33" s="117" t="n"/>
+      <c r="K33" s="117" t="n"/>
+      <c r="L33" s="117" t="n"/>
+      <c r="M33" s="117" t="n"/>
+      <c r="N33" s="117" t="n"/>
+      <c r="O33" s="117" t="n"/>
+      <c r="P33" s="117" t="n"/>
+      <c r="Q33" s="117" t="n"/>
+      <c r="R33" s="117" t="n"/>
+      <c r="S33" s="117" t="n"/>
+      <c r="T33" s="117" t="n"/>
+      <c r="U33" s="117" t="n"/>
+      <c r="V33" s="117" t="n"/>
+      <c r="W33" s="117" t="n"/>
+      <c r="X33" s="117" t="n"/>
+      <c r="Y33" s="117" t="n"/>
+      <c r="Z33" s="117" t="n"/>
+      <c r="AA33" s="117" t="n"/>
+      <c r="AB33" s="117" t="n"/>
+      <c r="AC33" s="117" t="n"/>
+      <c r="AD33" s="117" t="n"/>
+      <c r="AE33" s="117" t="n"/>
+      <c r="AF33" s="117" t="n"/>
+      <c r="AG33" s="117" t="n"/>
+      <c r="AH33" s="117" t="n"/>
+      <c r="AI33" s="119" t="n"/>
     </row>
     <row r="34" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A34" s="118" t="n">
-        <v>11</v>
+      <c r="A34" s="122">
+        <f>IF($C34="","",ROW()-23)</f>
+        <v/>
       </c>
       <c r="B34" s="114" t="n"/>
       <c r="C34" s="115" t="n"/>
       <c r="D34" s="114" t="n"/>
-      <c r="E34" s="6" t="n"/>
-      <c r="F34" s="6" t="n"/>
-      <c r="G34" s="6" t="n"/>
-      <c r="H34" s="6" t="n"/>
-      <c r="I34" s="6" t="n"/>
-      <c r="J34" s="6" t="n"/>
-      <c r="K34" s="6" t="n"/>
-      <c r="L34" s="6" t="n"/>
-      <c r="M34" s="6" t="n"/>
-      <c r="N34" s="6" t="n"/>
-      <c r="O34" s="6" t="n"/>
-      <c r="P34" s="6" t="n"/>
-      <c r="Q34" s="6" t="n"/>
-      <c r="R34" s="6" t="n"/>
-      <c r="S34" s="6" t="n"/>
-      <c r="T34" s="6" t="n"/>
-      <c r="U34" s="6" t="n"/>
-      <c r="V34" s="6" t="n"/>
-      <c r="W34" s="6" t="n"/>
-      <c r="X34" s="6" t="n"/>
-      <c r="Y34" s="6" t="n"/>
-      <c r="Z34" s="6" t="n"/>
-      <c r="AA34" s="6" t="n"/>
-      <c r="AB34" s="6" t="n"/>
-      <c r="AC34" s="6" t="n"/>
-      <c r="AD34" s="6" t="n"/>
-      <c r="AE34" s="6" t="n"/>
-      <c r="AF34" s="6" t="n"/>
-      <c r="AG34" s="6" t="n"/>
-      <c r="AH34" s="6" t="n"/>
-      <c r="AI34" s="26" t="n"/>
+      <c r="E34" s="117" t="n"/>
+      <c r="F34" s="117" t="n"/>
+      <c r="G34" s="117" t="n"/>
+      <c r="H34" s="117" t="n"/>
+      <c r="I34" s="117" t="n"/>
+      <c r="J34" s="117" t="n"/>
+      <c r="K34" s="117" t="n"/>
+      <c r="L34" s="117" t="n"/>
+      <c r="M34" s="117" t="n"/>
+      <c r="N34" s="117" t="n"/>
+      <c r="O34" s="117" t="n"/>
+      <c r="P34" s="117" t="n"/>
+      <c r="Q34" s="117" t="n"/>
+      <c r="R34" s="117" t="n"/>
+      <c r="S34" s="117" t="n"/>
+      <c r="T34" s="117" t="n"/>
+      <c r="U34" s="117" t="n"/>
+      <c r="V34" s="117" t="n"/>
+      <c r="W34" s="117" t="n"/>
+      <c r="X34" s="117" t="n"/>
+      <c r="Y34" s="117" t="n"/>
+      <c r="Z34" s="117" t="n"/>
+      <c r="AA34" s="117" t="n"/>
+      <c r="AB34" s="117" t="n"/>
+      <c r="AC34" s="117" t="n"/>
+      <c r="AD34" s="117" t="n"/>
+      <c r="AE34" s="117" t="n"/>
+      <c r="AF34" s="117" t="n"/>
+      <c r="AG34" s="117" t="n"/>
+      <c r="AH34" s="117" t="n"/>
+      <c r="AI34" s="119" t="n"/>
     </row>
     <row r="35" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A35" s="118" t="n">
-        <v>12</v>
+      <c r="A35" s="122">
+        <f>IF($C35="","",ROW()-23)</f>
+        <v/>
       </c>
       <c r="B35" s="114" t="n"/>
       <c r="C35" s="115" t="n"/>
       <c r="D35" s="114" t="n"/>
-      <c r="E35" s="6" t="n"/>
-      <c r="F35" s="6" t="n"/>
-      <c r="G35" s="6" t="n"/>
-      <c r="H35" s="6" t="n"/>
-      <c r="I35" s="6" t="n"/>
-      <c r="J35" s="6" t="n"/>
-      <c r="K35" s="6" t="n"/>
-      <c r="L35" s="6" t="n"/>
-      <c r="M35" s="6" t="n"/>
-      <c r="N35" s="6" t="n"/>
-      <c r="O35" s="6" t="n"/>
-      <c r="P35" s="6" t="n"/>
-      <c r="Q35" s="6" t="n"/>
-      <c r="R35" s="6" t="n"/>
-      <c r="S35" s="6" t="n"/>
-      <c r="T35" s="6" t="n"/>
-      <c r="U35" s="6" t="n"/>
-      <c r="V35" s="6" t="n"/>
-      <c r="W35" s="6" t="n"/>
-      <c r="X35" s="6" t="n"/>
-      <c r="Y35" s="6" t="n"/>
-      <c r="Z35" s="6" t="n"/>
-      <c r="AA35" s="6" t="n"/>
-      <c r="AB35" s="6" t="n"/>
-      <c r="AC35" s="6" t="n"/>
-      <c r="AD35" s="6" t="n"/>
-      <c r="AE35" s="6" t="n"/>
-      <c r="AF35" s="6" t="n"/>
-      <c r="AG35" s="6" t="n"/>
-      <c r="AH35" s="6" t="n"/>
-      <c r="AI35" s="26" t="n"/>
+      <c r="E35" s="117" t="n"/>
+      <c r="F35" s="117" t="n"/>
+      <c r="G35" s="117" t="n"/>
+      <c r="H35" s="117" t="n"/>
+      <c r="I35" s="117" t="n"/>
+      <c r="J35" s="117" t="n"/>
+      <c r="K35" s="117" t="n"/>
+      <c r="L35" s="117" t="n"/>
+      <c r="M35" s="117" t="n"/>
+      <c r="N35" s="117" t="n"/>
+      <c r="O35" s="117" t="n"/>
+      <c r="P35" s="117" t="n"/>
+      <c r="Q35" s="117" t="n"/>
+      <c r="R35" s="117" t="n"/>
+      <c r="S35" s="117" t="n"/>
+      <c r="T35" s="117" t="n"/>
+      <c r="U35" s="117" t="n"/>
+      <c r="V35" s="117" t="n"/>
+      <c r="W35" s="117" t="n"/>
+      <c r="X35" s="117" t="n"/>
+      <c r="Y35" s="117" t="n"/>
+      <c r="Z35" s="117" t="n"/>
+      <c r="AA35" s="117" t="n"/>
+      <c r="AB35" s="117" t="n"/>
+      <c r="AC35" s="117" t="n"/>
+      <c r="AD35" s="117" t="n"/>
+      <c r="AE35" s="117" t="n"/>
+      <c r="AF35" s="117" t="n"/>
+      <c r="AG35" s="117" t="n"/>
+      <c r="AH35" s="117" t="n"/>
+      <c r="AI35" s="119" t="n"/>
     </row>
     <row r="36" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A36" s="118" t="n">
-        <v>13</v>
+      <c r="A36" s="122">
+        <f>IF($C36="","",ROW()-23)</f>
+        <v/>
       </c>
       <c r="B36" s="114" t="n"/>
       <c r="C36" s="115" t="n"/>
       <c r="D36" s="114" t="n"/>
-      <c r="E36" s="6" t="n"/>
-      <c r="F36" s="6" t="n"/>
-      <c r="G36" s="6" t="n"/>
-      <c r="H36" s="6" t="n"/>
-      <c r="I36" s="6" t="n"/>
-      <c r="J36" s="6" t="n"/>
-      <c r="K36" s="6" t="n"/>
-      <c r="L36" s="6" t="n"/>
-      <c r="M36" s="6" t="n"/>
-      <c r="N36" s="6" t="n"/>
-      <c r="O36" s="6" t="n"/>
-      <c r="P36" s="6" t="n"/>
-      <c r="Q36" s="6" t="n"/>
-      <c r="R36" s="6" t="n"/>
-      <c r="S36" s="6" t="n"/>
-      <c r="T36" s="6" t="n"/>
-      <c r="U36" s="6" t="n"/>
-      <c r="V36" s="6" t="n"/>
-      <c r="W36" s="6" t="n"/>
-      <c r="X36" s="6" t="n"/>
-      <c r="Y36" s="6" t="n"/>
-      <c r="Z36" s="6" t="n"/>
-      <c r="AA36" s="6" t="n"/>
-      <c r="AB36" s="6" t="n"/>
-      <c r="AC36" s="6" t="n"/>
-      <c r="AD36" s="6" t="n"/>
-      <c r="AE36" s="6" t="n"/>
-      <c r="AF36" s="6" t="n"/>
-      <c r="AG36" s="6" t="n"/>
-      <c r="AH36" s="6" t="n"/>
-      <c r="AI36" s="26" t="n"/>
+      <c r="E36" s="117" t="n"/>
+      <c r="F36" s="117" t="n"/>
+      <c r="G36" s="117" t="n"/>
+      <c r="H36" s="117" t="n"/>
+      <c r="I36" s="117" t="n"/>
+      <c r="J36" s="117" t="n"/>
+      <c r="K36" s="117" t="n"/>
+      <c r="L36" s="117" t="n"/>
+      <c r="M36" s="117" t="n"/>
+      <c r="N36" s="117" t="n"/>
+      <c r="O36" s="117" t="n"/>
+      <c r="P36" s="117" t="n"/>
+      <c r="Q36" s="117" t="n"/>
+      <c r="R36" s="117" t="n"/>
+      <c r="S36" s="117" t="n"/>
+      <c r="T36" s="117" t="n"/>
+      <c r="U36" s="117" t="n"/>
+      <c r="V36" s="117" t="n"/>
+      <c r="W36" s="117" t="n"/>
+      <c r="X36" s="117" t="n"/>
+      <c r="Y36" s="117" t="n"/>
+      <c r="Z36" s="117" t="n"/>
+      <c r="AA36" s="117" t="n"/>
+      <c r="AB36" s="117" t="n"/>
+      <c r="AC36" s="117" t="n"/>
+      <c r="AD36" s="117" t="n"/>
+      <c r="AE36" s="117" t="n"/>
+      <c r="AF36" s="117" t="n"/>
+      <c r="AG36" s="117" t="n"/>
+      <c r="AH36" s="117" t="n"/>
+      <c r="AI36" s="119" t="n"/>
     </row>
     <row r="37" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A37" s="113" t="n">
-        <v>14</v>
+      <c r="A37" s="113">
+        <f>IF($C37="","",ROW()-23)</f>
+        <v/>
       </c>
       <c r="B37" s="114" t="n"/>
       <c r="C37" s="115" t="n"/>
       <c r="D37" s="114" t="n"/>
-      <c r="E37" s="6" t="n"/>
-      <c r="F37" s="6" t="n"/>
-      <c r="G37" s="6" t="n"/>
-      <c r="H37" s="6" t="n"/>
-      <c r="I37" s="6" t="n"/>
-      <c r="J37" s="6" t="n"/>
-      <c r="K37" s="6" t="n"/>
-      <c r="L37" s="6" t="n"/>
-      <c r="M37" s="6" t="n"/>
-      <c r="N37" s="6" t="n"/>
-      <c r="O37" s="6" t="n"/>
-      <c r="P37" s="6" t="n"/>
-      <c r="Q37" s="6" t="n"/>
-      <c r="R37" s="6" t="n"/>
-      <c r="S37" s="6" t="n"/>
-      <c r="T37" s="6" t="n"/>
-      <c r="U37" s="6" t="n"/>
-      <c r="V37" s="6" t="n"/>
-      <c r="W37" s="6" t="n"/>
-      <c r="X37" s="6" t="n"/>
-      <c r="Y37" s="6" t="n"/>
-      <c r="Z37" s="6" t="n"/>
-      <c r="AA37" s="6" t="n"/>
-      <c r="AB37" s="6" t="n"/>
-      <c r="AC37" s="6" t="n"/>
-      <c r="AD37" s="6" t="n"/>
-      <c r="AE37" s="6" t="n"/>
-      <c r="AF37" s="6" t="n"/>
-      <c r="AG37" s="6" t="n"/>
-      <c r="AH37" s="6" t="n"/>
-      <c r="AI37" s="26" t="n"/>
+      <c r="E37" s="117" t="n"/>
+      <c r="F37" s="117" t="n"/>
+      <c r="G37" s="117" t="n"/>
+      <c r="H37" s="117" t="n"/>
+      <c r="I37" s="117" t="n"/>
+      <c r="J37" s="117" t="n"/>
+      <c r="K37" s="117" t="n"/>
+      <c r="L37" s="117" t="n"/>
+      <c r="M37" s="117" t="n"/>
+      <c r="N37" s="117" t="n"/>
+      <c r="O37" s="117" t="n"/>
+      <c r="P37" s="117" t="n"/>
+      <c r="Q37" s="117" t="n"/>
+      <c r="R37" s="117" t="n"/>
+      <c r="S37" s="117" t="n"/>
+      <c r="T37" s="117" t="n"/>
+      <c r="U37" s="117" t="n"/>
+      <c r="V37" s="117" t="n"/>
+      <c r="W37" s="117" t="n"/>
+      <c r="X37" s="117" t="n"/>
+      <c r="Y37" s="117" t="n"/>
+      <c r="Z37" s="117" t="n"/>
+      <c r="AA37" s="117" t="n"/>
+      <c r="AB37" s="117" t="n"/>
+      <c r="AC37" s="117" t="n"/>
+      <c r="AD37" s="117" t="n"/>
+      <c r="AE37" s="117" t="n"/>
+      <c r="AF37" s="117" t="n"/>
+      <c r="AG37" s="117" t="n"/>
+      <c r="AH37" s="117" t="n"/>
+      <c r="AI37" s="119" t="n"/>
     </row>
     <row r="38" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A38" s="113" t="n">
-        <v>15</v>
+      <c r="A38" s="113">
+        <f>IF($C38="","",ROW()-23)</f>
+        <v/>
       </c>
       <c r="B38" s="114" t="n"/>
       <c r="C38" s="115" t="n"/>
       <c r="D38" s="114" t="n"/>
-      <c r="E38" s="6" t="n"/>
-      <c r="F38" s="6" t="n"/>
-      <c r="G38" s="6" t="n"/>
-      <c r="H38" s="6" t="n"/>
-      <c r="I38" s="6" t="n"/>
-      <c r="J38" s="6" t="n"/>
-      <c r="K38" s="6" t="n"/>
-      <c r="L38" s="6" t="n"/>
-      <c r="M38" s="6" t="n"/>
-      <c r="N38" s="6" t="n"/>
-      <c r="O38" s="6" t="n"/>
-      <c r="P38" s="6" t="n"/>
-      <c r="Q38" s="6" t="n"/>
-      <c r="R38" s="6" t="n"/>
-      <c r="S38" s="6" t="n"/>
-      <c r="T38" s="6" t="n"/>
-      <c r="U38" s="6" t="n"/>
-      <c r="V38" s="6" t="n"/>
-      <c r="W38" s="6" t="n"/>
-      <c r="X38" s="6" t="n"/>
-      <c r="Y38" s="6" t="n"/>
-      <c r="Z38" s="6" t="n"/>
-      <c r="AA38" s="6" t="n"/>
-      <c r="AB38" s="6" t="n"/>
-      <c r="AC38" s="6" t="n"/>
-      <c r="AD38" s="6" t="n"/>
-      <c r="AE38" s="6" t="n"/>
-      <c r="AF38" s="6" t="n"/>
-      <c r="AG38" s="6" t="n"/>
-      <c r="AH38" s="6" t="n"/>
-      <c r="AI38" s="26" t="n"/>
+      <c r="E38" s="117" t="n"/>
+      <c r="F38" s="117" t="n"/>
+      <c r="G38" s="117" t="n"/>
+      <c r="H38" s="117" t="n"/>
+      <c r="I38" s="117" t="n"/>
+      <c r="J38" s="117" t="n"/>
+      <c r="K38" s="117" t="n"/>
+      <c r="L38" s="117" t="n"/>
+      <c r="M38" s="117" t="n"/>
+      <c r="N38" s="117" t="n"/>
+      <c r="O38" s="117" t="n"/>
+      <c r="P38" s="117" t="n"/>
+      <c r="Q38" s="117" t="n"/>
+      <c r="R38" s="117" t="n"/>
+      <c r="S38" s="117" t="n"/>
+      <c r="T38" s="117" t="n"/>
+      <c r="U38" s="117" t="n"/>
+      <c r="V38" s="117" t="n"/>
+      <c r="W38" s="117" t="n"/>
+      <c r="X38" s="117" t="n"/>
+      <c r="Y38" s="117" t="n"/>
+      <c r="Z38" s="117" t="n"/>
+      <c r="AA38" s="117" t="n"/>
+      <c r="AB38" s="117" t="n"/>
+      <c r="AC38" s="117" t="n"/>
+      <c r="AD38" s="117" t="n"/>
+      <c r="AE38" s="117" t="n"/>
+      <c r="AF38" s="117" t="n"/>
+      <c r="AG38" s="117" t="n"/>
+      <c r="AH38" s="117" t="n"/>
+      <c r="AI38" s="119" t="n"/>
     </row>
     <row r="39" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A39" s="113" t="n">
-        <v>16</v>
+      <c r="A39" s="113">
+        <f>IF($C39="","",ROW()-23)</f>
+        <v/>
       </c>
       <c r="B39" s="114" t="n"/>
       <c r="C39" s="115" t="n"/>
       <c r="D39" s="114" t="n"/>
-      <c r="E39" s="6" t="n"/>
-      <c r="F39" s="6" t="n"/>
-      <c r="G39" s="6" t="n"/>
-      <c r="H39" s="6" t="n"/>
-      <c r="I39" s="6" t="n"/>
-      <c r="J39" s="6" t="n"/>
-      <c r="K39" s="6" t="n"/>
-      <c r="L39" s="6" t="n"/>
-      <c r="M39" s="6" t="n"/>
-      <c r="N39" s="6" t="n"/>
-      <c r="O39" s="6" t="n"/>
-      <c r="P39" s="6" t="n"/>
-      <c r="Q39" s="6" t="n"/>
-      <c r="R39" s="6" t="n"/>
-      <c r="S39" s="6" t="n"/>
-      <c r="T39" s="6" t="n"/>
-      <c r="U39" s="6" t="n"/>
-      <c r="V39" s="6" t="n"/>
-      <c r="W39" s="6" t="n"/>
-      <c r="X39" s="6" t="n"/>
-      <c r="Y39" s="6" t="n"/>
-      <c r="Z39" s="6" t="n"/>
-      <c r="AA39" s="6" t="n"/>
-      <c r="AB39" s="6" t="n"/>
-      <c r="AC39" s="6" t="n"/>
-      <c r="AD39" s="6" t="n"/>
-      <c r="AE39" s="6" t="n"/>
-      <c r="AF39" s="6" t="n"/>
-      <c r="AG39" s="6" t="n"/>
-      <c r="AH39" s="6" t="n"/>
-      <c r="AI39" s="26" t="n"/>
+      <c r="E39" s="117" t="n"/>
+      <c r="F39" s="117" t="n"/>
+      <c r="G39" s="117" t="n"/>
+      <c r="H39" s="117" t="n"/>
+      <c r="I39" s="117" t="n"/>
+      <c r="J39" s="117" t="n"/>
+      <c r="K39" s="117" t="n"/>
+      <c r="L39" s="117" t="n"/>
+      <c r="M39" s="117" t="n"/>
+      <c r="N39" s="117" t="n"/>
+      <c r="O39" s="117" t="n"/>
+      <c r="P39" s="117" t="n"/>
+      <c r="Q39" s="117" t="n"/>
+      <c r="R39" s="117" t="n"/>
+      <c r="S39" s="117" t="n"/>
+      <c r="T39" s="117" t="n"/>
+      <c r="U39" s="117" t="n"/>
+      <c r="V39" s="117" t="n"/>
+      <c r="W39" s="117" t="n"/>
+      <c r="X39" s="117" t="n"/>
+      <c r="Y39" s="117" t="n"/>
+      <c r="Z39" s="117" t="n"/>
+      <c r="AA39" s="117" t="n"/>
+      <c r="AB39" s="117" t="n"/>
+      <c r="AC39" s="117" t="n"/>
+      <c r="AD39" s="117" t="n"/>
+      <c r="AE39" s="117" t="n"/>
+      <c r="AF39" s="117" t="n"/>
+      <c r="AG39" s="117" t="n"/>
+      <c r="AH39" s="117" t="n"/>
+      <c r="AI39" s="119" t="n"/>
     </row>
     <row r="40" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A40" s="113" t="n">
-        <v>17</v>
+      <c r="A40" s="113">
+        <f>IF($C40="","",ROW()-23)</f>
+        <v/>
       </c>
       <c r="B40" s="114" t="n"/>
       <c r="C40" s="115" t="n"/>
       <c r="D40" s="114" t="n"/>
-      <c r="E40" s="27" t="n"/>
-      <c r="F40" s="27" t="n"/>
-      <c r="G40" s="27" t="n"/>
-      <c r="H40" s="27" t="n"/>
-      <c r="I40" s="27" t="n"/>
-      <c r="J40" s="27" t="n"/>
-      <c r="K40" s="27" t="n"/>
-      <c r="L40" s="27" t="n"/>
-      <c r="M40" s="27" t="n"/>
-      <c r="N40" s="27" t="n"/>
-      <c r="O40" s="27" t="n"/>
-      <c r="P40" s="27" t="n"/>
-      <c r="Q40" s="27" t="n"/>
-      <c r="R40" s="27" t="n"/>
-      <c r="S40" s="27" t="n"/>
-      <c r="T40" s="27" t="n"/>
-      <c r="U40" s="27" t="n"/>
-      <c r="V40" s="27" t="n"/>
-      <c r="W40" s="27" t="n"/>
-      <c r="X40" s="27" t="n"/>
-      <c r="Y40" s="27" t="n"/>
-      <c r="Z40" s="27" t="n"/>
-      <c r="AA40" s="27" t="n"/>
-      <c r="AB40" s="27" t="n"/>
-      <c r="AC40" s="27" t="n"/>
-      <c r="AD40" s="27" t="n"/>
-      <c r="AE40" s="27" t="n"/>
-      <c r="AF40" s="27" t="n"/>
-      <c r="AG40" s="27" t="n"/>
-      <c r="AH40" s="27" t="n"/>
-      <c r="AI40" s="29" t="n"/>
+      <c r="E40" s="125" t="n"/>
+      <c r="F40" s="125" t="n"/>
+      <c r="G40" s="125" t="n"/>
+      <c r="H40" s="125" t="n"/>
+      <c r="I40" s="125" t="n"/>
+      <c r="J40" s="125" t="n"/>
+      <c r="K40" s="125" t="n"/>
+      <c r="L40" s="125" t="n"/>
+      <c r="M40" s="125" t="n"/>
+      <c r="N40" s="125" t="n"/>
+      <c r="O40" s="125" t="n"/>
+      <c r="P40" s="125" t="n"/>
+      <c r="Q40" s="125" t="n"/>
+      <c r="R40" s="125" t="n"/>
+      <c r="S40" s="125" t="n"/>
+      <c r="T40" s="125" t="n"/>
+      <c r="U40" s="125" t="n"/>
+      <c r="V40" s="125" t="n"/>
+      <c r="W40" s="125" t="n"/>
+      <c r="X40" s="125" t="n"/>
+      <c r="Y40" s="125" t="n"/>
+      <c r="Z40" s="125" t="n"/>
+      <c r="AA40" s="125" t="n"/>
+      <c r="AB40" s="125" t="n"/>
+      <c r="AC40" s="125" t="n"/>
+      <c r="AD40" s="125" t="n"/>
+      <c r="AE40" s="125" t="n"/>
+      <c r="AF40" s="125" t="n"/>
+      <c r="AG40" s="125" t="n"/>
+      <c r="AH40" s="125" t="n"/>
+      <c r="AI40" s="127" t="n"/>
     </row>
     <row r="41" ht="15" customHeight="1" thickBot="1"/>
     <row r="42" ht="15" customHeight="1" thickBot="1">
-      <c r="A42" s="123" t="inlineStr">
+      <c r="A42" s="131" t="inlineStr">
         <is>
           <t>SPECIAL SHIFTING</t>
         </is>
       </c>
-      <c r="B42" s="120" t="n"/>
-      <c r="C42" s="120" t="n"/>
-      <c r="D42" s="124" t="n"/>
+      <c r="B42" s="128" t="n"/>
+      <c r="C42" s="128" t="n"/>
+      <c r="D42" s="132" t="n"/>
       <c r="E42" s="1">
-        <f>IF(1&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1),"ddd"),"")</f>
+        <f>IF(1&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+0,"ddd"),"")</f>
         <v/>
       </c>
       <c r="F42" s="1">
-        <f>IF(2&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,2),"ddd"),"")</f>
+        <f>IF(2&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+1,"ddd"),"")</f>
         <v/>
       </c>
       <c r="G42" s="1">
-        <f>IF(3&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,3),"ddd"),"")</f>
+        <f>IF(3&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+2,"ddd"),"")</f>
         <v/>
       </c>
       <c r="H42" s="1">
-        <f>IF(4&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,4),"ddd"),"")</f>
+        <f>IF(4&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+3,"ddd"),"")</f>
         <v/>
       </c>
       <c r="I42" s="1">
-        <f>IF(5&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,5),"ddd"),"")</f>
+        <f>IF(5&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+4,"ddd"),"")</f>
         <v/>
       </c>
       <c r="J42" s="1">
-        <f>IF(6&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,6),"ddd"),"")</f>
+        <f>IF(6&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+5,"ddd"),"")</f>
         <v/>
       </c>
       <c r="K42" s="1">
-        <f>IF(7&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,7),"ddd"),"")</f>
+        <f>IF(7&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+6,"ddd"),"")</f>
         <v/>
       </c>
       <c r="L42" s="1">
-        <f>IF(8&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,8),"ddd"),"")</f>
+        <f>IF(8&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+7,"ddd"),"")</f>
         <v/>
       </c>
       <c r="M42" s="1">
-        <f>IF(9&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,9),"ddd"),"")</f>
+        <f>IF(9&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+8,"ddd"),"")</f>
         <v/>
       </c>
       <c r="N42" s="1">
-        <f>IF(10&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,10),"ddd"),"")</f>
+        <f>IF(10&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+9,"ddd"),"")</f>
         <v/>
       </c>
       <c r="O42" s="1">
-        <f>IF(11&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,11),"ddd"),"")</f>
+        <f>IF(11&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+10,"ddd"),"")</f>
         <v/>
       </c>
       <c r="P42" s="1">
-        <f>IF(12&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,12),"ddd"),"")</f>
+        <f>IF(12&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+11,"ddd"),"")</f>
         <v/>
       </c>
       <c r="Q42" s="1">
-        <f>IF(13&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,13),"ddd"),"")</f>
+        <f>IF(13&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+12,"ddd"),"")</f>
         <v/>
       </c>
       <c r="R42" s="1">
-        <f>IF(14&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,14),"ddd"),"")</f>
+        <f>IF(14&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+13,"ddd"),"")</f>
         <v/>
       </c>
       <c r="S42" s="1">
-        <f>IF(15&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,15),"ddd"),"")</f>
+        <f>IF(15&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+14,"ddd"),"")</f>
         <v/>
       </c>
       <c r="T42" s="1">
-        <f>IF(16&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,16),"ddd"),"")</f>
+        <f>IF(16&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+15,"ddd"),"")</f>
         <v/>
       </c>
       <c r="U42" s="1">
-        <f>IF(17&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,17),"ddd"),"")</f>
+        <f>IF(17&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+16,"ddd"),"")</f>
         <v/>
       </c>
       <c r="V42" s="1">
-        <f>IF(18&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,18),"ddd"),"")</f>
+        <f>IF(18&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+17,"ddd"),"")</f>
         <v/>
       </c>
       <c r="W42" s="1">
-        <f>IF(19&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,19),"ddd"),"")</f>
+        <f>IF(19&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+18,"ddd"),"")</f>
         <v/>
       </c>
       <c r="X42" s="1">
-        <f>IF(20&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,20),"ddd"),"")</f>
+        <f>IF(20&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+19,"ddd"),"")</f>
         <v/>
       </c>
       <c r="Y42" s="1">
-        <f>IF(21&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,21),"ddd"),"")</f>
+        <f>IF(21&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+20,"ddd"),"")</f>
         <v/>
       </c>
       <c r="Z42" s="1">
-        <f>IF(22&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,22),"ddd"),"")</f>
+        <f>IF(22&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+21,"ddd"),"")</f>
         <v/>
       </c>
       <c r="AA42" s="1">
-        <f>IF(23&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,23),"ddd"),"")</f>
+        <f>IF(23&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+22,"ddd"),"")</f>
         <v/>
       </c>
       <c r="AB42" s="1">
-        <f>IF(24&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,24),"ddd"),"")</f>
+        <f>IF(24&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+23,"ddd"),"")</f>
         <v/>
       </c>
       <c r="AC42" s="1">
-        <f>IF(25&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,25),"ddd"),"")</f>
+        <f>IF(25&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+24,"ddd"),"")</f>
         <v/>
       </c>
       <c r="AD42" s="1">
-        <f>IF(26&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,26),"ddd"),"")</f>
+        <f>IF(26&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+25,"ddd"),"")</f>
         <v/>
       </c>
       <c r="AE42" s="1">
-        <f>IF(27&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,27),"ddd"),"")</f>
+        <f>IF(27&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+26,"ddd"),"")</f>
         <v/>
       </c>
       <c r="AF42" s="1">
-        <f>IF(28&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,28),"ddd"),"")</f>
+        <f>IF(28&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+27,"ddd"),"")</f>
         <v/>
       </c>
       <c r="AG42" s="1">
-        <f>IF(29&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,29),"ddd"),"")</f>
+        <f>IF(29&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+28,"ddd"),"")</f>
         <v/>
       </c>
       <c r="AH42" s="1">
-        <f>IF(30&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,30),"ddd"),"")</f>
+        <f>IF(30&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+29,"ddd"),"")</f>
         <v/>
       </c>
       <c r="AI42" s="1">
-        <f>IF(31&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,31),"ddd"),"")</f>
+        <f>IF(31&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+30,"ddd"),"")</f>
         <v/>
       </c>
     </row>
     <row r="43" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A43" s="121" t="n"/>
-      <c r="B43" s="122" t="n"/>
-      <c r="C43" s="122" t="n"/>
-      <c r="D43" s="125" t="n"/>
+      <c r="A43" s="129" t="n"/>
+      <c r="B43" s="130" t="n"/>
+      <c r="C43" s="130" t="n"/>
+      <c r="D43" s="133" t="n"/>
       <c r="E43" s="2">
         <f>IF(1&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),1,"")</f>
         <v/>
@@ -4114,202 +4210,224 @@
       </c>
     </row>
     <row r="44" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A44" s="113" t="n">
-        <v>1</v>
+      <c r="A44" s="113">
+        <f>IF($C44="","",ROW()-43)</f>
+        <v/>
       </c>
       <c r="B44" s="114" t="n"/>
       <c r="C44" s="115" t="n"/>
       <c r="D44" s="114" t="n"/>
-      <c r="E44" s="6" t="n"/>
-      <c r="F44" s="6" t="n"/>
-      <c r="G44" s="6" t="n"/>
-      <c r="H44" s="6" t="n"/>
-      <c r="I44" s="6" t="n"/>
-      <c r="J44" s="6" t="n"/>
-      <c r="K44" s="6" t="n"/>
-      <c r="L44" s="6" t="n"/>
-      <c r="M44" s="6" t="n"/>
-      <c r="N44" s="6" t="n"/>
-      <c r="O44" s="6" t="n"/>
-      <c r="P44" s="6" t="n"/>
-      <c r="Q44" s="6" t="n"/>
-      <c r="R44" s="6" t="n"/>
-      <c r="S44" s="6" t="n"/>
-      <c r="T44" s="6" t="n"/>
-      <c r="U44" s="6" t="n"/>
-      <c r="V44" s="6" t="n"/>
-      <c r="W44" s="6" t="n"/>
-      <c r="X44" s="6" t="n"/>
-      <c r="Y44" s="6" t="n"/>
-      <c r="Z44" s="6" t="n"/>
-      <c r="AA44" s="6" t="n"/>
-      <c r="AB44" s="6" t="n"/>
-      <c r="AC44" s="6" t="n"/>
-      <c r="AD44" s="6" t="n"/>
-      <c r="AE44" s="6" t="n"/>
-      <c r="AF44" s="6" t="n"/>
-      <c r="AG44" s="6" t="n"/>
-      <c r="AH44" s="6" t="n"/>
-      <c r="AI44" s="29" t="n"/>
+      <c r="E44" s="117" t="n"/>
+      <c r="F44" s="117" t="n"/>
+      <c r="G44" s="117" t="n"/>
+      <c r="H44" s="117" t="n"/>
+      <c r="I44" s="117" t="n"/>
+      <c r="J44" s="117" t="n"/>
+      <c r="K44" s="117" t="n"/>
+      <c r="L44" s="117" t="n"/>
+      <c r="M44" s="117" t="n"/>
+      <c r="N44" s="117" t="n"/>
+      <c r="O44" s="117" t="n"/>
+      <c r="P44" s="117" t="n"/>
+      <c r="Q44" s="117" t="n"/>
+      <c r="R44" s="117" t="n"/>
+      <c r="S44" s="117" t="n"/>
+      <c r="T44" s="117" t="n"/>
+      <c r="U44" s="117" t="n"/>
+      <c r="V44" s="117" t="n"/>
+      <c r="W44" s="117" t="n"/>
+      <c r="X44" s="117" t="n"/>
+      <c r="Y44" s="117" t="n"/>
+      <c r="Z44" s="117" t="n"/>
+      <c r="AA44" s="117" t="n"/>
+      <c r="AB44" s="117" t="n"/>
+      <c r="AC44" s="117" t="n"/>
+      <c r="AD44" s="117" t="n"/>
+      <c r="AE44" s="117" t="n"/>
+      <c r="AF44" s="117" t="n"/>
+      <c r="AG44" s="117" t="n"/>
+      <c r="AH44" s="117" t="n"/>
+      <c r="AI44" s="127" t="n"/>
     </row>
     <row r="45" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A45" s="126" t="n">
-        <v>2</v>
-      </c>
-      <c r="B45" s="127" t="n"/>
-      <c r="C45" s="128" t="n"/>
-      <c r="D45" s="127" t="n"/>
-      <c r="E45" s="14" t="n"/>
-      <c r="F45" s="14" t="n"/>
-      <c r="G45" s="14" t="n"/>
-      <c r="H45" s="14" t="n"/>
-      <c r="I45" s="14" t="n"/>
-      <c r="J45" s="14" t="n"/>
-      <c r="K45" s="14" t="n"/>
-      <c r="L45" s="14" t="n"/>
-      <c r="M45" s="14" t="n"/>
-      <c r="N45" s="14" t="n"/>
-      <c r="O45" s="14" t="n"/>
+      <c r="A45" s="134">
+        <f>IF($C45="","",ROW()-43)</f>
+        <v/>
+      </c>
+      <c r="B45" s="135" t="n"/>
+      <c r="C45" s="136" t="n"/>
+      <c r="D45" s="135" t="n"/>
+      <c r="E45" s="137" t="n"/>
+      <c r="F45" s="137" t="n"/>
+      <c r="G45" s="137" t="n"/>
+      <c r="H45" s="137" t="n"/>
+      <c r="I45" s="137" t="n"/>
+      <c r="J45" s="137" t="n"/>
+      <c r="K45" s="137" t="n"/>
+      <c r="L45" s="137" t="n"/>
+      <c r="M45" s="137" t="n"/>
+      <c r="N45" s="137" t="n"/>
+      <c r="O45" s="137" t="n"/>
+      <c r="P45" s="138" t="n"/>
+      <c r="Q45" s="138" t="n"/>
+      <c r="R45" s="138" t="n"/>
+      <c r="S45" s="138" t="n"/>
+      <c r="T45" s="138" t="n"/>
+      <c r="U45" s="138" t="n"/>
+      <c r="V45" s="138" t="n"/>
+      <c r="W45" s="138" t="n"/>
+      <c r="X45" s="138" t="n"/>
+      <c r="Y45" s="138" t="n"/>
+      <c r="Z45" s="138" t="n"/>
+      <c r="AA45" s="138" t="n"/>
+      <c r="AB45" s="138" t="n"/>
+      <c r="AC45" s="138" t="n"/>
+      <c r="AD45" s="138" t="n"/>
+      <c r="AE45" s="138" t="n"/>
+      <c r="AF45" s="138" t="n"/>
+      <c r="AG45" s="138" t="n"/>
+      <c r="AH45" s="138" t="n"/>
+      <c r="AI45" s="138" t="n"/>
     </row>
     <row r="46" ht="15" customHeight="1" thickBot="1">
-      <c r="A46" s="123" t="inlineStr">
+      <c r="A46" s="131" t="inlineStr">
         <is>
           <t>TRANSFERRED-IN MANPOWER</t>
         </is>
       </c>
-      <c r="B46" s="120" t="n"/>
-      <c r="C46" s="120" t="n"/>
-      <c r="D46" s="124" t="n"/>
+      <c r="B46" s="128" t="n"/>
+      <c r="C46" s="128" t="n"/>
+      <c r="D46" s="132" t="n"/>
       <c r="E46" s="1">
-        <f>IF(1&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1),"ddd"),"")</f>
+        <f>IF(1&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+0,"ddd"),"")</f>
         <v/>
       </c>
       <c r="F46" s="1">
-        <f>IF(2&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,2),"ddd"),"")</f>
+        <f>IF(2&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+1,"ddd"),"")</f>
         <v/>
       </c>
       <c r="G46" s="1">
-        <f>IF(3&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,3),"ddd"),"")</f>
+        <f>IF(3&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+2,"ddd"),"")</f>
         <v/>
       </c>
       <c r="H46" s="1">
-        <f>IF(4&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,4),"ddd"),"")</f>
+        <f>IF(4&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+3,"ddd"),"")</f>
         <v/>
       </c>
       <c r="I46" s="1">
-        <f>IF(5&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,5),"ddd"),"")</f>
+        <f>IF(5&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+4,"ddd"),"")</f>
         <v/>
       </c>
       <c r="J46" s="1">
-        <f>IF(6&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,6),"ddd"),"")</f>
+        <f>IF(6&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+5,"ddd"),"")</f>
         <v/>
       </c>
       <c r="K46" s="1">
-        <f>IF(7&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,7),"ddd"),"")</f>
+        <f>IF(7&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+6,"ddd"),"")</f>
         <v/>
       </c>
       <c r="L46" s="1">
-        <f>IF(8&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,8),"ddd"),"")</f>
+        <f>IF(8&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+7,"ddd"),"")</f>
         <v/>
       </c>
       <c r="M46" s="1">
-        <f>IF(9&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,9),"ddd"),"")</f>
+        <f>IF(9&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+8,"ddd"),"")</f>
         <v/>
       </c>
       <c r="N46" s="1">
-        <f>IF(10&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,10),"ddd"),"")</f>
+        <f>IF(10&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+9,"ddd"),"")</f>
         <v/>
       </c>
       <c r="O46" s="1">
-        <f>IF(11&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,11),"ddd"),"")</f>
+        <f>IF(11&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+10,"ddd"),"")</f>
         <v/>
       </c>
       <c r="P46" s="1">
-        <f>IF(12&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,12),"ddd"),"")</f>
+        <f>IF(12&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+11,"ddd"),"")</f>
         <v/>
       </c>
       <c r="Q46" s="1">
-        <f>IF(13&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,13),"ddd"),"")</f>
+        <f>IF(13&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+12,"ddd"),"")</f>
         <v/>
       </c>
       <c r="R46" s="1">
-        <f>IF(14&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,14),"ddd"),"")</f>
+        <f>IF(14&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+13,"ddd"),"")</f>
         <v/>
       </c>
       <c r="S46" s="1">
-        <f>IF(15&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,15),"ddd"),"")</f>
+        <f>IF(15&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+14,"ddd"),"")</f>
         <v/>
       </c>
       <c r="T46" s="1">
-        <f>IF(16&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,16),"ddd"),"")</f>
+        <f>IF(16&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+15,"ddd"),"")</f>
         <v/>
       </c>
       <c r="U46" s="1">
-        <f>IF(17&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,17),"ddd"),"")</f>
+        <f>IF(17&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+16,"ddd"),"")</f>
         <v/>
       </c>
       <c r="V46" s="1">
-        <f>IF(18&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,18),"ddd"),"")</f>
+        <f>IF(18&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+17,"ddd"),"")</f>
         <v/>
       </c>
       <c r="W46" s="1">
-        <f>IF(19&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,19),"ddd"),"")</f>
+        <f>IF(19&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+18,"ddd"),"")</f>
         <v/>
       </c>
       <c r="X46" s="1">
-        <f>IF(20&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,20),"ddd"),"")</f>
+        <f>IF(20&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+19,"ddd"),"")</f>
         <v/>
       </c>
       <c r="Y46" s="1">
-        <f>IF(21&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,21),"ddd"),"")</f>
+        <f>IF(21&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+20,"ddd"),"")</f>
         <v/>
       </c>
       <c r="Z46" s="1">
-        <f>IF(22&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,22),"ddd"),"")</f>
+        <f>IF(22&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+21,"ddd"),"")</f>
         <v/>
       </c>
       <c r="AA46" s="1">
-        <f>IF(23&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,23),"ddd"),"")</f>
+        <f>IF(23&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+22,"ddd"),"")</f>
         <v/>
       </c>
       <c r="AB46" s="1">
-        <f>IF(24&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,24),"ddd"),"")</f>
+        <f>IF(24&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+23,"ddd"),"")</f>
         <v/>
       </c>
       <c r="AC46" s="1">
-        <f>IF(25&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,25),"ddd"),"")</f>
+        <f>IF(25&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+24,"ddd"),"")</f>
         <v/>
       </c>
       <c r="AD46" s="1">
-        <f>IF(26&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,26),"ddd"),"")</f>
+        <f>IF(26&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+25,"ddd"),"")</f>
         <v/>
       </c>
       <c r="AE46" s="1">
-        <f>IF(27&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,27),"ddd"),"")</f>
+        <f>IF(27&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+26,"ddd"),"")</f>
         <v/>
       </c>
       <c r="AF46" s="1">
-        <f>IF(28&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,28),"ddd"),"")</f>
+        <f>IF(28&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+27,"ddd"),"")</f>
         <v/>
       </c>
       <c r="AG46" s="1">
-        <f>IF(29&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,29),"ddd"),"")</f>
+        <f>IF(29&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+28,"ddd"),"")</f>
         <v/>
       </c>
       <c r="AH46" s="1">
-        <f>IF(30&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,30),"ddd"),"")</f>
+        <f>IF(30&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+29,"ddd"),"")</f>
         <v/>
       </c>
       <c r="AI46" s="1">
-        <f>IF(31&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,31),"ddd"),"")</f>
+        <f>IF(31&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+30,"ddd"),"")</f>
         <v/>
       </c>
     </row>
     <row r="47" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A47" s="121" t="n"/>
-      <c r="B47" s="122" t="n"/>
-      <c r="C47" s="122" t="n"/>
-      <c r="D47" s="125" t="n"/>
+      <c r="A47" s="129" t="n"/>
+      <c r="B47" s="130" t="n"/>
+      <c r="C47" s="130" t="n"/>
+      <c r="D47" s="133" t="n"/>
       <c r="E47" s="2">
         <f>IF(1&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),1,"")</f>
         <v/>
@@ -4436,1128 +4554,1174 @@
       </c>
     </row>
     <row r="48" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A48" s="113" t="n">
-        <v>1</v>
+      <c r="A48" s="113">
+        <f>IF($C48="","",ROW()-47)</f>
+        <v/>
       </c>
       <c r="B48" s="114" t="n"/>
       <c r="C48" s="115" t="n"/>
       <c r="D48" s="114" t="n"/>
-      <c r="E48" s="6" t="n"/>
-      <c r="F48" s="6" t="n"/>
-      <c r="G48" s="6" t="n"/>
-      <c r="H48" s="6" t="n"/>
-      <c r="I48" s="6" t="n"/>
-      <c r="J48" s="6" t="n"/>
-      <c r="K48" s="6" t="n"/>
-      <c r="L48" s="6" t="n"/>
-      <c r="M48" s="6" t="n"/>
-      <c r="N48" s="6" t="n"/>
-      <c r="O48" s="6" t="n"/>
-      <c r="P48" s="6" t="n"/>
-      <c r="Q48" s="6" t="n"/>
-      <c r="R48" s="6" t="n"/>
-      <c r="S48" s="6" t="n"/>
-      <c r="T48" s="6" t="n"/>
-      <c r="U48" s="6" t="n"/>
-      <c r="V48" s="6" t="n"/>
-      <c r="W48" s="6" t="n"/>
-      <c r="X48" s="6" t="n"/>
-      <c r="Y48" s="6" t="n"/>
-      <c r="Z48" s="6" t="n"/>
-      <c r="AA48" s="6" t="n"/>
-      <c r="AB48" s="6" t="n"/>
-      <c r="AC48" s="6" t="n"/>
-      <c r="AD48" s="6" t="n"/>
-      <c r="AE48" s="6" t="n"/>
-      <c r="AF48" s="6" t="n"/>
-      <c r="AG48" s="6" t="n"/>
-      <c r="AH48" s="6" t="n"/>
-      <c r="AI48" s="6" t="n"/>
+      <c r="E48" s="117" t="n"/>
+      <c r="F48" s="117" t="n"/>
+      <c r="G48" s="117" t="n"/>
+      <c r="H48" s="117" t="n"/>
+      <c r="I48" s="117" t="n"/>
+      <c r="J48" s="117" t="n"/>
+      <c r="K48" s="117" t="n"/>
+      <c r="L48" s="117" t="n"/>
+      <c r="M48" s="117" t="n"/>
+      <c r="N48" s="117" t="n"/>
+      <c r="O48" s="117" t="n"/>
+      <c r="P48" s="117" t="n"/>
+      <c r="Q48" s="117" t="n"/>
+      <c r="R48" s="117" t="n"/>
+      <c r="S48" s="117" t="n"/>
+      <c r="T48" s="117" t="n"/>
+      <c r="U48" s="117" t="n"/>
+      <c r="V48" s="117" t="n"/>
+      <c r="W48" s="117" t="n"/>
+      <c r="X48" s="117" t="n"/>
+      <c r="Y48" s="117" t="n"/>
+      <c r="Z48" s="117" t="n"/>
+      <c r="AA48" s="117" t="n"/>
+      <c r="AB48" s="117" t="n"/>
+      <c r="AC48" s="117" t="n"/>
+      <c r="AD48" s="117" t="n"/>
+      <c r="AE48" s="117" t="n"/>
+      <c r="AF48" s="117" t="n"/>
+      <c r="AG48" s="117" t="n"/>
+      <c r="AH48" s="117" t="n"/>
+      <c r="AI48" s="117" t="n"/>
     </row>
     <row r="49" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A49" s="113" t="n">
-        <v>2</v>
+      <c r="A49" s="113">
+        <f>IF($C49="","",ROW()-47)</f>
+        <v/>
       </c>
       <c r="B49" s="114" t="n"/>
       <c r="C49" s="115" t="n"/>
       <c r="D49" s="114" t="n"/>
-      <c r="E49" s="6" t="n"/>
-      <c r="F49" s="6" t="n"/>
-      <c r="G49" s="6" t="n"/>
-      <c r="H49" s="6" t="n"/>
-      <c r="I49" s="6" t="n"/>
-      <c r="J49" s="6" t="n"/>
-      <c r="K49" s="6" t="n"/>
-      <c r="L49" s="6" t="n"/>
-      <c r="M49" s="6" t="n"/>
-      <c r="N49" s="6" t="n"/>
-      <c r="O49" s="6" t="n"/>
-      <c r="P49" s="6" t="n"/>
-      <c r="Q49" s="6" t="n"/>
-      <c r="R49" s="6" t="n"/>
-      <c r="S49" s="6" t="n"/>
-      <c r="T49" s="6" t="n"/>
-      <c r="U49" s="6" t="n"/>
-      <c r="V49" s="6" t="n"/>
-      <c r="W49" s="6" t="n"/>
-      <c r="X49" s="6" t="n"/>
-      <c r="Y49" s="6" t="n"/>
-      <c r="Z49" s="6" t="n"/>
-      <c r="AA49" s="6" t="n"/>
-      <c r="AB49" s="6" t="n"/>
-      <c r="AC49" s="6" t="n"/>
-      <c r="AD49" s="6" t="n"/>
-      <c r="AE49" s="6" t="n"/>
-      <c r="AF49" s="6" t="n"/>
-      <c r="AG49" s="6" t="n"/>
-      <c r="AH49" s="6" t="n"/>
-      <c r="AI49" s="6" t="n"/>
+      <c r="E49" s="117" t="n"/>
+      <c r="F49" s="117" t="n"/>
+      <c r="G49" s="117" t="n"/>
+      <c r="H49" s="117" t="n"/>
+      <c r="I49" s="117" t="n"/>
+      <c r="J49" s="117" t="n"/>
+      <c r="K49" s="117" t="n"/>
+      <c r="L49" s="117" t="n"/>
+      <c r="M49" s="117" t="n"/>
+      <c r="N49" s="117" t="n"/>
+      <c r="O49" s="117" t="n"/>
+      <c r="P49" s="117" t="n"/>
+      <c r="Q49" s="117" t="n"/>
+      <c r="R49" s="117" t="n"/>
+      <c r="S49" s="117" t="n"/>
+      <c r="T49" s="117" t="n"/>
+      <c r="U49" s="117" t="n"/>
+      <c r="V49" s="117" t="n"/>
+      <c r="W49" s="117" t="n"/>
+      <c r="X49" s="117" t="n"/>
+      <c r="Y49" s="117" t="n"/>
+      <c r="Z49" s="117" t="n"/>
+      <c r="AA49" s="117" t="n"/>
+      <c r="AB49" s="117" t="n"/>
+      <c r="AC49" s="117" t="n"/>
+      <c r="AD49" s="117" t="n"/>
+      <c r="AE49" s="117" t="n"/>
+      <c r="AF49" s="117" t="n"/>
+      <c r="AG49" s="117" t="n"/>
+      <c r="AH49" s="117" t="n"/>
+      <c r="AI49" s="117" t="n"/>
     </row>
     <row r="50" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A50" s="113" t="n">
-        <v>3</v>
+      <c r="A50" s="113">
+        <f>IF($C50="","",ROW()-47)</f>
+        <v/>
       </c>
       <c r="B50" s="114" t="n"/>
       <c r="C50" s="115" t="n"/>
       <c r="D50" s="114" t="n"/>
-      <c r="E50" s="6" t="n"/>
-      <c r="F50" s="6" t="n"/>
-      <c r="G50" s="6" t="n"/>
-      <c r="H50" s="6" t="n"/>
-      <c r="I50" s="6" t="n"/>
-      <c r="J50" s="6" t="n"/>
-      <c r="K50" s="6" t="n"/>
-      <c r="L50" s="6" t="n"/>
-      <c r="M50" s="6" t="n"/>
-      <c r="N50" s="6" t="n"/>
-      <c r="O50" s="6" t="n"/>
-      <c r="P50" s="6" t="n"/>
-      <c r="Q50" s="6" t="n"/>
-      <c r="R50" s="6" t="n"/>
-      <c r="S50" s="6" t="n"/>
-      <c r="T50" s="6" t="n"/>
-      <c r="U50" s="6" t="n"/>
-      <c r="V50" s="6" t="n"/>
-      <c r="W50" s="6" t="n"/>
-      <c r="X50" s="6" t="n"/>
-      <c r="Y50" s="6" t="n"/>
-      <c r="Z50" s="6" t="n"/>
-      <c r="AA50" s="6" t="n"/>
-      <c r="AB50" s="6" t="n"/>
-      <c r="AC50" s="6" t="n"/>
-      <c r="AD50" s="6" t="n"/>
-      <c r="AE50" s="6" t="n"/>
-      <c r="AF50" s="6" t="n"/>
-      <c r="AG50" s="6" t="n"/>
-      <c r="AH50" s="6" t="n"/>
-      <c r="AI50" s="6" t="n"/>
+      <c r="E50" s="117" t="n"/>
+      <c r="F50" s="117" t="n"/>
+      <c r="G50" s="117" t="n"/>
+      <c r="H50" s="117" t="n"/>
+      <c r="I50" s="117" t="n"/>
+      <c r="J50" s="117" t="n"/>
+      <c r="K50" s="117" t="n"/>
+      <c r="L50" s="117" t="n"/>
+      <c r="M50" s="117" t="n"/>
+      <c r="N50" s="117" t="n"/>
+      <c r="O50" s="117" t="n"/>
+      <c r="P50" s="117" t="n"/>
+      <c r="Q50" s="117" t="n"/>
+      <c r="R50" s="117" t="n"/>
+      <c r="S50" s="117" t="n"/>
+      <c r="T50" s="117" t="n"/>
+      <c r="U50" s="117" t="n"/>
+      <c r="V50" s="117" t="n"/>
+      <c r="W50" s="117" t="n"/>
+      <c r="X50" s="117" t="n"/>
+      <c r="Y50" s="117" t="n"/>
+      <c r="Z50" s="117" t="n"/>
+      <c r="AA50" s="117" t="n"/>
+      <c r="AB50" s="117" t="n"/>
+      <c r="AC50" s="117" t="n"/>
+      <c r="AD50" s="117" t="n"/>
+      <c r="AE50" s="117" t="n"/>
+      <c r="AF50" s="117" t="n"/>
+      <c r="AG50" s="117" t="n"/>
+      <c r="AH50" s="117" t="n"/>
+      <c r="AI50" s="117" t="n"/>
     </row>
     <row r="51" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A51" s="113" t="n">
-        <v>4</v>
+      <c r="A51" s="113">
+        <f>IF($C51="","",ROW()-47)</f>
+        <v/>
       </c>
       <c r="B51" s="114" t="n"/>
       <c r="C51" s="115" t="n"/>
       <c r="D51" s="114" t="n"/>
-      <c r="E51" s="6" t="n"/>
-      <c r="F51" s="6" t="n"/>
-      <c r="G51" s="6" t="n"/>
-      <c r="H51" s="6" t="n"/>
-      <c r="I51" s="6" t="n"/>
-      <c r="J51" s="6" t="n"/>
-      <c r="K51" s="6" t="n"/>
-      <c r="L51" s="6" t="n"/>
-      <c r="M51" s="6" t="n"/>
-      <c r="N51" s="6" t="n"/>
-      <c r="O51" s="6" t="n"/>
-      <c r="P51" s="6" t="n"/>
-      <c r="Q51" s="6" t="n"/>
-      <c r="R51" s="6" t="n"/>
-      <c r="S51" s="6" t="n"/>
-      <c r="T51" s="6" t="n"/>
-      <c r="U51" s="6" t="n"/>
-      <c r="V51" s="6" t="n"/>
-      <c r="W51" s="6" t="n"/>
-      <c r="X51" s="6" t="n"/>
-      <c r="Y51" s="6" t="n"/>
-      <c r="Z51" s="6" t="n"/>
-      <c r="AA51" s="6" t="n"/>
-      <c r="AB51" s="6" t="n"/>
-      <c r="AC51" s="6" t="n"/>
-      <c r="AD51" s="6" t="n"/>
-      <c r="AE51" s="6" t="n"/>
-      <c r="AF51" s="6" t="n"/>
-      <c r="AG51" s="6" t="n"/>
-      <c r="AH51" s="6" t="n"/>
-      <c r="AI51" s="6" t="n"/>
+      <c r="E51" s="117" t="n"/>
+      <c r="F51" s="117" t="n"/>
+      <c r="G51" s="117" t="n"/>
+      <c r="H51" s="117" t="n"/>
+      <c r="I51" s="117" t="n"/>
+      <c r="J51" s="117" t="n"/>
+      <c r="K51" s="117" t="n"/>
+      <c r="L51" s="117" t="n"/>
+      <c r="M51" s="117" t="n"/>
+      <c r="N51" s="117" t="n"/>
+      <c r="O51" s="117" t="n"/>
+      <c r="P51" s="117" t="n"/>
+      <c r="Q51" s="117" t="n"/>
+      <c r="R51" s="117" t="n"/>
+      <c r="S51" s="117" t="n"/>
+      <c r="T51" s="117" t="n"/>
+      <c r="U51" s="117" t="n"/>
+      <c r="V51" s="117" t="n"/>
+      <c r="W51" s="117" t="n"/>
+      <c r="X51" s="117" t="n"/>
+      <c r="Y51" s="117" t="n"/>
+      <c r="Z51" s="117" t="n"/>
+      <c r="AA51" s="117" t="n"/>
+      <c r="AB51" s="117" t="n"/>
+      <c r="AC51" s="117" t="n"/>
+      <c r="AD51" s="117" t="n"/>
+      <c r="AE51" s="117" t="n"/>
+      <c r="AF51" s="117" t="n"/>
+      <c r="AG51" s="117" t="n"/>
+      <c r="AH51" s="117" t="n"/>
+      <c r="AI51" s="117" t="n"/>
     </row>
     <row r="52" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A52" s="113" t="n">
-        <v>5</v>
+      <c r="A52" s="113">
+        <f>IF($C52="","",ROW()-47)</f>
+        <v/>
       </c>
       <c r="B52" s="114" t="n"/>
       <c r="C52" s="115" t="n"/>
       <c r="D52" s="114" t="n"/>
-      <c r="E52" s="6" t="n"/>
-      <c r="F52" s="6" t="n"/>
-      <c r="G52" s="6" t="n"/>
-      <c r="H52" s="6" t="n"/>
-      <c r="I52" s="6" t="n"/>
-      <c r="J52" s="6" t="n"/>
-      <c r="K52" s="6" t="n"/>
-      <c r="L52" s="6" t="n"/>
-      <c r="M52" s="6" t="n"/>
-      <c r="N52" s="6" t="n"/>
-      <c r="O52" s="6" t="n"/>
-      <c r="P52" s="6" t="n"/>
-      <c r="Q52" s="6" t="n"/>
-      <c r="R52" s="6" t="n"/>
-      <c r="S52" s="6" t="n"/>
-      <c r="T52" s="6" t="n"/>
-      <c r="U52" s="6" t="n"/>
-      <c r="V52" s="6" t="n"/>
-      <c r="W52" s="6" t="n"/>
-      <c r="X52" s="6" t="n"/>
-      <c r="Y52" s="6" t="n"/>
-      <c r="Z52" s="6" t="n"/>
-      <c r="AA52" s="6" t="n"/>
-      <c r="AB52" s="6" t="n"/>
-      <c r="AC52" s="6" t="n"/>
-      <c r="AD52" s="6" t="n"/>
-      <c r="AE52" s="6" t="n"/>
-      <c r="AF52" s="6" t="n"/>
-      <c r="AG52" s="6" t="n"/>
-      <c r="AH52" s="6" t="n"/>
-      <c r="AI52" s="6" t="n"/>
+      <c r="E52" s="117" t="n"/>
+      <c r="F52" s="117" t="n"/>
+      <c r="G52" s="117" t="n"/>
+      <c r="H52" s="117" t="n"/>
+      <c r="I52" s="117" t="n"/>
+      <c r="J52" s="117" t="n"/>
+      <c r="K52" s="117" t="n"/>
+      <c r="L52" s="117" t="n"/>
+      <c r="M52" s="117" t="n"/>
+      <c r="N52" s="117" t="n"/>
+      <c r="O52" s="117" t="n"/>
+      <c r="P52" s="117" t="n"/>
+      <c r="Q52" s="117" t="n"/>
+      <c r="R52" s="117" t="n"/>
+      <c r="S52" s="117" t="n"/>
+      <c r="T52" s="117" t="n"/>
+      <c r="U52" s="117" t="n"/>
+      <c r="V52" s="117" t="n"/>
+      <c r="W52" s="117" t="n"/>
+      <c r="X52" s="117" t="n"/>
+      <c r="Y52" s="117" t="n"/>
+      <c r="Z52" s="117" t="n"/>
+      <c r="AA52" s="117" t="n"/>
+      <c r="AB52" s="117" t="n"/>
+      <c r="AC52" s="117" t="n"/>
+      <c r="AD52" s="117" t="n"/>
+      <c r="AE52" s="117" t="n"/>
+      <c r="AF52" s="117" t="n"/>
+      <c r="AG52" s="117" t="n"/>
+      <c r="AH52" s="117" t="n"/>
+      <c r="AI52" s="117" t="n"/>
     </row>
     <row r="53" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A53" s="113" t="n">
-        <v>6</v>
+      <c r="A53" s="113">
+        <f>IF($C53="","",ROW()-47)</f>
+        <v/>
       </c>
       <c r="B53" s="114" t="n"/>
       <c r="C53" s="115" t="n"/>
       <c r="D53" s="114" t="n"/>
-      <c r="E53" s="6" t="n"/>
-      <c r="F53" s="6" t="n"/>
-      <c r="G53" s="6" t="n"/>
-      <c r="H53" s="6" t="n"/>
-      <c r="I53" s="6" t="n"/>
-      <c r="J53" s="6" t="n"/>
-      <c r="K53" s="6" t="n"/>
-      <c r="L53" s="6" t="n"/>
-      <c r="M53" s="6" t="n"/>
-      <c r="N53" s="6" t="n"/>
-      <c r="O53" s="6" t="n"/>
-      <c r="P53" s="6" t="n"/>
-      <c r="Q53" s="6" t="n"/>
-      <c r="R53" s="6" t="n"/>
-      <c r="S53" s="6" t="n"/>
-      <c r="T53" s="6" t="n"/>
-      <c r="U53" s="6" t="n"/>
-      <c r="V53" s="6" t="n"/>
-      <c r="W53" s="6" t="n"/>
-      <c r="X53" s="6" t="n"/>
-      <c r="Y53" s="6" t="n"/>
-      <c r="Z53" s="6" t="n"/>
-      <c r="AA53" s="6" t="n"/>
-      <c r="AB53" s="6" t="n"/>
-      <c r="AC53" s="6" t="n"/>
-      <c r="AD53" s="6" t="n"/>
-      <c r="AE53" s="6" t="n"/>
-      <c r="AF53" s="6" t="n"/>
-      <c r="AG53" s="6" t="n"/>
-      <c r="AH53" s="6" t="n"/>
-      <c r="AI53" s="6" t="n"/>
+      <c r="E53" s="117" t="n"/>
+      <c r="F53" s="117" t="n"/>
+      <c r="G53" s="117" t="n"/>
+      <c r="H53" s="117" t="n"/>
+      <c r="I53" s="117" t="n"/>
+      <c r="J53" s="117" t="n"/>
+      <c r="K53" s="117" t="n"/>
+      <c r="L53" s="117" t="n"/>
+      <c r="M53" s="117" t="n"/>
+      <c r="N53" s="117" t="n"/>
+      <c r="O53" s="117" t="n"/>
+      <c r="P53" s="117" t="n"/>
+      <c r="Q53" s="117" t="n"/>
+      <c r="R53" s="117" t="n"/>
+      <c r="S53" s="117" t="n"/>
+      <c r="T53" s="117" t="n"/>
+      <c r="U53" s="117" t="n"/>
+      <c r="V53" s="117" t="n"/>
+      <c r="W53" s="117" t="n"/>
+      <c r="X53" s="117" t="n"/>
+      <c r="Y53" s="117" t="n"/>
+      <c r="Z53" s="117" t="n"/>
+      <c r="AA53" s="117" t="n"/>
+      <c r="AB53" s="117" t="n"/>
+      <c r="AC53" s="117" t="n"/>
+      <c r="AD53" s="117" t="n"/>
+      <c r="AE53" s="117" t="n"/>
+      <c r="AF53" s="117" t="n"/>
+      <c r="AG53" s="117" t="n"/>
+      <c r="AH53" s="117" t="n"/>
+      <c r="AI53" s="117" t="n"/>
     </row>
     <row r="54" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A54" s="113" t="n">
-        <v>7</v>
+      <c r="A54" s="113">
+        <f>IF($C54="","",ROW()-47)</f>
+        <v/>
       </c>
       <c r="B54" s="114" t="n"/>
       <c r="C54" s="115" t="n"/>
       <c r="D54" s="114" t="n"/>
-      <c r="E54" s="6" t="n"/>
-      <c r="F54" s="6" t="n"/>
-      <c r="G54" s="6" t="n"/>
-      <c r="H54" s="6" t="n"/>
-      <c r="I54" s="6" t="n"/>
-      <c r="J54" s="6" t="n"/>
-      <c r="K54" s="6" t="n"/>
-      <c r="L54" s="6" t="n"/>
-      <c r="M54" s="6" t="n"/>
-      <c r="N54" s="6" t="n"/>
-      <c r="O54" s="6" t="n"/>
-      <c r="P54" s="6" t="n"/>
-      <c r="Q54" s="6" t="n"/>
-      <c r="R54" s="6" t="n"/>
-      <c r="S54" s="6" t="n"/>
-      <c r="T54" s="6" t="n"/>
-      <c r="U54" s="6" t="n"/>
-      <c r="V54" s="6" t="n"/>
-      <c r="W54" s="6" t="n"/>
-      <c r="X54" s="6" t="n"/>
-      <c r="Y54" s="6" t="n"/>
-      <c r="Z54" s="6" t="n"/>
-      <c r="AA54" s="6" t="n"/>
-      <c r="AB54" s="6" t="n"/>
-      <c r="AC54" s="6" t="n"/>
-      <c r="AD54" s="6" t="n"/>
-      <c r="AE54" s="6" t="n"/>
-      <c r="AF54" s="6" t="n"/>
-      <c r="AG54" s="6" t="n"/>
-      <c r="AH54" s="6" t="n"/>
-      <c r="AI54" s="6" t="n"/>
+      <c r="E54" s="117" t="n"/>
+      <c r="F54" s="117" t="n"/>
+      <c r="G54" s="117" t="n"/>
+      <c r="H54" s="117" t="n"/>
+      <c r="I54" s="117" t="n"/>
+      <c r="J54" s="117" t="n"/>
+      <c r="K54" s="117" t="n"/>
+      <c r="L54" s="117" t="n"/>
+      <c r="M54" s="117" t="n"/>
+      <c r="N54" s="117" t="n"/>
+      <c r="O54" s="117" t="n"/>
+      <c r="P54" s="117" t="n"/>
+      <c r="Q54" s="117" t="n"/>
+      <c r="R54" s="117" t="n"/>
+      <c r="S54" s="117" t="n"/>
+      <c r="T54" s="117" t="n"/>
+      <c r="U54" s="117" t="n"/>
+      <c r="V54" s="117" t="n"/>
+      <c r="W54" s="117" t="n"/>
+      <c r="X54" s="117" t="n"/>
+      <c r="Y54" s="117" t="n"/>
+      <c r="Z54" s="117" t="n"/>
+      <c r="AA54" s="117" t="n"/>
+      <c r="AB54" s="117" t="n"/>
+      <c r="AC54" s="117" t="n"/>
+      <c r="AD54" s="117" t="n"/>
+      <c r="AE54" s="117" t="n"/>
+      <c r="AF54" s="117" t="n"/>
+      <c r="AG54" s="117" t="n"/>
+      <c r="AH54" s="117" t="n"/>
+      <c r="AI54" s="117" t="n"/>
     </row>
     <row r="55" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A55" s="113" t="n">
-        <v>8</v>
+      <c r="A55" s="113">
+        <f>IF($C55="","",ROW()-47)</f>
+        <v/>
       </c>
       <c r="B55" s="114" t="n"/>
       <c r="C55" s="115" t="n"/>
       <c r="D55" s="114" t="n"/>
-      <c r="E55" s="6" t="n"/>
-      <c r="F55" s="6" t="n"/>
-      <c r="G55" s="6" t="n"/>
-      <c r="H55" s="6" t="n"/>
-      <c r="I55" s="6" t="n"/>
-      <c r="J55" s="6" t="n"/>
-      <c r="K55" s="6" t="n"/>
-      <c r="L55" s="6" t="n"/>
-      <c r="M55" s="6" t="n"/>
-      <c r="N55" s="6" t="n"/>
-      <c r="O55" s="6" t="n"/>
-      <c r="P55" s="6" t="n"/>
-      <c r="Q55" s="6" t="n"/>
-      <c r="R55" s="6" t="n"/>
-      <c r="S55" s="6" t="n"/>
-      <c r="T55" s="6" t="n"/>
-      <c r="U55" s="6" t="n"/>
-      <c r="V55" s="6" t="n"/>
-      <c r="W55" s="6" t="n"/>
-      <c r="X55" s="6" t="n"/>
-      <c r="Y55" s="6" t="n"/>
-      <c r="Z55" s="6" t="n"/>
-      <c r="AA55" s="6" t="n"/>
-      <c r="AB55" s="6" t="n"/>
-      <c r="AC55" s="6" t="n"/>
-      <c r="AD55" s="6" t="n"/>
-      <c r="AE55" s="6" t="n"/>
-      <c r="AF55" s="6" t="n"/>
-      <c r="AG55" s="6" t="n"/>
-      <c r="AH55" s="6" t="n"/>
-      <c r="AI55" s="6" t="n"/>
+      <c r="E55" s="117" t="n"/>
+      <c r="F55" s="117" t="n"/>
+      <c r="G55" s="117" t="n"/>
+      <c r="H55" s="117" t="n"/>
+      <c r="I55" s="117" t="n"/>
+      <c r="J55" s="117" t="n"/>
+      <c r="K55" s="117" t="n"/>
+      <c r="L55" s="117" t="n"/>
+      <c r="M55" s="117" t="n"/>
+      <c r="N55" s="117" t="n"/>
+      <c r="O55" s="117" t="n"/>
+      <c r="P55" s="117" t="n"/>
+      <c r="Q55" s="117" t="n"/>
+      <c r="R55" s="117" t="n"/>
+      <c r="S55" s="117" t="n"/>
+      <c r="T55" s="117" t="n"/>
+      <c r="U55" s="117" t="n"/>
+      <c r="V55" s="117" t="n"/>
+      <c r="W55" s="117" t="n"/>
+      <c r="X55" s="117" t="n"/>
+      <c r="Y55" s="117" t="n"/>
+      <c r="Z55" s="117" t="n"/>
+      <c r="AA55" s="117" t="n"/>
+      <c r="AB55" s="117" t="n"/>
+      <c r="AC55" s="117" t="n"/>
+      <c r="AD55" s="117" t="n"/>
+      <c r="AE55" s="117" t="n"/>
+      <c r="AF55" s="117" t="n"/>
+      <c r="AG55" s="117" t="n"/>
+      <c r="AH55" s="117" t="n"/>
+      <c r="AI55" s="117" t="n"/>
     </row>
     <row r="56" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A56" s="113" t="n">
-        <v>9</v>
+      <c r="A56" s="113">
+        <f>IF($C56="","",ROW()-47)</f>
+        <v/>
       </c>
       <c r="B56" s="114" t="n"/>
       <c r="C56" s="115" t="n"/>
       <c r="D56" s="114" t="n"/>
-      <c r="E56" s="32" t="n"/>
-      <c r="F56" s="32" t="n"/>
-      <c r="G56" s="32" t="n"/>
-      <c r="H56" s="32" t="n"/>
-      <c r="I56" s="6" t="n"/>
-      <c r="J56" s="6" t="n"/>
-      <c r="K56" s="6" t="n"/>
-      <c r="L56" s="6" t="n"/>
-      <c r="M56" s="6" t="n"/>
-      <c r="N56" s="6" t="n"/>
-      <c r="O56" s="6" t="n"/>
-      <c r="P56" s="6" t="n"/>
-      <c r="Q56" s="6" t="n"/>
-      <c r="R56" s="6" t="n"/>
-      <c r="S56" s="6" t="n"/>
-      <c r="T56" s="6" t="n"/>
-      <c r="U56" s="6" t="n"/>
-      <c r="V56" s="6" t="n"/>
-      <c r="W56" s="6" t="n"/>
-      <c r="X56" s="6" t="n"/>
-      <c r="Y56" s="6" t="n"/>
-      <c r="Z56" s="6" t="n"/>
-      <c r="AA56" s="6" t="n"/>
-      <c r="AB56" s="6" t="n"/>
-      <c r="AC56" s="6" t="n"/>
-      <c r="AD56" s="6" t="n"/>
-      <c r="AE56" s="6" t="n"/>
-      <c r="AF56" s="6" t="n"/>
-      <c r="AG56" s="6" t="n"/>
-      <c r="AH56" s="6" t="n"/>
-      <c r="AI56" s="6" t="n"/>
+      <c r="E56" s="139" t="n"/>
+      <c r="F56" s="139" t="n"/>
+      <c r="G56" s="139" t="n"/>
+      <c r="H56" s="139" t="n"/>
+      <c r="I56" s="117" t="n"/>
+      <c r="J56" s="117" t="n"/>
+      <c r="K56" s="117" t="n"/>
+      <c r="L56" s="117" t="n"/>
+      <c r="M56" s="117" t="n"/>
+      <c r="N56" s="117" t="n"/>
+      <c r="O56" s="117" t="n"/>
+      <c r="P56" s="117" t="n"/>
+      <c r="Q56" s="117" t="n"/>
+      <c r="R56" s="117" t="n"/>
+      <c r="S56" s="117" t="n"/>
+      <c r="T56" s="117" t="n"/>
+      <c r="U56" s="117" t="n"/>
+      <c r="V56" s="117" t="n"/>
+      <c r="W56" s="117" t="n"/>
+      <c r="X56" s="117" t="n"/>
+      <c r="Y56" s="117" t="n"/>
+      <c r="Z56" s="117" t="n"/>
+      <c r="AA56" s="117" t="n"/>
+      <c r="AB56" s="117" t="n"/>
+      <c r="AC56" s="117" t="n"/>
+      <c r="AD56" s="117" t="n"/>
+      <c r="AE56" s="117" t="n"/>
+      <c r="AF56" s="117" t="n"/>
+      <c r="AG56" s="117" t="n"/>
+      <c r="AH56" s="117" t="n"/>
+      <c r="AI56" s="117" t="n"/>
     </row>
     <row r="57" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A57" s="113" t="n">
-        <v>10</v>
+      <c r="A57" s="113">
+        <f>IF($C57="","",ROW()-47)</f>
+        <v/>
       </c>
       <c r="B57" s="114" t="n"/>
       <c r="C57" s="115" t="n"/>
       <c r="D57" s="116" t="n"/>
-      <c r="E57" s="6" t="n"/>
-      <c r="I57" s="23" t="n"/>
-      <c r="J57" s="6" t="n"/>
-      <c r="K57" s="6" t="n"/>
-      <c r="L57" s="6" t="n"/>
-      <c r="M57" s="6" t="n"/>
-      <c r="N57" s="6" t="n"/>
-      <c r="O57" s="6" t="n"/>
-      <c r="P57" s="6" t="n"/>
-      <c r="Q57" s="6" t="n"/>
-      <c r="R57" s="6" t="n"/>
-      <c r="S57" s="6" t="n"/>
-      <c r="T57" s="6" t="n"/>
-      <c r="U57" s="6" t="n"/>
-      <c r="V57" s="6" t="n"/>
-      <c r="W57" s="6" t="n"/>
-      <c r="X57" s="6" t="n"/>
-      <c r="Y57" s="6" t="n"/>
-      <c r="Z57" s="6" t="n"/>
-      <c r="AA57" s="6" t="n"/>
-      <c r="AB57" s="6" t="n"/>
-      <c r="AC57" s="6" t="n"/>
-      <c r="AD57" s="6" t="n"/>
-      <c r="AE57" s="6" t="n"/>
-      <c r="AF57" s="6" t="n"/>
-      <c r="AG57" s="6" t="n"/>
-      <c r="AH57" s="6" t="n"/>
-      <c r="AI57" s="6" t="n"/>
+      <c r="E57" s="117" t="n"/>
+      <c r="I57" s="120" t="n"/>
+      <c r="J57" s="117" t="n"/>
+      <c r="K57" s="117" t="n"/>
+      <c r="L57" s="117" t="n"/>
+      <c r="M57" s="117" t="n"/>
+      <c r="N57" s="117" t="n"/>
+      <c r="O57" s="117" t="n"/>
+      <c r="P57" s="117" t="n"/>
+      <c r="Q57" s="117" t="n"/>
+      <c r="R57" s="117" t="n"/>
+      <c r="S57" s="117" t="n"/>
+      <c r="T57" s="117" t="n"/>
+      <c r="U57" s="117" t="n"/>
+      <c r="V57" s="117" t="n"/>
+      <c r="W57" s="117" t="n"/>
+      <c r="X57" s="117" t="n"/>
+      <c r="Y57" s="117" t="n"/>
+      <c r="Z57" s="117" t="n"/>
+      <c r="AA57" s="117" t="n"/>
+      <c r="AB57" s="117" t="n"/>
+      <c r="AC57" s="117" t="n"/>
+      <c r="AD57" s="117" t="n"/>
+      <c r="AE57" s="117" t="n"/>
+      <c r="AF57" s="117" t="n"/>
+      <c r="AG57" s="117" t="n"/>
+      <c r="AH57" s="117" t="n"/>
+      <c r="AI57" s="117" t="n"/>
     </row>
     <row r="58" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A58" s="113" t="n">
-        <v>11</v>
+      <c r="A58" s="113">
+        <f>IF($C58="","",ROW()-47)</f>
+        <v/>
       </c>
       <c r="B58" s="114" t="n"/>
       <c r="C58" s="115" t="n"/>
       <c r="D58" s="116" t="n"/>
-      <c r="E58" s="6" t="n"/>
-      <c r="I58" s="23" t="n"/>
-      <c r="J58" s="6" t="n"/>
-      <c r="K58" s="6" t="n"/>
-      <c r="L58" s="6" t="n"/>
-      <c r="M58" s="6" t="n"/>
-      <c r="N58" s="6" t="n"/>
-      <c r="O58" s="6" t="n"/>
-      <c r="P58" s="6" t="n"/>
-      <c r="Q58" s="6" t="n"/>
-      <c r="R58" s="6" t="n"/>
-      <c r="S58" s="6" t="n"/>
-      <c r="T58" s="6" t="n"/>
-      <c r="U58" s="6" t="n"/>
-      <c r="V58" s="6" t="n"/>
-      <c r="W58" s="6" t="n"/>
-      <c r="X58" s="6" t="n"/>
-      <c r="Y58" s="6" t="n"/>
-      <c r="Z58" s="6" t="n"/>
-      <c r="AA58" s="6" t="n"/>
-      <c r="AB58" s="6" t="n"/>
-      <c r="AC58" s="6" t="n"/>
-      <c r="AD58" s="6" t="n"/>
-      <c r="AE58" s="6" t="n"/>
-      <c r="AF58" s="6" t="n"/>
-      <c r="AG58" s="6" t="n"/>
-      <c r="AH58" s="6" t="n"/>
-      <c r="AI58" s="6" t="n"/>
+      <c r="E58" s="117" t="n"/>
+      <c r="I58" s="120" t="n"/>
+      <c r="J58" s="117" t="n"/>
+      <c r="K58" s="117" t="n"/>
+      <c r="L58" s="117" t="n"/>
+      <c r="M58" s="117" t="n"/>
+      <c r="N58" s="117" t="n"/>
+      <c r="O58" s="117" t="n"/>
+      <c r="P58" s="117" t="n"/>
+      <c r="Q58" s="117" t="n"/>
+      <c r="R58" s="117" t="n"/>
+      <c r="S58" s="117" t="n"/>
+      <c r="T58" s="117" t="n"/>
+      <c r="U58" s="117" t="n"/>
+      <c r="V58" s="117" t="n"/>
+      <c r="W58" s="117" t="n"/>
+      <c r="X58" s="117" t="n"/>
+      <c r="Y58" s="117" t="n"/>
+      <c r="Z58" s="117" t="n"/>
+      <c r="AA58" s="117" t="n"/>
+      <c r="AB58" s="117" t="n"/>
+      <c r="AC58" s="117" t="n"/>
+      <c r="AD58" s="117" t="n"/>
+      <c r="AE58" s="117" t="n"/>
+      <c r="AF58" s="117" t="n"/>
+      <c r="AG58" s="117" t="n"/>
+      <c r="AH58" s="117" t="n"/>
+      <c r="AI58" s="117" t="n"/>
     </row>
     <row r="59" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A59" s="113" t="n">
-        <v>12</v>
+      <c r="A59" s="113">
+        <f>IF($C59="","",ROW()-47)</f>
+        <v/>
       </c>
       <c r="B59" s="114" t="n"/>
       <c r="C59" s="115" t="n"/>
       <c r="D59" s="116" t="n"/>
-      <c r="E59" s="6" t="n"/>
-      <c r="F59" s="129" t="n"/>
-      <c r="G59" s="129" t="n"/>
-      <c r="H59" s="130" t="n"/>
-      <c r="I59" s="23" t="n"/>
-      <c r="J59" s="6" t="n"/>
-      <c r="K59" s="6" t="n"/>
-      <c r="L59" s="6" t="n"/>
-      <c r="M59" s="6" t="n"/>
-      <c r="N59" s="6" t="n"/>
-      <c r="O59" s="6" t="n"/>
-      <c r="P59" s="6" t="n"/>
-      <c r="Q59" s="6" t="n"/>
-      <c r="R59" s="6" t="n"/>
-      <c r="S59" s="6" t="n"/>
-      <c r="T59" s="6" t="n"/>
-      <c r="U59" s="6" t="n"/>
-      <c r="V59" s="6" t="n"/>
-      <c r="W59" s="6" t="n"/>
-      <c r="X59" s="6" t="n"/>
-      <c r="Y59" s="6" t="n"/>
-      <c r="Z59" s="6" t="n"/>
-      <c r="AA59" s="6" t="n"/>
-      <c r="AB59" s="6" t="n"/>
-      <c r="AC59" s="6" t="n"/>
-      <c r="AD59" s="6" t="n"/>
-      <c r="AE59" s="6" t="n"/>
-      <c r="AF59" s="6" t="n"/>
-      <c r="AG59" s="6" t="n"/>
-      <c r="AH59" s="6" t="n"/>
-      <c r="AI59" s="6" t="n"/>
+      <c r="E59" s="117" t="n"/>
+      <c r="F59" s="140" t="n"/>
+      <c r="G59" s="140" t="n"/>
+      <c r="H59" s="141" t="n"/>
+      <c r="I59" s="120" t="n"/>
+      <c r="J59" s="117" t="n"/>
+      <c r="K59" s="117" t="n"/>
+      <c r="L59" s="117" t="n"/>
+      <c r="M59" s="117" t="n"/>
+      <c r="N59" s="117" t="n"/>
+      <c r="O59" s="117" t="n"/>
+      <c r="P59" s="117" t="n"/>
+      <c r="Q59" s="117" t="n"/>
+      <c r="R59" s="117" t="n"/>
+      <c r="S59" s="117" t="n"/>
+      <c r="T59" s="117" t="n"/>
+      <c r="U59" s="117" t="n"/>
+      <c r="V59" s="117" t="n"/>
+      <c r="W59" s="117" t="n"/>
+      <c r="X59" s="117" t="n"/>
+      <c r="Y59" s="117" t="n"/>
+      <c r="Z59" s="117" t="n"/>
+      <c r="AA59" s="117" t="n"/>
+      <c r="AB59" s="117" t="n"/>
+      <c r="AC59" s="117" t="n"/>
+      <c r="AD59" s="117" t="n"/>
+      <c r="AE59" s="117" t="n"/>
+      <c r="AF59" s="117" t="n"/>
+      <c r="AG59" s="117" t="n"/>
+      <c r="AH59" s="117" t="n"/>
+      <c r="AI59" s="117" t="n"/>
     </row>
     <row r="60" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A60" s="113" t="n">
-        <v>13</v>
+      <c r="A60" s="113">
+        <f>IF($C60="","",ROW()-47)</f>
+        <v/>
       </c>
       <c r="B60" s="114" t="n"/>
       <c r="C60" s="115" t="n"/>
       <c r="D60" s="116" t="n"/>
-      <c r="E60" s="6" t="n"/>
-      <c r="F60" s="129" t="n"/>
-      <c r="G60" s="129" t="n"/>
-      <c r="H60" s="130" t="n"/>
-      <c r="I60" s="23" t="n"/>
-      <c r="J60" s="6" t="n"/>
-      <c r="K60" s="6" t="n"/>
-      <c r="L60" s="6" t="n"/>
-      <c r="M60" s="6" t="n"/>
-      <c r="N60" s="6" t="n"/>
-      <c r="O60" s="6" t="n"/>
-      <c r="P60" s="6" t="n"/>
-      <c r="Q60" s="6" t="n"/>
-      <c r="R60" s="6" t="n"/>
-      <c r="S60" s="6" t="n"/>
-      <c r="T60" s="6" t="n"/>
-      <c r="U60" s="6" t="n"/>
-      <c r="V60" s="6" t="n"/>
-      <c r="W60" s="6" t="n"/>
-      <c r="X60" s="6" t="n"/>
-      <c r="Y60" s="6" t="n"/>
-      <c r="Z60" s="6" t="n"/>
-      <c r="AA60" s="6" t="n"/>
-      <c r="AB60" s="6" t="n"/>
-      <c r="AC60" s="6" t="n"/>
-      <c r="AD60" s="6" t="n"/>
-      <c r="AE60" s="6" t="n"/>
-      <c r="AF60" s="6" t="n"/>
-      <c r="AG60" s="6" t="n"/>
-      <c r="AH60" s="6" t="n"/>
-      <c r="AI60" s="6" t="n"/>
+      <c r="E60" s="117" t="n"/>
+      <c r="F60" s="140" t="n"/>
+      <c r="G60" s="140" t="n"/>
+      <c r="H60" s="141" t="n"/>
+      <c r="I60" s="120" t="n"/>
+      <c r="J60" s="117" t="n"/>
+      <c r="K60" s="117" t="n"/>
+      <c r="L60" s="117" t="n"/>
+      <c r="M60" s="117" t="n"/>
+      <c r="N60" s="117" t="n"/>
+      <c r="O60" s="117" t="n"/>
+      <c r="P60" s="117" t="n"/>
+      <c r="Q60" s="117" t="n"/>
+      <c r="R60" s="117" t="n"/>
+      <c r="S60" s="117" t="n"/>
+      <c r="T60" s="117" t="n"/>
+      <c r="U60" s="117" t="n"/>
+      <c r="V60" s="117" t="n"/>
+      <c r="W60" s="117" t="n"/>
+      <c r="X60" s="117" t="n"/>
+      <c r="Y60" s="117" t="n"/>
+      <c r="Z60" s="117" t="n"/>
+      <c r="AA60" s="117" t="n"/>
+      <c r="AB60" s="117" t="n"/>
+      <c r="AC60" s="117" t="n"/>
+      <c r="AD60" s="117" t="n"/>
+      <c r="AE60" s="117" t="n"/>
+      <c r="AF60" s="117" t="n"/>
+      <c r="AG60" s="117" t="n"/>
+      <c r="AH60" s="117" t="n"/>
+      <c r="AI60" s="117" t="n"/>
     </row>
     <row r="61" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A61" s="113" t="n">
-        <v>14</v>
+      <c r="A61" s="113">
+        <f>IF($C61="","",ROW()-47)</f>
+        <v/>
       </c>
       <c r="B61" s="114" t="n"/>
       <c r="C61" s="115" t="n"/>
       <c r="D61" s="116" t="n"/>
-      <c r="E61" s="6" t="n"/>
-      <c r="I61" s="23" t="n"/>
-      <c r="J61" s="6" t="n"/>
-      <c r="K61" s="6" t="n"/>
-      <c r="L61" s="6" t="n"/>
-      <c r="M61" s="6" t="n"/>
-      <c r="N61" s="6" t="n"/>
-      <c r="O61" s="6" t="n"/>
-      <c r="P61" s="6" t="n"/>
-      <c r="Q61" s="6" t="n"/>
-      <c r="R61" s="6" t="n"/>
-      <c r="S61" s="6" t="n"/>
-      <c r="T61" s="6" t="n"/>
-      <c r="U61" s="6" t="n"/>
-      <c r="V61" s="6" t="n"/>
-      <c r="W61" s="6" t="n"/>
-      <c r="X61" s="6" t="n"/>
-      <c r="Y61" s="6" t="n"/>
-      <c r="Z61" s="6" t="n"/>
-      <c r="AA61" s="6" t="n"/>
-      <c r="AB61" s="6" t="n"/>
-      <c r="AC61" s="6" t="n"/>
-      <c r="AD61" s="6" t="n"/>
-      <c r="AE61" s="6" t="n"/>
-      <c r="AF61" s="6" t="n"/>
-      <c r="AG61" s="6" t="n"/>
-      <c r="AH61" s="6" t="n"/>
-      <c r="AI61" s="6" t="n"/>
+      <c r="E61" s="117" t="n"/>
+      <c r="I61" s="120" t="n"/>
+      <c r="J61" s="117" t="n"/>
+      <c r="K61" s="117" t="n"/>
+      <c r="L61" s="117" t="n"/>
+      <c r="M61" s="117" t="n"/>
+      <c r="N61" s="117" t="n"/>
+      <c r="O61" s="117" t="n"/>
+      <c r="P61" s="117" t="n"/>
+      <c r="Q61" s="117" t="n"/>
+      <c r="R61" s="117" t="n"/>
+      <c r="S61" s="117" t="n"/>
+      <c r="T61" s="117" t="n"/>
+      <c r="U61" s="117" t="n"/>
+      <c r="V61" s="117" t="n"/>
+      <c r="W61" s="117" t="n"/>
+      <c r="X61" s="117" t="n"/>
+      <c r="Y61" s="117" t="n"/>
+      <c r="Z61" s="117" t="n"/>
+      <c r="AA61" s="117" t="n"/>
+      <c r="AB61" s="117" t="n"/>
+      <c r="AC61" s="117" t="n"/>
+      <c r="AD61" s="117" t="n"/>
+      <c r="AE61" s="117" t="n"/>
+      <c r="AF61" s="117" t="n"/>
+      <c r="AG61" s="117" t="n"/>
+      <c r="AH61" s="117" t="n"/>
+      <c r="AI61" s="117" t="n"/>
     </row>
     <row r="62" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A62" s="113" t="n">
-        <v>15</v>
+      <c r="A62" s="113">
+        <f>IF($C62="","",ROW()-47)</f>
+        <v/>
       </c>
       <c r="B62" s="114" t="n"/>
       <c r="C62" s="115" t="n"/>
       <c r="D62" s="116" t="n"/>
-      <c r="E62" s="6" t="n"/>
-      <c r="F62" s="129" t="n"/>
-      <c r="G62" s="129" t="n"/>
-      <c r="H62" s="130" t="n"/>
-      <c r="I62" s="23" t="n"/>
-      <c r="J62" s="6" t="n"/>
-      <c r="K62" s="6" t="n"/>
-      <c r="L62" s="6" t="n"/>
-      <c r="M62" s="6" t="n"/>
-      <c r="N62" s="6" t="n"/>
-      <c r="O62" s="6" t="n"/>
-      <c r="P62" s="6" t="n"/>
-      <c r="Q62" s="6" t="n"/>
-      <c r="R62" s="6" t="n"/>
-      <c r="S62" s="6" t="n"/>
-      <c r="T62" s="6" t="n"/>
-      <c r="U62" s="6" t="n"/>
-      <c r="V62" s="6" t="n"/>
-      <c r="W62" s="6" t="n"/>
-      <c r="X62" s="6" t="n"/>
-      <c r="Y62" s="6" t="n"/>
-      <c r="Z62" s="6" t="n"/>
-      <c r="AA62" s="6" t="n"/>
-      <c r="AB62" s="6" t="n"/>
-      <c r="AC62" s="6" t="n"/>
-      <c r="AD62" s="6" t="n"/>
-      <c r="AE62" s="6" t="n"/>
-      <c r="AF62" s="6" t="n"/>
-      <c r="AG62" s="6" t="n"/>
-      <c r="AH62" s="6" t="n"/>
-      <c r="AI62" s="6" t="n"/>
+      <c r="E62" s="117" t="n"/>
+      <c r="F62" s="140" t="n"/>
+      <c r="G62" s="140" t="n"/>
+      <c r="H62" s="141" t="n"/>
+      <c r="I62" s="120" t="n"/>
+      <c r="J62" s="117" t="n"/>
+      <c r="K62" s="117" t="n"/>
+      <c r="L62" s="117" t="n"/>
+      <c r="M62" s="117" t="n"/>
+      <c r="N62" s="117" t="n"/>
+      <c r="O62" s="117" t="n"/>
+      <c r="P62" s="117" t="n"/>
+      <c r="Q62" s="117" t="n"/>
+      <c r="R62" s="117" t="n"/>
+      <c r="S62" s="117" t="n"/>
+      <c r="T62" s="117" t="n"/>
+      <c r="U62" s="117" t="n"/>
+      <c r="V62" s="117" t="n"/>
+      <c r="W62" s="117" t="n"/>
+      <c r="X62" s="117" t="n"/>
+      <c r="Y62" s="117" t="n"/>
+      <c r="Z62" s="117" t="n"/>
+      <c r="AA62" s="117" t="n"/>
+      <c r="AB62" s="117" t="n"/>
+      <c r="AC62" s="117" t="n"/>
+      <c r="AD62" s="117" t="n"/>
+      <c r="AE62" s="117" t="n"/>
+      <c r="AF62" s="117" t="n"/>
+      <c r="AG62" s="117" t="n"/>
+      <c r="AH62" s="117" t="n"/>
+      <c r="AI62" s="117" t="n"/>
     </row>
     <row r="63" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A63" s="113" t="n">
-        <v>16</v>
+      <c r="A63" s="113">
+        <f>IF($C63="","",ROW()-47)</f>
+        <v/>
       </c>
       <c r="B63" s="114" t="n"/>
       <c r="C63" s="115" t="n"/>
       <c r="D63" s="116" t="n"/>
-      <c r="E63" s="6" t="n"/>
-      <c r="F63" s="129" t="n"/>
-      <c r="G63" s="129" t="n"/>
-      <c r="H63" s="130" t="n"/>
-      <c r="I63" s="23" t="n"/>
-      <c r="J63" s="6" t="n"/>
-      <c r="K63" s="6" t="n"/>
-      <c r="L63" s="6" t="n"/>
-      <c r="M63" s="6" t="n"/>
-      <c r="N63" s="6" t="n"/>
-      <c r="O63" s="6" t="n"/>
-      <c r="P63" s="6" t="n"/>
-      <c r="Q63" s="6" t="n"/>
-      <c r="R63" s="6" t="n"/>
-      <c r="S63" s="6" t="n"/>
-      <c r="T63" s="6" t="n"/>
-      <c r="U63" s="6" t="n"/>
-      <c r="V63" s="6" t="n"/>
-      <c r="W63" s="6" t="n"/>
-      <c r="X63" s="6" t="n"/>
-      <c r="Y63" s="6" t="n"/>
-      <c r="Z63" s="6" t="n"/>
-      <c r="AA63" s="6" t="n"/>
-      <c r="AB63" s="6" t="n"/>
-      <c r="AC63" s="6" t="n"/>
-      <c r="AD63" s="6" t="n"/>
-      <c r="AE63" s="6" t="n"/>
-      <c r="AF63" s="6" t="n"/>
-      <c r="AG63" s="6" t="n"/>
-      <c r="AH63" s="6" t="n"/>
-      <c r="AI63" s="6" t="n"/>
+      <c r="E63" s="117" t="n"/>
+      <c r="F63" s="140" t="n"/>
+      <c r="G63" s="140" t="n"/>
+      <c r="H63" s="141" t="n"/>
+      <c r="I63" s="120" t="n"/>
+      <c r="J63" s="117" t="n"/>
+      <c r="K63" s="117" t="n"/>
+      <c r="L63" s="117" t="n"/>
+      <c r="M63" s="117" t="n"/>
+      <c r="N63" s="117" t="n"/>
+      <c r="O63" s="117" t="n"/>
+      <c r="P63" s="117" t="n"/>
+      <c r="Q63" s="117" t="n"/>
+      <c r="R63" s="117" t="n"/>
+      <c r="S63" s="117" t="n"/>
+      <c r="T63" s="117" t="n"/>
+      <c r="U63" s="117" t="n"/>
+      <c r="V63" s="117" t="n"/>
+      <c r="W63" s="117" t="n"/>
+      <c r="X63" s="117" t="n"/>
+      <c r="Y63" s="117" t="n"/>
+      <c r="Z63" s="117" t="n"/>
+      <c r="AA63" s="117" t="n"/>
+      <c r="AB63" s="117" t="n"/>
+      <c r="AC63" s="117" t="n"/>
+      <c r="AD63" s="117" t="n"/>
+      <c r="AE63" s="117" t="n"/>
+      <c r="AF63" s="117" t="n"/>
+      <c r="AG63" s="117" t="n"/>
+      <c r="AH63" s="117" t="n"/>
+      <c r="AI63" s="117" t="n"/>
     </row>
     <row r="64" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A64" s="113" t="n">
-        <v>17</v>
+      <c r="A64" s="113">
+        <f>IF($C64="","",ROW()-47)</f>
+        <v/>
       </c>
       <c r="B64" s="114" t="n"/>
       <c r="C64" s="115" t="n"/>
       <c r="D64" s="116" t="n"/>
-      <c r="E64" s="6" t="n"/>
-      <c r="F64" s="129" t="n"/>
-      <c r="G64" s="129" t="n"/>
-      <c r="H64" s="130" t="n"/>
-      <c r="I64" s="23" t="n"/>
-      <c r="J64" s="6" t="n"/>
-      <c r="K64" s="6" t="n"/>
-      <c r="L64" s="6" t="n"/>
-      <c r="M64" s="6" t="n"/>
-      <c r="N64" s="6" t="n"/>
-      <c r="O64" s="6" t="n"/>
-      <c r="P64" s="6" t="n"/>
-      <c r="Q64" s="6" t="n"/>
-      <c r="R64" s="6" t="n"/>
-      <c r="S64" s="6" t="n"/>
-      <c r="T64" s="6" t="n"/>
-      <c r="U64" s="6" t="n"/>
-      <c r="V64" s="6" t="n"/>
-      <c r="W64" s="6" t="n"/>
-      <c r="X64" s="6" t="n"/>
-      <c r="Y64" s="6" t="n"/>
-      <c r="Z64" s="6" t="n"/>
-      <c r="AA64" s="6" t="n"/>
-      <c r="AB64" s="6" t="n"/>
-      <c r="AC64" s="6" t="n"/>
-      <c r="AD64" s="6" t="n"/>
-      <c r="AE64" s="6" t="n"/>
-      <c r="AF64" s="6" t="n"/>
-      <c r="AG64" s="6" t="n"/>
-      <c r="AH64" s="6" t="n"/>
-      <c r="AI64" s="6" t="n"/>
+      <c r="E64" s="117" t="n"/>
+      <c r="F64" s="140" t="n"/>
+      <c r="G64" s="140" t="n"/>
+      <c r="H64" s="141" t="n"/>
+      <c r="I64" s="120" t="n"/>
+      <c r="J64" s="117" t="n"/>
+      <c r="K64" s="117" t="n"/>
+      <c r="L64" s="117" t="n"/>
+      <c r="M64" s="117" t="n"/>
+      <c r="N64" s="117" t="n"/>
+      <c r="O64" s="117" t="n"/>
+      <c r="P64" s="117" t="n"/>
+      <c r="Q64" s="117" t="n"/>
+      <c r="R64" s="117" t="n"/>
+      <c r="S64" s="117" t="n"/>
+      <c r="T64" s="117" t="n"/>
+      <c r="U64" s="117" t="n"/>
+      <c r="V64" s="117" t="n"/>
+      <c r="W64" s="117" t="n"/>
+      <c r="X64" s="117" t="n"/>
+      <c r="Y64" s="117" t="n"/>
+      <c r="Z64" s="117" t="n"/>
+      <c r="AA64" s="117" t="n"/>
+      <c r="AB64" s="117" t="n"/>
+      <c r="AC64" s="117" t="n"/>
+      <c r="AD64" s="117" t="n"/>
+      <c r="AE64" s="117" t="n"/>
+      <c r="AF64" s="117" t="n"/>
+      <c r="AG64" s="117" t="n"/>
+      <c r="AH64" s="117" t="n"/>
+      <c r="AI64" s="117" t="n"/>
     </row>
     <row r="65" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A65" s="113" t="n">
-        <v>18</v>
+      <c r="A65" s="113">
+        <f>IF($C65="","",ROW()-47)</f>
+        <v/>
       </c>
       <c r="B65" s="114" t="n"/>
       <c r="C65" s="115" t="n"/>
       <c r="D65" s="116" t="n"/>
-      <c r="E65" s="6" t="n"/>
-      <c r="F65" s="129" t="n"/>
-      <c r="G65" s="129" t="n"/>
-      <c r="H65" s="130" t="n"/>
-      <c r="I65" s="23" t="n"/>
-      <c r="J65" s="6" t="n"/>
-      <c r="K65" s="6" t="n"/>
-      <c r="L65" s="6" t="n"/>
-      <c r="M65" s="6" t="n"/>
-      <c r="N65" s="6" t="n"/>
-      <c r="O65" s="6" t="n"/>
-      <c r="P65" s="6" t="n"/>
-      <c r="Q65" s="6" t="n"/>
-      <c r="R65" s="6" t="n"/>
-      <c r="S65" s="6" t="n"/>
-      <c r="T65" s="6" t="n"/>
-      <c r="U65" s="6" t="n"/>
-      <c r="V65" s="6" t="n"/>
-      <c r="W65" s="6" t="n"/>
-      <c r="X65" s="6" t="n"/>
-      <c r="Y65" s="6" t="n"/>
-      <c r="Z65" s="6" t="n"/>
-      <c r="AA65" s="6" t="n"/>
-      <c r="AB65" s="6" t="n"/>
-      <c r="AC65" s="6" t="n"/>
-      <c r="AD65" s="6" t="n"/>
-      <c r="AE65" s="6" t="n"/>
-      <c r="AF65" s="6" t="n"/>
-      <c r="AG65" s="6" t="n"/>
-      <c r="AH65" s="6" t="n"/>
-      <c r="AI65" s="6" t="n"/>
+      <c r="E65" s="117" t="n"/>
+      <c r="F65" s="140" t="n"/>
+      <c r="G65" s="140" t="n"/>
+      <c r="H65" s="141" t="n"/>
+      <c r="I65" s="120" t="n"/>
+      <c r="J65" s="117" t="n"/>
+      <c r="K65" s="117" t="n"/>
+      <c r="L65" s="117" t="n"/>
+      <c r="M65" s="117" t="n"/>
+      <c r="N65" s="117" t="n"/>
+      <c r="O65" s="117" t="n"/>
+      <c r="P65" s="117" t="n"/>
+      <c r="Q65" s="117" t="n"/>
+      <c r="R65" s="117" t="n"/>
+      <c r="S65" s="117" t="n"/>
+      <c r="T65" s="117" t="n"/>
+      <c r="U65" s="117" t="n"/>
+      <c r="V65" s="117" t="n"/>
+      <c r="W65" s="117" t="n"/>
+      <c r="X65" s="117" t="n"/>
+      <c r="Y65" s="117" t="n"/>
+      <c r="Z65" s="117" t="n"/>
+      <c r="AA65" s="117" t="n"/>
+      <c r="AB65" s="117" t="n"/>
+      <c r="AC65" s="117" t="n"/>
+      <c r="AD65" s="117" t="n"/>
+      <c r="AE65" s="117" t="n"/>
+      <c r="AF65" s="117" t="n"/>
+      <c r="AG65" s="117" t="n"/>
+      <c r="AH65" s="117" t="n"/>
+      <c r="AI65" s="117" t="n"/>
     </row>
     <row r="66" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A66" s="113" t="n">
-        <v>19</v>
+      <c r="A66" s="113">
+        <f>IF($C66="","",ROW()-47)</f>
+        <v/>
       </c>
       <c r="B66" s="114" t="n"/>
       <c r="C66" s="115" t="n"/>
       <c r="D66" s="116" t="n"/>
-      <c r="E66" s="131" t="n"/>
-      <c r="F66" s="7" t="n"/>
-      <c r="G66" s="7" t="n"/>
-      <c r="H66" s="23" t="n"/>
-      <c r="I66" s="23" t="n"/>
-      <c r="J66" s="6" t="n"/>
-      <c r="K66" s="6" t="n"/>
-      <c r="L66" s="6" t="n"/>
-      <c r="M66" s="6" t="n"/>
-      <c r="N66" s="6" t="n"/>
-      <c r="O66" s="6" t="n"/>
-      <c r="P66" s="6" t="n"/>
-      <c r="Q66" s="6" t="n"/>
-      <c r="R66" s="6" t="n"/>
-      <c r="S66" s="6" t="n"/>
-      <c r="T66" s="6" t="n"/>
-      <c r="U66" s="6" t="n"/>
-      <c r="V66" s="6" t="n"/>
-      <c r="W66" s="6" t="n"/>
-      <c r="X66" s="6" t="n"/>
-      <c r="Y66" s="6" t="n"/>
-      <c r="Z66" s="6" t="n"/>
-      <c r="AA66" s="6" t="n"/>
-      <c r="AB66" s="6" t="n"/>
-      <c r="AC66" s="6" t="n"/>
-      <c r="AD66" s="6" t="n"/>
-      <c r="AE66" s="6" t="n"/>
-      <c r="AF66" s="6" t="n"/>
-      <c r="AG66" s="6" t="n"/>
-      <c r="AH66" s="6" t="n"/>
-      <c r="AI66" s="6" t="n"/>
+      <c r="E66" s="142" t="n"/>
+      <c r="F66" s="118" t="n"/>
+      <c r="G66" s="118" t="n"/>
+      <c r="H66" s="120" t="n"/>
+      <c r="I66" s="120" t="n"/>
+      <c r="J66" s="117" t="n"/>
+      <c r="K66" s="117" t="n"/>
+      <c r="L66" s="117" t="n"/>
+      <c r="M66" s="117" t="n"/>
+      <c r="N66" s="117" t="n"/>
+      <c r="O66" s="117" t="n"/>
+      <c r="P66" s="117" t="n"/>
+      <c r="Q66" s="117" t="n"/>
+      <c r="R66" s="117" t="n"/>
+      <c r="S66" s="117" t="n"/>
+      <c r="T66" s="117" t="n"/>
+      <c r="U66" s="117" t="n"/>
+      <c r="V66" s="117" t="n"/>
+      <c r="W66" s="117" t="n"/>
+      <c r="X66" s="117" t="n"/>
+      <c r="Y66" s="117" t="n"/>
+      <c r="Z66" s="117" t="n"/>
+      <c r="AA66" s="117" t="n"/>
+      <c r="AB66" s="117" t="n"/>
+      <c r="AC66" s="117" t="n"/>
+      <c r="AD66" s="117" t="n"/>
+      <c r="AE66" s="117" t="n"/>
+      <c r="AF66" s="117" t="n"/>
+      <c r="AG66" s="117" t="n"/>
+      <c r="AH66" s="117" t="n"/>
+      <c r="AI66" s="117" t="n"/>
     </row>
     <row r="67" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A67" s="113" t="n">
-        <v>20</v>
+      <c r="A67" s="113">
+        <f>IF($C67="","",ROW()-47)</f>
+        <v/>
       </c>
       <c r="B67" s="114" t="n"/>
       <c r="C67" s="115" t="n"/>
       <c r="D67" s="116" t="n"/>
-      <c r="E67" s="131" t="n"/>
-      <c r="F67" s="7" t="n"/>
-      <c r="G67" s="7" t="n"/>
-      <c r="H67" s="23" t="n"/>
-      <c r="I67" s="23" t="n"/>
-      <c r="J67" s="6" t="n"/>
-      <c r="K67" s="6" t="n"/>
-      <c r="L67" s="6" t="n"/>
-      <c r="M67" s="6" t="n"/>
-      <c r="N67" s="6" t="n"/>
-      <c r="O67" s="6" t="n"/>
-      <c r="P67" s="6" t="n"/>
-      <c r="Q67" s="6" t="n"/>
-      <c r="R67" s="6" t="n"/>
-      <c r="S67" s="6" t="n"/>
-      <c r="T67" s="6" t="n"/>
-      <c r="U67" s="6" t="n"/>
-      <c r="V67" s="6" t="n"/>
-      <c r="W67" s="6" t="n"/>
-      <c r="X67" s="6" t="n"/>
-      <c r="Y67" s="6" t="n"/>
-      <c r="Z67" s="6" t="n"/>
-      <c r="AA67" s="6" t="n"/>
-      <c r="AB67" s="6" t="n"/>
-      <c r="AC67" s="6" t="n"/>
-      <c r="AD67" s="6" t="n"/>
-      <c r="AE67" s="6" t="n"/>
-      <c r="AF67" s="6" t="n"/>
-      <c r="AG67" s="6" t="n"/>
-      <c r="AH67" s="6" t="n"/>
-      <c r="AI67" s="6" t="n"/>
+      <c r="E67" s="142" t="n"/>
+      <c r="F67" s="118" t="n"/>
+      <c r="G67" s="118" t="n"/>
+      <c r="H67" s="120" t="n"/>
+      <c r="I67" s="120" t="n"/>
+      <c r="J67" s="117" t="n"/>
+      <c r="K67" s="117" t="n"/>
+      <c r="L67" s="117" t="n"/>
+      <c r="M67" s="117" t="n"/>
+      <c r="N67" s="117" t="n"/>
+      <c r="O67" s="117" t="n"/>
+      <c r="P67" s="117" t="n"/>
+      <c r="Q67" s="117" t="n"/>
+      <c r="R67" s="117" t="n"/>
+      <c r="S67" s="117" t="n"/>
+      <c r="T67" s="117" t="n"/>
+      <c r="U67" s="117" t="n"/>
+      <c r="V67" s="117" t="n"/>
+      <c r="W67" s="117" t="n"/>
+      <c r="X67" s="117" t="n"/>
+      <c r="Y67" s="117" t="n"/>
+      <c r="Z67" s="117" t="n"/>
+      <c r="AA67" s="117" t="n"/>
+      <c r="AB67" s="117" t="n"/>
+      <c r="AC67" s="117" t="n"/>
+      <c r="AD67" s="117" t="n"/>
+      <c r="AE67" s="117" t="n"/>
+      <c r="AF67" s="117" t="n"/>
+      <c r="AG67" s="117" t="n"/>
+      <c r="AH67" s="117" t="n"/>
+      <c r="AI67" s="117" t="n"/>
     </row>
     <row r="68" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A68" s="113" t="n">
-        <v>21</v>
+      <c r="A68" s="113">
+        <f>IF($C68="","",ROW()-47)</f>
+        <v/>
       </c>
       <c r="B68" s="114" t="n"/>
       <c r="C68" s="115" t="n"/>
       <c r="D68" s="116" t="n"/>
-      <c r="E68" s="131" t="n"/>
-      <c r="F68" s="7" t="n"/>
-      <c r="G68" s="7" t="n"/>
-      <c r="H68" s="23" t="n"/>
-      <c r="I68" s="23" t="n"/>
-      <c r="J68" s="6" t="n"/>
-      <c r="K68" s="6" t="n"/>
-      <c r="L68" s="6" t="n"/>
-      <c r="M68" s="6" t="n"/>
-      <c r="N68" s="6" t="n"/>
-      <c r="O68" s="6" t="n"/>
-      <c r="P68" s="6" t="n"/>
-      <c r="Q68" s="6" t="n"/>
-      <c r="R68" s="6" t="n"/>
-      <c r="S68" s="6" t="n"/>
-      <c r="T68" s="6" t="n"/>
-      <c r="U68" s="6" t="n"/>
-      <c r="V68" s="6" t="n"/>
-      <c r="W68" s="6" t="n"/>
-      <c r="X68" s="6" t="n"/>
-      <c r="Y68" s="6" t="n"/>
-      <c r="Z68" s="6" t="n"/>
-      <c r="AA68" s="6" t="n"/>
-      <c r="AB68" s="6" t="n"/>
-      <c r="AC68" s="6" t="n"/>
-      <c r="AD68" s="6" t="n"/>
-      <c r="AE68" s="6" t="n"/>
-      <c r="AF68" s="6" t="n"/>
-      <c r="AG68" s="6" t="n"/>
-      <c r="AH68" s="6" t="n"/>
-      <c r="AI68" s="6" t="n"/>
+      <c r="E68" s="142" t="n"/>
+      <c r="F68" s="118" t="n"/>
+      <c r="G68" s="118" t="n"/>
+      <c r="H68" s="120" t="n"/>
+      <c r="I68" s="120" t="n"/>
+      <c r="J68" s="117" t="n"/>
+      <c r="K68" s="117" t="n"/>
+      <c r="L68" s="117" t="n"/>
+      <c r="M68" s="117" t="n"/>
+      <c r="N68" s="117" t="n"/>
+      <c r="O68" s="117" t="n"/>
+      <c r="P68" s="117" t="n"/>
+      <c r="Q68" s="117" t="n"/>
+      <c r="R68" s="117" t="n"/>
+      <c r="S68" s="117" t="n"/>
+      <c r="T68" s="117" t="n"/>
+      <c r="U68" s="117" t="n"/>
+      <c r="V68" s="117" t="n"/>
+      <c r="W68" s="117" t="n"/>
+      <c r="X68" s="117" t="n"/>
+      <c r="Y68" s="117" t="n"/>
+      <c r="Z68" s="117" t="n"/>
+      <c r="AA68" s="117" t="n"/>
+      <c r="AB68" s="117" t="n"/>
+      <c r="AC68" s="117" t="n"/>
+      <c r="AD68" s="117" t="n"/>
+      <c r="AE68" s="117" t="n"/>
+      <c r="AF68" s="117" t="n"/>
+      <c r="AG68" s="117" t="n"/>
+      <c r="AH68" s="117" t="n"/>
+      <c r="AI68" s="117" t="n"/>
     </row>
     <row r="69" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A69" s="113" t="n">
-        <v>22</v>
+      <c r="A69" s="113">
+        <f>IF($C69="","",ROW()-47)</f>
+        <v/>
       </c>
       <c r="B69" s="114" t="n"/>
       <c r="C69" s="115" t="n"/>
       <c r="D69" s="116" t="n"/>
-      <c r="E69" s="131" t="n"/>
-      <c r="F69" s="7" t="n"/>
-      <c r="G69" s="7" t="n"/>
-      <c r="H69" s="23" t="n"/>
-      <c r="I69" s="23" t="n"/>
-      <c r="J69" s="6" t="n"/>
-      <c r="K69" s="6" t="n"/>
-      <c r="L69" s="6" t="n"/>
-      <c r="M69" s="6" t="n"/>
-      <c r="N69" s="6" t="n"/>
-      <c r="O69" s="6" t="n"/>
-      <c r="P69" s="6" t="n"/>
-      <c r="Q69" s="6" t="n"/>
-      <c r="R69" s="6" t="n"/>
-      <c r="S69" s="6" t="n"/>
-      <c r="T69" s="6" t="n"/>
-      <c r="U69" s="6" t="n"/>
-      <c r="V69" s="6" t="n"/>
-      <c r="W69" s="6" t="n"/>
-      <c r="X69" s="6" t="n"/>
-      <c r="Y69" s="6" t="n"/>
-      <c r="Z69" s="6" t="n"/>
-      <c r="AA69" s="6" t="n"/>
-      <c r="AB69" s="6" t="n"/>
-      <c r="AC69" s="6" t="n"/>
-      <c r="AD69" s="6" t="n"/>
-      <c r="AE69" s="6" t="n"/>
-      <c r="AF69" s="6" t="n"/>
-      <c r="AG69" s="6" t="n"/>
-      <c r="AH69" s="6" t="n"/>
-      <c r="AI69" s="6" t="n"/>
+      <c r="E69" s="142" t="n"/>
+      <c r="F69" s="118" t="n"/>
+      <c r="G69" s="118" t="n"/>
+      <c r="H69" s="120" t="n"/>
+      <c r="I69" s="120" t="n"/>
+      <c r="J69" s="117" t="n"/>
+      <c r="K69" s="117" t="n"/>
+      <c r="L69" s="117" t="n"/>
+      <c r="M69" s="117" t="n"/>
+      <c r="N69" s="117" t="n"/>
+      <c r="O69" s="117" t="n"/>
+      <c r="P69" s="117" t="n"/>
+      <c r="Q69" s="117" t="n"/>
+      <c r="R69" s="117" t="n"/>
+      <c r="S69" s="117" t="n"/>
+      <c r="T69" s="117" t="n"/>
+      <c r="U69" s="117" t="n"/>
+      <c r="V69" s="117" t="n"/>
+      <c r="W69" s="117" t="n"/>
+      <c r="X69" s="117" t="n"/>
+      <c r="Y69" s="117" t="n"/>
+      <c r="Z69" s="117" t="n"/>
+      <c r="AA69" s="117" t="n"/>
+      <c r="AB69" s="117" t="n"/>
+      <c r="AC69" s="117" t="n"/>
+      <c r="AD69" s="117" t="n"/>
+      <c r="AE69" s="117" t="n"/>
+      <c r="AF69" s="117" t="n"/>
+      <c r="AG69" s="117" t="n"/>
+      <c r="AH69" s="117" t="n"/>
+      <c r="AI69" s="117" t="n"/>
     </row>
     <row r="70" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A70" s="113" t="n">
-        <v>23</v>
+      <c r="A70" s="113">
+        <f>IF($C70="","",ROW()-47)</f>
+        <v/>
       </c>
       <c r="B70" s="114" t="n"/>
       <c r="C70" s="115" t="n"/>
       <c r="D70" s="116" t="n"/>
-      <c r="E70" s="131" t="n"/>
-      <c r="F70" s="7" t="n"/>
-      <c r="G70" s="7" t="n"/>
-      <c r="H70" s="23" t="n"/>
-      <c r="I70" s="23" t="n"/>
-      <c r="J70" s="6" t="n"/>
-      <c r="K70" s="6" t="n"/>
-      <c r="L70" s="6" t="n"/>
-      <c r="M70" s="6" t="n"/>
-      <c r="N70" s="6" t="n"/>
-      <c r="O70" s="6" t="n"/>
-      <c r="P70" s="6" t="n"/>
-      <c r="Q70" s="6" t="n"/>
-      <c r="R70" s="6" t="n"/>
-      <c r="S70" s="6" t="n"/>
-      <c r="T70" s="6" t="n"/>
-      <c r="U70" s="6" t="n"/>
-      <c r="V70" s="6" t="n"/>
-      <c r="W70" s="6" t="n"/>
-      <c r="X70" s="6" t="n"/>
-      <c r="Y70" s="6" t="n"/>
-      <c r="Z70" s="6" t="n"/>
-      <c r="AA70" s="6" t="n"/>
-      <c r="AB70" s="6" t="n"/>
-      <c r="AC70" s="6" t="n"/>
-      <c r="AD70" s="6" t="n"/>
-      <c r="AE70" s="6" t="n"/>
-      <c r="AF70" s="6" t="n"/>
-      <c r="AG70" s="6" t="n"/>
-      <c r="AH70" s="6" t="n"/>
-      <c r="AI70" s="6" t="n"/>
+      <c r="E70" s="142" t="n"/>
+      <c r="F70" s="118" t="n"/>
+      <c r="G70" s="118" t="n"/>
+      <c r="H70" s="120" t="n"/>
+      <c r="I70" s="120" t="n"/>
+      <c r="J70" s="117" t="n"/>
+      <c r="K70" s="117" t="n"/>
+      <c r="L70" s="117" t="n"/>
+      <c r="M70" s="117" t="n"/>
+      <c r="N70" s="117" t="n"/>
+      <c r="O70" s="117" t="n"/>
+      <c r="P70" s="117" t="n"/>
+      <c r="Q70" s="117" t="n"/>
+      <c r="R70" s="117" t="n"/>
+      <c r="S70" s="117" t="n"/>
+      <c r="T70" s="117" t="n"/>
+      <c r="U70" s="117" t="n"/>
+      <c r="V70" s="117" t="n"/>
+      <c r="W70" s="117" t="n"/>
+      <c r="X70" s="117" t="n"/>
+      <c r="Y70" s="117" t="n"/>
+      <c r="Z70" s="117" t="n"/>
+      <c r="AA70" s="117" t="n"/>
+      <c r="AB70" s="117" t="n"/>
+      <c r="AC70" s="117" t="n"/>
+      <c r="AD70" s="117" t="n"/>
+      <c r="AE70" s="117" t="n"/>
+      <c r="AF70" s="117" t="n"/>
+      <c r="AG70" s="117" t="n"/>
+      <c r="AH70" s="117" t="n"/>
+      <c r="AI70" s="117" t="n"/>
     </row>
     <row r="71" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A71" s="113" t="n">
-        <v>24</v>
+      <c r="A71" s="113">
+        <f>IF($C71="","",ROW()-47)</f>
+        <v/>
       </c>
       <c r="B71" s="114" t="n"/>
       <c r="C71" s="115" t="n"/>
       <c r="D71" s="116" t="n"/>
-      <c r="E71" s="131" t="n"/>
-      <c r="F71" s="7" t="n"/>
-      <c r="G71" s="7" t="n"/>
-      <c r="H71" s="23" t="n"/>
-      <c r="I71" s="23" t="n"/>
-      <c r="J71" s="6" t="n"/>
-      <c r="K71" s="6" t="n"/>
-      <c r="L71" s="6" t="n"/>
-      <c r="M71" s="6" t="n"/>
-      <c r="N71" s="6" t="n"/>
-      <c r="O71" s="6" t="n"/>
-      <c r="P71" s="6" t="n"/>
-      <c r="Q71" s="6" t="n"/>
-      <c r="R71" s="6" t="n"/>
-      <c r="S71" s="6" t="n"/>
-      <c r="T71" s="6" t="n"/>
-      <c r="U71" s="6" t="n"/>
-      <c r="V71" s="6" t="n"/>
-      <c r="W71" s="6" t="n"/>
-      <c r="X71" s="6" t="n"/>
-      <c r="Y71" s="6" t="n"/>
-      <c r="Z71" s="6" t="n"/>
-      <c r="AA71" s="6" t="n"/>
-      <c r="AB71" s="6" t="n"/>
-      <c r="AC71" s="6" t="n"/>
-      <c r="AD71" s="6" t="n"/>
-      <c r="AE71" s="6" t="n"/>
-      <c r="AF71" s="6" t="n"/>
-      <c r="AG71" s="6" t="n"/>
-      <c r="AH71" s="6" t="n"/>
-      <c r="AI71" s="6" t="n"/>
+      <c r="E71" s="142" t="n"/>
+      <c r="F71" s="118" t="n"/>
+      <c r="G71" s="118" t="n"/>
+      <c r="H71" s="120" t="n"/>
+      <c r="I71" s="120" t="n"/>
+      <c r="J71" s="117" t="n"/>
+      <c r="K71" s="117" t="n"/>
+      <c r="L71" s="117" t="n"/>
+      <c r="M71" s="117" t="n"/>
+      <c r="N71" s="117" t="n"/>
+      <c r="O71" s="117" t="n"/>
+      <c r="P71" s="117" t="n"/>
+      <c r="Q71" s="117" t="n"/>
+      <c r="R71" s="117" t="n"/>
+      <c r="S71" s="117" t="n"/>
+      <c r="T71" s="117" t="n"/>
+      <c r="U71" s="117" t="n"/>
+      <c r="V71" s="117" t="n"/>
+      <c r="W71" s="117" t="n"/>
+      <c r="X71" s="117" t="n"/>
+      <c r="Y71" s="117" t="n"/>
+      <c r="Z71" s="117" t="n"/>
+      <c r="AA71" s="117" t="n"/>
+      <c r="AB71" s="117" t="n"/>
+      <c r="AC71" s="117" t="n"/>
+      <c r="AD71" s="117" t="n"/>
+      <c r="AE71" s="117" t="n"/>
+      <c r="AF71" s="117" t="n"/>
+      <c r="AG71" s="117" t="n"/>
+      <c r="AH71" s="117" t="n"/>
+      <c r="AI71" s="117" t="n"/>
     </row>
     <row r="72" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A72" s="113" t="n">
-        <v>25</v>
+      <c r="A72" s="113">
+        <f>IF($C72="","",ROW()-47)</f>
+        <v/>
       </c>
       <c r="B72" s="114" t="n"/>
       <c r="C72" s="115" t="n"/>
       <c r="D72" s="116" t="n"/>
-      <c r="E72" s="6" t="n"/>
-      <c r="I72" s="23" t="n"/>
-      <c r="J72" s="6" t="n"/>
-      <c r="K72" s="6" t="n"/>
-      <c r="L72" s="6" t="n"/>
-      <c r="M72" s="6" t="n"/>
-      <c r="N72" s="6" t="n"/>
-      <c r="O72" s="6" t="n"/>
-      <c r="P72" s="6" t="n"/>
-      <c r="Q72" s="6" t="n"/>
-      <c r="R72" s="6" t="n"/>
-      <c r="S72" s="6" t="n"/>
-      <c r="T72" s="6" t="n"/>
-      <c r="U72" s="6" t="n"/>
-      <c r="V72" s="6" t="n"/>
-      <c r="W72" s="6" t="n"/>
-      <c r="X72" s="6" t="n"/>
-      <c r="Y72" s="6" t="n"/>
-      <c r="Z72" s="6" t="n"/>
-      <c r="AA72" s="6" t="n"/>
-      <c r="AB72" s="6" t="n"/>
-      <c r="AC72" s="6" t="n"/>
-      <c r="AD72" s="6" t="n"/>
-      <c r="AE72" s="6" t="n"/>
-      <c r="AF72" s="6" t="n"/>
-      <c r="AG72" s="6" t="n"/>
-      <c r="AH72" s="6" t="n"/>
-      <c r="AI72" s="6" t="n"/>
+      <c r="E72" s="117" t="n"/>
+      <c r="I72" s="120" t="n"/>
+      <c r="J72" s="117" t="n"/>
+      <c r="K72" s="117" t="n"/>
+      <c r="L72" s="117" t="n"/>
+      <c r="M72" s="117" t="n"/>
+      <c r="N72" s="117" t="n"/>
+      <c r="O72" s="117" t="n"/>
+      <c r="P72" s="117" t="n"/>
+      <c r="Q72" s="117" t="n"/>
+      <c r="R72" s="117" t="n"/>
+      <c r="S72" s="117" t="n"/>
+      <c r="T72" s="117" t="n"/>
+      <c r="U72" s="117" t="n"/>
+      <c r="V72" s="117" t="n"/>
+      <c r="W72" s="117" t="n"/>
+      <c r="X72" s="117" t="n"/>
+      <c r="Y72" s="117" t="n"/>
+      <c r="Z72" s="117" t="n"/>
+      <c r="AA72" s="117" t="n"/>
+      <c r="AB72" s="117" t="n"/>
+      <c r="AC72" s="117" t="n"/>
+      <c r="AD72" s="117" t="n"/>
+      <c r="AE72" s="117" t="n"/>
+      <c r="AF72" s="117" t="n"/>
+      <c r="AG72" s="117" t="n"/>
+      <c r="AH72" s="117" t="n"/>
+      <c r="AI72" s="117" t="n"/>
     </row>
     <row r="73" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A73" s="126" t="n">
-        <v>26</v>
-      </c>
-      <c r="B73" s="127" t="n"/>
-      <c r="C73" s="128" t="n"/>
-      <c r="D73" s="127" t="n"/>
-      <c r="E73" s="14" t="n"/>
-      <c r="F73" s="14" t="n"/>
-      <c r="G73" s="14" t="n"/>
-      <c r="H73" s="14" t="n"/>
-      <c r="I73" s="14" t="n"/>
-      <c r="J73" s="14" t="n"/>
-      <c r="K73" s="14" t="n"/>
-      <c r="L73" s="14" t="n"/>
-      <c r="M73" s="14" t="n"/>
-      <c r="N73" s="14" t="n"/>
-      <c r="O73" s="14" t="n"/>
+      <c r="A73" s="134">
+        <f>IF($C73="","",ROW()-47)</f>
+        <v/>
+      </c>
+      <c r="B73" s="135" t="n"/>
+      <c r="C73" s="136" t="n"/>
+      <c r="D73" s="135" t="n"/>
+      <c r="E73" s="137" t="n"/>
+      <c r="F73" s="137" t="n"/>
+      <c r="G73" s="137" t="n"/>
+      <c r="H73" s="137" t="n"/>
+      <c r="I73" s="137" t="n"/>
+      <c r="J73" s="137" t="n"/>
+      <c r="K73" s="137" t="n"/>
+      <c r="L73" s="137" t="n"/>
+      <c r="M73" s="137" t="n"/>
+      <c r="N73" s="137" t="n"/>
+      <c r="O73" s="137" t="n"/>
+      <c r="P73" s="138" t="n"/>
+      <c r="Q73" s="138" t="n"/>
+      <c r="R73" s="138" t="n"/>
+      <c r="S73" s="138" t="n"/>
+      <c r="T73" s="138" t="n"/>
+      <c r="U73" s="138" t="n"/>
+      <c r="V73" s="138" t="n"/>
+      <c r="W73" s="138" t="n"/>
+      <c r="X73" s="138" t="n"/>
+      <c r="Y73" s="138" t="n"/>
+      <c r="Z73" s="138" t="n"/>
+      <c r="AA73" s="138" t="n"/>
+      <c r="AB73" s="138" t="n"/>
+      <c r="AC73" s="138" t="n"/>
+      <c r="AD73" s="138" t="n"/>
+      <c r="AE73" s="138" t="n"/>
+      <c r="AF73" s="138" t="n"/>
+      <c r="AG73" s="138" t="n"/>
+      <c r="AH73" s="138" t="n"/>
+      <c r="AI73" s="138" t="n"/>
     </row>
     <row r="74" ht="15" customHeight="1" thickBot="1">
-      <c r="A74" s="132" t="inlineStr">
+      <c r="A74" s="143" t="inlineStr">
         <is>
           <t>TOTAL DAILY CREWS MANPOWER</t>
         </is>
       </c>
-      <c r="B74" s="120" t="n"/>
-      <c r="C74" s="124" t="n"/>
-      <c r="D74" s="123" t="inlineStr">
+      <c r="B74" s="128" t="n"/>
+      <c r="C74" s="132" t="n"/>
+      <c r="D74" s="131" t="inlineStr">
         <is>
           <t>SHIFT</t>
         </is>
       </c>
       <c r="E74" s="1">
-        <f>IF(1&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1),"ddd"),"")</f>
+        <f>IF(1&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+0,"ddd"),"")</f>
         <v/>
       </c>
       <c r="F74" s="1">
-        <f>IF(2&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,2),"ddd"),"")</f>
+        <f>IF(2&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+1,"ddd"),"")</f>
         <v/>
       </c>
       <c r="G74" s="1">
-        <f>IF(3&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,3),"ddd"),"")</f>
+        <f>IF(3&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+2,"ddd"),"")</f>
         <v/>
       </c>
       <c r="H74" s="1">
-        <f>IF(4&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,4),"ddd"),"")</f>
+        <f>IF(4&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+3,"ddd"),"")</f>
         <v/>
       </c>
       <c r="I74" s="1">
-        <f>IF(5&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,5),"ddd"),"")</f>
+        <f>IF(5&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+4,"ddd"),"")</f>
         <v/>
       </c>
       <c r="J74" s="1">
-        <f>IF(6&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,6),"ddd"),"")</f>
+        <f>IF(6&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+5,"ddd"),"")</f>
         <v/>
       </c>
       <c r="K74" s="1">
-        <f>IF(7&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,7),"ddd"),"")</f>
+        <f>IF(7&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+6,"ddd"),"")</f>
         <v/>
       </c>
       <c r="L74" s="1">
-        <f>IF(8&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,8),"ddd"),"")</f>
+        <f>IF(8&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+7,"ddd"),"")</f>
         <v/>
       </c>
       <c r="M74" s="1">
-        <f>IF(9&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,9),"ddd"),"")</f>
+        <f>IF(9&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+8,"ddd"),"")</f>
         <v/>
       </c>
       <c r="N74" s="1">
-        <f>IF(10&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,10),"ddd"),"")</f>
+        <f>IF(10&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+9,"ddd"),"")</f>
         <v/>
       </c>
       <c r="O74" s="1">
-        <f>IF(11&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,11),"ddd"),"")</f>
+        <f>IF(11&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+10,"ddd"),"")</f>
         <v/>
       </c>
       <c r="P74" s="1">
-        <f>IF(12&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,12),"ddd"),"")</f>
+        <f>IF(12&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+11,"ddd"),"")</f>
         <v/>
       </c>
       <c r="Q74" s="1">
-        <f>IF(13&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,13),"ddd"),"")</f>
+        <f>IF(13&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+12,"ddd"),"")</f>
         <v/>
       </c>
       <c r="R74" s="1">
-        <f>IF(14&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,14),"ddd"),"")</f>
+        <f>IF(14&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+13,"ddd"),"")</f>
         <v/>
       </c>
       <c r="S74" s="1">
-        <f>IF(15&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,15),"ddd"),"")</f>
+        <f>IF(15&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+14,"ddd"),"")</f>
         <v/>
       </c>
       <c r="T74" s="1">
-        <f>IF(16&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,16),"ddd"),"")</f>
+        <f>IF(16&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+15,"ddd"),"")</f>
         <v/>
       </c>
       <c r="U74" s="1">
-        <f>IF(17&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,17),"ddd"),"")</f>
+        <f>IF(17&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+16,"ddd"),"")</f>
         <v/>
       </c>
       <c r="V74" s="1">
-        <f>IF(18&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,18),"ddd"),"")</f>
+        <f>IF(18&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+17,"ddd"),"")</f>
         <v/>
       </c>
       <c r="W74" s="1">
-        <f>IF(19&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,19),"ddd"),"")</f>
+        <f>IF(19&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+18,"ddd"),"")</f>
         <v/>
       </c>
       <c r="X74" s="1">
-        <f>IF(20&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,20),"ddd"),"")</f>
+        <f>IF(20&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+19,"ddd"),"")</f>
         <v/>
       </c>
       <c r="Y74" s="1">
-        <f>IF(21&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,21),"ddd"),"")</f>
+        <f>IF(21&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+20,"ddd"),"")</f>
         <v/>
       </c>
       <c r="Z74" s="1">
-        <f>IF(22&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,22),"ddd"),"")</f>
+        <f>IF(22&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+21,"ddd"),"")</f>
         <v/>
       </c>
       <c r="AA74" s="1">
-        <f>IF(23&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,23),"ddd"),"")</f>
+        <f>IF(23&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+22,"ddd"),"")</f>
         <v/>
       </c>
       <c r="AB74" s="1">
-        <f>IF(24&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,24),"ddd"),"")</f>
+        <f>IF(24&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+23,"ddd"),"")</f>
         <v/>
       </c>
       <c r="AC74" s="1">
-        <f>IF(25&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,25),"ddd"),"")</f>
+        <f>IF(25&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+24,"ddd"),"")</f>
         <v/>
       </c>
       <c r="AD74" s="1">
-        <f>IF(26&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,26),"ddd"),"")</f>
+        <f>IF(26&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+25,"ddd"),"")</f>
         <v/>
       </c>
       <c r="AE74" s="1">
-        <f>IF(27&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,27),"ddd"),"")</f>
+        <f>IF(27&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+26,"ddd"),"")</f>
         <v/>
       </c>
       <c r="AF74" s="1">
-        <f>IF(28&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,28),"ddd"),"")</f>
+        <f>IF(28&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+27,"ddd"),"")</f>
         <v/>
       </c>
       <c r="AG74" s="1">
-        <f>IF(29&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,29),"ddd"),"")</f>
+        <f>IF(29&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+28,"ddd"),"")</f>
         <v/>
       </c>
       <c r="AH74" s="1">
-        <f>IF(30&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,30),"ddd"),"")</f>
+        <f>IF(30&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+29,"ddd"),"")</f>
         <v/>
       </c>
       <c r="AI74" s="1">
-        <f>IF(31&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,31),"ddd"),"")</f>
+        <f>IF(31&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),TEXT(DATE($AL$5,$AP$2,1)+30,"ddd"),"")</f>
         <v/>
       </c>
     </row>
     <row r="75" ht="16.2" customHeight="1" thickBot="1">
       <c r="A75" s="110" t="n"/>
-      <c r="C75" s="133" t="n"/>
+      <c r="C75" s="144" t="n"/>
       <c r="D75" s="105" t="n"/>
       <c r="E75" s="2">
         <f>IF(1&lt;=DAY(EOMONTH(DATE($AL$5,$AP$2,1),0)),1,"")</f>
@@ -5686,7 +5850,7 @@
     </row>
     <row r="76" ht="16.2" customHeight="1" thickBot="1">
       <c r="A76" s="110" t="n"/>
-      <c r="C76" s="133" t="n"/>
+      <c r="C76" s="144" t="n"/>
       <c r="D76" s="15" t="inlineStr">
         <is>
           <t>D</t>
@@ -5819,7 +5983,7 @@
     </row>
     <row r="77" ht="16.2" customHeight="1" thickBot="1">
       <c r="A77" s="110" t="n"/>
-      <c r="C77" s="133" t="n"/>
+      <c r="C77" s="144" t="n"/>
       <c r="D77" s="17" t="inlineStr">
         <is>
           <t>T</t>
@@ -5951,9 +6115,9 @@
       </c>
     </row>
     <row r="78" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A78" s="121" t="n"/>
-      <c r="B78" s="122" t="n"/>
-      <c r="C78" s="125" t="n"/>
+      <c r="A78" s="129" t="n"/>
+      <c r="B78" s="130" t="n"/>
+      <c r="C78" s="133" t="n"/>
       <c r="D78" s="19" t="inlineStr">
         <is>
           <t>G</t>
@@ -6086,7 +6250,7 @@
     </row>
     <row r="79" ht="15" customHeight="1" thickBot="1"/>
     <row r="80" ht="21" customHeight="1" thickBot="1">
-      <c r="E80" s="123" t="inlineStr">
+      <c r="E80" s="131" t="inlineStr">
         <is>
           <t>SHIFT</t>
         </is>
@@ -6098,7 +6262,7 @@
       <c r="J80" s="104" t="n"/>
     </row>
     <row r="81" ht="16.2" customHeight="1" thickBot="1">
-      <c r="E81" s="134" t="inlineStr">
+      <c r="E81" s="145" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -6114,7 +6278,7 @@
       <c r="J81" s="104" t="n"/>
     </row>
     <row r="82" ht="16.2" customHeight="1" thickBot="1">
-      <c r="E82" s="135" t="inlineStr">
+      <c r="E82" s="146" t="inlineStr">
         <is>
           <t>T</t>
         </is>
@@ -6133,25 +6297,25 @@
           <t>ABDULLAH A. ALSHEHRY</t>
         </is>
       </c>
-      <c r="N82" s="122" t="n"/>
-      <c r="O82" s="122" t="n"/>
-      <c r="P82" s="122" t="n"/>
-      <c r="Q82" s="122" t="n"/>
-      <c r="R82" s="122" t="n"/>
-      <c r="S82" s="122" t="n"/>
+      <c r="N82" s="130" t="n"/>
+      <c r="O82" s="130" t="n"/>
+      <c r="P82" s="130" t="n"/>
+      <c r="Q82" s="130" t="n"/>
+      <c r="R82" s="130" t="n"/>
+      <c r="S82" s="130" t="n"/>
       <c r="W82" s="96">
         <f>UPPER(TEXT(TODAY(),"DDDD dd/mm/yyyy"))</f>
         <v/>
       </c>
-      <c r="X82" s="122" t="n"/>
-      <c r="Y82" s="122" t="n"/>
-      <c r="Z82" s="122" t="n"/>
-      <c r="AA82" s="122" t="n"/>
-      <c r="AB82" s="122" t="n"/>
-      <c r="AC82" s="122" t="n"/>
+      <c r="X82" s="130" t="n"/>
+      <c r="Y82" s="130" t="n"/>
+      <c r="Z82" s="130" t="n"/>
+      <c r="AA82" s="130" t="n"/>
+      <c r="AB82" s="130" t="n"/>
+      <c r="AC82" s="130" t="n"/>
     </row>
     <row r="83" ht="16.2" customHeight="1" thickBot="1">
-      <c r="E83" s="136" t="inlineStr">
+      <c r="E83" s="147" t="inlineStr">
         <is>
           <t>G</t>
         </is>
@@ -6177,159 +6341,160 @@
       </c>
     </row>
     <row r="85">
-      <c r="E85" s="137" t="inlineStr">
+      <c r="E85" s="148" t="inlineStr">
         <is>
           <t>CODE LEGEND — ALL CODES</t>
         </is>
       </c>
     </row>
     <row r="86" ht="16" customHeight="1">
-      <c r="E86" s="138" t="inlineStr">
+      <c r="E86" s="149" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="F86" s="139" t="inlineStr">
+      <c r="F86" s="150" t="inlineStr">
         <is>
           <t>DAY</t>
         </is>
       </c>
-      <c r="K86" s="140" t="inlineStr">
+      <c r="K86" s="151" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="L86" s="139" t="inlineStr">
+      <c r="L86" s="150" t="inlineStr">
         <is>
           <t>TWILIGHT</t>
         </is>
       </c>
-      <c r="Q86" s="141" t="inlineStr">
+      <c r="Q86" s="152" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
-      <c r="R86" s="139" t="inlineStr">
+      <c r="R86" s="150" t="inlineStr">
         <is>
           <t>GRAVEYARD</t>
         </is>
       </c>
-      <c r="W86" s="142" t="inlineStr">
+      <c r="W86" s="153" t="inlineStr">
         <is>
           <t>TR</t>
         </is>
       </c>
-      <c r="X86" s="139" t="inlineStr">
+      <c r="X86" s="150" t="inlineStr">
         <is>
           <t>TRAINING</t>
         </is>
       </c>
-      <c r="AC86" s="143" t="inlineStr">
+      <c r="AC86" s="154" t="inlineStr">
         <is>
           <t>V</t>
         </is>
       </c>
-      <c r="AD86" s="139" t="inlineStr">
+      <c r="AD86" s="150" t="inlineStr">
         <is>
           <t>VACATION</t>
         </is>
       </c>
     </row>
     <row r="87" ht="16" customHeight="1">
-      <c r="E87" s="144" t="inlineStr">
+      <c r="E87" s="155" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="F87" s="139" t="inlineStr">
+      <c r="F87" s="150" t="inlineStr">
         <is>
           <t>REST/RDO</t>
         </is>
       </c>
-      <c r="K87" s="145" t="inlineStr">
+      <c r="K87" s="156" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="L87" s="139" t="inlineStr">
+      <c r="L87" s="150" t="inlineStr">
         <is>
           <t>ABSENT</t>
         </is>
       </c>
-      <c r="Q87" s="146" t="inlineStr">
+      <c r="Q87" s="157" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="R87" s="139" t="inlineStr">
+      <c r="R87" s="150" t="inlineStr">
         <is>
           <t>HOLIDAY</t>
         </is>
       </c>
-      <c r="W87" s="147" t="inlineStr">
+      <c r="W87" s="158" t="inlineStr">
         <is>
           <t>OT</t>
         </is>
       </c>
-      <c r="X87" s="139" t="inlineStr">
+      <c r="X87" s="150" t="inlineStr">
         <is>
           <t>OVERTIME</t>
         </is>
       </c>
-      <c r="AC87" s="148" t="inlineStr">
+      <c r="AC87" s="159" t="inlineStr">
         <is>
           <t>OS</t>
         </is>
       </c>
-      <c r="AD87" s="139" t="inlineStr">
+      <c r="AD87" s="150" t="inlineStr">
         <is>
           <t>OUTSTATION</t>
         </is>
       </c>
     </row>
     <row r="88" ht="16" customHeight="1">
-      <c r="E88" s="149" t="inlineStr">
+      <c r="E88" s="160" t="inlineStr">
         <is>
           <t>S/L</t>
         </is>
       </c>
-      <c r="F88" s="139" t="inlineStr">
+      <c r="F88" s="150" t="inlineStr">
         <is>
           <t>SICK LEAVE</t>
         </is>
       </c>
-      <c r="K88" s="150" t="inlineStr">
+      <c r="K88" s="161" t="inlineStr">
         <is>
           <t>C/T</t>
         </is>
       </c>
-      <c r="L88" s="139" t="inlineStr">
+      <c r="L88" s="150" t="inlineStr">
         <is>
           <t>COMP TIME</t>
         </is>
       </c>
-      <c r="Q88" s="151" t="inlineStr">
+      <c r="Q88" s="162" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="R88" s="139" t="inlineStr">
+      <c r="R88" s="150" t="inlineStr">
         <is>
           <t>LATE/LEAVE</t>
         </is>
       </c>
-      <c r="W88" s="152" t="inlineStr">
+      <c r="W88" s="163" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="X88" s="139" t="inlineStr">
+      <c r="X88" s="150" t="inlineStr">
         <is>
           <t>NOTE</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
   <mergeCells count="45">
     <mergeCell ref="X88:AA88"/>
     <mergeCell ref="E2:AC2"/>
@@ -6426,6 +6591,11 @@
       <formula>$D5="ACT/SUPV"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="C5:C73">
+    <cfRule type="expression" priority="28" dxfId="27">
+      <formula>AND($C5&lt;&gt;"",NOT(EXACT($C5,UPPER($C5))))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.3" bottom="0.3" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
